--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C03320-F724-41D2-81D4-0BB9B7ACA297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E427F809-67FD-4B1B-9E97-0B25848575D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$94</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="104">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -576,19 +576,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>周長測定動作</t>
-    <rPh sb="0" eb="2">
-      <t>シュウチョウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ソクテイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ドウサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>排出動作</t>
     <rPh sb="0" eb="2">
       <t>ハイシュツ</t>
@@ -633,6 +620,22 @@
   </si>
   <si>
     <t>In-winding measurement operation</t>
+  </si>
+  <si>
+    <t>周長測定子プリセット</t>
+    <rPh sb="0" eb="2">
+      <t>シュウチョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソクテイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Circumference gauge preset</t>
   </si>
 </sst>
 </file>
@@ -976,7 +979,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1038,7 +1041,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$96">
+    <xdr:sp macro="" textlink="$A$98">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -1407,7 +1410,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -1511,7 +1514,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="str">
-        <f t="shared" ref="D3:D62" si="0">B3&amp;C3</f>
+        <f t="shared" ref="D3:D64" si="0">B3&amp;C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="4">
@@ -1526,7 +1529,7 @@
         <v>71</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
@@ -1561,7 +1564,7 @@
         <v>79</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
@@ -1596,7 +1599,7 @@
         <v>83</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
@@ -1666,7 +1669,7 @@
         <v>71</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -1701,7 +1704,7 @@
         <v>78</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1736,7 +1739,7 @@
         <v>83</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1787,7 +1790,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4">
-        <f t="shared" ref="C11:C92" si="5">C10</f>
+        <f t="shared" ref="C11:C94" si="5">C10</f>
         <v>3</v>
       </c>
       <c r="D11" s="4" t="str">
@@ -1795,7 +1798,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="4">
-        <f t="shared" ref="E11:E72" si="6">E10+1</f>
+        <f t="shared" ref="E11:E74" si="6">E10+1</f>
         <v>2</v>
       </c>
       <c r="F11" s="5"/>
@@ -1806,7 +1809,7 @@
         <v>71</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1841,7 +1844,7 @@
         <v>78</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1876,7 +1879,7 @@
         <v>83</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -1943,10 +1946,10 @@
         <v>75</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -1978,10 +1981,10 @@
         <v>75</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2013,10 +2016,10 @@
         <v>75</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -2048,10 +2051,10 @@
         <v>75</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="6"/>
@@ -2083,10 +2086,10 @@
         <v>75</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="6"/>
@@ -2102,29 +2105,29 @@
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4">
-        <f t="shared" ref="C20" si="10">C14+1</f>
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>4</v>
       </c>
       <c r="D20" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ref="D20" si="10">B20&amp;C20</f>
+        <v>4</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" ref="E20" si="11">E14</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>7</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
+      <c r="K20" s="6"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
@@ -2137,7 +2140,7 @@
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4">
-        <f t="shared" ref="C21" si="12">C20</f>
+        <f t="shared" ref="C21" si="11">C14+1</f>
         <v>5</v>
       </c>
       <c r="D21" s="4" t="str">
@@ -2145,18 +2148,18 @@
         <v>5</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" ref="E21" si="13">E20+1</f>
-        <v>2</v>
+        <f t="shared" ref="E21" si="12">E14</f>
+        <v>1</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
@@ -2172,7 +2175,7 @@
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C22" si="13">C21</f>
         <v>5</v>
       </c>
       <c r="D22" s="4" t="str">
@@ -2180,27 +2183,27 @@
         <v>5</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E22" si="14">E21+1</f>
+        <v>2</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -2216,17 +2219,17 @@
       </c>
       <c r="E23" s="4">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -2242,26 +2245,26 @@
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4">
-        <f t="shared" ref="C24" si="14">C20+1</f>
-        <v>6</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="D24" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="4">
-        <f>E20</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -2277,7 +2280,7 @@
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4">
-        <f t="shared" ref="C25" si="15">C24</f>
+        <f t="shared" ref="C25" si="15">C21+1</f>
         <v>6</v>
       </c>
       <c r="D25" s="4" t="str">
@@ -2285,34 +2288,34 @@
         <v>6</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" ref="E25" si="16">E24+1</f>
-        <v>2</v>
-      </c>
-      <c r="F25" s="9"/>
+        <f>E21</f>
+        <v>1</v>
+      </c>
+      <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H25" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
+      <c r="H25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C26" si="16">C25</f>
         <v>6</v>
       </c>
       <c r="D26" s="4" t="str">
@@ -2320,27 +2323,27 @@
         <v>6</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="F26" s="5"/>
+        <f t="shared" ref="E26" si="17">E25+1</f>
+        <v>2</v>
+      </c>
+      <c r="F26" s="9"/>
       <c r="G26" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
+      <c r="H26" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
       <c r="R26" s="7"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -2356,47 +2359,53 @@
       </c>
       <c r="E27" s="4">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="F27" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H27" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
+      <c r="H27" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
       <c r="R27" s="7"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4">
-        <f t="shared" ref="C28" si="17">C24+1</f>
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>6</v>
       </c>
       <c r="D28" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" s="4">
-        <f>E24</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
+      <c r="G28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
@@ -2411,21 +2420,27 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4">
-        <f t="shared" ref="C29" si="18">C28</f>
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>6</v>
       </c>
       <c r="D29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f t="shared" ref="D29" si="18">B29&amp;C29</f>
+        <v>6</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" ref="E29" si="19">E28+1</f>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
+      <c r="G29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>97</v>
+      </c>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
@@ -2440,7 +2455,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C30" si="19">C25+1</f>
         <v>7</v>
       </c>
       <c r="D30" s="4" t="str">
@@ -2448,28 +2463,28 @@
         <v>7</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
+        <f>E25</f>
+        <v>1</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22"/>
       <c r="R30" s="7"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C31" si="20">C30</f>
         <v>7</v>
       </c>
       <c r="D31" s="4" t="str">
@@ -2477,21 +2492,21 @@
         <v>7</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
+        <f t="shared" ref="E31" si="21">E30+1</f>
+        <v>2</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
       <c r="R31" s="7"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -2507,7 +2522,7 @@
       </c>
       <c r="E32" s="4">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -2524,68 +2539,68 @@
       <c r="R32" s="7"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="26"/>
+      <c r="A33" s="4"/>
       <c r="B33" s="4"/>
-      <c r="C33" s="26">
-        <f t="shared" ref="C33" si="20">C28+1</f>
-        <v>8</v>
-      </c>
-      <c r="D33" s="26" t="str">
+      <c r="C33" s="4">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="D33" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" ref="E33" si="21">E28</f>
-        <v>1</v>
-      </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="26"/>
+      <c r="A34" s="4"/>
       <c r="B34" s="4"/>
-      <c r="C34" s="26">
-        <f t="shared" ref="C34" si="22">C33</f>
-        <v>8</v>
-      </c>
-      <c r="D34" s="26" t="str">
+      <c r="C34" s="4">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="D34" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" ref="E34" si="23">E33+1</f>
-        <v>2</v>
-      </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
       <c r="R34" s="7"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="26"/>
       <c r="B35" s="4"/>
       <c r="C35" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C35" si="22">C30+1</f>
         <v>8</v>
       </c>
       <c r="D35" s="26" t="str">
@@ -2593,8 +2608,8 @@
         <v>8</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E35" si="23">E30</f>
+        <v>1</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
@@ -2611,77 +2626,77 @@
       <c r="R35" s="7"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="4"/>
+      <c r="A36" s="26"/>
       <c r="B36" s="4"/>
-      <c r="C36" s="4">
+      <c r="C36" s="26">
+        <f t="shared" ref="C36" si="24">C35</f>
+        <v>8</v>
+      </c>
+      <c r="D36" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" ref="E36" si="25">E35+1</f>
+        <v>2</v>
+      </c>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="7"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="26"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="26">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="D36" s="4" t="str">
+      <c r="D37" s="26" t="str">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E36" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="7"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="7"/>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4">
-        <f t="shared" si="5"/>
-        <v>8</v>
-      </c>
-      <c r="D37" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
       <c r="E37" s="4">
         <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="23"/>
+      <c r="Q37" s="23"/>
       <c r="R37" s="7"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4">
-        <f t="shared" ref="C38" si="24">C33+1</f>
-        <v>9</v>
+        <f t="shared" si="5"/>
+        <v>8</v>
       </c>
       <c r="D38" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" ref="E38" si="25">E33</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -2701,16 +2716,16 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4">
-        <f t="shared" ref="C39" si="26">C38</f>
-        <v>9</v>
+        <f t="shared" si="5"/>
+        <v>8</v>
       </c>
       <c r="D39" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" ref="E39" si="27">E38+1</f>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -2730,7 +2745,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C40" si="26">C35+1</f>
         <v>9</v>
       </c>
       <c r="D40" s="4" t="str">
@@ -2738,8 +2753,8 @@
         <v>9</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E40" si="27">E35</f>
+        <v>1</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -2759,7 +2774,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C41" si="28">C40</f>
         <v>9</v>
       </c>
       <c r="D41" s="4" t="str">
@@ -2767,15 +2782,15 @@
         <v>9</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E41" si="29">E40+1</f>
+        <v>2</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
-      <c r="K41" s="13"/>
+      <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
@@ -2797,7 +2812,7 @@
       </c>
       <c r="E42" s="4">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -2817,23 +2832,23 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
-        <f t="shared" ref="C43" si="28">C38+1</f>
-        <v>10</v>
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
       <c r="D43" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" ref="E43" si="29">E38</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
+      <c r="K43" s="13"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
@@ -2846,16 +2861,16 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
-        <f t="shared" ref="C44" si="30">C43</f>
-        <v>10</v>
+        <f t="shared" si="5"/>
+        <v>9</v>
       </c>
       <c r="D44" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" ref="E44" si="31">E43+1</f>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -2875,7 +2890,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C45" si="30">C40+1</f>
         <v>10</v>
       </c>
       <c r="D45" s="4" t="str">
@@ -2883,8 +2898,8 @@
         <v>10</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E45" si="31">E40</f>
+        <v>1</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -2904,7 +2919,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C46" si="32">C45</f>
         <v>10</v>
       </c>
       <c r="D46" s="4" t="str">
@@ -2912,8 +2927,8 @@
         <v>10</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E46" si="33">E45+1</f>
+        <v>2</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -2942,7 +2957,7 @@
       </c>
       <c r="E47" s="4">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -2962,16 +2977,16 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
-        <f t="shared" ref="C48" si="32">C43+1</f>
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>10</v>
       </c>
       <c r="D48" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" ref="E48" si="33">E43</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -2991,16 +3006,16 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
-        <f t="shared" ref="C49" si="34">C48</f>
-        <v>11</v>
+        <f t="shared" si="5"/>
+        <v>10</v>
       </c>
       <c r="D49" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" ref="E49" si="35">E48+1</f>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -3020,7 +3035,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C50" si="34">C45+1</f>
         <v>11</v>
       </c>
       <c r="D50" s="4" t="str">
@@ -3028,8 +3043,8 @@
         <v>11</v>
       </c>
       <c r="E50" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E50" si="35">E45</f>
+        <v>1</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -3049,7 +3064,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C51" si="36">C50</f>
         <v>11</v>
       </c>
       <c r="D51" s="4" t="str">
@@ -3057,8 +3072,8 @@
         <v>11</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E51" si="37">E50+1</f>
+        <v>2</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -3087,7 +3102,7 @@
       </c>
       <c r="E52" s="4">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -3107,16 +3122,16 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
-        <f t="shared" ref="C53" si="36">C48+1</f>
-        <v>12</v>
+        <f t="shared" si="5"/>
+        <v>11</v>
       </c>
       <c r="D53" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" ref="E53" si="37">E48</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -3136,16 +3151,16 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
-        <f t="shared" ref="C54" si="38">C53</f>
-        <v>12</v>
+        <f t="shared" si="5"/>
+        <v>11</v>
       </c>
       <c r="D54" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" ref="E54" si="39">E53+1</f>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -3165,7 +3180,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C55" si="38">C50+1</f>
         <v>12</v>
       </c>
       <c r="D55" s="4" t="str">
@@ -3173,8 +3188,8 @@
         <v>12</v>
       </c>
       <c r="E55" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E55" si="39">E50</f>
+        <v>1</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -3194,7 +3209,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C56" si="40">C55</f>
         <v>12</v>
       </c>
       <c r="D56" s="4" t="str">
@@ -3202,8 +3217,8 @@
         <v>12</v>
       </c>
       <c r="E56" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E56" si="41">E55+1</f>
+        <v>2</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -3232,7 +3247,7 @@
       </c>
       <c r="E57" s="4">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -3252,16 +3267,16 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
-        <f t="shared" ref="C58:C88" si="40">C53+1</f>
-        <v>13</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="D58" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" ref="E58" si="41">E53</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -3281,16 +3296,16 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
-        <f t="shared" ref="C59:C89" si="42">C58</f>
-        <v>13</v>
+        <f t="shared" si="5"/>
+        <v>12</v>
       </c>
       <c r="D59" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E59" s="4">
-        <f t="shared" ref="E59" si="43">E58+1</f>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -3310,7 +3325,7 @@
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C60:C90" si="42">C55+1</f>
         <v>13</v>
       </c>
       <c r="D60" s="4" t="str">
@@ -3318,8 +3333,8 @@
         <v>13</v>
       </c>
       <c r="E60" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E60" si="43">E55</f>
+        <v>1</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -3339,7 +3354,7 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C61:C91" si="44">C60</f>
         <v>13</v>
       </c>
       <c r="D61" s="4" t="str">
@@ -3347,8 +3362,8 @@
         <v>13</v>
       </c>
       <c r="E61" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E61" si="45">E60+1</f>
+        <v>2</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -3377,7 +3392,7 @@
       </c>
       <c r="E62" s="4">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -3397,16 +3412,16 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
-        <f t="shared" si="40"/>
-        <v>14</v>
+        <f t="shared" si="5"/>
+        <v>13</v>
       </c>
       <c r="D63" s="4" t="str">
-        <f t="shared" ref="D63:D92" si="44">B63&amp;C63</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" ref="E63" si="45">E58</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -3426,16 +3441,16 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
-        <f t="shared" si="42"/>
-        <v>14</v>
+        <f t="shared" si="5"/>
+        <v>13</v>
       </c>
       <c r="D64" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" ref="E64" si="46">E63+1</f>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -3455,16 +3470,16 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="42"/>
         <v>14</v>
       </c>
       <c r="D65" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="D65:D94" si="46">B65&amp;C65</f>
         <v>14</v>
       </c>
       <c r="E65" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E65" si="47">E60</f>
+        <v>1</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -3484,16 +3499,16 @@
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4">
-        <f t="shared" si="5"/>
-        <v>14</v>
-      </c>
-      <c r="D66" s="4" t="str">
         <f t="shared" si="44"/>
         <v>14</v>
       </c>
+      <c r="D66" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v>14</v>
+      </c>
       <c r="E66" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E66" si="48">E65+1</f>
+        <v>2</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -3517,12 +3532,12 @@
         <v>14</v>
       </c>
       <c r="D67" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>14</v>
       </c>
       <c r="E67" s="4">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -3542,16 +3557,16 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4">
-        <f t="shared" si="40"/>
-        <v>15</v>
+        <f t="shared" si="5"/>
+        <v>14</v>
       </c>
       <c r="D68" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>15</v>
+        <f t="shared" si="46"/>
+        <v>14</v>
       </c>
       <c r="E68" s="4">
-        <f t="shared" ref="E68" si="47">E63</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -3571,16 +3586,16 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4">
-        <f t="shared" si="42"/>
-        <v>15</v>
+        <f t="shared" si="5"/>
+        <v>14</v>
       </c>
       <c r="D69" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>15</v>
+        <f t="shared" si="46"/>
+        <v>14</v>
       </c>
       <c r="E69" s="4">
-        <f t="shared" ref="E69" si="48">E68+1</f>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -3600,16 +3615,16 @@
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="42"/>
         <v>15</v>
       </c>
       <c r="D70" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>15</v>
       </c>
       <c r="E70" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E70" si="49">E65</f>
+        <v>1</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -3629,16 +3644,16 @@
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4">
-        <f t="shared" si="5"/>
-        <v>15</v>
-      </c>
-      <c r="D71" s="4" t="str">
         <f t="shared" si="44"/>
         <v>15</v>
       </c>
+      <c r="D71" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v>15</v>
+      </c>
       <c r="E71" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E71" si="50">E70+1</f>
+        <v>2</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -3662,12 +3677,12 @@
         <v>15</v>
       </c>
       <c r="D72" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>15</v>
       </c>
       <c r="E72" s="4">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -3687,16 +3702,16 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4">
-        <f t="shared" si="40"/>
-        <v>16</v>
+        <f t="shared" si="5"/>
+        <v>15</v>
       </c>
       <c r="D73" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>16</v>
+        <f t="shared" si="46"/>
+        <v>15</v>
       </c>
       <c r="E73" s="4">
-        <f t="shared" ref="E73" si="49">E68</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -3716,16 +3731,16 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4">
-        <f t="shared" si="42"/>
-        <v>16</v>
+        <f t="shared" si="5"/>
+        <v>15</v>
       </c>
       <c r="D74" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>16</v>
+        <f t="shared" si="46"/>
+        <v>15</v>
       </c>
       <c r="E74" s="4">
-        <f t="shared" ref="E74:E92" si="50">E73+1</f>
-        <v>2</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -3745,16 +3760,16 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="42"/>
         <v>16</v>
       </c>
       <c r="D75" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>16</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" si="50"/>
-        <v>3</v>
+        <f t="shared" ref="E75" si="51">E70</f>
+        <v>1</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -3774,16 +3789,16 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4">
-        <f t="shared" si="5"/>
-        <v>16</v>
-      </c>
-      <c r="D76" s="4" t="str">
         <f t="shared" si="44"/>
         <v>16</v>
       </c>
+      <c r="D76" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v>16</v>
+      </c>
       <c r="E76" s="4">
-        <f t="shared" si="50"/>
-        <v>4</v>
+        <f t="shared" ref="E76:E94" si="52">E75+1</f>
+        <v>2</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -3807,12 +3822,12 @@
         <v>16</v>
       </c>
       <c r="D77" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>16</v>
       </c>
       <c r="E77" s="4">
-        <f t="shared" si="50"/>
-        <v>5</v>
+        <f t="shared" si="52"/>
+        <v>3</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -3832,16 +3847,16 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4">
-        <f t="shared" si="40"/>
-        <v>17</v>
+        <f t="shared" si="5"/>
+        <v>16</v>
       </c>
       <c r="D78" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>17</v>
+        <f t="shared" si="46"/>
+        <v>16</v>
       </c>
       <c r="E78" s="4">
-        <f t="shared" ref="E78" si="51">E73</f>
-        <v>1</v>
+        <f t="shared" si="52"/>
+        <v>4</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -3861,16 +3876,16 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4">
-        <f t="shared" si="42"/>
-        <v>17</v>
+        <f t="shared" si="5"/>
+        <v>16</v>
       </c>
       <c r="D79" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>17</v>
+        <f t="shared" si="46"/>
+        <v>16</v>
       </c>
       <c r="E79" s="4">
-        <f t="shared" ref="E79" si="52">E78+1</f>
-        <v>2</v>
+        <f t="shared" si="52"/>
+        <v>5</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -3890,16 +3905,16 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="42"/>
         <v>17</v>
       </c>
       <c r="D80" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>17</v>
       </c>
       <c r="E80" s="4">
-        <f t="shared" si="50"/>
-        <v>3</v>
+        <f t="shared" ref="E80" si="53">E75</f>
+        <v>1</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -3919,16 +3934,16 @@
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="D81" s="4" t="str">
         <f t="shared" si="44"/>
         <v>17</v>
       </c>
+      <c r="D81" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v>17</v>
+      </c>
       <c r="E81" s="4">
-        <f t="shared" si="50"/>
-        <v>4</v>
+        <f t="shared" ref="E81" si="54">E80+1</f>
+        <v>2</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -3952,12 +3967,12 @@
         <v>17</v>
       </c>
       <c r="D82" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>17</v>
       </c>
       <c r="E82" s="4">
-        <f t="shared" si="50"/>
-        <v>5</v>
+        <f t="shared" si="52"/>
+        <v>3</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -3977,16 +3992,16 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4">
-        <f t="shared" si="40"/>
-        <v>18</v>
+        <f t="shared" si="5"/>
+        <v>17</v>
       </c>
       <c r="D83" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>18</v>
+        <f t="shared" si="46"/>
+        <v>17</v>
       </c>
       <c r="E83" s="4">
-        <f t="shared" ref="E83" si="53">E78</f>
-        <v>1</v>
+        <f t="shared" si="52"/>
+        <v>4</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -4006,16 +4021,16 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4">
-        <f t="shared" si="42"/>
-        <v>18</v>
+        <f t="shared" si="5"/>
+        <v>17</v>
       </c>
       <c r="D84" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>18</v>
+        <f t="shared" si="46"/>
+        <v>17</v>
       </c>
       <c r="E84" s="4">
-        <f t="shared" ref="E84" si="54">E83+1</f>
-        <v>2</v>
+        <f t="shared" si="52"/>
+        <v>5</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
@@ -4035,16 +4050,16 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="42"/>
         <v>18</v>
       </c>
       <c r="D85" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>18</v>
       </c>
       <c r="E85" s="4">
-        <f t="shared" si="50"/>
-        <v>3</v>
+        <f t="shared" ref="E85" si="55">E80</f>
+        <v>1</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
@@ -4064,16 +4079,16 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4">
-        <f t="shared" si="5"/>
-        <v>18</v>
-      </c>
-      <c r="D86" s="4" t="str">
         <f t="shared" si="44"/>
         <v>18</v>
       </c>
+      <c r="D86" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v>18</v>
+      </c>
       <c r="E86" s="4">
-        <f t="shared" si="50"/>
-        <v>4</v>
+        <f t="shared" ref="E86" si="56">E85+1</f>
+        <v>2</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
@@ -4097,12 +4112,12 @@
         <v>18</v>
       </c>
       <c r="D87" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>18</v>
       </c>
       <c r="E87" s="4">
-        <f t="shared" si="50"/>
-        <v>5</v>
+        <f t="shared" si="52"/>
+        <v>3</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -4122,16 +4137,16 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4">
-        <f t="shared" si="40"/>
-        <v>19</v>
+        <f t="shared" si="5"/>
+        <v>18</v>
       </c>
       <c r="D88" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>19</v>
+        <f t="shared" si="46"/>
+        <v>18</v>
       </c>
       <c r="E88" s="4">
-        <f t="shared" ref="E88" si="55">E83</f>
-        <v>1</v>
+        <f t="shared" si="52"/>
+        <v>4</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
@@ -4151,16 +4166,16 @@
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4">
-        <f t="shared" si="42"/>
-        <v>19</v>
+        <f t="shared" si="5"/>
+        <v>18</v>
       </c>
       <c r="D89" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>19</v>
+        <f t="shared" si="46"/>
+        <v>18</v>
       </c>
       <c r="E89" s="4">
-        <f t="shared" ref="E89" si="56">E88+1</f>
-        <v>2</v>
+        <f t="shared" si="52"/>
+        <v>5</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
@@ -4180,16 +4195,16 @@
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="42"/>
         <v>19</v>
       </c>
       <c r="D90" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>19</v>
       </c>
       <c r="E90" s="4">
-        <f t="shared" si="50"/>
-        <v>3</v>
+        <f t="shared" ref="E90" si="57">E85</f>
+        <v>1</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
@@ -4209,16 +4224,16 @@
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4">
-        <f t="shared" si="5"/>
-        <v>19</v>
-      </c>
-      <c r="D91" s="4" t="str">
         <f t="shared" si="44"/>
         <v>19</v>
       </c>
+      <c r="D91" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v>19</v>
+      </c>
       <c r="E91" s="4">
-        <f t="shared" si="50"/>
-        <v>4</v>
+        <f t="shared" ref="E91" si="58">E90+1</f>
+        <v>2</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
@@ -4242,12 +4257,12 @@
         <v>19</v>
       </c>
       <c r="D92" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>19</v>
       </c>
       <c r="E92" s="4">
-        <f t="shared" si="50"/>
-        <v>5</v>
+        <f t="shared" si="52"/>
+        <v>3</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
@@ -4264,94 +4279,152 @@
       <c r="R92" s="7"/>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="15"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="15"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="16"/>
-      <c r="G93" s="16"/>
-      <c r="H93" s="16"/>
-      <c r="I93" s="16"/>
-      <c r="J93" s="16"/>
-      <c r="K93" s="16"/>
-      <c r="L93" s="16"/>
-      <c r="M93" s="16"/>
-      <c r="N93" s="16"/>
-      <c r="O93" s="17"/>
-      <c r="P93" s="17"/>
-      <c r="Q93" s="17"/>
-      <c r="R93" s="17"/>
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="D93" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v>19</v>
+      </c>
+      <c r="E93" s="4">
+        <f t="shared" si="52"/>
+        <v>4</v>
+      </c>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="7"/>
+      <c r="P93" s="7"/>
+      <c r="Q93" s="7"/>
+      <c r="R93" s="7"/>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="D94" s="4" t="str">
+        <f t="shared" si="46"/>
+        <v>19</v>
+      </c>
+      <c r="E94" s="4">
+        <f t="shared" si="52"/>
+        <v>5</v>
+      </c>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+      <c r="K94" s="5"/>
+      <c r="L94" s="5"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="7"/>
+      <c r="P94" s="7"/>
+      <c r="Q94" s="7"/>
+      <c r="R94" s="7"/>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" t="s">
+      <c r="A95" s="15"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="16"/>
+      <c r="G95" s="16"/>
+      <c r="H95" s="16"/>
+      <c r="I95" s="16"/>
+      <c r="J95" s="16"/>
+      <c r="K95" s="16"/>
+      <c r="L95" s="16"/>
+      <c r="M95" s="16"/>
+      <c r="N95" s="16"/>
+      <c r="O95" s="17"/>
+      <c r="P95" s="17"/>
+      <c r="Q95" s="17"/>
+      <c r="R95" s="17"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" t="s">
         <v>9</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F97" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96">
-        <f>MAX(A$2:A$93)</f>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98">
+        <f>MAX(A$2:A$95)</f>
         <v>0</v>
       </c>
-      <c r="F96">
-        <f>MAX(F$2:F$93)</f>
+      <c r="F98">
+        <f>MAX(F$2:F$95)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" t="s">
         <v>40</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D99" t="s">
         <v>14</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E99" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98">
-        <f>ROW(A94)-ROW(A1)-1</f>
-        <v>92</v>
-      </c>
-      <c r="D98">
-        <f>COUNTIF(D$2:D$93,D97)</f>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100">
+        <f>ROW(A96)-ROW(A1)-1</f>
+        <v>94</v>
+      </c>
+      <c r="D100">
+        <f>COUNTIF(D$2:D$95,D99)</f>
         <v>0</v>
       </c>
-      <c r="E98" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$93,$D$2:$D$93,E97)</f>
+      <c r="E100" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$95,$D$2:$D$95,E99)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D99" t="s">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="D101" t="s">
         <v>12</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E101" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D100">
-        <f>COUNTIF(D$2:D$93,D99)</f>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="D102">
+        <f>COUNTIF(D$2:D$95,D101)</f>
         <v>0</v>
       </c>
-      <c r="E100" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$93,$D$2:$D$93,E99)</f>
+      <c r="E102" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$95,$D$2:$D$95,E101)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R92" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R92">
-      <sortCondition ref="D1:D92"/>
+  <autoFilter ref="A1:R94" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R94">
+      <sortCondition ref="D1:D94"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:R93">
+  <conditionalFormatting sqref="A2:R95">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
@@ -4521,23 +4594,23 @@
         <v>1</v>
       </c>
       <c r="J3" cm="1">
-        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),"")</f>
+        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$95&amp;info_index!$E$2:$E$95,0),"")</f>
         <v>1</v>
       </c>
       <c r="K3" t="str" cm="1">
-        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$93,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),1)&amp;"","")</f>
-        <v>Home return operation</v>
+        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$95,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$95&amp;info_index!$E$2:$E$95,0),1)&amp;"","")</f>
+        <v>原点復帰動作</v>
       </c>
       <c r="L3" t="str" cm="1">
         <f t="array" aca="1" ref="L3:L202" ca="1">IF(LEN(_xlfn.ANCHORARRAY($J3)),IF(LEN(_xlfn.ANCHORARRAY(K3)),_xlfn.ANCHORARRAY(K3),"unknown"),"")</f>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N3" t="str" cm="1">
         <f t="array" aca="1" ref="N3:N202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(L3)),"【"&amp;G3:G202&amp;H3:H202&amp;"】 "&amp;_xlfn.ANCHORARRAY(L3),"")</f>
-        <v>【11】 Home return operation</v>
+        <v>【11】 原点復帰動作</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$93,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),1)&amp;"","")</f>
+        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$95,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$95&amp;info_index!$E$2:$E$95,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="P3" t="str" cm="1">
@@ -4545,7 +4618,7 @@
         <v>unknown</v>
       </c>
       <c r="Q3" t="str" cm="1">
-        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$93,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$95,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$95&amp;info_index!$E$2:$E$95,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="R3" t="str" cm="1">
@@ -4565,14 +4638,14 @@
         <f t="array" aca="1" ref="AB3:AB202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AA3)),_xlfn.ANCHORARRAY(AA3),"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;$B$7&amp;_xlfn.ANCHORARRAY(L3)&amp;CHAR(10)&amp;CHAR(9)&amp;IF(H3:H202=1,"IF ","ELSIF ")&amp;$B$26&amp;" = "&amp;H3:H202&amp;" THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC3" t="str" cm="1">
         <f t="array" aca="1" ref="AC3:AC202" ca="1">IF(LEN(AB3:AB202),AB3:AB202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"IF "&amp;$B$27&amp;" = '"&amp;$L$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -4580,54 +4653,54 @@
         <f t="array" aca="1" ref="AD3:AD202" ca="1">IF(LEN(AC3:AC202),AC3:AC202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(L3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE3" t="str" cm="1">
         <f t="array" aca="1" ref="AE3:AE202" ca="1">IF(LEN(AD3:AD202),AD3:AD202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;N$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF3" t="str" cm="1">
         <f t="array" aca="1" ref="AF3:AF202" ca="1">IF(LEN(AE3:AE202),AE3:AE202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(N3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';</v>
+			strRt	:= '【11】 原点復帰動作';</v>
       </c>
       <c r="AG3" t="str" cm="1">
         <f t="array" aca="1" ref="AG3:AG202" ca="1">IF(LEN(AF3:AF202),AF3:AF202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;P$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH3" t="str" cm="1">
         <f t="array" aca="1" ref="AH3:AH202" ca="1">IF(LEN(AG3:AG202),AG3:AG202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(P3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -4635,12 +4708,12 @@
         <f t="array" aca="1" ref="AI3:AI202" ca="1">IF(LEN(AH3:AH202),AH3:AH202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;R$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4649,12 +4722,12 @@
         <f t="array" aca="1" ref="AJ3:AJ202" ca="1">IF(LEN(AI3:AI202),AI3:AI202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(R3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4664,12 +4737,12 @@
         <f t="array" aca="1" ref="AK3:AK202" ca="1">IF(LEN(AJ3:AJ202),AJ3:AJ202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 3"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4682,12 +4755,12 @@
         <f t="array" aca="1" ref="AL3:AL202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AK3)),_xlfn.ANCHORARRAY(AK3),"")&amp;IF(I3:I202="●",CHAR(10)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 2"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4700,12 +4773,12 @@
         <f t="array" aca="1" ref="AM3:AM202" ca="1">_xlfn.ANCHORARRAY(AL3)</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4721,7 +4794,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" ref="G4:G67" si="0">E4&amp;F4</f>
+        <f t="shared" ref="G4:G17" si="0">E4&amp;F4</f>
         <v>1</v>
       </c>
       <c r="H4">
@@ -4737,15 +4810,15 @@
       </c>
       <c r="K4" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="L4" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="N4" t="str">
         <f ca="1"/>
-        <v>【12】 Supply preparation operation</v>
+        <v>【12】 供給準備動作</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -4774,75 +4847,75 @@
       <c r="AB4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';</v>
+			strRt	:= '供給準備動作';</v>
       </c>
       <c r="AE4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';</v>
+			strRt	:= '【12】 供給準備動作';</v>
       </c>
       <c r="AG4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4850,12 +4923,12 @@
       <c r="AJ4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4864,12 +4937,12 @@
       <c r="AK4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4881,12 +4954,12 @@
       <c r="AL4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4898,12 +4971,12 @@
       <c r="AM4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4941,15 +5014,15 @@
       </c>
       <c r="K5" t="str">
         <f ca="1"/>
-        <v>Supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>Supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="N5" t="str">
         <f ca="1"/>
-        <v>【13】 Supply operation</v>
+        <v>【13】 供給動作</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -4978,75 +5051,75 @@
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';</v>
+			strRt	:= '供給動作';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Supply operation';</v>
+			strRt	:= '【13】 供給動作';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Supply operation';
+			strRt	:= '【13】 供給動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Supply operation';
+			strRt	:= '【13】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Supply operation';
+			strRt	:= '【13】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5054,12 +5127,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Supply operation';
+			strRt	:= '【13】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5068,12 +5141,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Supply operation';
+			strRt	:= '【13】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5085,12 +5158,12 @@
       <c r="AL5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Supply operation';
+			strRt	:= '【13】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5102,12 +5175,12 @@
       <c r="AM5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Supply operation';
+			strRt	:= '【13】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5144,15 +5217,15 @@
       </c>
       <c r="K6" t="str">
         <f ca="1"/>
-        <v>Supply completion operation</v>
+        <v>供給終了動作</v>
       </c>
       <c r="L6" t="str">
         <f ca="1"/>
-        <v>Supply completion operation</v>
+        <v>供給終了動作</v>
       </c>
       <c r="N6" t="str">
         <f ca="1"/>
-        <v>【14】 Supply completion operation</v>
+        <v>【14】 供給終了動作</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -5181,75 +5254,75 @@
       <c r="AB6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';</v>
+			strRt	:= '供給終了動作';</v>
       </c>
       <c r="AE6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply completion operation';</v>
+			strRt	:= '【14】 供給終了動作';</v>
       </c>
       <c r="AG6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply completion operation';
+			strRt	:= '【14】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply completion operation';
+			strRt	:= '【14】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply completion operation';
+			strRt	:= '【14】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5257,12 +5330,12 @@
       <c r="AJ6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply completion operation';
+			strRt	:= '【14】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5271,12 +5344,12 @@
       <c r="AK6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply completion operation';
+			strRt	:= '【14】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5288,12 +5361,12 @@
       <c r="AL6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply completion operation';
+			strRt	:= '【14】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5305,12 +5378,12 @@
       <c r="AM6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply completion operation';
+			strRt	:= '【14】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5965,12 +6038,12 @@
         <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5978,12 +6051,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5991,12 +6064,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Supply operation';
+			strRt	:= '【13】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6004,12 +6077,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply completion operation';
+			strRt	:= '【14】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6022,12 +6095,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6035,12 +6108,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6048,12 +6121,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Supply operation';
+			strRt	:= '【23】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6061,12 +6134,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply completion operation';
+			strRt	:= '【24】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6079,12 +6152,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6092,12 +6165,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6105,12 +6178,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Supply operation';
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6118,12 +6191,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Supply completion operation';
+			strRt	:= '【34】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6136,12 +6209,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6149,12 +6222,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Winding preparation operation';
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6162,12 +6235,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding operation';
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6175,12 +6248,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding completion operation';
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6188,12 +6261,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Circumference measurement operation';
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6201,12 +6274,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Discharge operation';
+			strRt	:= '【46】 周長測定動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6219,12 +6305,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6232,12 +6318,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6245,12 +6331,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6258,12 +6344,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6276,12 +6362,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6289,12 +6375,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 In-winding measurement operation';
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6302,12 +6388,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Circumference measurement operation';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6315,12 +6401,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+			strRt	:= '【64】 周長測定動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6356,15 +6455,15 @@
       </c>
       <c r="K13" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L13" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N13" t="str">
         <f ca="1"/>
-        <v>【21】 Home return operation</v>
+        <v>【21】 原点復帰動作</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -6396,7 +6495,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC13" t="str">
@@ -6404,7 +6503,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -6413,20 +6512,20 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF13" t="str">
@@ -6434,24 +6533,24 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';</v>
+			strRt	:= '【21】 原点復帰動作';</v>
       </c>
       <c r="AG13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH13" t="str">
@@ -6459,12 +6558,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -6473,12 +6572,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6488,12 +6587,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6504,12 +6603,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6523,12 +6622,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6542,12 +6641,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6589,15 +6688,15 @@
       </c>
       <c r="K14" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="L14" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="N14" t="str">
         <f ca="1"/>
-        <v>【22】 Supply preparation operation</v>
+        <v>【22】 供給準備動作</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -6626,75 +6725,75 @@
       <c r="AB14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';</v>
+			strRt	:= '供給準備動作';</v>
       </c>
       <c r="AE14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';</v>
+			strRt	:= '【22】 供給準備動作';</v>
       </c>
       <c r="AG14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6702,12 +6801,12 @@
       <c r="AJ14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6716,12 +6815,12 @@
       <c r="AK14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6733,12 +6832,12 @@
       <c r="AL14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6750,12 +6849,12 @@
       <c r="AM14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6786,15 +6885,15 @@
       </c>
       <c r="K15" t="str">
         <f ca="1"/>
-        <v>Supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="L15" t="str">
         <f ca="1"/>
-        <v>Supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="N15" t="str">
         <f ca="1"/>
-        <v>【23】 Supply operation</v>
+        <v>【23】 供給動作</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -6823,75 +6922,75 @@
       <c r="AB15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';</v>
+			strRt	:= '供給動作';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Supply operation';</v>
+			strRt	:= '【23】 供給動作';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Supply operation';
+			strRt	:= '【23】 供給動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Supply operation';
+			strRt	:= '【23】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Supply operation';
+			strRt	:= '【23】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6899,12 +6998,12 @@
       <c r="AJ15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Supply operation';
+			strRt	:= '【23】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6913,12 +7012,12 @@
       <c r="AK15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Supply operation';
+			strRt	:= '【23】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6930,12 +7029,12 @@
       <c r="AL15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Supply operation';
+			strRt	:= '【23】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6947,12 +7046,12 @@
       <c r="AM15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Supply operation';
+			strRt	:= '【23】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6983,15 +7082,15 @@
       </c>
       <c r="K16" t="str">
         <f ca="1"/>
-        <v>Supply completion operation</v>
+        <v>供給終了動作</v>
       </c>
       <c r="L16" t="str">
         <f ca="1"/>
-        <v>Supply completion operation</v>
+        <v>供給終了動作</v>
       </c>
       <c r="N16" t="str">
         <f ca="1"/>
-        <v>【24】 Supply completion operation</v>
+        <v>【24】 供給終了動作</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -7020,75 +7119,75 @@
       <c r="AB16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';</v>
+			strRt	:= '供給終了動作';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply completion operation';</v>
+			strRt	:= '【24】 供給終了動作';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply completion operation';
+			strRt	:= '【24】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply completion operation';
+			strRt	:= '【24】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply completion operation';
+			strRt	:= '【24】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7096,12 +7195,12 @@
       <c r="AJ16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply completion operation';
+			strRt	:= '【24】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7110,12 +7209,12 @@
       <c r="AK16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply completion operation';
+			strRt	:= '【24】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7127,12 +7226,12 @@
       <c r="AL16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply completion operation';
+			strRt	:= '【24】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7144,12 +7243,12 @@
       <c r="AM16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply completion operation';
+			strRt	:= '【24】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7782,7 +7881,7 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <f>F13+1</f>
@@ -7804,15 +7903,15 @@
       </c>
       <c r="K23" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L23" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N23" t="str">
         <f ca="1"/>
-        <v>【31】 Home return operation</v>
+        <v>【31】 原点復帰動作</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -7844,7 +7943,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC23" t="str">
@@ -7852,7 +7951,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -7861,20 +7960,20 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF23" t="str">
@@ -7882,24 +7981,24 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';</v>
+			strRt	:= '【31】 原点復帰動作';</v>
       </c>
       <c r="AG23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH23" t="str">
@@ -7907,12 +8006,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -7921,12 +8020,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7936,12 +8035,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7952,12 +8051,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7971,12 +8070,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7990,12 +8089,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8026,15 +8125,15 @@
       </c>
       <c r="K24" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="L24" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="N24" t="str">
         <f ca="1"/>
-        <v>【32】 Supply preparation operation</v>
+        <v>【32】 供給準備動作</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -8063,75 +8162,75 @@
       <c r="AB24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';</v>
+			strRt	:= '供給準備動作';</v>
       </c>
       <c r="AE24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';</v>
+			strRt	:= '【32】 供給準備動作';</v>
       </c>
       <c r="AG24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8139,12 +8238,12 @@
       <c r="AJ24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8153,12 +8252,12 @@
       <c r="AK24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8170,12 +8269,12 @@
       <c r="AL24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8187,12 +8286,12 @@
       <c r="AM24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8229,15 +8328,15 @@
       </c>
       <c r="K25" t="str">
         <f ca="1"/>
-        <v>Supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="L25" t="str">
         <f ca="1"/>
-        <v>Supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="N25" t="str">
         <f ca="1"/>
-        <v>【33】 Supply operation</v>
+        <v>【33】 供給動作</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -8266,75 +8365,75 @@
       <c r="AB25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';</v>
+			strRt	:= '供給動作';</v>
       </c>
       <c r="AE25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Supply operation';</v>
+			strRt	:= '【33】 供給動作';</v>
       </c>
       <c r="AG25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Supply operation';
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Supply operation';
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Supply operation';
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8342,12 +8441,12 @@
       <c r="AJ25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Supply operation';
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8356,12 +8455,12 @@
       <c r="AK25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Supply operation';
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8373,12 +8472,12 @@
       <c r="AL25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Supply operation';
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8390,12 +8489,12 @@
       <c r="AM25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Supply operation';
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8432,15 +8531,15 @@
       </c>
       <c r="K26" t="str">
         <f ca="1"/>
-        <v>Supply completion operation</v>
+        <v>供給終了動作</v>
       </c>
       <c r="L26" t="str">
         <f ca="1"/>
-        <v>Supply completion operation</v>
+        <v>供給終了動作</v>
       </c>
       <c r="N26" t="str">
         <f ca="1"/>
-        <v>【34】 Supply completion operation</v>
+        <v>【34】 供給終了動作</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -8469,75 +8568,75 @@
       <c r="AB26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';</v>
+			strRt	:= '供給終了動作';</v>
       </c>
       <c r="AE26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Supply completion operation';</v>
+			strRt	:= '【34】 供給終了動作';</v>
       </c>
       <c r="AG26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Supply completion operation';
+			strRt	:= '【34】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Supply completion operation';
+			strRt	:= '【34】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Supply completion operation';
+			strRt	:= '【34】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8545,12 +8644,12 @@
       <c r="AJ26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Supply completion operation';
+			strRt	:= '【34】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8559,12 +8658,12 @@
       <c r="AK26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Supply completion operation';
+			strRt	:= '【34】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8576,12 +8675,12 @@
       <c r="AL26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Supply completion operation';
+			strRt	:= '【34】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8593,12 +8692,12 @@
       <c r="AM26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Supply completion operation';
+			strRt	:= '【34】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9265,15 +9364,15 @@
       </c>
       <c r="K33" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L33" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N33" t="str">
         <f ca="1"/>
-        <v>【41】 Home return operation</v>
+        <v>【41】 原点復帰動作</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -9305,7 +9404,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC33" t="str">
@@ -9313,7 +9412,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -9322,20 +9421,20 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF33" t="str">
@@ -9343,24 +9442,24 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';</v>
+			strRt	:= '【41】 原点復帰動作';</v>
       </c>
       <c r="AG33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH33" t="str">
@@ -9368,12 +9467,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -9382,12 +9481,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9397,12 +9496,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9413,12 +9512,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9432,12 +9531,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9451,12 +9550,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9487,15 +9586,15 @@
       </c>
       <c r="K34" t="str">
         <f ca="1"/>
-        <v>Winding preparation operation</v>
+        <v>周長測定子プリセット</v>
       </c>
       <c r="L34" t="str">
         <f ca="1"/>
-        <v>Winding preparation operation</v>
+        <v>周長測定子プリセット</v>
       </c>
       <c r="N34" t="str">
         <f ca="1"/>
-        <v>【42】 Winding preparation operation</v>
+        <v>【42】 周長測定子プリセット</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -9524,75 +9623,75 @@
       <c r="AB34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';</v>
+			strRt	:= '周長測定子プリセット';</v>
       </c>
       <c r="AE34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Winding preparation operation';</v>
+			strRt	:= '【42】 周長測定子プリセット';</v>
       </c>
       <c r="AG34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Winding preparation operation';
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Winding preparation operation';
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Winding preparation operation';
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9600,12 +9699,12 @@
       <c r="AJ34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Winding preparation operation';
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9614,12 +9713,12 @@
       <c r="AK34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Winding preparation operation';
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9631,12 +9730,12 @@
       <c r="AL34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Winding preparation operation';
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9648,12 +9747,12 @@
       <c r="AM34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Winding preparation operation';
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9684,15 +9783,15 @@
       </c>
       <c r="K35" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻き準備動作</v>
       </c>
       <c r="L35" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻き準備動作</v>
       </c>
       <c r="N35" t="str">
         <f ca="1"/>
-        <v>【43】 Winding operation</v>
+        <v>【43】 巻き準備動作</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -9721,75 +9820,75 @@
       <c r="AB35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';</v>
+			strRt	:= '巻き準備動作';</v>
       </c>
       <c r="AE35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding operation';</v>
+			strRt	:= '【43】 巻き準備動作';</v>
       </c>
       <c r="AG35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding operation';
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding operation';
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding operation';
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9797,12 +9896,12 @@
       <c r="AJ35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding operation';
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9811,12 +9910,12 @@
       <c r="AK35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding operation';
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9828,12 +9927,12 @@
       <c r="AL35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding operation';
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9845,12 +9944,12 @@
       <c r="AM35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding operation';
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9881,15 +9980,15 @@
       </c>
       <c r="K36" t="str">
         <f ca="1"/>
-        <v>Winding completion operation</v>
+        <v>巻き動作</v>
       </c>
       <c r="L36" t="str">
         <f ca="1"/>
-        <v>Winding completion operation</v>
+        <v>巻き動作</v>
       </c>
       <c r="N36" t="str">
         <f ca="1"/>
-        <v>【44】 Winding completion operation</v>
+        <v>【44】 巻き動作</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -9918,75 +10017,75 @@
       <c r="AB36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';</v>
+			strRt	:= '巻き動作';</v>
       </c>
       <c r="AE36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding completion operation';</v>
+			strRt	:= '【44】 巻き動作';</v>
       </c>
       <c r="AG36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding completion operation';
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding completion operation';
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding completion operation';
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9994,12 +10093,12 @@
       <c r="AJ36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding completion operation';
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10008,12 +10107,12 @@
       <c r="AK36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding completion operation';
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10025,12 +10124,12 @@
       <c r="AL36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding completion operation';
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10042,12 +10141,12 @@
       <c r="AM36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding completion operation';
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10078,15 +10177,15 @@
       </c>
       <c r="K37" t="str">
         <f ca="1"/>
-        <v>Circumference measurement operation</v>
+        <v>巻き終了動作</v>
       </c>
       <c r="L37" t="str">
         <f ca="1"/>
-        <v>Circumference measurement operation</v>
+        <v>巻き終了動作</v>
       </c>
       <c r="N37" t="str">
         <f ca="1"/>
-        <v>【45】 Circumference measurement operation</v>
+        <v>【45】 巻き終了動作</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -10115,75 +10214,75 @@
       <c r="AB37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';</v>
+			strRt	:= '巻き終了動作';</v>
       </c>
       <c r="AE37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Circumference measurement operation';</v>
+			strRt	:= '【45】 巻き終了動作';</v>
       </c>
       <c r="AG37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Circumference measurement operation';
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Circumference measurement operation';
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Circumference measurement operation';
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10191,12 +10290,12 @@
       <c r="AJ37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Circumference measurement operation';
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10205,12 +10304,12 @@
       <c r="AK37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Circumference measurement operation';
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10222,12 +10321,12 @@
       <c r="AL37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Circumference measurement operation';
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10239,12 +10338,12 @@
       <c r="AM37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Circumference measurement operation';
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10275,15 +10374,15 @@
       </c>
       <c r="K38" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v>周長測定動作</v>
       </c>
       <c r="L38" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v>周長測定動作</v>
       </c>
       <c r="N38" t="str">
         <f ca="1"/>
-        <v>【46】 Discharge operation</v>
+        <v>【46】 周長測定動作</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -10312,75 +10411,75 @@
       <c r="AB38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';</v>
+			strRt	:= '周長測定動作';</v>
       </c>
       <c r="AE38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Discharge operation';</v>
+			strRt	:= '【46】 周長測定動作';</v>
       </c>
       <c r="AG38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Discharge operation';
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Discharge operation';
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Discharge operation';
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10388,12 +10487,12 @@
       <c r="AJ38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Discharge operation';
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10402,12 +10501,12 @@
       <c r="AK38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Discharge operation';
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10419,12 +10518,12 @@
       <c r="AL38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Discharge operation';
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10436,12 +10535,12 @@
       <c r="AM38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Discharge operation';
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10467,26 +10566,26 @@
       <c r="I39" t="str">
         <v/>
       </c>
-      <c r="J39" t="str">
-        <v/>
+      <c r="J39">
+        <v>19</v>
       </c>
       <c r="K39" t="str">
         <f ca="1"/>
-        <v/>
+        <v>排出動作</v>
       </c>
       <c r="L39" t="str">
         <f ca="1"/>
-        <v/>
+        <v>排出動作</v>
       </c>
       <c r="N39" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【47】 排出動作</v>
       </c>
       <c r="O39" t="str">
         <v/>
       </c>
       <c r="P39" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q39" t="str">
         <f ca="1"/>
@@ -10494,63 +10593,158 @@
       </c>
       <c r="R39" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';</v>
       </c>
       <c r="AE39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';</v>
       </c>
       <c r="AG39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM39" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="40" spans="6:39" x14ac:dyDescent="0.55000000000000004">
@@ -10882,19 +11076,19 @@
         <v/>
       </c>
       <c r="J43">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K43" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L43" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N43" t="str">
         <f ca="1"/>
-        <v>【51】 Home return operation</v>
+        <v>【51】 原点復帰動作</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -10926,7 +11120,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC43" t="str">
@@ -10934,7 +11128,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -10943,20 +11137,20 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF43" t="str">
@@ -10964,24 +11158,24 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';</v>
+			strRt	:= '【51】 原点復帰動作';</v>
       </c>
       <c r="AG43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH43" t="str">
@@ -10989,12 +11183,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -11003,12 +11197,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11018,12 +11212,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11034,12 +11228,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11053,12 +11247,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11072,12 +11266,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11104,19 +11298,19 @@
         <v/>
       </c>
       <c r="J44">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K44" t="str">
         <f ca="1"/>
-        <v>Winding clamping operation</v>
+        <v>巻き押え動作</v>
       </c>
       <c r="L44" t="str">
         <f ca="1"/>
-        <v>Winding clamping operation</v>
+        <v>巻き押え動作</v>
       </c>
       <c r="N44" t="str">
         <f ca="1"/>
-        <v>【52】 Winding clamping operation</v>
+        <v>【52】 巻き押え動作</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -11145,75 +11339,75 @@
       <c r="AB44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';</v>
+			strRt	:= '巻き押え動作';</v>
       </c>
       <c r="AE44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';</v>
+			strRt	:= '【52】 巻き押え動作';</v>
       </c>
       <c r="AG44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11221,12 +11415,12 @@
       <c r="AJ44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11235,12 +11429,12 @@
       <c r="AK44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11252,12 +11446,12 @@
       <c r="AL44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11269,12 +11463,12 @@
       <c r="AM44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11301,19 +11495,19 @@
         <v/>
       </c>
       <c r="J45">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K45" t="str">
         <f ca="1"/>
-        <v>Winding welding operation</v>
+        <v>巻き溶接動作</v>
       </c>
       <c r="L45" t="str">
         <f ca="1"/>
-        <v>Winding welding operation</v>
+        <v>巻き溶接動作</v>
       </c>
       <c r="N45" t="str">
         <f ca="1"/>
-        <v>【53】 Winding welding operation</v>
+        <v>【53】 巻き溶接動作</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -11342,75 +11536,75 @@
       <c r="AB45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';</v>
+			strRt	:= '巻き溶接動作';</v>
       </c>
       <c r="AE45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';</v>
+			strRt	:= '【53】 巻き溶接動作';</v>
       </c>
       <c r="AG45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11418,12 +11612,12 @@
       <c r="AJ45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11432,12 +11626,12 @@
       <c r="AK45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11449,12 +11643,12 @@
       <c r="AL45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11466,12 +11660,12 @@
       <c r="AM45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11498,19 +11692,19 @@
         <v/>
       </c>
       <c r="J46">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K46" t="str">
         <f ca="1"/>
-        <v>Foil wax welding operation</v>
+        <v>箔ロウ溶接動作</v>
       </c>
       <c r="L46" t="str">
         <f ca="1"/>
-        <v>Foil wax welding operation</v>
+        <v>箔ロウ溶接動作</v>
       </c>
       <c r="N46" t="str">
         <f ca="1"/>
-        <v>【54】 Foil wax welding operation</v>
+        <v>【54】 箔ロウ溶接動作</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -11539,75 +11733,75 @@
       <c r="AB46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';</v>
+			strRt	:= '箔ロウ溶接動作';</v>
       </c>
       <c r="AE46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';</v>
+			strRt	:= '【54】 箔ロウ溶接動作';</v>
       </c>
       <c r="AG46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11615,12 +11809,12 @@
       <c r="AJ46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11629,12 +11823,12 @@
       <c r="AK46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11646,12 +11840,12 @@
       <c r="AL46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11663,12 +11857,12 @@
       <c r="AM46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12313,19 +12507,19 @@
         <v/>
       </c>
       <c r="J53">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K53" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L53" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N53" t="str">
         <f ca="1"/>
-        <v>【61】 Home return operation</v>
+        <v>【61】 原点復帰動作</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -12357,7 +12551,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC53" t="str">
@@ -12365,7 +12559,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -12374,20 +12568,20 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF53" t="str">
@@ -12395,24 +12589,24 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';</v>
+			strRt	:= '【61】 原点復帰動作';</v>
       </c>
       <c r="AG53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH53" t="str">
@@ -12420,12 +12614,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -12434,12 +12628,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12449,12 +12643,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12465,12 +12659,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12484,12 +12678,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12503,12 +12697,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12535,19 +12729,19 @@
         <v/>
       </c>
       <c r="J54">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K54" t="str">
         <f ca="1"/>
-        <v>In-winding measurement operation</v>
+        <v>周長測定子プリセット</v>
       </c>
       <c r="L54" t="str">
         <f ca="1"/>
-        <v>In-winding measurement operation</v>
+        <v>周長測定子プリセット</v>
       </c>
       <c r="N54" t="str">
         <f ca="1"/>
-        <v>【62】 In-winding measurement operation</v>
+        <v>【62】 周長測定子プリセット</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -12576,75 +12770,75 @@
       <c r="AB54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';</v>
+			strRt	:= '周長測定子プリセット';</v>
       </c>
       <c r="AE54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 In-winding measurement operation';</v>
+			strRt	:= '【62】 周長測定子プリセット';</v>
       </c>
       <c r="AG54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 In-winding measurement operation';
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 In-winding measurement operation';
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 In-winding measurement operation';
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12652,12 +12846,12 @@
       <c r="AJ54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 In-winding measurement operation';
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12666,12 +12860,12 @@
       <c r="AK54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 In-winding measurement operation';
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12683,12 +12877,12 @@
       <c r="AL54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 In-winding measurement operation';
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12700,12 +12894,12 @@
       <c r="AM54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 In-winding measurement operation';
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12732,19 +12926,19 @@
         <v/>
       </c>
       <c r="J55">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K55" t="str">
         <f ca="1"/>
-        <v>Circumference measurement operation</v>
+        <v>巻き中測定動作</v>
       </c>
       <c r="L55" t="str">
         <f ca="1"/>
-        <v>Circumference measurement operation</v>
+        <v>巻き中測定動作</v>
       </c>
       <c r="N55" t="str">
         <f ca="1"/>
-        <v>【63】 Circumference measurement operation</v>
+        <v>【63】 巻き中測定動作</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -12773,75 +12967,75 @@
       <c r="AB55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';</v>
+			strRt	:= '巻き中測定動作';</v>
       </c>
       <c r="AE55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Circumference measurement operation';</v>
+			strRt	:= '【63】 巻き中測定動作';</v>
       </c>
       <c r="AG55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Circumference measurement operation';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Circumference measurement operation';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Circumference measurement operation';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12849,12 +13043,12 @@
       <c r="AJ55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Circumference measurement operation';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12863,12 +13057,12 @@
       <c r="AK55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Circumference measurement operation';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12880,12 +13074,12 @@
       <c r="AL55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Circumference measurement operation';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12897,12 +13091,12 @@
       <c r="AM55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Circumference measurement operation';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12929,19 +13123,19 @@
         <v/>
       </c>
       <c r="J56">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K56" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v>周長測定動作</v>
       </c>
       <c r="L56" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v>周長測定動作</v>
       </c>
       <c r="N56" t="str">
         <f ca="1"/>
-        <v>【64】 Discharge operation</v>
+        <v>【64】 周長測定動作</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -12970,75 +13164,75 @@
       <c r="AB56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';</v>
+			strRt	:= '周長測定動作';</v>
       </c>
       <c r="AE56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';</v>
+			strRt	:= '【64】 周長測定動作';</v>
       </c>
       <c r="AG56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13046,12 +13240,12 @@
       <c r="AJ56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13060,12 +13254,12 @@
       <c r="AK56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13077,12 +13271,12 @@
       <c r="AL56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13094,12 +13288,12 @@
       <c r="AM56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13125,26 +13319,26 @@
       <c r="I57" t="str">
         <v/>
       </c>
-      <c r="J57" t="str">
-        <v/>
+      <c r="J57">
+        <v>28</v>
       </c>
       <c r="K57" t="str">
         <f ca="1"/>
-        <v/>
+        <v>排出動作</v>
       </c>
       <c r="L57" t="str">
         <f ca="1"/>
-        <v/>
+        <v>排出動作</v>
       </c>
       <c r="N57" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【65】 排出動作</v>
       </c>
       <c r="O57" t="str">
         <v/>
       </c>
       <c r="P57" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q57" t="str">
         <f ca="1"/>
@@ -13152,63 +13346,158 @@
       </c>
       <c r="R57" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';</v>
       </c>
       <c r="AE57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';</v>
       </c>
       <c r="AG57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM57" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="58" spans="6:39" x14ac:dyDescent="0.55000000000000004">
@@ -13727,7 +14016,7 @@
         <v>6</v>
       </c>
       <c r="G63" t="str">
-        <f t="shared" ref="G33:G96" si="5">E63&amp;F63</f>
+        <f t="shared" ref="G63:G96" si="5">E63&amp;F63</f>
         <v>6</v>
       </c>
       <c r="H63">
@@ -28013,12 +28302,12 @@
         <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28026,12 +28315,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28039,12 +28328,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Supply operation';
+			strRt	:= '【13】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28052,12 +28341,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply completion operation';
+			strRt	:= '【14】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28070,12 +28359,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28083,12 +28372,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28096,12 +28385,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Supply operation';
+			strRt	:= '【23】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28109,12 +28398,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply completion operation';
+			strRt	:= '【24】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28127,12 +28416,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28140,12 +28429,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28153,12 +28442,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Supply operation';
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28166,12 +28455,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply completion operation
+	//供給終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply completion operation';
+			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Supply completion operation';
+			strRt	:= '【34】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28184,12 +28473,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28197,12 +28486,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding preparation operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Winding preparation operation';
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28210,12 +28499,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding operation';
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28223,12 +28512,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding completion operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding completion operation';
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28236,12 +28525,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measurement operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Circumference measurement operation';
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28249,12 +28538,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Discharge operation';
+			strRt	:= '【46】 周長測定動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//排出動作
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28267,12 +28569,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28280,12 +28582,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28293,12 +28595,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28306,12 +28608,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28324,12 +28626,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28337,12 +28639,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//In-winding measurement operation
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 In-winding measurement operation';
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28350,12 +28652,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Circumference measurement operation';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28363,12 +28665,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+			strRt	:= '【64】 周長測定動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//排出動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E427F809-67FD-4B1B-9E97-0B25848575D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65C1191-5F7A-4D89-8C97-FA0CBBF5EBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$96</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="107">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -637,6 +637,29 @@
   <si>
     <t>Circumference gauge preset</t>
   </si>
+  <si>
+    <t>供給開始動作</t>
+    <rPh sb="0" eb="2">
+      <t>キョウキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Supply start operation</t>
+  </si>
+  <si>
+    <t>供給開始動作</t>
+    <rPh sb="2" eb="4">
+      <t>カイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -1041,7 +1064,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$98">
+    <xdr:sp macro="" textlink="$A$100">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -1410,7 +1433,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R104"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -1514,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="str">
-        <f t="shared" ref="D3:D64" si="0">B3&amp;C3</f>
+        <f t="shared" ref="D3:D66" si="0">B3&amp;C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="4">
@@ -1545,7 +1568,7 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4">
-        <f t="shared" ref="C4:C5" si="1">C3</f>
+        <f t="shared" ref="C4:C6" si="1">C3</f>
         <v>1</v>
       </c>
       <c r="D4" s="4" t="str">
@@ -1553,7 +1576,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" ref="E4:E5" si="2">E3+1</f>
+        <f t="shared" ref="E4:E6" si="2">E3+1</f>
         <v>3</v>
       </c>
       <c r="F4" s="9"/>
@@ -1561,10 +1584,10 @@
         <v>72</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
@@ -1596,10 +1619,10 @@
         <v>72</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
@@ -1615,42 +1638,42 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4">
-        <f>C2+1</f>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="D6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" ref="D6" si="3">B6&amp;C6</f>
+        <v>1</v>
       </c>
       <c r="E6" s="4">
-        <f>E2</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
       <c r="R6" s="7"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4">
-        <f>C6</f>
+        <f>C2+1</f>
         <v>2</v>
       </c>
       <c r="D7" s="4" t="str">
@@ -1658,18 +1681,18 @@
         <v>2</v>
       </c>
       <c r="E7" s="4">
-        <f>E6+1</f>
-        <v>2</v>
+        <f>E2</f>
+        <v>1</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -1685,7 +1708,7 @@
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4">
-        <f t="shared" ref="C8:C9" si="3">C7</f>
+        <f>C7</f>
         <v>2</v>
       </c>
       <c r="D8" s="4" t="str">
@@ -1693,18 +1716,18 @@
         <v>2</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" ref="E8:E9" si="4">E7+1</f>
-        <v>3</v>
+        <f>E7+1</f>
+        <v>2</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1720,7 +1743,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="C9:C11" si="4">C8</f>
         <v>2</v>
       </c>
       <c r="D9" s="4" t="str">
@@ -1728,18 +1751,18 @@
         <v>2</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" ref="E9:E11" si="5">E8+1</f>
+        <v>3</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1755,26 +1778,26 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4">
-        <f>C6+1</f>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="D10" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4">
-        <f>E6</f>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>4</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1790,26 +1813,26 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4">
-        <f t="shared" ref="C11:C94" si="5">C10</f>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="D11" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="D11" si="6">B11&amp;C11</f>
+        <v>2</v>
       </c>
       <c r="E11" s="4">
-        <f t="shared" ref="E11:E74" si="6">E10+1</f>
-        <v>2</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1825,7 +1848,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4">
-        <f t="shared" si="5"/>
+        <f>C7+1</f>
         <v>3</v>
       </c>
       <c r="D12" s="4" t="str">
@@ -1833,18 +1856,18 @@
         <v>3</v>
       </c>
       <c r="E12" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f>E7</f>
+        <v>1</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
         <v>74</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1860,7 +1883,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C13:C96" si="7">C12</f>
         <v>3</v>
       </c>
       <c r="D13" s="4" t="str">
@@ -1868,18 +1891,18 @@
         <v>3</v>
       </c>
       <c r="E13" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E13:E76" si="8">E12+1</f>
+        <v>2</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
         <v>74</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -1895,26 +1918,26 @@
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4">
-        <f>C10+1</f>
-        <v>4</v>
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4">
-        <f>E10</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1930,26 +1953,26 @@
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4">
-        <f t="shared" ref="C15" si="7">C14</f>
-        <v>4</v>
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="D15" s="4" t="str">
         <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="8"/>
         <v>4</v>
-      </c>
-      <c r="E15" s="4">
-        <f t="shared" ref="E15" si="8">E14+1</f>
-        <v>2</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -1965,7 +1988,7 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4">
-        <f t="shared" si="5"/>
+        <f>C12+1</f>
         <v>4</v>
       </c>
       <c r="D16" s="4" t="str">
@@ -1973,18 +1996,18 @@
         <v>4</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f>E12</f>
+        <v>1</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2000,7 +2023,7 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C17" si="9">C16</f>
         <v>4</v>
       </c>
       <c r="D17" s="4" t="str">
@@ -2008,18 +2031,18 @@
         <v>4</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E17" si="10">E16+1</f>
+        <v>2</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -2035,7 +2058,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="D18" s="4" t="str">
@@ -2043,21 +2066,21 @@
         <v>4</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J18" s="5"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
@@ -2070,29 +2093,29 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="D19" s="4" t="str">
-        <f t="shared" ref="D19" si="9">B19&amp;C19</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="6"/>
-        <v>6</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J19" s="5"/>
-      <c r="K19" s="6"/>
+      <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
@@ -2105,26 +2128,26 @@
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="D20" s="4" t="str">
-        <f t="shared" ref="D20" si="10">B20&amp;C20</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="6"/>
-        <v>7</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
@@ -2140,29 +2163,29 @@
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4">
-        <f t="shared" ref="C21" si="11">C14+1</f>
-        <v>5</v>
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="D21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ref="D21" si="11">B21&amp;C21</f>
+        <v>4</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" ref="E21" si="12">E14</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+      <c r="K21" s="6"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
@@ -2175,29 +2198,29 @@
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4">
-        <f t="shared" ref="C22" si="13">C21</f>
-        <v>5</v>
+        <f t="shared" si="7"/>
+        <v>4</v>
       </c>
       <c r="D22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ref="D22" si="12">B22&amp;C22</f>
+        <v>4</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" ref="E22" si="14">E21+1</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>7</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
+      <c r="K22" s="6"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
@@ -2210,7 +2233,7 @@
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C23" si="13">C16+1</f>
         <v>5</v>
       </c>
       <c r="D23" s="4" t="str">
@@ -2218,34 +2241,34 @@
         <v>5</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E23" si="14">E16</f>
+        <v>1</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C24" si="15">C23</f>
         <v>5</v>
       </c>
       <c r="D24" s="4" t="str">
@@ -2253,53 +2276,53 @@
         <v>5</v>
       </c>
       <c r="E24" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E24" si="16">E23+1</f>
+        <v>2</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4">
-        <f t="shared" ref="C25" si="15">C21+1</f>
-        <v>6</v>
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="D25" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="4">
-        <f>E21</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -2315,42 +2338,42 @@
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4">
-        <f t="shared" ref="C26" si="16">C25</f>
-        <v>6</v>
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="D26" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" ref="E26" si="17">E25+1</f>
-        <v>2</v>
-      </c>
-      <c r="F26" s="9"/>
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22"/>
+        <v>76</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
       <c r="R26" s="7"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C27" si="17">C23+1</f>
         <v>6</v>
       </c>
       <c r="D27" s="4" t="str">
@@ -2358,18 +2381,18 @@
         <v>6</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f>E23</f>
+        <v>1</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
         <v>77</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -2385,7 +2408,7 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C28" si="18">C27</f>
         <v>6</v>
       </c>
       <c r="D28" s="4" t="str">
@@ -2393,18 +2416,18 @@
         <v>6</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E28" si="19">E27+1</f>
+        <v>2</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="5" t="s">
         <v>77</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
@@ -2420,56 +2443,62 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="D29" s="4" t="str">
-        <f t="shared" ref="D29" si="18">B29&amp;C29</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="F29" s="9"/>
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H29" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="22"/>
-      <c r="Q29" s="22"/>
+      <c r="H29" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="21"/>
       <c r="R29" s="7"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
-        <f t="shared" ref="C30" si="19">C25+1</f>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="D30" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" s="4">
-        <f>E25</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
+      <c r="G30" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
@@ -2484,21 +2513,27 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4">
-        <f t="shared" ref="C31" si="20">C30</f>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="D31" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f t="shared" ref="D31" si="20">B31&amp;C31</f>
+        <v>6</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" ref="E31" si="21">E30+1</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
+      <c r="G31" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>97</v>
+      </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
@@ -2513,7 +2548,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C32" si="21">C27+1</f>
         <v>7</v>
       </c>
       <c r="D32" s="4" t="str">
@@ -2521,28 +2556,28 @@
         <v>7</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
+        <f>E27</f>
+        <v>1</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
       <c r="R32" s="7"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C33" si="22">C32</f>
         <v>7</v>
       </c>
       <c r="D33" s="4" t="str">
@@ -2550,28 +2585,28 @@
         <v>7</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
+        <f t="shared" ref="E33" si="23">E32+1</f>
+        <v>2</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22"/>
       <c r="R33" s="7"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="D34" s="4" t="str">
@@ -2579,8 +2614,8 @@
         <v>7</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -2597,68 +2632,68 @@
       <c r="R34" s="7"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="26"/>
+      <c r="A35" s="4"/>
       <c r="B35" s="4"/>
-      <c r="C35" s="26">
-        <f t="shared" ref="C35" si="22">C30+1</f>
-        <v>8</v>
-      </c>
-      <c r="D35" s="26" t="str">
+      <c r="C35" s="4">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="D35" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" ref="E35" si="23">E30</f>
-        <v>1</v>
-      </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="26"/>
+      <c r="A36" s="4"/>
       <c r="B36" s="4"/>
-      <c r="C36" s="26">
-        <f t="shared" ref="C36" si="24">C35</f>
-        <v>8</v>
-      </c>
-      <c r="D36" s="26" t="str">
+      <c r="C36" s="4">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="D36" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" ref="E36" si="25">E35+1</f>
-        <v>2</v>
-      </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="26"/>
       <c r="B37" s="4"/>
       <c r="C37" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C37" si="24">C32+1</f>
         <v>8</v>
       </c>
       <c r="D37" s="26" t="str">
@@ -2666,8 +2701,8 @@
         <v>8</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E37" si="25">E32</f>
+        <v>1</v>
       </c>
       <c r="F37" s="11"/>
       <c r="G37" s="11"/>
@@ -2684,77 +2719,77 @@
       <c r="R37" s="7"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="4"/>
+      <c r="A38" s="26"/>
       <c r="B38" s="4"/>
-      <c r="C38" s="4">
-        <f t="shared" si="5"/>
+      <c r="C38" s="26">
+        <f t="shared" ref="C38" si="26">C37</f>
         <v>8</v>
       </c>
-      <c r="D38" s="4" t="str">
+      <c r="D38" s="26" t="str">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
+        <f t="shared" ref="E38" si="27">E37+1</f>
+        <v>2</v>
+      </c>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="23"/>
       <c r="R38" s="7"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="4"/>
+      <c r="A39" s="26"/>
       <c r="B39" s="4"/>
-      <c r="C39" s="4">
-        <f t="shared" si="5"/>
+      <c r="C39" s="26">
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="D39" s="4" t="str">
+      <c r="D39" s="26" t="str">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="7"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="11"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="23"/>
+      <c r="Q39" s="23"/>
       <c r="R39" s="7"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
-        <f t="shared" ref="C40" si="26">C35+1</f>
-        <v>9</v>
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="D40" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" ref="E40" si="27">E35</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -2774,16 +2809,16 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
-        <f t="shared" ref="C41" si="28">C40</f>
-        <v>9</v>
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="D41" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" ref="E41" si="29">E40+1</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -2803,7 +2838,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C42" si="28">C37+1</f>
         <v>9</v>
       </c>
       <c r="D42" s="4" t="str">
@@ -2811,8 +2846,8 @@
         <v>9</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E42" si="29">E37</f>
+        <v>1</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -2832,7 +2867,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C43" si="30">C42</f>
         <v>9</v>
       </c>
       <c r="D43" s="4" t="str">
@@ -2840,15 +2875,15 @@
         <v>9</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E43" si="31">E42+1</f>
+        <v>2</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
-      <c r="K43" s="13"/>
+      <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
@@ -2861,7 +2896,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="D44" s="4" t="str">
@@ -2869,8 +2904,8 @@
         <v>9</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -2890,23 +2925,23 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
-        <f t="shared" ref="C45" si="30">C40+1</f>
-        <v>10</v>
+        <f t="shared" si="7"/>
+        <v>9</v>
       </c>
       <c r="D45" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" ref="E45" si="31">E40</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
+      <c r="K45" s="13"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
@@ -2919,16 +2954,16 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
-        <f t="shared" ref="C46" si="32">C45</f>
-        <v>10</v>
+        <f t="shared" si="7"/>
+        <v>9</v>
       </c>
       <c r="D46" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" ref="E46" si="33">E45+1</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -2948,7 +2983,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C47" si="32">C42+1</f>
         <v>10</v>
       </c>
       <c r="D47" s="4" t="str">
@@ -2956,8 +2991,8 @@
         <v>10</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E47" si="33">E42</f>
+        <v>1</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -2977,7 +3012,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C48" si="34">C47</f>
         <v>10</v>
       </c>
       <c r="D48" s="4" t="str">
@@ -2985,8 +3020,8 @@
         <v>10</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E48" si="35">E47+1</f>
+        <v>2</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -3006,7 +3041,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="D49" s="4" t="str">
@@ -3014,8 +3049,8 @@
         <v>10</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -3035,16 +3070,16 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <f t="shared" ref="C50" si="34">C45+1</f>
-        <v>11</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="D50" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E50" s="4">
-        <f t="shared" ref="E50" si="35">E45</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -3064,16 +3099,16 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
-        <f t="shared" ref="C51" si="36">C50</f>
-        <v>11</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="D51" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" ref="E51" si="37">E50+1</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -3093,7 +3128,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C52" si="36">C47+1</f>
         <v>11</v>
       </c>
       <c r="D52" s="4" t="str">
@@ -3101,8 +3136,8 @@
         <v>11</v>
       </c>
       <c r="E52" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E52" si="37">E47</f>
+        <v>1</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -3122,7 +3157,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C53" si="38">C52</f>
         <v>11</v>
       </c>
       <c r="D53" s="4" t="str">
@@ -3130,8 +3165,8 @@
         <v>11</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E53" si="39">E52+1</f>
+        <v>2</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -3151,7 +3186,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="D54" s="4" t="str">
@@ -3159,8 +3194,8 @@
         <v>11</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -3180,16 +3215,16 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
-        <f t="shared" ref="C55" si="38">C50+1</f>
-        <v>12</v>
+        <f t="shared" si="7"/>
+        <v>11</v>
       </c>
       <c r="D55" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E55" s="4">
-        <f t="shared" ref="E55" si="39">E50</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -3209,16 +3244,16 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
-        <f t="shared" ref="C56" si="40">C55</f>
-        <v>12</v>
+        <f t="shared" si="7"/>
+        <v>11</v>
       </c>
       <c r="D56" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E56" s="4">
-        <f t="shared" ref="E56" si="41">E55+1</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -3238,7 +3273,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C57" si="40">C52+1</f>
         <v>12</v>
       </c>
       <c r="D57" s="4" t="str">
@@ -3246,8 +3281,8 @@
         <v>12</v>
       </c>
       <c r="E57" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E57" si="41">E52</f>
+        <v>1</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -3267,7 +3302,7 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C58" si="42">C57</f>
         <v>12</v>
       </c>
       <c r="D58" s="4" t="str">
@@ -3275,8 +3310,8 @@
         <v>12</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E58" si="43">E57+1</f>
+        <v>2</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -3296,7 +3331,7 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="D59" s="4" t="str">
@@ -3304,8 +3339,8 @@
         <v>12</v>
       </c>
       <c r="E59" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -3325,16 +3360,16 @@
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <f t="shared" ref="C60:C90" si="42">C55+1</f>
-        <v>13</v>
+        <f t="shared" si="7"/>
+        <v>12</v>
       </c>
       <c r="D60" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E60" s="4">
-        <f t="shared" ref="E60" si="43">E55</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -3354,16 +3389,16 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
-        <f t="shared" ref="C61:C91" si="44">C60</f>
-        <v>13</v>
+        <f t="shared" si="7"/>
+        <v>12</v>
       </c>
       <c r="D61" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E61" s="4">
-        <f t="shared" ref="E61" si="45">E60+1</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -3383,7 +3418,7 @@
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C62:C92" si="44">C57+1</f>
         <v>13</v>
       </c>
       <c r="D62" s="4" t="str">
@@ -3391,8 +3426,8 @@
         <v>13</v>
       </c>
       <c r="E62" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E62" si="45">E57</f>
+        <v>1</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -3412,7 +3447,7 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="C63:C93" si="46">C62</f>
         <v>13</v>
       </c>
       <c r="D63" s="4" t="str">
@@ -3420,8 +3455,8 @@
         <v>13</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E63" si="47">E62+1</f>
+        <v>2</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -3441,7 +3476,7 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="D64" s="4" t="str">
@@ -3449,8 +3484,8 @@
         <v>13</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -3470,16 +3505,16 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4">
-        <f t="shared" si="42"/>
-        <v>14</v>
+        <f t="shared" si="7"/>
+        <v>13</v>
       </c>
       <c r="D65" s="4" t="str">
-        <f t="shared" ref="D65:D94" si="46">B65&amp;C65</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E65" s="4">
-        <f t="shared" ref="E65" si="47">E60</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -3499,16 +3534,16 @@
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4">
-        <f t="shared" si="44"/>
-        <v>14</v>
+        <f t="shared" si="7"/>
+        <v>13</v>
       </c>
       <c r="D66" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E66" s="4">
-        <f t="shared" ref="E66" si="48">E65+1</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -3528,16 +3563,16 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="44"/>
         <v>14</v>
       </c>
       <c r="D67" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="D67:D96" si="48">B67&amp;C67</f>
         <v>14</v>
       </c>
       <c r="E67" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E67" si="49">E62</f>
+        <v>1</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -3557,16 +3592,16 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4">
-        <f t="shared" si="5"/>
-        <v>14</v>
-      </c>
-      <c r="D68" s="4" t="str">
         <f t="shared" si="46"/>
         <v>14</v>
       </c>
+      <c r="D68" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>14</v>
+      </c>
       <c r="E68" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E68" si="50">E67+1</f>
+        <v>2</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -3586,16 +3621,16 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="D69" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>14</v>
       </c>
       <c r="E69" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -3615,16 +3650,16 @@
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4">
-        <f t="shared" si="42"/>
-        <v>15</v>
+        <f t="shared" si="7"/>
+        <v>14</v>
       </c>
       <c r="D70" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>15</v>
+        <f t="shared" si="48"/>
+        <v>14</v>
       </c>
       <c r="E70" s="4">
-        <f t="shared" ref="E70" si="49">E65</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -3644,16 +3679,16 @@
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4">
-        <f t="shared" si="44"/>
-        <v>15</v>
+        <f t="shared" si="7"/>
+        <v>14</v>
       </c>
       <c r="D71" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>15</v>
+        <f t="shared" si="48"/>
+        <v>14</v>
       </c>
       <c r="E71" s="4">
-        <f t="shared" ref="E71" si="50">E70+1</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -3673,16 +3708,16 @@
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="44"/>
         <v>15</v>
       </c>
       <c r="D72" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>15</v>
       </c>
       <c r="E72" s="4">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <f t="shared" ref="E72" si="51">E67</f>
+        <v>1</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -3702,16 +3737,16 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4">
-        <f t="shared" si="5"/>
-        <v>15</v>
-      </c>
-      <c r="D73" s="4" t="str">
         <f t="shared" si="46"/>
         <v>15</v>
       </c>
+      <c r="D73" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>15</v>
+      </c>
       <c r="E73" s="4">
-        <f t="shared" si="6"/>
-        <v>4</v>
+        <f t="shared" ref="E73" si="52">E72+1</f>
+        <v>2</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -3731,16 +3766,16 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="D74" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>15</v>
       </c>
       <c r="E74" s="4">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -3760,16 +3795,16 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4">
-        <f t="shared" si="42"/>
-        <v>16</v>
+        <f t="shared" si="7"/>
+        <v>15</v>
       </c>
       <c r="D75" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>16</v>
+        <f t="shared" si="48"/>
+        <v>15</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" ref="E75" si="51">E70</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -3789,16 +3824,16 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4">
-        <f t="shared" si="44"/>
-        <v>16</v>
+        <f t="shared" si="7"/>
+        <v>15</v>
       </c>
       <c r="D76" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>16</v>
+        <f t="shared" si="48"/>
+        <v>15</v>
       </c>
       <c r="E76" s="4">
-        <f t="shared" ref="E76:E94" si="52">E75+1</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -3818,16 +3853,16 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="44"/>
         <v>16</v>
       </c>
       <c r="D77" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>16</v>
       </c>
       <c r="E77" s="4">
-        <f t="shared" si="52"/>
-        <v>3</v>
+        <f t="shared" ref="E77" si="53">E72</f>
+        <v>1</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -3847,16 +3882,16 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4">
-        <f t="shared" si="5"/>
-        <v>16</v>
-      </c>
-      <c r="D78" s="4" t="str">
         <f t="shared" si="46"/>
         <v>16</v>
       </c>
+      <c r="D78" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>16</v>
+      </c>
       <c r="E78" s="4">
-        <f t="shared" si="52"/>
-        <v>4</v>
+        <f t="shared" ref="E78:E96" si="54">E77+1</f>
+        <v>2</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -3876,16 +3911,16 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="D79" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>16</v>
       </c>
       <c r="E79" s="4">
-        <f t="shared" si="52"/>
-        <v>5</v>
+        <f t="shared" si="54"/>
+        <v>3</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -3905,16 +3940,16 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4">
-        <f t="shared" si="42"/>
-        <v>17</v>
+        <f t="shared" si="7"/>
+        <v>16</v>
       </c>
       <c r="D80" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>17</v>
+        <f t="shared" si="48"/>
+        <v>16</v>
       </c>
       <c r="E80" s="4">
-        <f t="shared" ref="E80" si="53">E75</f>
-        <v>1</v>
+        <f t="shared" si="54"/>
+        <v>4</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -3934,16 +3969,16 @@
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4">
-        <f t="shared" si="44"/>
-        <v>17</v>
+        <f t="shared" si="7"/>
+        <v>16</v>
       </c>
       <c r="D81" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>17</v>
+        <f t="shared" si="48"/>
+        <v>16</v>
       </c>
       <c r="E81" s="4">
-        <f t="shared" ref="E81" si="54">E80+1</f>
-        <v>2</v>
+        <f t="shared" si="54"/>
+        <v>5</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -3963,16 +3998,16 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="44"/>
         <v>17</v>
       </c>
       <c r="D82" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>17</v>
       </c>
       <c r="E82" s="4">
-        <f t="shared" si="52"/>
-        <v>3</v>
+        <f t="shared" ref="E82" si="55">E77</f>
+        <v>1</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -3992,16 +4027,16 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4">
-        <f t="shared" si="5"/>
-        <v>17</v>
-      </c>
-      <c r="D83" s="4" t="str">
         <f t="shared" si="46"/>
         <v>17</v>
       </c>
+      <c r="D83" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>17</v>
+      </c>
       <c r="E83" s="4">
-        <f t="shared" si="52"/>
-        <v>4</v>
+        <f t="shared" ref="E83" si="56">E82+1</f>
+        <v>2</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -4021,16 +4056,16 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="D84" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>17</v>
       </c>
       <c r="E84" s="4">
-        <f t="shared" si="52"/>
-        <v>5</v>
+        <f t="shared" si="54"/>
+        <v>3</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
@@ -4050,16 +4085,16 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4">
-        <f t="shared" si="42"/>
-        <v>18</v>
+        <f t="shared" si="7"/>
+        <v>17</v>
       </c>
       <c r="D85" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>18</v>
+        <f t="shared" si="48"/>
+        <v>17</v>
       </c>
       <c r="E85" s="4">
-        <f t="shared" ref="E85" si="55">E80</f>
-        <v>1</v>
+        <f t="shared" si="54"/>
+        <v>4</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
@@ -4079,16 +4114,16 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4">
-        <f t="shared" si="44"/>
-        <v>18</v>
+        <f t="shared" si="7"/>
+        <v>17</v>
       </c>
       <c r="D86" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>18</v>
+        <f t="shared" si="48"/>
+        <v>17</v>
       </c>
       <c r="E86" s="4">
-        <f t="shared" ref="E86" si="56">E85+1</f>
-        <v>2</v>
+        <f t="shared" si="54"/>
+        <v>5</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
@@ -4108,16 +4143,16 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="44"/>
         <v>18</v>
       </c>
       <c r="D87" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>18</v>
       </c>
       <c r="E87" s="4">
-        <f t="shared" si="52"/>
-        <v>3</v>
+        <f t="shared" ref="E87" si="57">E82</f>
+        <v>1</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -4137,16 +4172,16 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4">
-        <f t="shared" si="5"/>
-        <v>18</v>
-      </c>
-      <c r="D88" s="4" t="str">
         <f t="shared" si="46"/>
         <v>18</v>
       </c>
+      <c r="D88" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>18</v>
+      </c>
       <c r="E88" s="4">
-        <f t="shared" si="52"/>
-        <v>4</v>
+        <f t="shared" ref="E88" si="58">E87+1</f>
+        <v>2</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
@@ -4166,16 +4201,16 @@
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="D89" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>18</v>
       </c>
       <c r="E89" s="4">
-        <f t="shared" si="52"/>
-        <v>5</v>
+        <f t="shared" si="54"/>
+        <v>3</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
@@ -4195,16 +4230,16 @@
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4">
-        <f t="shared" si="42"/>
-        <v>19</v>
+        <f t="shared" si="7"/>
+        <v>18</v>
       </c>
       <c r="D90" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>19</v>
+        <f t="shared" si="48"/>
+        <v>18</v>
       </c>
       <c r="E90" s="4">
-        <f t="shared" ref="E90" si="57">E85</f>
-        <v>1</v>
+        <f t="shared" si="54"/>
+        <v>4</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
@@ -4224,16 +4259,16 @@
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4">
-        <f t="shared" si="44"/>
-        <v>19</v>
+        <f t="shared" si="7"/>
+        <v>18</v>
       </c>
       <c r="D91" s="4" t="str">
-        <f t="shared" si="46"/>
-        <v>19</v>
+        <f t="shared" si="48"/>
+        <v>18</v>
       </c>
       <c r="E91" s="4">
-        <f t="shared" ref="E91" si="58">E90+1</f>
-        <v>2</v>
+        <f t="shared" si="54"/>
+        <v>5</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
@@ -4253,16 +4288,16 @@
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="44"/>
         <v>19</v>
       </c>
       <c r="D92" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>19</v>
       </c>
       <c r="E92" s="4">
-        <f t="shared" si="52"/>
-        <v>3</v>
+        <f t="shared" ref="E92" si="59">E87</f>
+        <v>1</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
@@ -4282,16 +4317,16 @@
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4">
-        <f t="shared" si="5"/>
-        <v>19</v>
-      </c>
-      <c r="D93" s="4" t="str">
         <f t="shared" si="46"/>
         <v>19</v>
       </c>
+      <c r="D93" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>19</v>
+      </c>
       <c r="E93" s="4">
-        <f t="shared" si="52"/>
-        <v>4</v>
+        <f t="shared" ref="E93" si="60">E92+1</f>
+        <v>2</v>
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
@@ -4311,16 +4346,16 @@
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="D94" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>19</v>
       </c>
       <c r="E94" s="4">
-        <f t="shared" si="52"/>
-        <v>5</v>
+        <f t="shared" si="54"/>
+        <v>3</v>
       </c>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
@@ -4337,94 +4372,152 @@
       <c r="R94" s="7"/>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="15"/>
-      <c r="B95" s="15"/>
-      <c r="C95" s="15"/>
-      <c r="D95" s="15"/>
-      <c r="E95" s="15"/>
-      <c r="F95" s="16"/>
-      <c r="G95" s="16"/>
-      <c r="H95" s="16"/>
-      <c r="I95" s="16"/>
-      <c r="J95" s="16"/>
-      <c r="K95" s="16"/>
-      <c r="L95" s="16"/>
-      <c r="M95" s="16"/>
-      <c r="N95" s="16"/>
-      <c r="O95" s="17"/>
-      <c r="P95" s="17"/>
-      <c r="Q95" s="17"/>
-      <c r="R95" s="17"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" t="s">
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="D95" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>19</v>
+      </c>
+      <c r="E95" s="4">
+        <f t="shared" si="54"/>
+        <v>4</v>
+      </c>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="5"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="7"/>
+      <c r="P95" s="7"/>
+      <c r="Q95" s="7"/>
+      <c r="R95" s="7"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
+      <c r="C96" s="4">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="D96" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v>19</v>
+      </c>
+      <c r="E96" s="4">
+        <f t="shared" si="54"/>
+        <v>5</v>
+      </c>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+      <c r="K96" s="5"/>
+      <c r="L96" s="5"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="7"/>
+      <c r="P96" s="7"/>
+      <c r="Q96" s="7"/>
+      <c r="R96" s="7"/>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="15"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="16"/>
+      <c r="G97" s="16"/>
+      <c r="H97" s="16"/>
+      <c r="I97" s="16"/>
+      <c r="J97" s="16"/>
+      <c r="K97" s="16"/>
+      <c r="L97" s="16"/>
+      <c r="M97" s="16"/>
+      <c r="N97" s="16"/>
+      <c r="O97" s="17"/>
+      <c r="P97" s="17"/>
+      <c r="Q97" s="17"/>
+      <c r="R97" s="17"/>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" t="s">
         <v>9</v>
       </c>
-      <c r="F97" t="s">
+      <c r="F99" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98">
-        <f>MAX(A$2:A$95)</f>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100">
+        <f>MAX(A$2:A$97)</f>
         <v>0</v>
       </c>
-      <c r="F98">
-        <f>MAX(F$2:F$95)</f>
+      <c r="F100">
+        <f>MAX(F$2:F$97)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" t="s">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" t="s">
         <v>40</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D101" t="s">
         <v>14</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E101" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100">
-        <f>ROW(A96)-ROW(A1)-1</f>
-        <v>94</v>
-      </c>
-      <c r="D100">
-        <f>COUNTIF(D$2:D$95,D99)</f>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102">
+        <f>ROW(A98)-ROW(A1)-1</f>
+        <v>96</v>
+      </c>
+      <c r="D102">
+        <f>COUNTIF(D$2:D$97,D101)</f>
         <v>0</v>
       </c>
-      <c r="E100" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$95,$D$2:$D$95,E99)</f>
+      <c r="E102" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$97,$D$2:$D$97,E101)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D101" t="s">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="D103" t="s">
         <v>12</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E103" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D102">
-        <f>COUNTIF(D$2:D$95,D101)</f>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="D104">
+        <f>COUNTIF(D$2:D$97,D103)</f>
         <v>0</v>
       </c>
-      <c r="E102" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$95,$D$2:$D$95,E101)</f>
+      <c r="E104" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$97,$D$2:$D$97,E103)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R94" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R94">
-      <sortCondition ref="D1:D94"/>
+  <autoFilter ref="A1:R96" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R96">
+      <sortCondition ref="D1:D96"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:R95">
+  <conditionalFormatting sqref="A2:R97">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
@@ -4580,7 +4673,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -4594,11 +4687,11 @@
         <v>1</v>
       </c>
       <c r="J3" cm="1">
-        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$95&amp;info_index!$E$2:$E$95,0),"")</f>
+        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$97&amp;info_index!$E$2:$E$97,0),"")</f>
         <v>1</v>
       </c>
       <c r="K3" t="str" cm="1">
-        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$95,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$95&amp;info_index!$E$2:$E$95,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$97,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$97&amp;info_index!$E$2:$E$97,0),1)&amp;"","")</f>
         <v>原点復帰動作</v>
       </c>
       <c r="L3" t="str" cm="1">
@@ -4610,7 +4703,7 @@
         <v>【11】 原点復帰動作</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$95,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$95&amp;info_index!$E$2:$E$95,0),1)&amp;"","")</f>
+        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$97,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$97&amp;info_index!$E$2:$E$97,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="P3" t="str" cm="1">
@@ -4618,7 +4711,7 @@
         <v>unknown</v>
       </c>
       <c r="Q3" t="str" cm="1">
-        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$95,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$95&amp;info_index!$E$2:$E$95,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$97,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$97&amp;info_index!$E$2:$E$97,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="R3" t="str" cm="1">
@@ -4992,7 +5085,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -5014,15 +5107,15 @@
       </c>
       <c r="K5" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>供給開始動作</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>供給開始動作</v>
       </c>
       <c r="N5" t="str">
         <f ca="1"/>
-        <v>【13】 供給動作</v>
+        <v>【13】 供給開始動作</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -5051,75 +5144,75 @@
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= '供給開始動作';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= '供給開始動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給動作';</v>
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 供給開始動作';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5127,12 +5220,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5141,12 +5234,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5158,12 +5251,12 @@
       <c r="AL5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5175,12 +5268,12 @@
       <c r="AM5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5217,15 +5310,15 @@
       </c>
       <c r="K6" t="str">
         <f ca="1"/>
-        <v>供給終了動作</v>
+        <v>供給動作</v>
       </c>
       <c r="L6" t="str">
         <f ca="1"/>
-        <v>供給終了動作</v>
+        <v>供給動作</v>
       </c>
       <c r="N6" t="str">
         <f ca="1"/>
-        <v>【14】 供給終了動作</v>
+        <v>【14】 供給動作</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -5254,75 +5347,75 @@
       <c r="AB6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';</v>
+			strRt	:= '供給動作';</v>
       </c>
       <c r="AE6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給終了動作';</v>
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 供給動作';</v>
       </c>
       <c r="AG6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 供給動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5330,12 +5423,12 @@
       <c r="AJ6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5344,12 +5437,12 @@
       <c r="AK6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5361,12 +5454,12 @@
       <c r="AL6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5378,12 +5471,12 @@
       <c r="AM6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5415,26 +5508,26 @@
       <c r="I7" t="str">
         <v/>
       </c>
-      <c r="J7" t="str">
-        <v/>
+      <c r="J7">
+        <v>5</v>
       </c>
       <c r="K7" t="str">
         <f ca="1"/>
-        <v/>
+        <v>供給終了動作</v>
       </c>
       <c r="L7" t="str">
         <f ca="1"/>
-        <v/>
+        <v>供給終了動作</v>
       </c>
       <c r="N7" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【15】 供給終了動作</v>
       </c>
       <c r="O7" t="str">
         <v/>
       </c>
       <c r="P7" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q7" t="str">
         <f ca="1"/>
@@ -5442,63 +5535,158 @@
       </c>
       <c r="R7" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';</v>
       </c>
       <c r="AE7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 供給終了動作';</v>
       </c>
       <c r="AG7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM7" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.55000000000000004">
@@ -6035,7 +6223,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//原点復帰動作
@@ -6064,12 +6252,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
+	//供給開始動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 供給開始動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
 	//供給動作
-	ELSIF uiInfoIdx = 3 THEN
+	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給動作';
+			strRt	:= '【14】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6078,11 +6279,11 @@
 			uiErrCode	:= 3;
 		END_IF;
 	//供給終了動作
-	ELSIF uiInfoIdx = 4 THEN
+	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給終了動作';
+			strRt	:= '【15】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6121,12 +6322,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
+	//供給開始動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
 	//供給動作
-	ELSIF uiInfoIdx = 3 THEN
+	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給動作';
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6135,11 +6349,11 @@
 			uiErrCode	:= 3;
 		END_IF;
 	//供給終了動作
-	ELSIF uiInfoIdx = 4 THEN
+	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給終了動作';
+			strRt	:= '【25】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6451,7 +6665,7 @@
         <v/>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K13" t="str">
         <f ca="1"/>
@@ -6684,7 +6898,7 @@
         <v/>
       </c>
       <c r="J14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K14" t="str">
         <f ca="1"/>
@@ -6881,19 +7095,19 @@
         <v/>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>供給開始動作</v>
       </c>
       <c r="L15" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>供給開始動作</v>
       </c>
       <c r="N15" t="str">
         <f ca="1"/>
-        <v>【23】 供給動作</v>
+        <v>【23】 供給開始動作</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -6922,75 +7136,75 @@
       <c r="AB15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= '供給開始動作';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= '供給開始動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給動作';</v>
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6998,12 +7212,12 @@
       <c r="AJ15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7012,12 +7226,12 @@
       <c r="AK15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7029,12 +7243,12 @@
       <c r="AL15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7046,12 +7260,12 @@
       <c r="AM15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給動作';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7078,19 +7292,19 @@
         <v/>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" t="str">
         <f ca="1"/>
-        <v>供給終了動作</v>
+        <v>供給動作</v>
       </c>
       <c r="L16" t="str">
         <f ca="1"/>
-        <v>供給終了動作</v>
+        <v>供給動作</v>
       </c>
       <c r="N16" t="str">
         <f ca="1"/>
-        <v>【24】 供給終了動作</v>
+        <v>【24】 供給動作</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -7119,75 +7333,75 @@
       <c r="AB16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';</v>
+			strRt	:= '供給動作';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給終了動作';</v>
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7195,12 +7409,12 @@
       <c r="AJ16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7209,12 +7423,12 @@
       <c r="AK16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7226,12 +7440,12 @@
       <c r="AL16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7243,12 +7457,12 @@
       <c r="AM16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給終了動作
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給終了動作';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7274,26 +7488,26 @@
       <c r="I17" t="str">
         <v/>
       </c>
-      <c r="J17" t="str">
-        <v/>
+      <c r="J17">
+        <v>10</v>
       </c>
       <c r="K17" t="str">
         <f ca="1"/>
-        <v/>
+        <v>供給終了動作</v>
       </c>
       <c r="L17" t="str">
         <f ca="1"/>
-        <v/>
+        <v>供給終了動作</v>
       </c>
       <c r="N17" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【25】 供給終了動作</v>
       </c>
       <c r="O17" t="str">
         <v/>
       </c>
       <c r="P17" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q17" t="str">
         <f ca="1"/>
@@ -7301,63 +7515,158 @@
       </c>
       <c r="R17" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';</v>
       </c>
       <c r="AE17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 供給終了動作';</v>
       </c>
       <c r="AG17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM17" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//供給終了動作
+	ELSIF uiInfoIdx = 5 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 供給終了動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.55000000000000004">
@@ -7899,7 +8208,7 @@
         <v/>
       </c>
       <c r="J23">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K23" t="str">
         <f ca="1"/>
@@ -8121,7 +8430,7 @@
         <v/>
       </c>
       <c r="J24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K24" t="str">
         <f ca="1"/>
@@ -8324,7 +8633,7 @@
         <v/>
       </c>
       <c r="J25">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K25" t="str">
         <f ca="1"/>
@@ -8527,7 +8836,7 @@
         <v/>
       </c>
       <c r="J26">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K26" t="str">
         <f ca="1"/>
@@ -9360,7 +9669,7 @@
         <v/>
       </c>
       <c r="J33">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K33" t="str">
         <f ca="1"/>
@@ -9582,7 +9891,7 @@
         <v/>
       </c>
       <c r="J34">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K34" t="str">
         <f ca="1"/>
@@ -9779,7 +10088,7 @@
         <v/>
       </c>
       <c r="J35">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K35" t="str">
         <f ca="1"/>
@@ -9976,7 +10285,7 @@
         <v/>
       </c>
       <c r="J36">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K36" t="str">
         <f ca="1"/>
@@ -10173,7 +10482,7 @@
         <v/>
       </c>
       <c r="J37">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K37" t="str">
         <f ca="1"/>
@@ -10370,7 +10679,7 @@
         <v/>
       </c>
       <c r="J38">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K38" t="str">
         <f ca="1"/>
@@ -10567,7 +10876,7 @@
         <v/>
       </c>
       <c r="J39">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K39" t="str">
         <f ca="1"/>
@@ -11076,7 +11385,7 @@
         <v/>
       </c>
       <c r="J43">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K43" t="str">
         <f ca="1"/>
@@ -11298,7 +11607,7 @@
         <v/>
       </c>
       <c r="J44">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K44" t="str">
         <f ca="1"/>
@@ -11495,7 +11804,7 @@
         <v/>
       </c>
       <c r="J45">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K45" t="str">
         <f ca="1"/>
@@ -11692,7 +12001,7 @@
         <v/>
       </c>
       <c r="J46">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K46" t="str">
         <f ca="1"/>
@@ -12507,7 +12816,7 @@
         <v/>
       </c>
       <c r="J53">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K53" t="str">
         <f ca="1"/>
@@ -12729,7 +13038,7 @@
         <v/>
       </c>
       <c r="J54">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K54" t="str">
         <f ca="1"/>
@@ -12926,7 +13235,7 @@
         <v/>
       </c>
       <c r="J55">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K55" t="str">
         <f ca="1"/>
@@ -13123,7 +13432,7 @@
         <v/>
       </c>
       <c r="J56">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K56" t="str">
         <f ca="1"/>
@@ -13320,7 +13629,7 @@
         <v/>
       </c>
       <c r="J57">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K57" t="str">
         <f ca="1"/>
@@ -28299,7 +28608,7 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//原点復帰動作
@@ -28328,12 +28637,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
+	//供給開始動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 供給開始動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
 	//供給動作
-	ELSIF uiInfoIdx = 3 THEN
+	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給動作';
+			strRt	:= '【14】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28342,11 +28664,11 @@
 			uiErrCode	:= 3;
 		END_IF;
 	//供給終了動作
-	ELSIF uiInfoIdx = 4 THEN
+	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給終了動作';
+			strRt	:= '【15】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28385,12 +28707,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
+	//供給開始動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
 	//供給動作
-	ELSIF uiInfoIdx = 3 THEN
+	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給動作';
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28399,11 +28734,11 @@
 			uiErrCode	:= 3;
 		END_IF;
 	//供給終了動作
-	ELSIF uiInfoIdx = 4 THEN
+	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= '供給終了動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給終了動作';
+			strRt	:= '【25】 供給終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0ACF775-1A37-410C-9663-A2EF9F00605A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E389CE54-2AA0-4BF7-8B1C-73B97E0E5004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -4994,15 +4994,15 @@
       </c>
       <c r="K3" t="str" cm="1">
         <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$107,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$107&amp;info_index!$E$2:$E$107,0),1)&amp;"","")</f>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L3" t="str" cm="1">
         <f t="array" aca="1" ref="L3:L202" ca="1">IF(LEN(_xlfn.ANCHORARRAY($J3)),IF(LEN(_xlfn.ANCHORARRAY(K3)),_xlfn.ANCHORARRAY(K3),"unknown"),"")</f>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N3" t="str" cm="1">
         <f t="array" aca="1" ref="N3:N202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(L3)),"【"&amp;G3:G202&amp;H3:H202&amp;"】 "&amp;_xlfn.ANCHORARRAY(L3),"")</f>
-        <v>【11】 Home return operation</v>
+        <v>【11】 原点復帰動作</v>
       </c>
       <c r="O3" t="str" cm="1">
         <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$107,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$107&amp;info_index!$E$2:$E$107,0),1)&amp;"","")</f>
@@ -5033,14 +5033,14 @@
         <f t="array" aca="1" ref="AB3:AB202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AA3)),_xlfn.ANCHORARRAY(AA3),"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;$B$7&amp;_xlfn.ANCHORARRAY(L3)&amp;CHAR(10)&amp;CHAR(9)&amp;IF(H3:H202=1,"IF ","ELSIF ")&amp;$B$26&amp;" = "&amp;H3:H202&amp;" THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC3" t="str" cm="1">
         <f t="array" aca="1" ref="AC3:AC202" ca="1">IF(LEN(AB3:AB202),AB3:AB202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"IF "&amp;$B$27&amp;" = '"&amp;$L$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -5048,54 +5048,54 @@
         <f t="array" aca="1" ref="AD3:AD202" ca="1">IF(LEN(AC3:AC202),AC3:AC202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(L3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE3" t="str" cm="1">
         <f t="array" aca="1" ref="AE3:AE202" ca="1">IF(LEN(AD3:AD202),AD3:AD202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;N$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF3" t="str" cm="1">
         <f t="array" aca="1" ref="AF3:AF202" ca="1">IF(LEN(AE3:AE202),AE3:AE202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(N3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';</v>
       </c>
       <c r="AG3" t="str" cm="1">
         <f t="array" aca="1" ref="AG3:AG202" ca="1">IF(LEN(AF3:AF202),AF3:AF202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;P$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH3" t="str" cm="1">
         <f t="array" aca="1" ref="AH3:AH202" ca="1">IF(LEN(AG3:AG202),AG3:AG202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(P3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -5103,12 +5103,12 @@
         <f t="array" aca="1" ref="AI3:AI202" ca="1">IF(LEN(AH3:AH202),AH3:AH202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;R$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5117,12 +5117,12 @@
         <f t="array" aca="1" ref="AJ3:AJ202" ca="1">IF(LEN(AI3:AI202),AI3:AI202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(R3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5132,12 +5132,12 @@
         <f t="array" aca="1" ref="AK3:AK202" ca="1">IF(LEN(AJ3:AJ202),AJ3:AJ202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 3"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5150,12 +5150,12 @@
         <f t="array" aca="1" ref="AL3:AL202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AK3)),_xlfn.ANCHORARRAY(AK3),"")&amp;IF(I3:I202="●",CHAR(10)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 2"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5168,12 +5168,12 @@
         <f t="array" aca="1" ref="AM3:AM202" ca="1">_xlfn.ANCHORARRAY(AL3)</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5205,15 +5205,15 @@
       </c>
       <c r="K4" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="L4" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="N4" t="str">
         <f ca="1"/>
-        <v>【12】 Supply preparation operation</v>
+        <v>【12】 供給準備動作</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -5242,75 +5242,75 @@
       <c r="AB4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';</v>
+			strRt	:= '供給準備動作';</v>
       </c>
       <c r="AE4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';</v>
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';</v>
       </c>
       <c r="AG4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5318,12 +5318,12 @@
       <c r="AJ4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5332,12 +5332,12 @@
       <c r="AK4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5349,12 +5349,12 @@
       <c r="AL4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5366,12 +5366,12 @@
       <c r="AM4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -5409,15 +5409,15 @@
       </c>
       <c r="K5" t="str">
         <f ca="1"/>
-        <v>Winding start operation</v>
+        <v>巻取り開始動作</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>Winding start operation</v>
+        <v>巻取り開始動作</v>
       </c>
       <c r="N5" t="str">
         <f ca="1"/>
-        <v>【13】 Winding start operation</v>
+        <v>【13】 巻取り開始動作</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -5446,75 +5446,75 @@
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';</v>
+			strRt	:= '巻取り開始動作';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
+			strRt	:= '巻取り開始動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Winding start operation';</v>
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 巻取り開始動作';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5522,12 +5522,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5536,12 +5536,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5553,12 +5553,12 @@
       <c r="AL5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5570,12 +5570,12 @@
       <c r="AM5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5612,15 +5612,15 @@
       </c>
       <c r="K6" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻取り動作</v>
       </c>
       <c r="L6" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻取り動作</v>
       </c>
       <c r="N6" t="str">
         <f ca="1"/>
-        <v>【14】 Winding operation</v>
+        <v>【14】 巻取り動作</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -5649,75 +5649,75 @@
       <c r="AB6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';</v>
+			strRt	:= '巻取り動作';</v>
       </c>
       <c r="AE6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻取り動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Winding operation';</v>
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 巻取り動作';</v>
       </c>
       <c r="AG6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5725,12 +5725,12 @@
       <c r="AJ6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5739,12 +5739,12 @@
       <c r="AK6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5756,12 +5756,12 @@
       <c r="AL6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5773,12 +5773,12 @@
       <c r="AM6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5815,15 +5815,15 @@
       </c>
       <c r="K7" t="str">
         <f ca="1"/>
-        <v>Winding end operation</v>
+        <v>巻取り終了動作</v>
       </c>
       <c r="L7" t="str">
         <f ca="1"/>
-        <v>Winding end operation</v>
+        <v>巻取り終了動作</v>
       </c>
       <c r="N7" t="str">
         <f ca="1"/>
-        <v>【15】 Winding end operation</v>
+        <v>【15】 巻取り終了動作</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -5852,75 +5852,75 @@
       <c r="AB7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';</v>
+			strRt	:= '巻取り終了動作';</v>
       </c>
       <c r="AE7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
+			strRt	:= '巻取り終了動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Winding end operation';</v>
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 巻取り終了動作';</v>
       </c>
       <c r="AG7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5928,12 +5928,12 @@
       <c r="AJ7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5942,12 +5942,12 @@
       <c r="AK7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5959,12 +5959,12 @@
       <c r="AL7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5976,12 +5976,12 @@
       <c r="AM7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6615,15 +6615,15 @@
       </c>
       <c r="K11" t="str">
         <f ca="1"/>
-        <v>Cutting Operation</v>
+        <v>カット動作</v>
       </c>
       <c r="L11" t="str">
         <f ca="1"/>
-        <v>Cutting Operation</v>
+        <v>カット動作</v>
       </c>
       <c r="N11" t="str">
         <f ca="1"/>
-        <v>【19】 Cutting Operation</v>
+        <v>【19】 カット動作</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -6652,75 +6652,75 @@
       <c r="AB11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN</v>
       </c>
       <c r="AC11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';</v>
+			strRt	:= 'カット動作';</v>
       </c>
       <c r="AE11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
+			strRt	:= 'カット動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 Cutting Operation';</v>
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 カット動作';</v>
       </c>
       <c r="AG11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 カット動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6728,12 +6728,12 @@
       <c r="AJ11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6742,12 +6742,12 @@
       <c r="AK11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6759,12 +6759,12 @@
       <c r="AL11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6776,12 +6776,12 @@
       <c r="AM11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7000,15 +7000,15 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7016,12 +7016,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7029,12 +7029,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7042,12 +7042,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7055,12 +7055,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7107,12 +7107,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7138,12 +7138,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7151,12 +7151,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7164,12 +7164,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7177,12 +7177,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7190,12 +7190,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7242,12 +7242,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7273,12 +7273,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7286,12 +7286,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7299,12 +7299,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7312,12 +7312,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7330,12 +7330,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7343,12 +7343,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7356,12 +7356,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7369,12 +7369,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7382,12 +7382,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Winding completion operation';
+			strRt	:= '巻き終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7395,12 +7395,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7408,12 +7408,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7426,12 +7426,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7439,12 +7439,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7452,12 +7452,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '巻き溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7465,12 +7465,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7483,12 +7483,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7496,12 +7496,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7509,12 +7509,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 In-winding measurement operation';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7522,12 +7522,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7535,12 +7535,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7576,15 +7576,15 @@
       </c>
       <c r="K13" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L13" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N13" t="str">
         <f ca="1"/>
-        <v>【21】 Home return operation</v>
+        <v>【21】 原点復帰動作</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -7616,7 +7616,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC13" t="str">
@@ -7624,7 +7624,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -7633,20 +7633,20 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF13" t="str">
@@ -7654,24 +7654,24 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';</v>
       </c>
       <c r="AG13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH13" t="str">
@@ -7679,12 +7679,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -7693,12 +7693,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7708,12 +7708,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7724,12 +7724,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7743,12 +7743,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7762,12 +7762,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7809,15 +7809,15 @@
       </c>
       <c r="K14" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="L14" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="N14" t="str">
         <f ca="1"/>
-        <v>【22】 Supply preparation operation</v>
+        <v>【22】 供給準備動作</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -7846,75 +7846,75 @@
       <c r="AB14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';</v>
+			strRt	:= '供給準備動作';</v>
       </c>
       <c r="AE14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';</v>
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';</v>
       </c>
       <c r="AG14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7922,12 +7922,12 @@
       <c r="AJ14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7936,12 +7936,12 @@
       <c r="AK14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7953,12 +7953,12 @@
       <c r="AL14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7970,12 +7970,12 @@
       <c r="AM14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8006,15 +8006,15 @@
       </c>
       <c r="K15" t="str">
         <f ca="1"/>
-        <v>Winding start operation</v>
+        <v>巻取り開始動作</v>
       </c>
       <c r="L15" t="str">
         <f ca="1"/>
-        <v>Winding start operation</v>
+        <v>巻取り開始動作</v>
       </c>
       <c r="N15" t="str">
         <f ca="1"/>
-        <v>【23】 Winding start operation</v>
+        <v>【23】 巻取り開始動作</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -8043,75 +8043,75 @@
       <c r="AB15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';</v>
+			strRt	:= '巻取り開始動作';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
+			strRt	:= '巻取り開始動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Winding start operation';</v>
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 巻取り開始動作';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8119,12 +8119,12 @@
       <c r="AJ15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8133,12 +8133,12 @@
       <c r="AK15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8150,12 +8150,12 @@
       <c r="AL15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8167,12 +8167,12 @@
       <c r="AM15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8203,15 +8203,15 @@
       </c>
       <c r="K16" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻取り動作</v>
       </c>
       <c r="L16" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻取り動作</v>
       </c>
       <c r="N16" t="str">
         <f ca="1"/>
-        <v>【24】 Winding operation</v>
+        <v>【24】 巻取り動作</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -8240,75 +8240,75 @@
       <c r="AB16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';</v>
+			strRt	:= '巻取り動作';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻取り動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Winding operation';</v>
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 巻取り動作';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8316,12 +8316,12 @@
       <c r="AJ16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8330,12 +8330,12 @@
       <c r="AK16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8347,12 +8347,12 @@
       <c r="AL16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8364,12 +8364,12 @@
       <c r="AM16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8400,15 +8400,15 @@
       </c>
       <c r="K17" t="str">
         <f ca="1"/>
-        <v>Winding end operation</v>
+        <v>巻取り終了動作</v>
       </c>
       <c r="L17" t="str">
         <f ca="1"/>
-        <v>Winding end operation</v>
+        <v>巻取り終了動作</v>
       </c>
       <c r="N17" t="str">
         <f ca="1"/>
-        <v>【25】 Winding end operation</v>
+        <v>【25】 巻取り終了動作</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -8437,75 +8437,75 @@
       <c r="AB17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';</v>
+			strRt	:= '巻取り終了動作';</v>
       </c>
       <c r="AE17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
+			strRt	:= '巻取り終了動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Winding end operation';</v>
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 巻取り終了動作';</v>
       </c>
       <c r="AG17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8513,12 +8513,12 @@
       <c r="AJ17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8527,12 +8527,12 @@
       <c r="AK17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8544,12 +8544,12 @@
       <c r="AL17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8561,12 +8561,12 @@
       <c r="AM17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9188,15 +9188,15 @@
       </c>
       <c r="K21" t="str">
         <f ca="1"/>
-        <v>Cutting Operation</v>
+        <v>カット動作</v>
       </c>
       <c r="L21" t="str">
         <f ca="1"/>
-        <v>Cutting Operation</v>
+        <v>カット動作</v>
       </c>
       <c r="N21" t="str">
         <f ca="1"/>
-        <v>【29】 Cutting Operation</v>
+        <v>【29】 カット動作</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -9225,75 +9225,75 @@
       <c r="AB21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN</v>
       </c>
       <c r="AC21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';</v>
+			strRt	:= 'カット動作';</v>
       </c>
       <c r="AE21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
+			strRt	:= 'カット動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 Cutting Operation';</v>
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 カット動作';</v>
       </c>
       <c r="AG21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 カット動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9301,12 +9301,12 @@
       <c r="AJ21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9315,12 +9315,12 @@
       <c r="AK21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9332,12 +9332,12 @@
       <c r="AL21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9349,12 +9349,12 @@
       <c r="AM21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9572,7 +9572,7 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <f>F13+1</f>
@@ -9594,15 +9594,15 @@
       </c>
       <c r="K23" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L23" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N23" t="str">
         <f ca="1"/>
-        <v>【31】 Home return operation</v>
+        <v>【31】 原点復帰動作</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -9634,7 +9634,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC23" t="str">
@@ -9642,7 +9642,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -9651,20 +9651,20 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF23" t="str">
@@ -9672,24 +9672,24 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';</v>
       </c>
       <c r="AG23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH23" t="str">
@@ -9697,12 +9697,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -9711,12 +9711,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9726,12 +9726,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9742,12 +9742,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9761,12 +9761,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9780,12 +9780,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9816,15 +9816,15 @@
       </c>
       <c r="K24" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="L24" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="N24" t="str">
         <f ca="1"/>
-        <v>【32】 Supply preparation operation</v>
+        <v>【32】 供給準備動作</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -9853,75 +9853,75 @@
       <c r="AB24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';</v>
+			strRt	:= '供給準備動作';</v>
       </c>
       <c r="AE24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';</v>
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';</v>
       </c>
       <c r="AG24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9929,12 +9929,12 @@
       <c r="AJ24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9943,12 +9943,12 @@
       <c r="AK24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9960,12 +9960,12 @@
       <c r="AL24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9977,12 +9977,12 @@
       <c r="AM24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10019,15 +10019,15 @@
       </c>
       <c r="K25" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻取り動作</v>
       </c>
       <c r="L25" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻取り動作</v>
       </c>
       <c r="N25" t="str">
         <f ca="1"/>
-        <v>【33】 Winding operation</v>
+        <v>【33】 巻取り動作</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -10056,75 +10056,75 @@
       <c r="AB25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';</v>
+			strRt	:= '巻取り動作';</v>
       </c>
       <c r="AE25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻取り動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Winding operation';</v>
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 巻取り動作';</v>
       </c>
       <c r="AG25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10132,12 +10132,12 @@
       <c r="AJ25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10146,12 +10146,12 @@
       <c r="AK25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10163,12 +10163,12 @@
       <c r="AL25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10180,12 +10180,12 @@
       <c r="AM25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10222,15 +10222,15 @@
       </c>
       <c r="K26" t="str">
         <f ca="1"/>
-        <v>Winding end operation</v>
+        <v>巻取り終了動作</v>
       </c>
       <c r="L26" t="str">
         <f ca="1"/>
-        <v>Winding end operation</v>
+        <v>巻取り終了動作</v>
       </c>
       <c r="N26" t="str">
         <f ca="1"/>
-        <v>【34】 Winding end operation</v>
+        <v>【34】 巻取り終了動作</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -10259,75 +10259,75 @@
       <c r="AB26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';</v>
+			strRt	:= '巻取り終了動作';</v>
       </c>
       <c r="AE26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
+			strRt	:= '巻取り終了動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Winding end operation';</v>
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 巻取り終了動作';</v>
       </c>
       <c r="AG26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10335,12 +10335,12 @@
       <c r="AJ26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10349,12 +10349,12 @@
       <c r="AK26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10366,12 +10366,12 @@
       <c r="AL26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10383,12 +10383,12 @@
       <c r="AM26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11055,15 +11055,15 @@
       </c>
       <c r="K33" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L33" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N33" t="str">
         <f ca="1"/>
-        <v>【41】 Home return operation</v>
+        <v>【41】 原点復帰動作</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -11095,7 +11095,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC33" t="str">
@@ -11103,7 +11103,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -11112,20 +11112,20 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF33" t="str">
@@ -11133,24 +11133,24 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';</v>
       </c>
       <c r="AG33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH33" t="str">
@@ -11158,12 +11158,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -11172,12 +11172,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11187,12 +11187,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11203,12 +11203,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11222,12 +11222,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11241,12 +11241,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11277,15 +11277,15 @@
       </c>
       <c r="K34" t="str">
         <f ca="1"/>
-        <v>Circumference gauge preset</v>
+        <v>周長測定子プリセット</v>
       </c>
       <c r="L34" t="str">
         <f ca="1"/>
-        <v>Circumference gauge preset</v>
+        <v>周長測定子プリセット</v>
       </c>
       <c r="N34" t="str">
         <f ca="1"/>
-        <v>【42】 Circumference gauge preset</v>
+        <v>【42】 周長測定子プリセット</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -11314,75 +11314,75 @@
       <c r="AB34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';</v>
+			strRt	:= '周長測定子プリセット';</v>
       </c>
       <c r="AE34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';</v>
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';</v>
       </c>
       <c r="AG34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11390,12 +11390,12 @@
       <c r="AJ34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11404,12 +11404,12 @@
       <c r="AK34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11421,12 +11421,12 @@
       <c r="AL34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11438,12 +11438,12 @@
       <c r="AM34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11474,15 +11474,15 @@
       </c>
       <c r="K35" t="str">
         <f ca="1"/>
-        <v>Winding preparation operation</v>
+        <v>巻き準備動作</v>
       </c>
       <c r="L35" t="str">
         <f ca="1"/>
-        <v>Winding preparation operation</v>
+        <v>巻き準備動作</v>
       </c>
       <c r="N35" t="str">
         <f ca="1"/>
-        <v>【43】 Winding preparation operation</v>
+        <v>【43】 巻き準備動作</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -11511,75 +11511,75 @@
       <c r="AB35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';</v>
+			strRt	:= '巻き準備動作';</v>
       </c>
       <c r="AE35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';</v>
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';</v>
       </c>
       <c r="AG35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11587,12 +11587,12 @@
       <c r="AJ35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11601,12 +11601,12 @@
       <c r="AK35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11618,12 +11618,12 @@
       <c r="AL35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11635,12 +11635,12 @@
       <c r="AM35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11671,15 +11671,15 @@
       </c>
       <c r="K36" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻き動作</v>
       </c>
       <c r="L36" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻き動作</v>
       </c>
       <c r="N36" t="str">
         <f ca="1"/>
-        <v>【44】 Winding operation</v>
+        <v>【44】 巻き動作</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -11708,75 +11708,75 @@
       <c r="AB36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';</v>
+			strRt	:= '巻き動作';</v>
       </c>
       <c r="AE36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';</v>
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';</v>
       </c>
       <c r="AG36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11784,12 +11784,12 @@
       <c r="AJ36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11798,12 +11798,12 @@
       <c r="AK36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11815,12 +11815,12 @@
       <c r="AL36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11832,12 +11832,12 @@
       <c r="AM36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11868,15 +11868,15 @@
       </c>
       <c r="K37" t="str">
         <f ca="1"/>
-        <v>Winding completion operation</v>
+        <v>巻き終了動作</v>
       </c>
       <c r="L37" t="str">
         <f ca="1"/>
-        <v>Winding completion operation</v>
+        <v>巻き終了動作</v>
       </c>
       <c r="N37" t="str">
         <f ca="1"/>
-        <v>【45】 Winding completion operation</v>
+        <v>【45】 巻き終了動作</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -11905,75 +11905,75 @@
       <c r="AB37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';</v>
+			strRt	:= '巻き終了動作';</v>
       </c>
       <c r="AE37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
+			strRt	:= '巻き終了動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Winding completion operation';</v>
+			strRt	:= '巻き終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 巻き終了動作';</v>
       </c>
       <c r="AG37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Winding completion operation';
+			strRt	:= '巻き終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Winding completion operation';
+			strRt	:= '巻き終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Winding completion operation';
+			strRt	:= '巻き終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11981,12 +11981,12 @@
       <c r="AJ37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Winding completion operation';
+			strRt	:= '巻き終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11995,12 +11995,12 @@
       <c r="AK37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Winding completion operation';
+			strRt	:= '巻き終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12012,12 +12012,12 @@
       <c r="AL37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Winding completion operation';
+			strRt	:= '巻き終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12029,12 +12029,12 @@
       <c r="AM37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Winding completion operation';
+			strRt	:= '巻き終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12065,15 +12065,15 @@
       </c>
       <c r="K38" t="str">
         <f ca="1"/>
-        <v>Circumference measurement operation</v>
+        <v>周長測定動作</v>
       </c>
       <c r="L38" t="str">
         <f ca="1"/>
-        <v>Circumference measurement operation</v>
+        <v>周長測定動作</v>
       </c>
       <c r="N38" t="str">
         <f ca="1"/>
-        <v>【46】 Circumference measurement operation</v>
+        <v>【46】 周長測定動作</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -12102,75 +12102,75 @@
       <c r="AB38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';</v>
+			strRt	:= '周長測定動作';</v>
       </c>
       <c r="AE38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';</v>
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';</v>
       </c>
       <c r="AG38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12178,12 +12178,12 @@
       <c r="AJ38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12192,12 +12192,12 @@
       <c r="AK38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12209,12 +12209,12 @@
       <c r="AL38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12226,12 +12226,12 @@
       <c r="AM38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12262,15 +12262,15 @@
       </c>
       <c r="K39" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v>排出動作</v>
       </c>
       <c r="L39" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v>排出動作</v>
       </c>
       <c r="N39" t="str">
         <f ca="1"/>
-        <v>【47】 Discharge operation</v>
+        <v>【47】 排出動作</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -12299,75 +12299,75 @@
       <c r="AB39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';</v>
+			strRt	:= '排出動作';</v>
       </c>
       <c r="AE39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '排出動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 Discharge operation';</v>
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';</v>
       </c>
       <c r="AG39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12375,12 +12375,12 @@
       <c r="AJ39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12389,12 +12389,12 @@
       <c r="AK39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12406,12 +12406,12 @@
       <c r="AL39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12423,12 +12423,12 @@
       <c r="AM39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12771,15 +12771,15 @@
       </c>
       <c r="K43" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L43" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N43" t="str">
         <f ca="1"/>
-        <v>【51】 Home return operation</v>
+        <v>【51】 原点復帰動作</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -12811,7 +12811,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC43" t="str">
@@ -12819,7 +12819,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -12828,20 +12828,20 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF43" t="str">
@@ -12849,24 +12849,24 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';</v>
       </c>
       <c r="AG43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH43" t="str">
@@ -12874,12 +12874,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -12888,12 +12888,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12903,12 +12903,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12919,12 +12919,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12938,12 +12938,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12957,12 +12957,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12993,15 +12993,15 @@
       </c>
       <c r="K44" t="str">
         <f ca="1"/>
-        <v>Winding clamping operation</v>
+        <v>巻き押え動作</v>
       </c>
       <c r="L44" t="str">
         <f ca="1"/>
-        <v>Winding clamping operation</v>
+        <v>巻き押え動作</v>
       </c>
       <c r="N44" t="str">
         <f ca="1"/>
-        <v>【52】 Winding clamping operation</v>
+        <v>【52】 巻き押え動作</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -13030,75 +13030,75 @@
       <c r="AB44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';</v>
+			strRt	:= '巻き押え動作';</v>
       </c>
       <c r="AE44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';</v>
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';</v>
       </c>
       <c r="AG44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13106,12 +13106,12 @@
       <c r="AJ44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13120,12 +13120,12 @@
       <c r="AK44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13137,12 +13137,12 @@
       <c r="AL44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13154,12 +13154,12 @@
       <c r="AM44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13190,15 +13190,15 @@
       </c>
       <c r="K45" t="str">
         <f ca="1"/>
-        <v>Winding welding operation</v>
+        <v>巻き溶接動作</v>
       </c>
       <c r="L45" t="str">
         <f ca="1"/>
-        <v>Winding welding operation</v>
+        <v>巻き溶接動作</v>
       </c>
       <c r="N45" t="str">
         <f ca="1"/>
-        <v>【53】 Winding welding operation</v>
+        <v>【53】 巻き溶接動作</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -13227,75 +13227,75 @@
       <c r="AB45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';</v>
+			strRt	:= '巻き溶接動作';</v>
       </c>
       <c r="AE45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
+			strRt	:= '巻き溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';</v>
+			strRt	:= '巻き溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 巻き溶接動作';</v>
       </c>
       <c r="AG45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '巻き溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '巻き溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '巻き溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13303,12 +13303,12 @@
       <c r="AJ45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '巻き溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13317,12 +13317,12 @@
       <c r="AK45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '巻き溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13334,12 +13334,12 @@
       <c r="AL45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '巻き溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13351,12 +13351,12 @@
       <c r="AM45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '巻き溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13387,15 +13387,15 @@
       </c>
       <c r="K46" t="str">
         <f ca="1"/>
-        <v>Foil wax welding operation</v>
+        <v>箔ロウ溶接動作</v>
       </c>
       <c r="L46" t="str">
         <f ca="1"/>
-        <v>Foil wax welding operation</v>
+        <v>箔ロウ溶接動作</v>
       </c>
       <c r="N46" t="str">
         <f ca="1"/>
-        <v>【54】 Foil wax welding operation</v>
+        <v>【54】 箔ロウ溶接動作</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -13424,75 +13424,75 @@
       <c r="AB46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';</v>
+			strRt	:= '箔ロウ溶接動作';</v>
       </c>
       <c r="AE46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';</v>
+			strRt	:= '箔ロウ溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 箔ロウ溶接動作';</v>
       </c>
       <c r="AG46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13500,12 +13500,12 @@
       <c r="AJ46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13514,12 +13514,12 @@
       <c r="AK46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13531,12 +13531,12 @@
       <c r="AL46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13548,12 +13548,12 @@
       <c r="AM46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14202,15 +14202,15 @@
       </c>
       <c r="K53" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L53" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N53" t="str">
         <f ca="1"/>
-        <v>【61】 Home return operation</v>
+        <v>【61】 原点復帰動作</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -14242,7 +14242,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC53" t="str">
@@ -14250,7 +14250,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -14259,20 +14259,20 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF53" t="str">
@@ -14280,24 +14280,24 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';</v>
       </c>
       <c r="AG53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH53" t="str">
@@ -14305,12 +14305,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -14319,12 +14319,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14334,12 +14334,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14350,12 +14350,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14369,12 +14369,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14388,12 +14388,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14424,15 +14424,15 @@
       </c>
       <c r="K54" t="str">
         <f ca="1"/>
-        <v>Circumference gauge preset</v>
+        <v>周長測定子プリセット</v>
       </c>
       <c r="L54" t="str">
         <f ca="1"/>
-        <v>Circumference gauge preset</v>
+        <v>周長測定子プリセット</v>
       </c>
       <c r="N54" t="str">
         <f ca="1"/>
-        <v>【62】 Circumference gauge preset</v>
+        <v>【62】 周長測定子プリセット</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -14461,75 +14461,75 @@
       <c r="AB54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';</v>
+			strRt	:= '周長測定子プリセット';</v>
       </c>
       <c r="AE54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Circumference gauge preset';</v>
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 周長測定子プリセット';</v>
       </c>
       <c r="AG54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14537,12 +14537,12 @@
       <c r="AJ54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14551,12 +14551,12 @@
       <c r="AK54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14568,12 +14568,12 @@
       <c r="AL54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14585,12 +14585,12 @@
       <c r="AM54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14621,15 +14621,15 @@
       </c>
       <c r="K55" t="str">
         <f ca="1"/>
-        <v>In-winding measurement operation</v>
+        <v>巻き中測定動作</v>
       </c>
       <c r="L55" t="str">
         <f ca="1"/>
-        <v>In-winding measurement operation</v>
+        <v>巻き中測定動作</v>
       </c>
       <c r="N55" t="str">
         <f ca="1"/>
-        <v>【63】 In-winding measurement operation</v>
+        <v>【63】 巻き中測定動作</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -14658,75 +14658,75 @@
       <c r="AB55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';</v>
+			strRt	:= '巻き中測定動作';</v>
       </c>
       <c r="AE55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 In-winding measurement operation';</v>
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 巻き中測定動作';</v>
       </c>
       <c r="AG55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 In-winding measurement operation';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 In-winding measurement operation';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 In-winding measurement operation';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14734,12 +14734,12 @@
       <c r="AJ55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 In-winding measurement operation';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14748,12 +14748,12 @@
       <c r="AK55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 In-winding measurement operation';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14765,12 +14765,12 @@
       <c r="AL55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 In-winding measurement operation';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14782,12 +14782,12 @@
       <c r="AM55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 In-winding measurement operation';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14818,15 +14818,15 @@
       </c>
       <c r="K56" t="str">
         <f ca="1"/>
-        <v>Circumference measurement operation</v>
+        <v>周長測定動作</v>
       </c>
       <c r="L56" t="str">
         <f ca="1"/>
-        <v>Circumference measurement operation</v>
+        <v>周長測定動作</v>
       </c>
       <c r="N56" t="str">
         <f ca="1"/>
-        <v>【64】 Circumference measurement operation</v>
+        <v>【64】 周長測定動作</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -14855,75 +14855,75 @@
       <c r="AB56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';</v>
+			strRt	:= '周長測定動作';</v>
       </c>
       <c r="AE56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Circumference measurement operation';</v>
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 周長測定動作';</v>
       </c>
       <c r="AG56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14931,12 +14931,12 @@
       <c r="AJ56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14945,12 +14945,12 @@
       <c r="AK56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14962,12 +14962,12 @@
       <c r="AL56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14979,12 +14979,12 @@
       <c r="AM56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15015,15 +15015,15 @@
       </c>
       <c r="K57" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v>排出動作</v>
       </c>
       <c r="L57" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v>排出動作</v>
       </c>
       <c r="N57" t="str">
         <f ca="1"/>
-        <v>【65】 Discharge operation</v>
+        <v>【65】 排出動作</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -15052,75 +15052,75 @@
       <c r="AB57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';</v>
+			strRt	:= '排出動作';</v>
       </c>
       <c r="AE57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '排出動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 Discharge operation';</v>
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';</v>
       </c>
       <c r="AG57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15128,12 +15128,12 @@
       <c r="AJ57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15142,12 +15142,12 @@
       <c r="AK57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15159,12 +15159,12 @@
       <c r="AL57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15176,12 +15176,12 @@
       <c r="AM57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -29990,15 +29990,15 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30006,12 +30006,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30019,12 +30019,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30032,12 +30032,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30045,12 +30045,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30097,12 +30097,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30128,12 +30128,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30141,12 +30141,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30154,12 +30154,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding start operation
+	//巻取り開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding start operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Winding start operation';
+			strRt	:= '巻取り開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 巻取り開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30167,12 +30167,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30180,12 +30180,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30232,12 +30232,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Cutting Operation
+	//カット動作
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cutting Operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 Cutting Operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30263,12 +30263,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30276,12 +30276,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30289,12 +30289,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻取り動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 Winding operation';
+			strRt	:= '巻取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 巻取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30302,12 +30302,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding end operation
+	//巻取り終了動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding end operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 Winding end operation';
+			strRt	:= '巻取り終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 巻取り終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30320,12 +30320,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30333,12 +30333,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30346,12 +30346,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30359,12 +30359,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30372,12 +30372,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding completion operation
+	//巻き終了動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding completion operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Winding completion operation';
+			strRt	:= '巻き終了動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 巻き終了動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30385,12 +30385,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30398,12 +30398,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30416,12 +30416,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30429,12 +30429,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30442,12 +30442,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding welding operation
+	//巻き溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Winding welding operation';
+			strRt	:= '巻き溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 巻き溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30455,12 +30455,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil wax welding operation
+	//箔ロウ溶接動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil wax welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 Foil wax welding operation';
+			strRt	:= '箔ロウ溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 箔ロウ溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30473,12 +30473,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30486,12 +30486,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30499,12 +30499,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//In-winding measurement operation
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'In-winding measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 In-winding measurement operation';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30512,12 +30512,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30525,12 +30525,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
+	//排出動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 Discharge operation';
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E389CE54-2AA0-4BF7-8B1C-73B97E0E5004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF4365D-A74E-4F69-A298-121A89A80F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//原点復帰動作
@@ -29990,7 +29990,7 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//原点復帰動作

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF4365D-A74E-4F69-A298-121A89A80F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15322D5-6B7D-4563-AF61-03B37189C2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//原点復帰動作
@@ -29990,7 +29990,7 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//原点復帰動作

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15322D5-6B7D-4563-AF61-03B37189C2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9761B3AB-33DB-4EED-92AF-18215131552D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="108">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -488,38 +488,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>巻き終了動作</t>
-    <rPh sb="0" eb="1">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ドウサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>巻き押え動作</t>
     <rPh sb="0" eb="1">
       <t>マ</t>
     </rPh>
     <rPh sb="2" eb="3">
       <t>オサ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ドウサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>巻き溶接動作</t>
-    <rPh sb="0" eb="1">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ヨウセツ</t>
     </rPh>
     <rPh sb="4" eb="6">
       <t>ドウサ</t>
@@ -572,9 +546,6 @@
     <t>Winding operation</t>
   </si>
   <si>
-    <t>Winding completion operation</t>
-  </si>
-  <si>
     <t>Circumference measurement operation</t>
   </si>
   <si>
@@ -582,9 +553,6 @@
   </si>
   <si>
     <t>Winding clamping operation</t>
-  </si>
-  <si>
-    <t>Winding welding operation</t>
   </si>
   <si>
     <t>Foil wax welding operation</t>
@@ -659,6 +627,48 @@
   </si>
   <si>
     <t>Winding end operation</t>
+  </si>
+  <si>
+    <t>溶接動作</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウセツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箔ロウ巻き動作</t>
+    <rPh sb="0" eb="1">
+      <t>ハク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Foil brazing operation</t>
+  </si>
+  <si>
+    <t>Welding operation</t>
+  </si>
+  <si>
+    <t>供給動作</t>
+    <rPh sb="0" eb="2">
+      <t>キョウキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>supply operation</t>
   </si>
 </sst>
 </file>
@@ -1552,7 +1562,7 @@
         <v>71</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
@@ -1584,10 +1594,10 @@
         <v>72</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
@@ -1619,10 +1629,10 @@
         <v>72</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
@@ -1654,10 +1664,10 @@
         <v>72</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
@@ -1776,10 +1786,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
@@ -1878,7 +1888,7 @@
         <v>71</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -1910,10 +1920,10 @@
         <v>73</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1945,10 +1955,10 @@
         <v>73</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -1980,10 +1990,10 @@
         <v>73</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2102,10 +2112,10 @@
         <v>73</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
@@ -2204,7 +2214,7 @@
         <v>71</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -2236,10 +2246,10 @@
         <v>74</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -2271,10 +2281,10 @@
         <v>74</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -2341,10 +2351,10 @@
         <v>75</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -2379,7 +2389,7 @@
         <v>79</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -2414,7 +2424,7 @@
         <v>78</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -2446,10 +2456,10 @@
         <v>75</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="6"/>
@@ -2481,10 +2491,10 @@
         <v>75</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="6"/>
@@ -2516,10 +2526,10 @@
         <v>75</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="6"/>
@@ -2586,10 +2596,10 @@
         <v>76</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
@@ -2621,10 +2631,10 @@
         <v>76</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -2656,10 +2666,10 @@
         <v>76</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -2726,10 +2736,10 @@
         <v>77</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
@@ -2764,7 +2774,7 @@
         <v>80</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
@@ -2796,10 +2806,10 @@
         <v>77</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
@@ -2831,10 +2841,10 @@
         <v>77</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
@@ -4975,7 +4985,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -4994,15 +5004,15 @@
       </c>
       <c r="K3" t="str" cm="1">
         <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$107,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$107&amp;info_index!$E$2:$E$107,0),1)&amp;"","")</f>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L3" t="str" cm="1">
         <f t="array" aca="1" ref="L3:L202" ca="1">IF(LEN(_xlfn.ANCHORARRAY($J3)),IF(LEN(_xlfn.ANCHORARRAY(K3)),_xlfn.ANCHORARRAY(K3),"unknown"),"")</f>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N3" t="str" cm="1">
         <f t="array" aca="1" ref="N3:N202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(L3)),"【"&amp;G3:G202&amp;H3:H202&amp;"】 "&amp;_xlfn.ANCHORARRAY(L3),"")</f>
-        <v>【11】 原点復帰動作</v>
+        <v>【11】 Home return operation</v>
       </c>
       <c r="O3" t="str" cm="1">
         <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$107,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$107&amp;info_index!$E$2:$E$107,0),1)&amp;"","")</f>
@@ -5033,14 +5043,14 @@
         <f t="array" aca="1" ref="AB3:AB202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AA3)),_xlfn.ANCHORARRAY(AA3),"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;$B$7&amp;_xlfn.ANCHORARRAY(L3)&amp;CHAR(10)&amp;CHAR(9)&amp;IF(H3:H202=1,"IF ","ELSIF ")&amp;$B$26&amp;" = "&amp;H3:H202&amp;" THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC3" t="str" cm="1">
         <f t="array" aca="1" ref="AC3:AC202" ca="1">IF(LEN(AB3:AB202),AB3:AB202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"IF "&amp;$B$27&amp;" = '"&amp;$L$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -5048,54 +5058,54 @@
         <f t="array" aca="1" ref="AD3:AD202" ca="1">IF(LEN(AC3:AC202),AC3:AC202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(L3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE3" t="str" cm="1">
         <f t="array" aca="1" ref="AE3:AE202" ca="1">IF(LEN(AD3:AD202),AD3:AD202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;N$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF3" t="str" cm="1">
         <f t="array" aca="1" ref="AF3:AF202" ca="1">IF(LEN(AE3:AE202),AE3:AE202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(N3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Home return operation';</v>
       </c>
       <c r="AG3" t="str" cm="1">
         <f t="array" aca="1" ref="AG3:AG202" ca="1">IF(LEN(AF3:AF202),AF3:AF202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;P$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH3" t="str" cm="1">
         <f t="array" aca="1" ref="AH3:AH202" ca="1">IF(LEN(AG3:AG202),AG3:AG202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(P3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -5103,12 +5113,12 @@
         <f t="array" aca="1" ref="AI3:AI202" ca="1">IF(LEN(AH3:AH202),AH3:AH202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;R$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5117,12 +5127,12 @@
         <f t="array" aca="1" ref="AJ3:AJ202" ca="1">IF(LEN(AI3:AI202),AI3:AI202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(R3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5132,12 +5142,12 @@
         <f t="array" aca="1" ref="AK3:AK202" ca="1">IF(LEN(AJ3:AJ202),AJ3:AJ202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 3"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5150,12 +5160,12 @@
         <f t="array" aca="1" ref="AL3:AL202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AK3)),_xlfn.ANCHORARRAY(AK3),"")&amp;IF(I3:I202="●",CHAR(10)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 2"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5168,12 +5178,12 @@
         <f t="array" aca="1" ref="AM3:AM202" ca="1">_xlfn.ANCHORARRAY(AL3)</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5205,15 +5215,15 @@
       </c>
       <c r="K4" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="L4" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="N4" t="str">
         <f ca="1"/>
-        <v>【12】 供給準備動作</v>
+        <v>【12】 Supply preparation operation</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -5242,75 +5252,75 @@
       <c r="AB4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';</v>
       </c>
       <c r="AE4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Supply preparation operation';</v>
       </c>
       <c r="AG4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5318,12 +5328,12 @@
       <c r="AJ4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5332,12 +5342,12 @@
       <c r="AK4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5349,12 +5359,12 @@
       <c r="AL4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5366,12 +5376,12 @@
       <c r="AM4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5387,7 +5397,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -5409,15 +5419,15 @@
       </c>
       <c r="K5" t="str">
         <f ca="1"/>
-        <v>巻取り開始動作</v>
+        <v>Winding start operation</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>巻取り開始動作</v>
+        <v>Winding start operation</v>
       </c>
       <c r="N5" t="str">
         <f ca="1"/>
-        <v>【13】 巻取り開始動作</v>
+        <v>【13】 Winding start operation</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -5446,75 +5456,75 @@
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';</v>
+			strRt	:= 'Winding start operation';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
+			strRt	:= 'Winding start operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 巻取り開始動作';</v>
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Winding start operation';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5522,12 +5532,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5536,12 +5546,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5553,12 +5563,12 @@
       <c r="AL5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5570,12 +5580,12 @@
       <c r="AM5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5612,15 +5622,15 @@
       </c>
       <c r="K6" t="str">
         <f ca="1"/>
-        <v>巻取り動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="L6" t="str">
         <f ca="1"/>
-        <v>巻取り動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="N6" t="str">
         <f ca="1"/>
-        <v>【14】 巻取り動作</v>
+        <v>【14】 Winding operation</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -5649,75 +5659,75 @@
       <c r="AB6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';</v>
+			strRt	:= 'Winding operation';</v>
       </c>
       <c r="AE6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 巻取り動作';</v>
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 Winding operation';</v>
       </c>
       <c r="AG6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5725,12 +5735,12 @@
       <c r="AJ6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5739,12 +5749,12 @@
       <c r="AK6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5756,12 +5766,12 @@
       <c r="AL6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5773,12 +5783,12 @@
       <c r="AM6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5815,15 +5825,15 @@
       </c>
       <c r="K7" t="str">
         <f ca="1"/>
-        <v>巻取り終了動作</v>
+        <v>Winding end operation</v>
       </c>
       <c r="L7" t="str">
         <f ca="1"/>
-        <v>巻取り終了動作</v>
+        <v>Winding end operation</v>
       </c>
       <c r="N7" t="str">
         <f ca="1"/>
-        <v>【15】 巻取り終了動作</v>
+        <v>【15】 Winding end operation</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -5852,75 +5862,75 @@
       <c r="AB7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';</v>
+			strRt	:= 'Winding end operation';</v>
       </c>
       <c r="AE7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
+			strRt	:= 'Winding end operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 巻取り終了動作';</v>
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 Winding end operation';</v>
       </c>
       <c r="AG7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5928,12 +5938,12 @@
       <c r="AJ7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5942,12 +5952,12 @@
       <c r="AK7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5959,12 +5969,12 @@
       <c r="AL7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5976,12 +5986,12 @@
       <c r="AM7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6615,15 +6625,15 @@
       </c>
       <c r="K11" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cutting Operation</v>
       </c>
       <c r="L11" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cutting Operation</v>
       </c>
       <c r="N11" t="str">
         <f ca="1"/>
-        <v>【19】 カット動作</v>
+        <v>【19】 Cutting Operation</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -6652,75 +6662,75 @@
       <c r="AB11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN</v>
       </c>
       <c r="AC11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';</v>
+			strRt	:= 'Cutting Operation';</v>
       </c>
       <c r="AE11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cutting Operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 カット動作';</v>
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 Cutting Operation';</v>
       </c>
       <c r="AG11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6728,12 +6738,12 @@
       <c r="AJ11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6742,12 +6752,12 @@
       <c r="AK11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6759,12 +6769,12 @@
       <c r="AL11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6776,12 +6786,12 @@
       <c r="AM11" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7000,15 +7010,15 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7016,12 +7026,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7029,12 +7039,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7042,12 +7052,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7055,12 +7065,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7107,12 +7117,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7138,12 +7148,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7151,12 +7161,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7164,12 +7174,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7177,12 +7187,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7190,12 +7200,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7242,12 +7252,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7273,12 +7283,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7286,12 +7296,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7299,12 +7309,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 巻取り動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7312,12 +7322,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7330,12 +7340,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7343,12 +7353,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7356,12 +7366,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7369,12 +7379,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7382,12 +7392,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 巻き終了動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7395,12 +7405,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7408,12 +7418,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7426,12 +7436,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7439,12 +7449,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7452,12 +7462,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 巻き溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7465,12 +7475,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 箔ロウ溶接動作';
+			strRt	:= 'Foil wax welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 Foil wax welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7483,12 +7493,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7496,12 +7506,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7509,12 +7519,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= 'In-winding measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 In-winding measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7522,12 +7532,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7535,12 +7545,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7576,15 +7586,15 @@
       </c>
       <c r="K13" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L13" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N13" t="str">
         <f ca="1"/>
-        <v>【21】 原点復帰動作</v>
+        <v>【21】 Home return operation</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -7616,7 +7626,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC13" t="str">
@@ -7624,7 +7634,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -7633,20 +7643,20 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF13" t="str">
@@ -7654,24 +7664,24 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Home return operation';</v>
       </c>
       <c r="AG13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH13" t="str">
@@ -7679,12 +7689,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -7693,12 +7703,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7708,12 +7718,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7724,12 +7734,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7743,12 +7753,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7762,12 +7772,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7809,15 +7819,15 @@
       </c>
       <c r="K14" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="L14" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="N14" t="str">
         <f ca="1"/>
-        <v>【22】 供給準備動作</v>
+        <v>【22】 Supply preparation operation</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -7846,75 +7856,75 @@
       <c r="AB14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';</v>
       </c>
       <c r="AE14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Supply preparation operation';</v>
       </c>
       <c r="AG14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7922,12 +7932,12 @@
       <c r="AJ14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7936,12 +7946,12 @@
       <c r="AK14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7953,12 +7963,12 @@
       <c r="AL14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7970,12 +7980,12 @@
       <c r="AM14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8006,15 +8016,15 @@
       </c>
       <c r="K15" t="str">
         <f ca="1"/>
-        <v>巻取り開始動作</v>
+        <v>Winding start operation</v>
       </c>
       <c r="L15" t="str">
         <f ca="1"/>
-        <v>巻取り開始動作</v>
+        <v>Winding start operation</v>
       </c>
       <c r="N15" t="str">
         <f ca="1"/>
-        <v>【23】 巻取り開始動作</v>
+        <v>【23】 Winding start operation</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -8043,75 +8053,75 @@
       <c r="AB15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';</v>
+			strRt	:= 'Winding start operation';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
+			strRt	:= 'Winding start operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 巻取り開始動作';</v>
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Winding start operation';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8119,12 +8129,12 @@
       <c r="AJ15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8133,12 +8143,12 @@
       <c r="AK15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8150,12 +8160,12 @@
       <c r="AL15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8167,12 +8177,12 @@
       <c r="AM15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8203,15 +8213,15 @@
       </c>
       <c r="K16" t="str">
         <f ca="1"/>
-        <v>巻取り動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="L16" t="str">
         <f ca="1"/>
-        <v>巻取り動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="N16" t="str">
         <f ca="1"/>
-        <v>【24】 巻取り動作</v>
+        <v>【24】 Winding operation</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -8240,75 +8250,75 @@
       <c r="AB16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';</v>
+			strRt	:= 'Winding operation';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 巻取り動作';</v>
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Winding operation';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8316,12 +8326,12 @@
       <c r="AJ16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8330,12 +8340,12 @@
       <c r="AK16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8347,12 +8357,12 @@
       <c r="AL16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8364,12 +8374,12 @@
       <c r="AM16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8400,15 +8410,15 @@
       </c>
       <c r="K17" t="str">
         <f ca="1"/>
-        <v>巻取り終了動作</v>
+        <v>Winding end operation</v>
       </c>
       <c r="L17" t="str">
         <f ca="1"/>
-        <v>巻取り終了動作</v>
+        <v>Winding end operation</v>
       </c>
       <c r="N17" t="str">
         <f ca="1"/>
-        <v>【25】 巻取り終了動作</v>
+        <v>【25】 Winding end operation</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -8437,75 +8447,75 @@
       <c r="AB17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';</v>
+			strRt	:= 'Winding end operation';</v>
       </c>
       <c r="AE17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
+			strRt	:= 'Winding end operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 巻取り終了動作';</v>
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 Winding end operation';</v>
       </c>
       <c r="AG17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8513,12 +8523,12 @@
       <c r="AJ17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8527,12 +8537,12 @@
       <c r="AK17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8544,12 +8554,12 @@
       <c r="AL17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8561,12 +8571,12 @@
       <c r="AM17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9188,15 +9198,15 @@
       </c>
       <c r="K21" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cutting Operation</v>
       </c>
       <c r="L21" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cutting Operation</v>
       </c>
       <c r="N21" t="str">
         <f ca="1"/>
-        <v>【29】 カット動作</v>
+        <v>【29】 Cutting Operation</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -9225,75 +9235,75 @@
       <c r="AB21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN</v>
       </c>
       <c r="AC21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';</v>
+			strRt	:= 'Cutting Operation';</v>
       </c>
       <c r="AE21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cutting Operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 カット動作';</v>
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 Cutting Operation';</v>
       </c>
       <c r="AG21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9301,12 +9311,12 @@
       <c r="AJ21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9315,12 +9325,12 @@
       <c r="AK21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9332,12 +9342,12 @@
       <c r="AL21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9349,12 +9359,12 @@
       <c r="AM21" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9572,7 +9582,7 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <f>F13+1</f>
@@ -9594,15 +9604,15 @@
       </c>
       <c r="K23" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L23" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N23" t="str">
         <f ca="1"/>
-        <v>【31】 原点復帰動作</v>
+        <v>【31】 Home return operation</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -9634,7 +9644,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC23" t="str">
@@ -9642,7 +9652,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -9651,20 +9661,20 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF23" t="str">
@@ -9672,24 +9682,24 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';</v>
       </c>
       <c r="AG23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH23" t="str">
@@ -9697,12 +9707,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -9711,12 +9721,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9726,12 +9736,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9742,12 +9752,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9761,12 +9771,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9780,12 +9790,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9816,15 +9826,15 @@
       </c>
       <c r="K24" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="L24" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="N24" t="str">
         <f ca="1"/>
-        <v>【32】 供給準備動作</v>
+        <v>【32】 Supply preparation operation</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -9853,75 +9863,75 @@
       <c r="AB24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';</v>
       </c>
       <c r="AE24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';</v>
       </c>
       <c r="AG24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9929,12 +9939,12 @@
       <c r="AJ24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9943,12 +9953,12 @@
       <c r="AK24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9960,12 +9970,12 @@
       <c r="AL24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9977,12 +9987,12 @@
       <c r="AM24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10019,15 +10029,15 @@
       </c>
       <c r="K25" t="str">
         <f ca="1"/>
-        <v>巻取り動作</v>
+        <v>supply operation</v>
       </c>
       <c r="L25" t="str">
         <f ca="1"/>
-        <v>巻取り動作</v>
+        <v>supply operation</v>
       </c>
       <c r="N25" t="str">
         <f ca="1"/>
-        <v>【33】 巻取り動作</v>
+        <v>【33】 supply operation</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -10056,75 +10066,75 @@
       <c r="AB25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';</v>
+			strRt	:= 'supply operation';</v>
       </c>
       <c r="AE25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 巻取り動作';</v>
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';</v>
       </c>
       <c r="AG25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 巻取り動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 巻取り動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 巻取り動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10132,12 +10142,12 @@
       <c r="AJ25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 巻取り動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10146,12 +10156,12 @@
       <c r="AK25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 巻取り動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10163,12 +10173,12 @@
       <c r="AL25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 巻取り動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10180,12 +10190,12 @@
       <c r="AM25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 巻取り動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10222,15 +10232,15 @@
       </c>
       <c r="K26" t="str">
         <f ca="1"/>
-        <v>巻取り終了動作</v>
+        <v>Winding end operation</v>
       </c>
       <c r="L26" t="str">
         <f ca="1"/>
-        <v>巻取り終了動作</v>
+        <v>Winding end operation</v>
       </c>
       <c r="N26" t="str">
         <f ca="1"/>
-        <v>【34】 巻取り終了動作</v>
+        <v>【34】 Winding end operation</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -10259,75 +10269,75 @@
       <c r="AB26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';</v>
+			strRt	:= 'Winding end operation';</v>
       </c>
       <c r="AE26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
+			strRt	:= 'Winding end operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 巻取り終了動作';</v>
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 Winding end operation';</v>
       </c>
       <c r="AG26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10335,12 +10345,12 @@
       <c r="AJ26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10349,12 +10359,12 @@
       <c r="AK26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10366,12 +10376,12 @@
       <c r="AL26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10383,12 +10393,12 @@
       <c r="AM26" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11055,15 +11065,15 @@
       </c>
       <c r="K33" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L33" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N33" t="str">
         <f ca="1"/>
-        <v>【41】 原点復帰動作</v>
+        <v>【41】 Home return operation</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -11095,7 +11105,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC33" t="str">
@@ -11103,7 +11113,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -11112,20 +11122,20 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF33" t="str">
@@ -11133,24 +11143,24 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';</v>
       </c>
       <c r="AG33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH33" t="str">
@@ -11158,12 +11168,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -11172,12 +11182,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11187,12 +11197,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11203,12 +11213,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11222,12 +11232,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11241,12 +11251,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11277,15 +11287,15 @@
       </c>
       <c r="K34" t="str">
         <f ca="1"/>
-        <v>周長測定子プリセット</v>
+        <v>Circumference gauge preset</v>
       </c>
       <c r="L34" t="str">
         <f ca="1"/>
-        <v>周長測定子プリセット</v>
+        <v>Circumference gauge preset</v>
       </c>
       <c r="N34" t="str">
         <f ca="1"/>
-        <v>【42】 周長測定子プリセット</v>
+        <v>【42】 Circumference gauge preset</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -11314,75 +11324,75 @@
       <c r="AB34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';</v>
+			strRt	:= 'Circumference gauge preset';</v>
       </c>
       <c r="AE34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';</v>
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';</v>
       </c>
       <c r="AG34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11390,12 +11400,12 @@
       <c r="AJ34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11404,12 +11414,12 @@
       <c r="AK34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11421,12 +11431,12 @@
       <c r="AL34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11438,12 +11448,12 @@
       <c r="AM34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11474,15 +11484,15 @@
       </c>
       <c r="K35" t="str">
         <f ca="1"/>
-        <v>巻き準備動作</v>
+        <v>Winding preparation operation</v>
       </c>
       <c r="L35" t="str">
         <f ca="1"/>
-        <v>巻き準備動作</v>
+        <v>Winding preparation operation</v>
       </c>
       <c r="N35" t="str">
         <f ca="1"/>
-        <v>【43】 巻き準備動作</v>
+        <v>【43】 Winding preparation operation</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -11511,75 +11521,75 @@
       <c r="AB35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';</v>
+			strRt	:= 'Winding preparation operation';</v>
       </c>
       <c r="AE35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';</v>
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';</v>
       </c>
       <c r="AG35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11587,12 +11597,12 @@
       <c r="AJ35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11601,12 +11611,12 @@
       <c r="AK35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11618,12 +11628,12 @@
       <c r="AL35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11635,12 +11645,12 @@
       <c r="AM35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11671,15 +11681,15 @@
       </c>
       <c r="K36" t="str">
         <f ca="1"/>
-        <v>巻き動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="L36" t="str">
         <f ca="1"/>
-        <v>巻き動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="N36" t="str">
         <f ca="1"/>
-        <v>【44】 巻き動作</v>
+        <v>【44】 Winding operation</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -11708,75 +11718,75 @@
       <c r="AB36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';</v>
+			strRt	:= 'Winding operation';</v>
       </c>
       <c r="AE36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';</v>
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';</v>
       </c>
       <c r="AG36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11784,12 +11794,12 @@
       <c r="AJ36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11798,12 +11808,12 @@
       <c r="AK36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11815,12 +11825,12 @@
       <c r="AL36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11832,12 +11842,12 @@
       <c r="AM36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11868,15 +11878,15 @@
       </c>
       <c r="K37" t="str">
         <f ca="1"/>
-        <v>巻き終了動作</v>
+        <v>Foil brazing operation</v>
       </c>
       <c r="L37" t="str">
         <f ca="1"/>
-        <v>巻き終了動作</v>
+        <v>Foil brazing operation</v>
       </c>
       <c r="N37" t="str">
         <f ca="1"/>
-        <v>【45】 巻き終了動作</v>
+        <v>【45】 Foil brazing operation</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -11905,75 +11915,75 @@
       <c r="AB37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';</v>
+			strRt	:= 'Foil brazing operation';</v>
       </c>
       <c r="AE37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 巻き終了動作';</v>
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';</v>
       </c>
       <c r="AG37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 巻き終了動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 巻き終了動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 巻き終了動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11981,12 +11991,12 @@
       <c r="AJ37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 巻き終了動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11995,12 +12005,12 @@
       <c r="AK37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 巻き終了動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12012,12 +12022,12 @@
       <c r="AL37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 巻き終了動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12029,12 +12039,12 @@
       <c r="AM37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 巻き終了動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12065,15 +12075,15 @@
       </c>
       <c r="K38" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>Circumference measurement operation</v>
       </c>
       <c r="L38" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>Circumference measurement operation</v>
       </c>
       <c r="N38" t="str">
         <f ca="1"/>
-        <v>【46】 周長測定動作</v>
+        <v>【46】 Circumference measurement operation</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -12102,75 +12112,75 @@
       <c r="AB38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';</v>
+			strRt	:= 'Circumference measurement operation';</v>
       </c>
       <c r="AE38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';</v>
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';</v>
       </c>
       <c r="AG38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12178,12 +12188,12 @@
       <c r="AJ38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12192,12 +12202,12 @@
       <c r="AK38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12209,12 +12219,12 @@
       <c r="AL38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12226,12 +12236,12 @@
       <c r="AM38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12262,15 +12272,15 @@
       </c>
       <c r="K39" t="str">
         <f ca="1"/>
-        <v>排出動作</v>
+        <v>Discharge operation</v>
       </c>
       <c r="L39" t="str">
         <f ca="1"/>
-        <v>排出動作</v>
+        <v>Discharge operation</v>
       </c>
       <c r="N39" t="str">
         <f ca="1"/>
-        <v>【47】 排出動作</v>
+        <v>【47】 Discharge operation</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -12299,75 +12309,75 @@
       <c r="AB39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';</v>
+			strRt	:= 'Discharge operation';</v>
       </c>
       <c r="AE39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 排出動作';</v>
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 Discharge operation';</v>
       </c>
       <c r="AG39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12375,12 +12385,12 @@
       <c r="AJ39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12389,12 +12399,12 @@
       <c r="AK39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12406,12 +12416,12 @@
       <c r="AL39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12423,12 +12433,12 @@
       <c r="AM39" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12771,15 +12781,15 @@
       </c>
       <c r="K43" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L43" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N43" t="str">
         <f ca="1"/>
-        <v>【51】 原点復帰動作</v>
+        <v>【51】 Home return operation</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -12811,7 +12821,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC43" t="str">
@@ -12819,7 +12829,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -12828,20 +12838,20 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF43" t="str">
@@ -12849,24 +12859,24 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';</v>
       </c>
       <c r="AG43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH43" t="str">
@@ -12874,12 +12884,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -12888,12 +12898,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12903,12 +12913,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12919,12 +12929,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12938,12 +12948,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12957,12 +12967,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12993,15 +13003,15 @@
       </c>
       <c r="K44" t="str">
         <f ca="1"/>
-        <v>巻き押え動作</v>
+        <v>Winding clamping operation</v>
       </c>
       <c r="L44" t="str">
         <f ca="1"/>
-        <v>巻き押え動作</v>
+        <v>Winding clamping operation</v>
       </c>
       <c r="N44" t="str">
         <f ca="1"/>
-        <v>【52】 巻き押え動作</v>
+        <v>【52】 Winding clamping operation</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -13030,75 +13040,75 @@
       <c r="AB44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';</v>
+			strRt	:= 'Winding clamping operation';</v>
       </c>
       <c r="AE44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';</v>
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';</v>
       </c>
       <c r="AG44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13106,12 +13116,12 @@
       <c r="AJ44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13120,12 +13130,12 @@
       <c r="AK44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13137,12 +13147,12 @@
       <c r="AL44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13154,12 +13164,12 @@
       <c r="AM44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13190,15 +13200,15 @@
       </c>
       <c r="K45" t="str">
         <f ca="1"/>
-        <v>巻き溶接動作</v>
+        <v>Welding operation</v>
       </c>
       <c r="L45" t="str">
         <f ca="1"/>
-        <v>巻き溶接動作</v>
+        <v>Welding operation</v>
       </c>
       <c r="N45" t="str">
         <f ca="1"/>
-        <v>【53】 巻き溶接動作</v>
+        <v>【53】 Welding operation</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -13227,75 +13237,75 @@
       <c r="AB45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';</v>
+			strRt	:= 'Welding operation';</v>
       </c>
       <c r="AE45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 巻き溶接動作';</v>
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';</v>
       </c>
       <c r="AG45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 巻き溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 巻き溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 巻き溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13303,12 +13313,12 @@
       <c r="AJ45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 巻き溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13317,12 +13327,12 @@
       <c r="AK45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 巻き溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13334,12 +13344,12 @@
       <c r="AL45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 巻き溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13351,12 +13361,12 @@
       <c r="AM45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 巻き溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13387,15 +13397,15 @@
       </c>
       <c r="K46" t="str">
         <f ca="1"/>
-        <v>箔ロウ溶接動作</v>
+        <v>Foil wax welding operation</v>
       </c>
       <c r="L46" t="str">
         <f ca="1"/>
-        <v>箔ロウ溶接動作</v>
+        <v>Foil wax welding operation</v>
       </c>
       <c r="N46" t="str">
         <f ca="1"/>
-        <v>【54】 箔ロウ溶接動作</v>
+        <v>【54】 Foil wax welding operation</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -13424,75 +13434,75 @@
       <c r="AB46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';</v>
+			strRt	:= 'Foil wax welding operation';</v>
       </c>
       <c r="AE46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
+			strRt	:= 'Foil wax welding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 箔ロウ溶接動作';</v>
+			strRt	:= 'Foil wax welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 Foil wax welding operation';</v>
       </c>
       <c r="AG46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 箔ロウ溶接動作';
+			strRt	:= 'Foil wax welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 Foil wax welding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 箔ロウ溶接動作';
+			strRt	:= 'Foil wax welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 Foil wax welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 箔ロウ溶接動作';
+			strRt	:= 'Foil wax welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 Foil wax welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13500,12 +13510,12 @@
       <c r="AJ46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 箔ロウ溶接動作';
+			strRt	:= 'Foil wax welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 Foil wax welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13514,12 +13524,12 @@
       <c r="AK46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 箔ロウ溶接動作';
+			strRt	:= 'Foil wax welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 Foil wax welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13531,12 +13541,12 @@
       <c r="AL46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 箔ロウ溶接動作';
+			strRt	:= 'Foil wax welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 Foil wax welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13548,12 +13558,12 @@
       <c r="AM46" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 箔ロウ溶接動作';
+			strRt	:= 'Foil wax welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 Foil wax welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14202,15 +14212,15 @@
       </c>
       <c r="K53" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L53" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N53" t="str">
         <f ca="1"/>
-        <v>【61】 原点復帰動作</v>
+        <v>【61】 Home return operation</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -14242,7 +14252,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC53" t="str">
@@ -14250,7 +14260,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -14259,20 +14269,20 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF53" t="str">
@@ -14280,24 +14290,24 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Home return operation';</v>
       </c>
       <c r="AG53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH53" t="str">
@@ -14305,12 +14315,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -14319,12 +14329,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14334,12 +14344,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14350,12 +14360,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14369,12 +14379,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14388,12 +14398,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14424,15 +14434,15 @@
       </c>
       <c r="K54" t="str">
         <f ca="1"/>
-        <v>周長測定子プリセット</v>
+        <v>Circumference gauge preset</v>
       </c>
       <c r="L54" t="str">
         <f ca="1"/>
-        <v>周長測定子プリセット</v>
+        <v>Circumference gauge preset</v>
       </c>
       <c r="N54" t="str">
         <f ca="1"/>
-        <v>【62】 周長測定子プリセット</v>
+        <v>【62】 Circumference gauge preset</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -14461,75 +14471,75 @@
       <c r="AB54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';</v>
+			strRt	:= 'Circumference gauge preset';</v>
       </c>
       <c r="AE54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 周長測定子プリセット';</v>
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Circumference gauge preset';</v>
       </c>
       <c r="AG54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14537,12 +14547,12 @@
       <c r="AJ54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14551,12 +14561,12 @@
       <c r="AK54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14568,12 +14578,12 @@
       <c r="AL54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14585,12 +14595,12 @@
       <c r="AM54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14621,15 +14631,15 @@
       </c>
       <c r="K55" t="str">
         <f ca="1"/>
-        <v>巻き中測定動作</v>
+        <v>In-winding measurement operation</v>
       </c>
       <c r="L55" t="str">
         <f ca="1"/>
-        <v>巻き中測定動作</v>
+        <v>In-winding measurement operation</v>
       </c>
       <c r="N55" t="str">
         <f ca="1"/>
-        <v>【63】 巻き中測定動作</v>
+        <v>【63】 In-winding measurement operation</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -14658,75 +14668,75 @@
       <c r="AB55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';</v>
+			strRt	:= 'In-winding measurement operation';</v>
       </c>
       <c r="AE55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'In-winding measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';</v>
+			strRt	:= 'In-winding measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 In-winding measurement operation';</v>
       </c>
       <c r="AG55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= 'In-winding measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 In-winding measurement operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= 'In-winding measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 In-winding measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= 'In-winding measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 In-winding measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14734,12 +14744,12 @@
       <c r="AJ55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= 'In-winding measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 In-winding measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14748,12 +14758,12 @@
       <c r="AK55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= 'In-winding measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 In-winding measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14765,12 +14775,12 @@
       <c r="AL55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= 'In-winding measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 In-winding measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14782,12 +14792,12 @@
       <c r="AM55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= 'In-winding measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 In-winding measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14818,15 +14828,15 @@
       </c>
       <c r="K56" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>Circumference measurement operation</v>
       </c>
       <c r="L56" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>Circumference measurement operation</v>
       </c>
       <c r="N56" t="str">
         <f ca="1"/>
-        <v>【64】 周長測定動作</v>
+        <v>【64】 Circumference measurement operation</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -14855,75 +14865,75 @@
       <c r="AB56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';</v>
+			strRt	:= 'Circumference measurement operation';</v>
       </c>
       <c r="AE56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 周長測定動作';</v>
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 Circumference measurement operation';</v>
       </c>
       <c r="AG56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14931,12 +14941,12 @@
       <c r="AJ56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14945,12 +14955,12 @@
       <c r="AK56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14962,12 +14972,12 @@
       <c r="AL56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14979,12 +14989,12 @@
       <c r="AM56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15015,15 +15025,15 @@
       </c>
       <c r="K57" t="str">
         <f ca="1"/>
-        <v>排出動作</v>
+        <v>Discharge operation</v>
       </c>
       <c r="L57" t="str">
         <f ca="1"/>
-        <v>排出動作</v>
+        <v>Discharge operation</v>
       </c>
       <c r="N57" t="str">
         <f ca="1"/>
-        <v>【65】 排出動作</v>
+        <v>【65】 Discharge operation</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -15052,75 +15062,75 @@
       <c r="AB57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';</v>
+			strRt	:= 'Discharge operation';</v>
       </c>
       <c r="AE57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 排出動作';</v>
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 Discharge operation';</v>
       </c>
       <c r="AG57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15128,12 +15138,12 @@
       <c r="AJ57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15142,12 +15152,12 @@
       <c r="AK57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15159,12 +15169,12 @@
       <c r="AL57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15176,12 +15186,12 @@
       <c r="AM57" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -29990,15 +30000,15 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30006,12 +30016,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30019,12 +30029,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30032,12 +30042,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【14】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30045,12 +30055,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【15】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30097,12 +30107,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【19】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【19】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30128,12 +30138,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30141,12 +30151,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30154,12 +30164,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り開始動作
+	//Winding start operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 巻取り開始動作';
+			strRt	:= 'Winding start operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Winding start operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30167,12 +30177,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 巻取り動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30180,12 +30190,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30232,12 +30242,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cutting Operation
 	ELSIF uiInfoIdx = 9 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【29】 カット動作';
+			strRt	:= 'Cutting Operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【29】 Cutting Operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30263,12 +30273,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30276,12 +30286,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30289,12 +30299,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 巻取り動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30302,12 +30312,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻取り終了動作
+	//Winding end operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻取り終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【34】 巻取り終了動作';
+			strRt	:= 'Winding end operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【34】 Winding end operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30320,12 +30330,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30333,12 +30343,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30346,12 +30356,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30359,12 +30369,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30372,12 +30382,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き終了動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き終了動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 巻き終了動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30385,12 +30395,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30398,12 +30408,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【47】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【47】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30416,12 +30426,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30429,12 +30439,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30442,12 +30452,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 巻き溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30455,12 +30465,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ溶接動作
+	//Foil wax welding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【54】 箔ロウ溶接動作';
+			strRt	:= 'Foil wax welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【54】 Foil wax welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30473,12 +30483,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30486,12 +30496,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30499,12 +30509,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き中測定動作
+	//In-winding measurement operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= 'In-winding measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 In-winding measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30512,12 +30522,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -30525,12 +30535,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【65】 排出動作';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【65】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9761B3AB-33DB-4EED-92AF-18215131552D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47144346-D403-4660-B160-BA06B567716D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//Home return operation
@@ -30000,7 +30000,7 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//Home return operation
@@ -30565,5 +30565,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BB96DE-F511-4C52-B393-D36C6E8B4305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E627EF4-7A78-4191-A463-4D59576B8779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="111">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -529,9 +529,6 @@
     <t>Winding clamping operation</t>
   </si>
   <si>
-    <t>In-winding measurement operation</t>
-  </si>
-  <si>
     <t>周長測定子プリセット</t>
     <rPh sb="0" eb="2">
       <t>シュウチョウ</t>
@@ -618,6 +615,35 @@
   </si>
   <si>
     <t>Cut operation</t>
+  </si>
+  <si>
+    <t>計測準備</t>
+    <rPh sb="0" eb="2">
+      <t>ケイソク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジュンビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>排出動作</t>
+    <rPh sb="0" eb="2">
+      <t>ハイシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Measurement preparation</t>
+  </si>
+  <si>
+    <t>Measurement operation during winding</t>
+  </si>
+  <si>
+    <t>Discharge operation</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1049,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$95">
+    <xdr:sp macro="" textlink="$A$96">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -1392,7 +1418,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -1473,10 +1499,10 @@
         <v>72</v>
       </c>
       <c r="H2" s="31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I2" s="28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J2" s="28"/>
       <c r="K2" s="28"/>
@@ -1496,7 +1522,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="str">
-        <f t="shared" ref="D3:D61" si="0">B3&amp;C3</f>
+        <f t="shared" ref="D3:D62" si="0">B3&amp;C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="4">
@@ -1508,10 +1534,10 @@
         <v>72</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
@@ -1543,10 +1569,10 @@
         <v>72</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
@@ -1578,10 +1604,10 @@
         <v>72</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
@@ -1613,10 +1639,10 @@
         <v>72</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
@@ -1648,10 +1674,10 @@
         <v>73</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -1683,10 +1709,10 @@
         <v>73</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1718,10 +1744,10 @@
         <v>73</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1753,10 +1779,10 @@
         <v>73</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1788,10 +1814,10 @@
         <v>73</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1842,7 +1868,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4">
-        <f t="shared" ref="C13:C91" si="7">C12</f>
+        <f t="shared" ref="C13:C92" si="7">C12</f>
         <v>3</v>
       </c>
       <c r="D13" s="4" t="str">
@@ -1850,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="4">
-        <f t="shared" ref="E13:E71" si="8">E12+1</f>
+        <f t="shared" ref="E13:E72" si="8">E12+1</f>
         <v>2</v>
       </c>
       <c r="F13" s="5"/>
@@ -1893,10 +1919,10 @@
         <v>74</v>
       </c>
       <c r="H14" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1963,10 +1989,10 @@
         <v>75</v>
       </c>
       <c r="H16" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>90</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2068,10 +2094,10 @@
         <v>75</v>
       </c>
       <c r="H19" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="6"/>
@@ -2208,10 +2234,10 @@
         <v>76</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -2246,7 +2272,7 @@
         <v>69</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -2278,10 +2304,10 @@
         <v>77</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
@@ -2313,10 +2339,10 @@
         <v>77</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -2332,36 +2358,42 @@
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4">
-        <f>C24+1</f>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="D27" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f t="shared" ref="D27" si="16">B27&amp;C27</f>
+        <v>6</v>
       </c>
       <c r="E27" s="4">
-        <f>E24</f>
-        <v>1</v>
-      </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
       <c r="R27" s="7"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4">
-        <f t="shared" ref="C28" si="16">C27</f>
+        <f>C24+1</f>
         <v>7</v>
       </c>
       <c r="D28" s="4" t="str">
@@ -2369,8 +2401,8 @@
         <v>7</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" ref="E28" si="17">E27+1</f>
-        <v>2</v>
+        <f>E24</f>
+        <v>1</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
@@ -2390,7 +2422,7 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C29" si="17">C28</f>
         <v>7</v>
       </c>
       <c r="D29" s="4" t="str">
@@ -2398,21 +2430,21 @@
         <v>7</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
+        <f t="shared" ref="E29" si="18">E28+1</f>
+        <v>2</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
       <c r="R29" s="7"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -2428,7 +2460,7 @@
       </c>
       <c r="E30" s="4">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -2457,7 +2489,7 @@
       </c>
       <c r="E31" s="4">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -2474,39 +2506,39 @@
       <c r="R31" s="7"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="26"/>
+      <c r="A32" s="4"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="26">
-        <f t="shared" ref="C32" si="18">C27+1</f>
-        <v>8</v>
-      </c>
-      <c r="D32" s="26" t="str">
+      <c r="C32" s="4">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="D32" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" ref="E32" si="19">E27</f>
-        <v>1</v>
-      </c>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="23"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
       <c r="R32" s="7"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="26"/>
       <c r="B33" s="4"/>
       <c r="C33" s="26">
-        <f t="shared" ref="C33" si="20">C32</f>
+        <f t="shared" ref="C33" si="19">C28+1</f>
         <v>8</v>
       </c>
       <c r="D33" s="26" t="str">
@@ -2514,8 +2546,8 @@
         <v>8</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" ref="E33" si="21">E32+1</f>
-        <v>2</v>
+        <f t="shared" ref="E33" si="20">E28</f>
+        <v>1</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
@@ -2535,7 +2567,7 @@
       <c r="A34" s="26"/>
       <c r="B34" s="4"/>
       <c r="C34" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C34" si="21">C33</f>
         <v>8</v>
       </c>
       <c r="D34" s="26" t="str">
@@ -2543,8 +2575,8 @@
         <v>8</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E34" si="22">E33+1</f>
+        <v>2</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
@@ -2561,32 +2593,32 @@
       <c r="R34" s="7"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="4"/>
+      <c r="A35" s="26"/>
       <c r="B35" s="4"/>
-      <c r="C35" s="4">
+      <c r="C35" s="26">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="D35" s="4" t="str">
+      <c r="D35" s="26" t="str">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="E35" s="4">
         <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
       <c r="R35" s="7"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -2602,7 +2634,7 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -2622,16 +2654,16 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4">
-        <f t="shared" ref="C37" si="22">C32+1</f>
-        <v>9</v>
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="D37" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" ref="E37" si="23">E32</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -2651,7 +2683,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4">
-        <f t="shared" ref="C38" si="24">C37</f>
+        <f t="shared" ref="C38" si="23">C33+1</f>
         <v>9</v>
       </c>
       <c r="D38" s="4" t="str">
@@ -2659,8 +2691,8 @@
         <v>9</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" ref="E38" si="25">E37+1</f>
-        <v>2</v>
+        <f t="shared" ref="E38" si="24">E33</f>
+        <v>1</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -2680,7 +2712,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C39" si="25">C38</f>
         <v>9</v>
       </c>
       <c r="D39" s="4" t="str">
@@ -2688,8 +2720,8 @@
         <v>9</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E39" si="26">E38+1</f>
+        <v>2</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -2718,14 +2750,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
-      <c r="K40" s="13"/>
+      <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
@@ -2747,14 +2779,14 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
+      <c r="K41" s="13"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
@@ -2767,16 +2799,16 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
-        <f t="shared" ref="C42" si="26">C37+1</f>
-        <v>10</v>
+        <f t="shared" si="7"/>
+        <v>9</v>
       </c>
       <c r="D42" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" ref="E42" si="27">E37</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -2796,7 +2828,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
-        <f t="shared" ref="C43" si="28">C42</f>
+        <f t="shared" ref="C43" si="27">C38+1</f>
         <v>10</v>
       </c>
       <c r="D43" s="4" t="str">
@@ -2804,8 +2836,8 @@
         <v>10</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" ref="E43" si="29">E42+1</f>
-        <v>2</v>
+        <f t="shared" ref="E43" si="28">E38</f>
+        <v>1</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -2825,7 +2857,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C44" si="29">C43</f>
         <v>10</v>
       </c>
       <c r="D44" s="4" t="str">
@@ -2833,8 +2865,8 @@
         <v>10</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E44" si="30">E43+1</f>
+        <v>2</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -2863,7 +2895,7 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -2892,7 +2924,7 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -2912,16 +2944,16 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
-        <f t="shared" ref="C47" si="30">C42+1</f>
-        <v>11</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="D47" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" ref="E47" si="31">E42</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -2941,7 +2973,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
-        <f t="shared" ref="C48" si="32">C47</f>
+        <f t="shared" ref="C48" si="31">C43+1</f>
         <v>11</v>
       </c>
       <c r="D48" s="4" t="str">
@@ -2949,8 +2981,8 @@
         <v>11</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" ref="E48" si="33">E47+1</f>
-        <v>2</v>
+        <f t="shared" ref="E48" si="32">E43</f>
+        <v>1</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -2970,7 +3002,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C49" si="33">C48</f>
         <v>11</v>
       </c>
       <c r="D49" s="4" t="str">
@@ -2978,8 +3010,8 @@
         <v>11</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E49" si="34">E48+1</f>
+        <v>2</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -3008,7 +3040,7 @@
       </c>
       <c r="E50" s="4">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -3037,7 +3069,7 @@
       </c>
       <c r="E51" s="4">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -3057,16 +3089,16 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
-        <f t="shared" ref="C52" si="34">C47+1</f>
-        <v>12</v>
+        <f t="shared" si="7"/>
+        <v>11</v>
       </c>
       <c r="D52" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E52" s="4">
-        <f t="shared" ref="E52" si="35">E47</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -3086,7 +3118,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
-        <f t="shared" ref="C53" si="36">C52</f>
+        <f t="shared" ref="C53" si="35">C48+1</f>
         <v>12</v>
       </c>
       <c r="D53" s="4" t="str">
@@ -3094,8 +3126,8 @@
         <v>12</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" ref="E53" si="37">E52+1</f>
-        <v>2</v>
+        <f t="shared" ref="E53" si="36">E48</f>
+        <v>1</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -3115,7 +3147,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C54" si="37">C53</f>
         <v>12</v>
       </c>
       <c r="D54" s="4" t="str">
@@ -3123,8 +3155,8 @@
         <v>12</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E54" si="38">E53+1</f>
+        <v>2</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -3153,7 +3185,7 @@
       </c>
       <c r="E55" s="4">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -3182,7 +3214,7 @@
       </c>
       <c r="E56" s="4">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -3202,16 +3234,16 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4">
-        <f t="shared" ref="C57:C87" si="38">C52+1</f>
-        <v>13</v>
+        <f t="shared" si="7"/>
+        <v>12</v>
       </c>
       <c r="D57" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E57" s="4">
-        <f t="shared" ref="E57" si="39">E52</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -3231,7 +3263,7 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
-        <f t="shared" ref="C58:C88" si="40">C57</f>
+        <f t="shared" ref="C58:C88" si="39">C53+1</f>
         <v>13</v>
       </c>
       <c r="D58" s="4" t="str">
@@ -3239,8 +3271,8 @@
         <v>13</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" ref="E58" si="41">E57+1</f>
-        <v>2</v>
+        <f t="shared" ref="E58" si="40">E53</f>
+        <v>1</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -3260,7 +3292,7 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C59:C89" si="41">C58</f>
         <v>13</v>
       </c>
       <c r="D59" s="4" t="str">
@@ -3268,8 +3300,8 @@
         <v>13</v>
       </c>
       <c r="E59" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E59" si="42">E58+1</f>
+        <v>2</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -3298,7 +3330,7 @@
       </c>
       <c r="E60" s="4">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -3327,7 +3359,7 @@
       </c>
       <c r="E61" s="4">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -3347,16 +3379,16 @@
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
-        <f t="shared" si="38"/>
-        <v>14</v>
+        <f t="shared" si="7"/>
+        <v>13</v>
       </c>
       <c r="D62" s="4" t="str">
-        <f t="shared" ref="D62:D91" si="42">B62&amp;C62</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E62" s="4">
-        <f t="shared" ref="E62" si="43">E57</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -3376,16 +3408,16 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>14</v>
       </c>
       <c r="D63" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="D63:D92" si="43">B63&amp;C63</f>
         <v>14</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" ref="E63" si="44">E62+1</f>
-        <v>2</v>
+        <f t="shared" ref="E63" si="44">E58</f>
+        <v>1</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -3405,16 +3437,16 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="41"/>
         <v>14</v>
       </c>
       <c r="D64" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>14</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E64" si="45">E63+1</f>
+        <v>2</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -3438,12 +3470,12 @@
         <v>14</v>
       </c>
       <c r="D65" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>14</v>
       </c>
       <c r="E65" s="4">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -3467,12 +3499,12 @@
         <v>14</v>
       </c>
       <c r="D66" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>14</v>
       </c>
       <c r="E66" s="4">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -3492,16 +3524,16 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4">
-        <f t="shared" si="38"/>
-        <v>15</v>
+        <f t="shared" si="7"/>
+        <v>14</v>
       </c>
       <c r="D67" s="4" t="str">
-        <f t="shared" si="42"/>
-        <v>15</v>
+        <f t="shared" si="43"/>
+        <v>14</v>
       </c>
       <c r="E67" s="4">
-        <f t="shared" ref="E67" si="45">E62</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -3521,16 +3553,16 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>15</v>
       </c>
       <c r="D68" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>15</v>
       </c>
       <c r="E68" s="4">
-        <f t="shared" ref="E68" si="46">E67+1</f>
-        <v>2</v>
+        <f t="shared" ref="E68" si="46">E63</f>
+        <v>1</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -3550,16 +3582,16 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="D69" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>15</v>
       </c>
       <c r="E69" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E69" si="47">E68+1</f>
+        <v>2</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -3583,12 +3615,12 @@
         <v>15</v>
       </c>
       <c r="D70" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>15</v>
       </c>
       <c r="E70" s="4">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -3612,12 +3644,12 @@
         <v>15</v>
       </c>
       <c r="D71" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>15</v>
       </c>
       <c r="E71" s="4">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -3637,16 +3669,16 @@
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4">
-        <f t="shared" si="38"/>
-        <v>16</v>
+        <f t="shared" si="7"/>
+        <v>15</v>
       </c>
       <c r="D72" s="4" t="str">
-        <f t="shared" si="42"/>
-        <v>16</v>
+        <f t="shared" si="43"/>
+        <v>15</v>
       </c>
       <c r="E72" s="4">
-        <f t="shared" ref="E72" si="47">E67</f>
-        <v>1</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -3666,16 +3698,16 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>16</v>
       </c>
       <c r="D73" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>16</v>
       </c>
       <c r="E73" s="4">
-        <f t="shared" ref="E73:E91" si="48">E72+1</f>
-        <v>2</v>
+        <f t="shared" ref="E73" si="48">E68</f>
+        <v>1</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -3695,16 +3727,16 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="41"/>
         <v>16</v>
       </c>
       <c r="D74" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>16</v>
       </c>
       <c r="E74" s="4">
-        <f t="shared" si="48"/>
-        <v>3</v>
+        <f t="shared" ref="E74:E92" si="49">E73+1</f>
+        <v>2</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -3728,12 +3760,12 @@
         <v>16</v>
       </c>
       <c r="D75" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>16</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" si="48"/>
-        <v>4</v>
+        <f t="shared" si="49"/>
+        <v>3</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -3757,12 +3789,12 @@
         <v>16</v>
       </c>
       <c r="D76" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>16</v>
       </c>
       <c r="E76" s="4">
-        <f t="shared" si="48"/>
-        <v>5</v>
+        <f t="shared" si="49"/>
+        <v>4</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -3782,16 +3814,16 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4">
-        <f t="shared" si="38"/>
-        <v>17</v>
+        <f t="shared" si="7"/>
+        <v>16</v>
       </c>
       <c r="D77" s="4" t="str">
-        <f t="shared" si="42"/>
-        <v>17</v>
+        <f t="shared" si="43"/>
+        <v>16</v>
       </c>
       <c r="E77" s="4">
-        <f t="shared" ref="E77" si="49">E72</f>
-        <v>1</v>
+        <f t="shared" si="49"/>
+        <v>5</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -3811,16 +3843,16 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>17</v>
       </c>
       <c r="D78" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>17</v>
       </c>
       <c r="E78" s="4">
-        <f t="shared" ref="E78" si="50">E77+1</f>
-        <v>2</v>
+        <f t="shared" ref="E78" si="50">E73</f>
+        <v>1</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -3840,16 +3872,16 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="41"/>
         <v>17</v>
       </c>
       <c r="D79" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>17</v>
       </c>
       <c r="E79" s="4">
-        <f t="shared" si="48"/>
-        <v>3</v>
+        <f t="shared" ref="E79" si="51">E78+1</f>
+        <v>2</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -3873,12 +3905,12 @@
         <v>17</v>
       </c>
       <c r="D80" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>17</v>
       </c>
       <c r="E80" s="4">
-        <f t="shared" si="48"/>
-        <v>4</v>
+        <f t="shared" si="49"/>
+        <v>3</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -3902,12 +3934,12 @@
         <v>17</v>
       </c>
       <c r="D81" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>17</v>
       </c>
       <c r="E81" s="4">
-        <f t="shared" si="48"/>
-        <v>5</v>
+        <f t="shared" si="49"/>
+        <v>4</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -3927,16 +3959,16 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4">
-        <f t="shared" si="38"/>
-        <v>18</v>
+        <f t="shared" si="7"/>
+        <v>17</v>
       </c>
       <c r="D82" s="4" t="str">
-        <f t="shared" si="42"/>
-        <v>18</v>
+        <f t="shared" si="43"/>
+        <v>17</v>
       </c>
       <c r="E82" s="4">
-        <f t="shared" ref="E82" si="51">E77</f>
-        <v>1</v>
+        <f t="shared" si="49"/>
+        <v>5</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -3956,16 +3988,16 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>18</v>
       </c>
       <c r="D83" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>18</v>
       </c>
       <c r="E83" s="4">
-        <f t="shared" ref="E83" si="52">E82+1</f>
-        <v>2</v>
+        <f t="shared" ref="E83" si="52">E78</f>
+        <v>1</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -3985,16 +4017,16 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="41"/>
         <v>18</v>
       </c>
       <c r="D84" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>18</v>
       </c>
       <c r="E84" s="4">
-        <f t="shared" si="48"/>
-        <v>3</v>
+        <f t="shared" ref="E84" si="53">E83+1</f>
+        <v>2</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
@@ -4018,12 +4050,12 @@
         <v>18</v>
       </c>
       <c r="D85" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>18</v>
       </c>
       <c r="E85" s="4">
-        <f t="shared" si="48"/>
-        <v>4</v>
+        <f t="shared" si="49"/>
+        <v>3</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
@@ -4047,12 +4079,12 @@
         <v>18</v>
       </c>
       <c r="D86" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>18</v>
       </c>
       <c r="E86" s="4">
-        <f t="shared" si="48"/>
-        <v>5</v>
+        <f t="shared" si="49"/>
+        <v>4</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
@@ -4072,16 +4104,16 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4">
-        <f t="shared" si="38"/>
-        <v>19</v>
+        <f t="shared" si="7"/>
+        <v>18</v>
       </c>
       <c r="D87" s="4" t="str">
-        <f t="shared" si="42"/>
-        <v>19</v>
+        <f t="shared" si="43"/>
+        <v>18</v>
       </c>
       <c r="E87" s="4">
-        <f t="shared" ref="E87" si="53">E82</f>
-        <v>1</v>
+        <f t="shared" si="49"/>
+        <v>5</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -4101,16 +4133,16 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>19</v>
       </c>
       <c r="D88" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>19</v>
       </c>
       <c r="E88" s="4">
-        <f t="shared" ref="E88" si="54">E87+1</f>
-        <v>2</v>
+        <f t="shared" ref="E88" si="54">E83</f>
+        <v>1</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
@@ -4130,16 +4162,16 @@
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="41"/>
         <v>19</v>
       </c>
       <c r="D89" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>19</v>
       </c>
       <c r="E89" s="4">
-        <f t="shared" si="48"/>
-        <v>3</v>
+        <f t="shared" ref="E89" si="55">E88+1</f>
+        <v>2</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
@@ -4163,12 +4195,12 @@
         <v>19</v>
       </c>
       <c r="D90" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>19</v>
       </c>
       <c r="E90" s="4">
-        <f t="shared" si="48"/>
-        <v>4</v>
+        <f t="shared" si="49"/>
+        <v>3</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
@@ -4192,12 +4224,12 @@
         <v>19</v>
       </c>
       <c r="D91" s="4" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>19</v>
       </c>
       <c r="E91" s="4">
-        <f t="shared" si="48"/>
-        <v>5</v>
+        <f t="shared" si="49"/>
+        <v>4</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
@@ -4214,94 +4246,123 @@
       <c r="R91" s="7"/>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="15"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="16"/>
-      <c r="H92" s="16"/>
-      <c r="I92" s="16"/>
-      <c r="J92" s="16"/>
-      <c r="K92" s="16"/>
-      <c r="L92" s="16"/>
-      <c r="M92" s="16"/>
-      <c r="N92" s="16"/>
-      <c r="O92" s="17"/>
-      <c r="P92" s="17"/>
-      <c r="Q92" s="17"/>
-      <c r="R92" s="17"/>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" t="s">
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
+      <c r="C92" s="4">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="D92" s="4" t="str">
+        <f t="shared" si="43"/>
+        <v>19</v>
+      </c>
+      <c r="E92" s="4">
+        <f t="shared" si="49"/>
+        <v>5</v>
+      </c>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="7"/>
+      <c r="P92" s="7"/>
+      <c r="Q92" s="7"/>
+      <c r="R92" s="7"/>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="15"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="16"/>
+      <c r="H93" s="16"/>
+      <c r="I93" s="16"/>
+      <c r="J93" s="16"/>
+      <c r="K93" s="16"/>
+      <c r="L93" s="16"/>
+      <c r="M93" s="16"/>
+      <c r="N93" s="16"/>
+      <c r="O93" s="17"/>
+      <c r="P93" s="17"/>
+      <c r="Q93" s="17"/>
+      <c r="R93" s="17"/>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" t="s">
         <v>9</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F95" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95">
-        <f>MAX(A$2:A$92)</f>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96">
+        <f>MAX(A$2:A$93)</f>
         <v>0</v>
       </c>
-      <c r="F95">
-        <f>MAX(F$2:F$92)</f>
+      <c r="F96">
+        <f>MAX(F$2:F$93)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" t="s">
         <v>40</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D97" t="s">
         <v>14</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E97" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97">
-        <f>ROW(A93)-ROW(A1)-1</f>
-        <v>91</v>
-      </c>
-      <c r="D97">
-        <f>COUNTIF(D$2:D$92,D96)</f>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98">
+        <f>ROW(A94)-ROW(A1)-1</f>
+        <v>92</v>
+      </c>
+      <c r="D98">
+        <f>COUNTIF(D$2:D$93,D97)</f>
         <v>0</v>
       </c>
-      <c r="E97" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$92,$D$2:$D$92,E96)</f>
+      <c r="E98" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$93,$D$2:$D$93,E97)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D98" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D99" t="s">
         <v>12</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E99" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D99">
-        <f>COUNTIF(D$2:D$92,D98)</f>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D100">
+        <f>COUNTIF(D$2:D$93,D99)</f>
         <v>0</v>
       </c>
-      <c r="E99" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$92,$D$2:$D$92,E98)</f>
+      <c r="E100" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$93,$D$2:$D$93,E99)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R91" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R91">
-      <sortCondition ref="D1:D91"/>
+  <autoFilter ref="A1:R92" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R92">
+      <sortCondition ref="D1:D92"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:R92">
+  <conditionalFormatting sqref="A2:R93">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
@@ -4471,11 +4532,11 @@
         <v>1</v>
       </c>
       <c r="J3" cm="1">
-        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$92&amp;info_index!$E$2:$E$92,0),"")</f>
+        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),"")</f>
         <v>1</v>
       </c>
       <c r="K3" t="str" cm="1">
-        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$92,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$92&amp;info_index!$E$2:$E$92,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$93,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),1)&amp;"","")</f>
         <v>原点復帰動作</v>
       </c>
       <c r="L3" t="str" cm="1">
@@ -4487,7 +4548,7 @@
         <v>【11】 原点復帰動作</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$92,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$92&amp;info_index!$E$2:$E$92,0),1)&amp;"","")</f>
+        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$93,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="P3" t="str" cm="1">
@@ -4495,7 +4556,7 @@
         <v>unknown</v>
       </c>
       <c r="Q3" t="str" cm="1">
-        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$92,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$92&amp;info_index!$E$2:$E$92,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$93,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="R3" t="str" cm="1">
@@ -6334,12 +6395,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 巻き中測定動作';
+			strRt	:= '【62】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6347,12 +6408,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 周長測定動作';
+			strRt	:= '【63】 巻き中測定動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12476,15 +12550,15 @@
       </c>
       <c r="K54" t="str">
         <f ca="1"/>
-        <v>巻き中測定動作</v>
+        <v>計測準備</v>
       </c>
       <c r="L54" t="str">
         <f ca="1"/>
-        <v>巻き中測定動作</v>
+        <v>計測準備</v>
       </c>
       <c r="N54" t="str">
         <f ca="1"/>
-        <v>【62】 巻き中測定動作</v>
+        <v>【62】 計測準備</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -12513,75 +12587,75 @@
       <c r="AB54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';</v>
+			strRt	:= '計測準備';</v>
       </c>
       <c r="AE54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 巻き中測定動作';</v>
+			strRt	:= '【62】 計測準備';</v>
       </c>
       <c r="AG54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 巻き中測定動作';
+			strRt	:= '【62】 計測準備';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 巻き中測定動作';
+			strRt	:= '【62】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 巻き中測定動作';
+			strRt	:= '【62】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12589,12 +12663,12 @@
       <c r="AJ54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 巻き中測定動作';
+			strRt	:= '【62】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12603,12 +12677,12 @@
       <c r="AK54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 巻き中測定動作';
+			strRt	:= '【62】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12620,12 +12694,12 @@
       <c r="AL54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 巻き中測定動作';
+			strRt	:= '【62】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12637,12 +12711,12 @@
       <c r="AM54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 巻き中測定動作';
+			strRt	:= '【62】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12673,15 +12747,15 @@
       </c>
       <c r="K55" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>巻き中測定動作</v>
       </c>
       <c r="L55" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>巻き中測定動作</v>
       </c>
       <c r="N55" t="str">
         <f ca="1"/>
-        <v>【63】 周長測定動作</v>
+        <v>【63】 巻き中測定動作</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -12710,75 +12784,75 @@
       <c r="AB55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';</v>
+			strRt	:= '巻き中測定動作';</v>
       </c>
       <c r="AE55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 周長測定動作';</v>
+			strRt	:= '【63】 巻き中測定動作';</v>
       </c>
       <c r="AG55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 周長測定動作';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 周長測定動作';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 周長測定動作';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12786,12 +12860,12 @@
       <c r="AJ55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 周長測定動作';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12800,12 +12874,12 @@
       <c r="AK55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 周長測定動作';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12817,12 +12891,12 @@
       <c r="AL55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 周長測定動作';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12834,12 +12908,12 @@
       <c r="AM55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 周長測定動作';
+			strRt	:= '【63】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12865,26 +12939,26 @@
       <c r="I56" t="str">
         <v/>
       </c>
-      <c r="J56" t="str">
-        <v/>
+      <c r="J56">
+        <v>26</v>
       </c>
       <c r="K56" t="str">
         <f ca="1"/>
-        <v/>
+        <v>排出動作</v>
       </c>
       <c r="L56" t="str">
         <f ca="1"/>
-        <v/>
+        <v>排出動作</v>
       </c>
       <c r="N56" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【64】 排出動作</v>
       </c>
       <c r="O56" t="str">
         <v/>
       </c>
       <c r="P56" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q56" t="str">
         <f ca="1"/>
@@ -12892,63 +12966,158 @@
       </c>
       <c r="R56" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';</v>
       </c>
       <c r="AE56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 排出動作';</v>
       </c>
       <c r="AG56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 排出動作';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM56" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 排出動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="57" spans="6:39" x14ac:dyDescent="0.55000000000000004">
@@ -28179,12 +28348,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き中測定動作
+	//計測準備
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 巻き中測定動作';
+			strRt	:= '【62】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28192,12 +28361,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 周長測定動作';
+			strRt	:= '【63】 巻き中測定動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//排出動作
+	ELSIF uiInfoIdx = 4 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【64】 排出動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E627EF4-7A78-4191-A463-4D59576B8779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED407A9-B030-4436-A768-87CA48B05C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$93</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -645,6 +645,22 @@
   <si>
     <t>Discharge operation</t>
   </si>
+  <si>
+    <t>供給確認動作</t>
+    <rPh sb="0" eb="2">
+      <t>キョウキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Supply confirmation operation</t>
+  </si>
 </sst>
 </file>
 
@@ -1049,7 +1065,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$96">
+    <xdr:sp macro="" textlink="$A$97">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -1418,7 +1434,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -1522,7 +1538,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="str">
-        <f t="shared" ref="D3:D62" si="0">B3&amp;C3</f>
+        <f t="shared" ref="D3:D63" si="0">B3&amp;C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="4">
@@ -1728,7 +1744,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4">
-        <f t="shared" ref="C9:C11" si="4">C8</f>
+        <f t="shared" ref="C9:C12" si="4">C8</f>
         <v>2</v>
       </c>
       <c r="D9" s="4" t="str">
@@ -1736,7 +1752,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" ref="E9:E11" si="5">E8+1</f>
+        <f t="shared" ref="E9:E12" si="5">E8+1</f>
         <v>3</v>
       </c>
       <c r="F9" s="5"/>
@@ -1833,26 +1849,26 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4">
-        <f>C7+1</f>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="D12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="D12" si="7">B12&amp;C12</f>
+        <v>2</v>
       </c>
       <c r="E12" s="4">
-        <f>E7</f>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>6</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1868,7 +1884,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4">
-        <f t="shared" ref="C13:C92" si="7">C12</f>
+        <f>C7+1</f>
         <v>3</v>
       </c>
       <c r="D13" s="4" t="str">
@@ -1876,18 +1892,18 @@
         <v>3</v>
       </c>
       <c r="E13" s="4">
-        <f t="shared" ref="E13:E72" si="8">E12+1</f>
-        <v>2</v>
+        <f>E7</f>
+        <v>1</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
         <v>74</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -1903,7 +1919,7 @@
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C14:C93" si="8">C13</f>
         <v>3</v>
       </c>
       <c r="D14" s="4" t="str">
@@ -1911,18 +1927,18 @@
         <v>3</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E14:E73" si="9">E13+1</f>
+        <v>2</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
         <v>74</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1938,26 +1954,26 @@
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4">
-        <f>C12+1</f>
-        <v>4</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="D15" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4">
-        <f>E12</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -1973,7 +1989,7 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4">
-        <f t="shared" ref="C16" si="9">C15</f>
+        <f>C13+1</f>
         <v>4</v>
       </c>
       <c r="D16" s="4" t="str">
@@ -1981,18 +1997,18 @@
         <v>4</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" ref="E16" si="10">E15+1</f>
-        <v>2</v>
+        <f>E13</f>
+        <v>1</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2008,7 +2024,7 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C17" si="10">C16</f>
         <v>4</v>
       </c>
       <c r="D17" s="4" t="str">
@@ -2016,18 +2032,18 @@
         <v>4</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E17" si="11">E16+1</f>
+        <v>2</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -2043,7 +2059,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="D18" s="4" t="str">
@@ -2051,18 +2067,18 @@
         <v>4</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -2078,7 +2094,7 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="D19" s="4" t="str">
@@ -2086,21 +2102,21 @@
         <v>4</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J19" s="5"/>
-      <c r="K19" s="6"/>
+      <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
@@ -2113,26 +2129,26 @@
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="D20" s="4" t="str">
-        <f t="shared" ref="D20" si="11">B20&amp;C20</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="8"/>
-        <v>6</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="6"/>
@@ -2148,29 +2164,29 @@
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4">
-        <f>C15+1</f>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="D21" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ref="D21" si="12">B21&amp;C21</f>
+        <v>4</v>
       </c>
       <c r="E21" s="4">
-        <f>E15</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>6</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
+      <c r="K21" s="6"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
@@ -2183,7 +2199,7 @@
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4">
-        <f t="shared" ref="C22" si="12">C21</f>
+        <f>C16+1</f>
         <v>5</v>
       </c>
       <c r="D22" s="4" t="str">
@@ -2191,18 +2207,18 @@
         <v>5</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" ref="E22" si="13">E21+1</f>
-        <v>2</v>
+        <f>E16</f>
+        <v>1</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -2218,7 +2234,7 @@
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C23" si="13">C22</f>
         <v>5</v>
       </c>
       <c r="D23" s="4" t="str">
@@ -2226,53 +2242,53 @@
         <v>5</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E23" si="14">E22+1</f>
+        <v>2</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
       <c r="R23" s="7"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4">
-        <f>C21+1</f>
-        <v>6</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="D24" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="4">
-        <f>E21</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -2288,7 +2304,7 @@
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4">
-        <f t="shared" ref="C25" si="14">C24</f>
+        <f>C22+1</f>
         <v>6</v>
       </c>
       <c r="D25" s="4" t="str">
@@ -2296,34 +2312,34 @@
         <v>6</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" ref="E25" si="15">E24+1</f>
-        <v>2</v>
-      </c>
-      <c r="F25" s="9"/>
+        <f>E22</f>
+        <v>1</v>
+      </c>
+      <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H25" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
+      <c r="H25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C26" si="15">C25</f>
         <v>6</v>
       </c>
       <c r="D26" s="4" t="str">
@@ -2331,53 +2347,53 @@
         <v>6</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="F26" s="5"/>
+        <f t="shared" ref="E26" si="16">E25+1</f>
+        <v>2</v>
+      </c>
+      <c r="F26" s="9"/>
       <c r="G26" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
+      <c r="H26" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
       <c r="R26" s="7"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="D27" s="4" t="str">
-        <f t="shared" ref="D27" si="16">B27&amp;C27</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
         <v>77</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -2393,36 +2409,42 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4">
-        <f>C24+1</f>
-        <v>7</v>
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="D28" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f t="shared" ref="D28" si="17">B28&amp;C28</f>
+        <v>6</v>
       </c>
       <c r="E28" s="4">
-        <f>E24</f>
-        <v>1</v>
-      </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
       <c r="R28" s="7"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4">
-        <f t="shared" ref="C29" si="17">C28</f>
+        <f>C25+1</f>
         <v>7</v>
       </c>
       <c r="D29" s="4" t="str">
@@ -2430,8 +2452,8 @@
         <v>7</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" ref="E29" si="18">E28+1</f>
-        <v>2</v>
+        <f>E25</f>
+        <v>1</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
@@ -2451,7 +2473,7 @@
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C30" si="18">C29</f>
         <v>7</v>
       </c>
       <c r="D30" s="4" t="str">
@@ -2459,28 +2481,28 @@
         <v>7</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
+        <f t="shared" ref="E30" si="19">E29+1</f>
+        <v>2</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22"/>
       <c r="R30" s="7"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="D31" s="4" t="str">
@@ -2488,8 +2510,8 @@
         <v>7</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -2509,7 +2531,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="D32" s="4" t="str">
@@ -2517,8 +2539,8 @@
         <v>7</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -2535,39 +2557,39 @@
       <c r="R32" s="7"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="26"/>
+      <c r="A33" s="4"/>
       <c r="B33" s="4"/>
-      <c r="C33" s="26">
-        <f t="shared" ref="C33" si="19">C28+1</f>
-        <v>8</v>
-      </c>
-      <c r="D33" s="26" t="str">
+      <c r="C33" s="4">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="D33" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" ref="E33" si="20">E28</f>
-        <v>1</v>
-      </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="26"/>
       <c r="B34" s="4"/>
       <c r="C34" s="26">
-        <f t="shared" ref="C34" si="21">C33</f>
+        <f t="shared" ref="C34" si="20">C29+1</f>
         <v>8</v>
       </c>
       <c r="D34" s="26" t="str">
@@ -2575,8 +2597,8 @@
         <v>8</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" ref="E34" si="22">E33+1</f>
-        <v>2</v>
+        <f t="shared" ref="E34" si="21">E29</f>
+        <v>1</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
@@ -2596,7 +2618,7 @@
       <c r="A35" s="26"/>
       <c r="B35" s="4"/>
       <c r="C35" s="26">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C35" si="22">C34</f>
         <v>8</v>
       </c>
       <c r="D35" s="26" t="str">
@@ -2604,8 +2626,8 @@
         <v>8</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E35" si="23">E34+1</f>
+        <v>2</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
@@ -2622,39 +2644,39 @@
       <c r="R35" s="7"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="4"/>
+      <c r="A36" s="26"/>
       <c r="B36" s="4"/>
-      <c r="C36" s="4">
-        <f t="shared" si="7"/>
+      <c r="C36" s="26">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="D36" s="4" t="str">
+      <c r="D36" s="26" t="str">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="7"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="7"/>
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
       <c r="R36" s="7"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="D37" s="4" t="str">
@@ -2662,8 +2684,8 @@
         <v>8</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -2683,16 +2705,16 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4">
-        <f t="shared" ref="C38" si="23">C33+1</f>
-        <v>9</v>
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="D38" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" ref="E38" si="24">E33</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -2712,7 +2734,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4">
-        <f t="shared" ref="C39" si="25">C38</f>
+        <f t="shared" ref="C39" si="24">C34+1</f>
         <v>9</v>
       </c>
       <c r="D39" s="4" t="str">
@@ -2720,8 +2742,8 @@
         <v>9</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" ref="E39" si="26">E38+1</f>
-        <v>2</v>
+        <f t="shared" ref="E39" si="25">E34</f>
+        <v>1</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -2741,7 +2763,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C40" si="26">C39</f>
         <v>9</v>
       </c>
       <c r="D40" s="4" t="str">
@@ -2749,8 +2771,8 @@
         <v>9</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E40" si="27">E39+1</f>
+        <v>2</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -2770,7 +2792,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="D41" s="4" t="str">
@@ -2778,15 +2800,15 @@
         <v>9</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
-      <c r="K41" s="13"/>
+      <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
@@ -2799,7 +2821,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="D42" s="4" t="str">
@@ -2807,15 +2829,15 @@
         <v>9</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
+      <c r="K42" s="13"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
@@ -2828,16 +2850,16 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
-        <f t="shared" ref="C43" si="27">C38+1</f>
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="D43" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" ref="E43" si="28">E38</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -2857,7 +2879,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
-        <f t="shared" ref="C44" si="29">C43</f>
+        <f t="shared" ref="C44" si="28">C39+1</f>
         <v>10</v>
       </c>
       <c r="D44" s="4" t="str">
@@ -2865,8 +2887,8 @@
         <v>10</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" ref="E44" si="30">E43+1</f>
-        <v>2</v>
+        <f t="shared" ref="E44" si="29">E39</f>
+        <v>1</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -2886,7 +2908,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C45" si="30">C44</f>
         <v>10</v>
       </c>
       <c r="D45" s="4" t="str">
@@ -2894,8 +2916,8 @@
         <v>10</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E45" si="31">E44+1</f>
+        <v>2</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -2915,7 +2937,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="D46" s="4" t="str">
@@ -2923,8 +2945,8 @@
         <v>10</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -2944,7 +2966,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="D47" s="4" t="str">
@@ -2952,8 +2974,8 @@
         <v>10</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -2973,16 +2995,16 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
-        <f t="shared" ref="C48" si="31">C43+1</f>
-        <v>11</v>
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="D48" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" ref="E48" si="32">E43</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -3002,7 +3024,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
-        <f t="shared" ref="C49" si="33">C48</f>
+        <f t="shared" ref="C49" si="32">C44+1</f>
         <v>11</v>
       </c>
       <c r="D49" s="4" t="str">
@@ -3010,8 +3032,8 @@
         <v>11</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" ref="E49" si="34">E48+1</f>
-        <v>2</v>
+        <f t="shared" ref="E49" si="33">E44</f>
+        <v>1</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -3031,7 +3053,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C50" si="34">C49</f>
         <v>11</v>
       </c>
       <c r="D50" s="4" t="str">
@@ -3039,8 +3061,8 @@
         <v>11</v>
       </c>
       <c r="E50" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E50" si="35">E49+1</f>
+        <v>2</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -3060,7 +3082,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="D51" s="4" t="str">
@@ -3068,8 +3090,8 @@
         <v>11</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -3089,7 +3111,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="D52" s="4" t="str">
@@ -3097,8 +3119,8 @@
         <v>11</v>
       </c>
       <c r="E52" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -3118,16 +3140,16 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
-        <f t="shared" ref="C53" si="35">C48+1</f>
-        <v>12</v>
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="D53" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" ref="E53" si="36">E48</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -3147,7 +3169,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
-        <f t="shared" ref="C54" si="37">C53</f>
+        <f t="shared" ref="C54" si="36">C49+1</f>
         <v>12</v>
       </c>
       <c r="D54" s="4" t="str">
@@ -3155,8 +3177,8 @@
         <v>12</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" ref="E54" si="38">E53+1</f>
-        <v>2</v>
+        <f t="shared" ref="E54" si="37">E49</f>
+        <v>1</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -3176,7 +3198,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C55" si="38">C54</f>
         <v>12</v>
       </c>
       <c r="D55" s="4" t="str">
@@ -3184,8 +3206,8 @@
         <v>12</v>
       </c>
       <c r="E55" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E55" si="39">E54+1</f>
+        <v>2</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -3205,7 +3227,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="D56" s="4" t="str">
@@ -3213,8 +3235,8 @@
         <v>12</v>
       </c>
       <c r="E56" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -3234,7 +3256,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="D57" s="4" t="str">
@@ -3242,8 +3264,8 @@
         <v>12</v>
       </c>
       <c r="E57" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -3263,16 +3285,16 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
-        <f t="shared" ref="C58:C88" si="39">C53+1</f>
-        <v>13</v>
+        <f t="shared" si="8"/>
+        <v>12</v>
       </c>
       <c r="D58" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" ref="E58" si="40">E53</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -3292,7 +3314,7 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
-        <f t="shared" ref="C59:C89" si="41">C58</f>
+        <f t="shared" ref="C59:C89" si="40">C54+1</f>
         <v>13</v>
       </c>
       <c r="D59" s="4" t="str">
@@ -3300,8 +3322,8 @@
         <v>13</v>
       </c>
       <c r="E59" s="4">
-        <f t="shared" ref="E59" si="42">E58+1</f>
-        <v>2</v>
+        <f t="shared" ref="E59" si="41">E54</f>
+        <v>1</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -3321,7 +3343,7 @@
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="C60:C90" si="42">C59</f>
         <v>13</v>
       </c>
       <c r="D60" s="4" t="str">
@@ -3329,8 +3351,8 @@
         <v>13</v>
       </c>
       <c r="E60" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E60" si="43">E59+1</f>
+        <v>2</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -3350,7 +3372,7 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="D61" s="4" t="str">
@@ -3358,8 +3380,8 @@
         <v>13</v>
       </c>
       <c r="E61" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -3379,7 +3401,7 @@
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="D62" s="4" t="str">
@@ -3387,8 +3409,8 @@
         <v>13</v>
       </c>
       <c r="E62" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -3408,16 +3430,16 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
-        <f t="shared" si="39"/>
-        <v>14</v>
+        <f t="shared" si="8"/>
+        <v>13</v>
       </c>
       <c r="D63" s="4" t="str">
-        <f t="shared" ref="D63:D92" si="43">B63&amp;C63</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" ref="E63" si="44">E58</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -3437,16 +3459,16 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>14</v>
       </c>
       <c r="D64" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="D64:D93" si="44">B64&amp;C64</f>
         <v>14</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" ref="E64" si="45">E63+1</f>
-        <v>2</v>
+        <f t="shared" ref="E64" si="45">E59</f>
+        <v>1</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -3466,16 +3488,16 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="42"/>
         <v>14</v>
       </c>
       <c r="D65" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>14</v>
       </c>
       <c r="E65" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E65" si="46">E64+1</f>
+        <v>2</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -3495,16 +3517,16 @@
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="D66" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>14</v>
       </c>
       <c r="E66" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -3524,16 +3546,16 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="D67" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>14</v>
       </c>
       <c r="E67" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -3553,16 +3575,16 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4">
-        <f t="shared" si="39"/>
-        <v>15</v>
+        <f t="shared" si="8"/>
+        <v>14</v>
       </c>
       <c r="D68" s="4" t="str">
-        <f t="shared" si="43"/>
-        <v>15</v>
+        <f t="shared" si="44"/>
+        <v>14</v>
       </c>
       <c r="E68" s="4">
-        <f t="shared" ref="E68" si="46">E63</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -3582,16 +3604,16 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>15</v>
       </c>
       <c r="D69" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>15</v>
       </c>
       <c r="E69" s="4">
-        <f t="shared" ref="E69" si="47">E68+1</f>
-        <v>2</v>
+        <f t="shared" ref="E69" si="47">E64</f>
+        <v>1</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -3611,16 +3633,16 @@
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="42"/>
         <v>15</v>
       </c>
       <c r="D70" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>15</v>
       </c>
       <c r="E70" s="4">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" ref="E70" si="48">E69+1</f>
+        <v>2</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -3640,16 +3662,16 @@
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="D71" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>15</v>
       </c>
       <c r="E71" s="4">
-        <f t="shared" si="8"/>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -3669,16 +3691,16 @@
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="D72" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>15</v>
       </c>
       <c r="E72" s="4">
-        <f t="shared" si="8"/>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -3698,16 +3720,16 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4">
-        <f t="shared" si="39"/>
-        <v>16</v>
+        <f t="shared" si="8"/>
+        <v>15</v>
       </c>
       <c r="D73" s="4" t="str">
-        <f t="shared" si="43"/>
-        <v>16</v>
+        <f t="shared" si="44"/>
+        <v>15</v>
       </c>
       <c r="E73" s="4">
-        <f t="shared" ref="E73" si="48">E68</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -3727,16 +3749,16 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>16</v>
       </c>
       <c r="D74" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>16</v>
       </c>
       <c r="E74" s="4">
-        <f t="shared" ref="E74:E92" si="49">E73+1</f>
-        <v>2</v>
+        <f t="shared" ref="E74" si="49">E69</f>
+        <v>1</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -3756,16 +3778,16 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="42"/>
         <v>16</v>
       </c>
       <c r="D75" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>16</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" si="49"/>
-        <v>3</v>
+        <f t="shared" ref="E75:E93" si="50">E74+1</f>
+        <v>2</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -3785,16 +3807,16 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="D76" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>16</v>
       </c>
       <c r="E76" s="4">
-        <f t="shared" si="49"/>
-        <v>4</v>
+        <f t="shared" si="50"/>
+        <v>3</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -3814,16 +3836,16 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="D77" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>16</v>
       </c>
       <c r="E77" s="4">
-        <f t="shared" si="49"/>
-        <v>5</v>
+        <f t="shared" si="50"/>
+        <v>4</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -3843,16 +3865,16 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4">
-        <f t="shared" si="39"/>
-        <v>17</v>
+        <f t="shared" si="8"/>
+        <v>16</v>
       </c>
       <c r="D78" s="4" t="str">
-        <f t="shared" si="43"/>
-        <v>17</v>
+        <f t="shared" si="44"/>
+        <v>16</v>
       </c>
       <c r="E78" s="4">
-        <f t="shared" ref="E78" si="50">E73</f>
-        <v>1</v>
+        <f t="shared" si="50"/>
+        <v>5</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -3872,16 +3894,16 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>17</v>
       </c>
       <c r="D79" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>17</v>
       </c>
       <c r="E79" s="4">
-        <f t="shared" ref="E79" si="51">E78+1</f>
-        <v>2</v>
+        <f t="shared" ref="E79" si="51">E74</f>
+        <v>1</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -3901,16 +3923,16 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="42"/>
         <v>17</v>
       </c>
       <c r="D80" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>17</v>
       </c>
       <c r="E80" s="4">
-        <f t="shared" si="49"/>
-        <v>3</v>
+        <f t="shared" ref="E80" si="52">E79+1</f>
+        <v>2</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -3930,16 +3952,16 @@
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="D81" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>17</v>
       </c>
       <c r="E81" s="4">
-        <f t="shared" si="49"/>
-        <v>4</v>
+        <f t="shared" si="50"/>
+        <v>3</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -3959,16 +3981,16 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="D82" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>17</v>
       </c>
       <c r="E82" s="4">
-        <f t="shared" si="49"/>
-        <v>5</v>
+        <f t="shared" si="50"/>
+        <v>4</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -3988,16 +4010,16 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4">
-        <f t="shared" si="39"/>
-        <v>18</v>
+        <f t="shared" si="8"/>
+        <v>17</v>
       </c>
       <c r="D83" s="4" t="str">
-        <f t="shared" si="43"/>
-        <v>18</v>
+        <f t="shared" si="44"/>
+        <v>17</v>
       </c>
       <c r="E83" s="4">
-        <f t="shared" ref="E83" si="52">E78</f>
-        <v>1</v>
+        <f t="shared" si="50"/>
+        <v>5</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -4017,16 +4039,16 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>18</v>
       </c>
       <c r="D84" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>18</v>
       </c>
       <c r="E84" s="4">
-        <f t="shared" ref="E84" si="53">E83+1</f>
-        <v>2</v>
+        <f t="shared" ref="E84" si="53">E79</f>
+        <v>1</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
@@ -4046,16 +4068,16 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="42"/>
         <v>18</v>
       </c>
       <c r="D85" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>18</v>
       </c>
       <c r="E85" s="4">
-        <f t="shared" si="49"/>
-        <v>3</v>
+        <f t="shared" ref="E85" si="54">E84+1</f>
+        <v>2</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
@@ -4075,16 +4097,16 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="D86" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>18</v>
       </c>
       <c r="E86" s="4">
-        <f t="shared" si="49"/>
-        <v>4</v>
+        <f t="shared" si="50"/>
+        <v>3</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
@@ -4104,16 +4126,16 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="D87" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>18</v>
       </c>
       <c r="E87" s="4">
-        <f t="shared" si="49"/>
-        <v>5</v>
+        <f t="shared" si="50"/>
+        <v>4</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -4133,16 +4155,16 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4">
-        <f t="shared" si="39"/>
-        <v>19</v>
+        <f t="shared" si="8"/>
+        <v>18</v>
       </c>
       <c r="D88" s="4" t="str">
-        <f t="shared" si="43"/>
-        <v>19</v>
+        <f t="shared" si="44"/>
+        <v>18</v>
       </c>
       <c r="E88" s="4">
-        <f t="shared" ref="E88" si="54">E83</f>
-        <v>1</v>
+        <f t="shared" si="50"/>
+        <v>5</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
@@ -4162,16 +4184,16 @@
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>19</v>
       </c>
       <c r="D89" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>19</v>
       </c>
       <c r="E89" s="4">
-        <f t="shared" ref="E89" si="55">E88+1</f>
-        <v>2</v>
+        <f t="shared" ref="E89" si="55">E84</f>
+        <v>1</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
@@ -4191,16 +4213,16 @@
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="42"/>
         <v>19</v>
       </c>
       <c r="D90" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>19</v>
       </c>
       <c r="E90" s="4">
-        <f t="shared" si="49"/>
-        <v>3</v>
+        <f t="shared" ref="E90" si="56">E89+1</f>
+        <v>2</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
@@ -4220,16 +4242,16 @@
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="D91" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>19</v>
       </c>
       <c r="E91" s="4">
-        <f t="shared" si="49"/>
-        <v>4</v>
+        <f t="shared" si="50"/>
+        <v>3</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
@@ -4249,16 +4271,16 @@
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="D92" s="4" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>19</v>
       </c>
       <c r="E92" s="4">
-        <f t="shared" si="49"/>
-        <v>5</v>
+        <f t="shared" si="50"/>
+        <v>4</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
@@ -4275,94 +4297,123 @@
       <c r="R92" s="7"/>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="15"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="15"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="16"/>
-      <c r="G93" s="16"/>
-      <c r="H93" s="16"/>
-      <c r="I93" s="16"/>
-      <c r="J93" s="16"/>
-      <c r="K93" s="16"/>
-      <c r="L93" s="16"/>
-      <c r="M93" s="16"/>
-      <c r="N93" s="16"/>
-      <c r="O93" s="17"/>
-      <c r="P93" s="17"/>
-      <c r="Q93" s="17"/>
-      <c r="R93" s="17"/>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" t="s">
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4">
+        <f t="shared" si="8"/>
+        <v>19</v>
+      </c>
+      <c r="D93" s="4" t="str">
+        <f t="shared" si="44"/>
+        <v>19</v>
+      </c>
+      <c r="E93" s="4">
+        <f t="shared" si="50"/>
+        <v>5</v>
+      </c>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+      <c r="K93" s="5"/>
+      <c r="L93" s="5"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="7"/>
+      <c r="P93" s="7"/>
+      <c r="Q93" s="7"/>
+      <c r="R93" s="7"/>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="15"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="15"/>
+      <c r="D94" s="15"/>
+      <c r="E94" s="15"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="16"/>
+      <c r="H94" s="16"/>
+      <c r="I94" s="16"/>
+      <c r="J94" s="16"/>
+      <c r="K94" s="16"/>
+      <c r="L94" s="16"/>
+      <c r="M94" s="16"/>
+      <c r="N94" s="16"/>
+      <c r="O94" s="17"/>
+      <c r="P94" s="17"/>
+      <c r="Q94" s="17"/>
+      <c r="R94" s="17"/>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
         <v>9</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F96" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96">
-        <f>MAX(A$2:A$93)</f>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97">
+        <f>MAX(A$2:A$94)</f>
         <v>0</v>
       </c>
-      <c r="F96">
-        <f>MAX(F$2:F$93)</f>
+      <c r="F97">
+        <f>MAX(F$2:F$94)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" t="s">
         <v>40</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D98" t="s">
         <v>14</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E98" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98">
-        <f>ROW(A94)-ROW(A1)-1</f>
-        <v>92</v>
-      </c>
-      <c r="D98">
-        <f>COUNTIF(D$2:D$93,D97)</f>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99">
+        <f>ROW(A95)-ROW(A1)-1</f>
+        <v>93</v>
+      </c>
+      <c r="D99">
+        <f>COUNTIF(D$2:D$94,D98)</f>
         <v>0</v>
       </c>
-      <c r="E98" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$93,$D$2:$D$93,E97)</f>
+      <c r="E99" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$94,$D$2:$D$94,E98)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D99" t="s">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="D100" t="s">
         <v>12</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E100" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D100">
-        <f>COUNTIF(D$2:D$93,D99)</f>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="D101">
+        <f>COUNTIF(D$2:D$94,D100)</f>
         <v>0</v>
       </c>
-      <c r="E100" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$93,$D$2:$D$93,E99)</f>
+      <c r="E101" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$94,$D$2:$D$94,E100)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R92" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R92">
-      <sortCondition ref="D1:D92"/>
+  <autoFilter ref="A1:R93" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R93">
+      <sortCondition ref="D1:D93"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:R93">
+  <conditionalFormatting sqref="A2:R94">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
@@ -4518,7 +4569,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\精度を高める\rtc\[20260130_1906_幅50巻.xlsx]Sheet1</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -4532,23 +4583,23 @@
         <v>1</v>
       </c>
       <c r="J3" cm="1">
-        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),"")</f>
+        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$94&amp;info_index!$E$2:$E$94,0),"")</f>
         <v>1</v>
       </c>
       <c r="K3" t="str" cm="1">
-        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$93,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),1)&amp;"","")</f>
-        <v>原点復帰動作</v>
+        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$94,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$94&amp;info_index!$E$2:$E$94,0),1)&amp;"","")</f>
+        <v>Return to origin operation</v>
       </c>
       <c r="L3" t="str" cm="1">
         <f t="array" aca="1" ref="L3:L202" ca="1">IF(LEN(_xlfn.ANCHORARRAY($J3)),IF(LEN(_xlfn.ANCHORARRAY(K3)),_xlfn.ANCHORARRAY(K3),"unknown"),"")</f>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="N3" t="str" cm="1">
         <f t="array" aca="1" ref="N3:N202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(L3)),"【"&amp;G3:G202&amp;H3:H202&amp;"】 "&amp;_xlfn.ANCHORARRAY(L3),"")</f>
-        <v>【11】 原点復帰動作</v>
+        <v>【11】 Return to origin operation</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$93,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),1)&amp;"","")</f>
+        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$94,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$94&amp;info_index!$E$2:$E$94,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="P3" t="str" cm="1">
@@ -4556,7 +4607,7 @@
         <v>unknown</v>
       </c>
       <c r="Q3" t="str" cm="1">
-        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$93,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$93&amp;info_index!$E$2:$E$93,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$94,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$94&amp;info_index!$E$2:$E$94,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="R3" t="str" cm="1">
@@ -4576,14 +4627,14 @@
         <f t="array" aca="1" ref="AB3:AB202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AA3)),_xlfn.ANCHORARRAY(AA3),"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;$B$7&amp;_xlfn.ANCHORARRAY(L3)&amp;CHAR(10)&amp;CHAR(9)&amp;IF(H3:H202=1,"IF ","ELSIF ")&amp;$B$26&amp;" = "&amp;H3:H202&amp;" THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC3" t="str" cm="1">
         <f t="array" aca="1" ref="AC3:AC202" ca="1">IF(LEN(AB3:AB202),AB3:AB202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"IF "&amp;$B$27&amp;" = '"&amp;$L$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -4591,54 +4642,54 @@
         <f t="array" aca="1" ref="AD3:AD202" ca="1">IF(LEN(AC3:AC202),AC3:AC202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(L3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE3" t="str" cm="1">
         <f t="array" aca="1" ref="AE3:AE202" ca="1">IF(LEN(AD3:AD202),AD3:AD202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;N$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF3" t="str" cm="1">
         <f t="array" aca="1" ref="AF3:AF202" ca="1">IF(LEN(AE3:AE202),AE3:AE202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(N3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';</v>
+			strRt	:= '【11】 Return to origin operation';</v>
       </c>
       <c r="AG3" t="str" cm="1">
         <f t="array" aca="1" ref="AG3:AG202" ca="1">IF(LEN(AF3:AF202),AF3:AF202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;P$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH3" t="str" cm="1">
         <f t="array" aca="1" ref="AH3:AH202" ca="1">IF(LEN(AG3:AG202),AG3:AG202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(P3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -4646,12 +4697,12 @@
         <f t="array" aca="1" ref="AI3:AI202" ca="1">IF(LEN(AH3:AH202),AH3:AH202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;R$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4660,12 +4711,12 @@
         <f t="array" aca="1" ref="AJ3:AJ202" ca="1">IF(LEN(AI3:AI202),AI3:AI202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(R3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4675,12 +4726,12 @@
         <f t="array" aca="1" ref="AK3:AK202" ca="1">IF(LEN(AJ3:AJ202),AJ3:AJ202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 3"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4693,12 +4744,12 @@
         <f t="array" aca="1" ref="AL3:AL202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AK3)),_xlfn.ANCHORARRAY(AK3),"")&amp;IF(I3:I202="●",CHAR(10)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 2"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4711,12 +4762,12 @@
         <f t="array" aca="1" ref="AM3:AM202" ca="1">_xlfn.ANCHORARRAY(AL3)</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4748,15 +4799,15 @@
       </c>
       <c r="K4" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="L4" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="N4" t="str">
         <f ca="1"/>
-        <v>【12】 供給準備動作</v>
+        <v>【12】 Preparation for supply operation</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -4785,75 +4836,75 @@
       <c r="AB4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Preparation for supply operation';</v>
       </c>
       <c r="AE4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';</v>
+			strRt	:= '【12】 Preparation for supply operation';</v>
       </c>
       <c r="AG4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4861,12 +4912,12 @@
       <c r="AJ4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4875,12 +4926,12 @@
       <c r="AK4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4892,12 +4943,12 @@
       <c r="AL4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4909,12 +4960,12 @@
       <c r="AM4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4930,7 +4981,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\精度を高める\rtc\[20260130_1906_幅50巻.xlsx]Sheet1 によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -4952,15 +5003,15 @@
       </c>
       <c r="K5" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="N5" t="str">
         <f ca="1"/>
-        <v>【13】 供給開始動作</v>
+        <v>【13】 Start supply operation</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -4989,75 +5040,75 @@
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';</v>
+			strRt	:= 'Start supply operation';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給開始動作';</v>
+			strRt	:= '【13】 Start supply operation';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給開始動作';
+			strRt	:= '【13】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給開始動作';
+			strRt	:= '【13】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給開始動作';
+			strRt	:= '【13】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5065,12 +5116,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給開始動作';
+			strRt	:= '【13】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5079,12 +5130,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給開始動作';
+			strRt	:= '【13】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5096,12 +5147,12 @@
       <c r="AL5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給開始動作';
+			strRt	:= '【13】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5113,12 +5164,12 @@
       <c r="AM5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給開始動作';
+			strRt	:= '【13】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5155,15 +5206,15 @@
       </c>
       <c r="K6" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply operation</v>
       </c>
       <c r="L6" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply operation</v>
       </c>
       <c r="N6" t="str">
         <f ca="1"/>
-        <v>【14】 供給動作</v>
+        <v>【14】 Supply operation</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -5192,75 +5243,75 @@
       <c r="AB6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= 'Supply operation';</v>
       </c>
       <c r="AE6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給動作';</v>
+			strRt	:= '【14】 Supply operation';</v>
       </c>
       <c r="AG6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給動作';
+			strRt	:= '【14】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給動作';
+			strRt	:= '【14】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給動作';
+			strRt	:= '【14】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5268,12 +5319,12 @@
       <c r="AJ6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給動作';
+			strRt	:= '【14】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5282,12 +5333,12 @@
       <c r="AK6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給動作';
+			strRt	:= '【14】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5299,12 +5350,12 @@
       <c r="AL6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給動作';
+			strRt	:= '【14】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5316,12 +5367,12 @@
       <c r="AM6" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給動作';
+			strRt	:= '【14】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5358,15 +5409,15 @@
       </c>
       <c r="K7" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="L7" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="N7" t="str">
         <f ca="1"/>
-        <v>【15】 カット動作</v>
+        <v>【15】 Cut operation</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -5395,75 +5446,75 @@
       <c r="AB7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';</v>
+			strRt	:= 'Cut operation';</v>
       </c>
       <c r="AE7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 カット動作';</v>
+			strRt	:= '【15】 Cut operation';</v>
       </c>
       <c r="AG7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 カット動作';
+			strRt	:= '【15】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 カット動作';
+			strRt	:= '【15】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 カット動作';
+			strRt	:= '【15】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5471,12 +5522,12 @@
       <c r="AJ7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 カット動作';
+			strRt	:= '【15】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5485,12 +5536,12 @@
       <c r="AK7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 カット動作';
+			strRt	:= '【15】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5502,12 +5553,12 @@
       <c r="AL7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 カット動作';
+			strRt	:= '【15】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5519,12 +5570,12 @@
       <c r="AM7" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 カット動作';
+			strRt	:= '【15】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6068,15 +6119,15 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\精度を高める\rtc\[20260130_1906_幅50巻.xlsx]Sheet1 によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6084,12 +6135,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6097,12 +6148,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給開始動作';
+			strRt	:= '【13】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6110,12 +6161,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給動作';
+			strRt	:= '【14】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6123,12 +6174,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 カット動作';
+			strRt	:= '【15】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6141,12 +6192,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6154,12 +6205,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6167,12 +6218,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= '【23】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6180,12 +6231,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= '【24】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6193,12 +6244,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+			strRt	:= '【25】 Cut operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6211,12 +6275,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6224,12 +6288,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6237,12 +6301,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6255,12 +6319,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6268,12 +6332,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6281,12 +6345,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6294,12 +6358,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6307,12 +6371,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6320,12 +6384,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6338,12 +6402,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6351,12 +6415,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6364,12 +6428,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6382,12 +6446,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6395,12 +6459,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 計測準備';
+			strRt	:= '【62】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6408,12 +6472,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= '【63】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6421,12 +6485,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 排出動作';
+			strRt	:= '【64】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6462,15 +6526,15 @@
       </c>
       <c r="K13" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="L13" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="N13" t="str">
         <f ca="1"/>
-        <v>【21】 原点復帰動作</v>
+        <v>【21】 Return to origin operation</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -6502,7 +6566,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC13" t="str">
@@ -6510,7 +6574,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -6519,20 +6583,20 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF13" t="str">
@@ -6540,24 +6604,24 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';</v>
+			strRt	:= '【21】 Return to origin operation';</v>
       </c>
       <c r="AG13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH13" t="str">
@@ -6565,12 +6629,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -6579,12 +6643,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6594,12 +6658,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6610,12 +6674,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6629,12 +6693,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6648,12 +6712,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6695,15 +6759,15 @@
       </c>
       <c r="K14" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="L14" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="N14" t="str">
         <f ca="1"/>
-        <v>【22】 供給準備動作</v>
+        <v>【22】 Preparation for supply operation</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -6732,75 +6796,75 @@
       <c r="AB14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Preparation for supply operation';</v>
       </c>
       <c r="AE14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';</v>
+			strRt	:= '【22】 Preparation for supply operation';</v>
       </c>
       <c r="AG14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6808,12 +6872,12 @@
       <c r="AJ14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6822,12 +6886,12 @@
       <c r="AK14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6839,12 +6903,12 @@
       <c r="AL14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6856,12 +6920,12 @@
       <c r="AM14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6892,15 +6956,15 @@
       </c>
       <c r="K15" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="L15" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="N15" t="str">
         <f ca="1"/>
-        <v>【23】 供給開始動作</v>
+        <v>【23】 Start supply operation</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -6929,75 +6993,75 @@
       <c r="AB15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';</v>
+			strRt	:= 'Start supply operation';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';</v>
+			strRt	:= '【23】 Start supply operation';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= '【23】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= '【23】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= '【23】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7005,12 +7069,12 @@
       <c r="AJ15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= '【23】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7019,12 +7083,12 @@
       <c r="AK15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= '【23】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7036,12 +7100,12 @@
       <c r="AL15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= '【23】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7053,12 +7117,12 @@
       <c r="AM15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= '【23】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7089,15 +7153,15 @@
       </c>
       <c r="K16" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply operation</v>
       </c>
       <c r="L16" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply operation</v>
       </c>
       <c r="N16" t="str">
         <f ca="1"/>
-        <v>【24】 供給動作</v>
+        <v>【24】 Supply operation</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -7126,75 +7190,75 @@
       <c r="AB16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= 'Supply operation';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';</v>
+			strRt	:= '【24】 Supply operation';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= '【24】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= '【24】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= '【24】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7202,12 +7266,12 @@
       <c r="AJ16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= '【24】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7216,12 +7280,12 @@
       <c r="AK16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= '【24】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7233,12 +7297,12 @@
       <c r="AL16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= '【24】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7250,12 +7314,12 @@
       <c r="AM16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= '【24】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7286,15 +7350,15 @@
       </c>
       <c r="K17" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="L17" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="N17" t="str">
         <f ca="1"/>
-        <v>【25】 カット動作</v>
+        <v>【25】 Cut operation</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -7323,75 +7387,75 @@
       <c r="AB17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';</v>
+			strRt	:= 'Cut operation';</v>
       </c>
       <c r="AE17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';</v>
+			strRt	:= '【25】 Cut operation';</v>
       </c>
       <c r="AG17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+			strRt	:= '【25】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+			strRt	:= '【25】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+			strRt	:= '【25】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7399,12 +7463,12 @@
       <c r="AJ17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+			strRt	:= '【25】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7413,12 +7477,12 @@
       <c r="AK17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+			strRt	:= '【25】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7430,12 +7494,12 @@
       <c r="AL17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+			strRt	:= '【25】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7447,12 +7511,12 @@
       <c r="AM17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+			strRt	:= '【25】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7478,26 +7542,26 @@
       <c r="I18" t="str">
         <v/>
       </c>
-      <c r="J18" t="str">
-        <v/>
+      <c r="J18">
+        <v>11</v>
       </c>
       <c r="K18" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Supply confirmation operation</v>
       </c>
       <c r="L18" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Supply confirmation operation</v>
       </c>
       <c r="N18" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【26】 Supply confirmation operation</v>
       </c>
       <c r="O18" t="str">
         <v/>
       </c>
       <c r="P18" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q18" t="str">
         <f ca="1"/>
@@ -7505,63 +7569,158 @@
       </c>
       <c r="R18" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';</v>
       </c>
       <c r="AE18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Supply confirmation operation';</v>
       </c>
       <c r="AG18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Supply confirmation operation';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Supply confirmation operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Supply confirmation operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Supply confirmation operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Supply confirmation operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Supply confirmation operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM18" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Supply confirmation operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.55000000000000004">
@@ -7983,7 +8142,7 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <f>F13+1</f>
@@ -8001,19 +8160,19 @@
         <v/>
       </c>
       <c r="J23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K23" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L23" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N23" t="str">
         <f ca="1"/>
-        <v>【31】 原点復帰動作</v>
+        <v>【31】 Home return operation</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -8045,7 +8204,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC23" t="str">
@@ -8053,7 +8212,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -8062,20 +8221,20 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF23" t="str">
@@ -8083,24 +8242,24 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';</v>
+			strRt	:= '【31】 Home return operation';</v>
       </c>
       <c r="AG23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH23" t="str">
@@ -8108,12 +8267,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -8122,12 +8281,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8137,12 +8296,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8153,12 +8312,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8172,12 +8331,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8191,12 +8350,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8223,19 +8382,19 @@
         <v/>
       </c>
       <c r="J24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K24" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="L24" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="N24" t="str">
         <f ca="1"/>
-        <v>【32】 供給準備動作</v>
+        <v>【32】 Supply preparation operation</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -8264,75 +8423,75 @@
       <c r="AB24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';</v>
       </c>
       <c r="AE24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';</v>
+			strRt	:= '【32】 Supply preparation operation';</v>
       </c>
       <c r="AG24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8340,12 +8499,12 @@
       <c r="AJ24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8354,12 +8513,12 @@
       <c r="AK24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8371,12 +8530,12 @@
       <c r="AL24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8388,12 +8547,12 @@
       <c r="AM24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8426,19 +8585,19 @@
         <v/>
       </c>
       <c r="J25">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>supply operation</v>
       </c>
       <c r="L25" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>supply operation</v>
       </c>
       <c r="N25" t="str">
         <f ca="1"/>
-        <v>【33】 供給動作</v>
+        <v>【33】 supply operation</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -8467,75 +8626,75 @@
       <c r="AB25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= 'supply operation';</v>
       </c>
       <c r="AE25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';</v>
+			strRt	:= '【33】 supply operation';</v>
       </c>
       <c r="AG25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8543,12 +8702,12 @@
       <c r="AJ25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8557,12 +8716,12 @@
       <c r="AK25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8574,12 +8733,12 @@
       <c r="AL25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8591,12 +8750,12 @@
       <c r="AM25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9367,19 +9526,19 @@
         <v/>
       </c>
       <c r="J33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K33" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L33" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N33" t="str">
         <f ca="1"/>
-        <v>【41】 原点復帰動作</v>
+        <v>【41】 Home return operation</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -9411,7 +9570,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC33" t="str">
@@ -9419,7 +9578,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -9428,20 +9587,20 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF33" t="str">
@@ -9449,24 +9608,24 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';</v>
+			strRt	:= '【41】 Home return operation';</v>
       </c>
       <c r="AG33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH33" t="str">
@@ -9474,12 +9633,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -9488,12 +9647,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9503,12 +9662,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9519,12 +9678,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9538,12 +9697,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9557,12 +9716,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9589,19 +9748,19 @@
         <v/>
       </c>
       <c r="J34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K34" t="str">
         <f ca="1"/>
-        <v>周長測定子プリセット</v>
+        <v>Circumference gauge preset</v>
       </c>
       <c r="L34" t="str">
         <f ca="1"/>
-        <v>周長測定子プリセット</v>
+        <v>Circumference gauge preset</v>
       </c>
       <c r="N34" t="str">
         <f ca="1"/>
-        <v>【42】 周長測定子プリセット</v>
+        <v>【42】 Circumference gauge preset</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -9630,75 +9789,75 @@
       <c r="AB34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';</v>
+			strRt	:= 'Circumference gauge preset';</v>
       </c>
       <c r="AE34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';</v>
+			strRt	:= '【42】 Circumference gauge preset';</v>
       </c>
       <c r="AG34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9706,12 +9865,12 @@
       <c r="AJ34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9720,12 +9879,12 @@
       <c r="AK34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9737,12 +9896,12 @@
       <c r="AL34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9754,12 +9913,12 @@
       <c r="AM34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9786,19 +9945,19 @@
         <v/>
       </c>
       <c r="J35">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K35" t="str">
         <f ca="1"/>
-        <v>巻き準備動作</v>
+        <v>Winding preparation operation</v>
       </c>
       <c r="L35" t="str">
         <f ca="1"/>
-        <v>巻き準備動作</v>
+        <v>Winding preparation operation</v>
       </c>
       <c r="N35" t="str">
         <f ca="1"/>
-        <v>【43】 巻き準備動作</v>
+        <v>【43】 Winding preparation operation</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -9827,75 +9986,75 @@
       <c r="AB35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';</v>
+			strRt	:= 'Winding preparation operation';</v>
       </c>
       <c r="AE35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';</v>
+			strRt	:= '【43】 Winding preparation operation';</v>
       </c>
       <c r="AG35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9903,12 +10062,12 @@
       <c r="AJ35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9917,12 +10076,12 @@
       <c r="AK35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9934,12 +10093,12 @@
       <c r="AL35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9951,12 +10110,12 @@
       <c r="AM35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9983,19 +10142,19 @@
         <v/>
       </c>
       <c r="J36">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K36" t="str">
         <f ca="1"/>
-        <v>巻き動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="L36" t="str">
         <f ca="1"/>
-        <v>巻き動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="N36" t="str">
         <f ca="1"/>
-        <v>【44】 巻き動作</v>
+        <v>【44】 Winding operation</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -10024,75 +10183,75 @@
       <c r="AB36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';</v>
+			strRt	:= 'Winding operation';</v>
       </c>
       <c r="AE36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';</v>
+			strRt	:= '【44】 Winding operation';</v>
       </c>
       <c r="AG36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10100,12 +10259,12 @@
       <c r="AJ36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10114,12 +10273,12 @@
       <c r="AK36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10131,12 +10290,12 @@
       <c r="AL36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10148,12 +10307,12 @@
       <c r="AM36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10180,19 +10339,19 @@
         <v/>
       </c>
       <c r="J37">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K37" t="str">
         <f ca="1"/>
-        <v>箔ロウ巻き動作</v>
+        <v>Foil brazing operation</v>
       </c>
       <c r="L37" t="str">
         <f ca="1"/>
-        <v>箔ロウ巻き動作</v>
+        <v>Foil brazing operation</v>
       </c>
       <c r="N37" t="str">
         <f ca="1"/>
-        <v>【45】 箔ロウ巻き動作</v>
+        <v>【45】 Foil brazing operation</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -10221,75 +10380,75 @@
       <c r="AB37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';</v>
+			strRt	:= 'Foil brazing operation';</v>
       </c>
       <c r="AE37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';</v>
+			strRt	:= '【45】 Foil brazing operation';</v>
       </c>
       <c r="AG37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10297,12 +10456,12 @@
       <c r="AJ37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10311,12 +10470,12 @@
       <c r="AK37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10328,12 +10487,12 @@
       <c r="AL37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10345,12 +10504,12 @@
       <c r="AM37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10377,19 +10536,19 @@
         <v/>
       </c>
       <c r="J38">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K38" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>Circumference measurement operation</v>
       </c>
       <c r="L38" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>Circumference measurement operation</v>
       </c>
       <c r="N38" t="str">
         <f ca="1"/>
-        <v>【46】 周長測定動作</v>
+        <v>【46】 Circumference measurement operation</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -10418,75 +10577,75 @@
       <c r="AB38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';</v>
+			strRt	:= 'Circumference measurement operation';</v>
       </c>
       <c r="AE38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';</v>
+			strRt	:= '【46】 Circumference measurement operation';</v>
       </c>
       <c r="AG38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10494,12 +10653,12 @@
       <c r="AJ38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10508,12 +10667,12 @@
       <c r="AK38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10525,12 +10684,12 @@
       <c r="AL38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10542,12 +10701,12 @@
       <c r="AM38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10988,19 +11147,19 @@
         <v/>
       </c>
       <c r="J43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L43" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N43" t="str">
         <f ca="1"/>
-        <v>【51】 原点復帰動作</v>
+        <v>【51】 Home return operation</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -11032,7 +11191,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC43" t="str">
@@ -11040,7 +11199,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -11049,20 +11208,20 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF43" t="str">
@@ -11070,24 +11229,24 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';</v>
+			strRt	:= '【51】 Home return operation';</v>
       </c>
       <c r="AG43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH43" t="str">
@@ -11095,12 +11254,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -11109,12 +11268,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11124,12 +11283,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11140,12 +11299,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11159,12 +11318,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11178,12 +11337,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11210,19 +11369,19 @@
         <v/>
       </c>
       <c r="J44">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K44" t="str">
         <f ca="1"/>
-        <v>巻き押え動作</v>
+        <v>Winding clamping operation</v>
       </c>
       <c r="L44" t="str">
         <f ca="1"/>
-        <v>巻き押え動作</v>
+        <v>Winding clamping operation</v>
       </c>
       <c r="N44" t="str">
         <f ca="1"/>
-        <v>【52】 巻き押え動作</v>
+        <v>【52】 Winding clamping operation</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -11251,75 +11410,75 @@
       <c r="AB44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';</v>
+			strRt	:= 'Winding clamping operation';</v>
       </c>
       <c r="AE44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';</v>
+			strRt	:= '【52】 Winding clamping operation';</v>
       </c>
       <c r="AG44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11327,12 +11486,12 @@
       <c r="AJ44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11341,12 +11500,12 @@
       <c r="AK44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11358,12 +11517,12 @@
       <c r="AL44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11375,12 +11534,12 @@
       <c r="AM44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11407,19 +11566,19 @@
         <v/>
       </c>
       <c r="J45">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K45" t="str">
         <f ca="1"/>
-        <v>溶接動作</v>
+        <v>Welding operation</v>
       </c>
       <c r="L45" t="str">
         <f ca="1"/>
-        <v>溶接動作</v>
+        <v>Welding operation</v>
       </c>
       <c r="N45" t="str">
         <f ca="1"/>
-        <v>【53】 溶接動作</v>
+        <v>【53】 Welding operation</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -11448,75 +11607,75 @@
       <c r="AB45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';</v>
+			strRt	:= 'Welding operation';</v>
       </c>
       <c r="AE45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';</v>
+			strRt	:= '【53】 Welding operation';</v>
       </c>
       <c r="AG45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11524,12 +11683,12 @@
       <c r="AJ45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11538,12 +11697,12 @@
       <c r="AK45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11555,12 +11714,12 @@
       <c r="AL45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11572,12 +11731,12 @@
       <c r="AM45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12324,19 +12483,19 @@
         <v/>
       </c>
       <c r="J53">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K53" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="L53" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="N53" t="str">
         <f ca="1"/>
-        <v>【61】 原点復帰動作</v>
+        <v>【61】 Return to origin operation</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -12368,7 +12527,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC53" t="str">
@@ -12376,7 +12535,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -12385,20 +12544,20 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF53" t="str">
@@ -12406,24 +12565,24 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';</v>
+			strRt	:= '【61】 Return to origin operation';</v>
       </c>
       <c r="AG53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH53" t="str">
@@ -12431,12 +12590,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -12445,12 +12604,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12460,12 +12619,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12476,12 +12635,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12495,12 +12654,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12514,12 +12673,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12546,19 +12705,19 @@
         <v/>
       </c>
       <c r="J54">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K54" t="str">
         <f ca="1"/>
-        <v>計測準備</v>
+        <v>Measurement preparation</v>
       </c>
       <c r="L54" t="str">
         <f ca="1"/>
-        <v>計測準備</v>
+        <v>Measurement preparation</v>
       </c>
       <c r="N54" t="str">
         <f ca="1"/>
-        <v>【62】 計測準備</v>
+        <v>【62】 Measurement preparation</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -12587,75 +12746,75 @@
       <c r="AB54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';</v>
+			strRt	:= 'Measurement preparation';</v>
       </c>
       <c r="AE54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 計測準備';</v>
+			strRt	:= '【62】 Measurement preparation';</v>
       </c>
       <c r="AG54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 計測準備';
+			strRt	:= '【62】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 計測準備';
+			strRt	:= '【62】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 計測準備';
+			strRt	:= '【62】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12663,12 +12822,12 @@
       <c r="AJ54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 計測準備';
+			strRt	:= '【62】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12677,12 +12836,12 @@
       <c r="AK54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 計測準備';
+			strRt	:= '【62】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12694,12 +12853,12 @@
       <c r="AL54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 計測準備';
+			strRt	:= '【62】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12711,12 +12870,12 @@
       <c r="AM54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 計測準備';
+			strRt	:= '【62】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12743,19 +12902,19 @@
         <v/>
       </c>
       <c r="J55">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K55" t="str">
         <f ca="1"/>
-        <v>巻き中測定動作</v>
+        <v>Measurement operation during winding</v>
       </c>
       <c r="L55" t="str">
         <f ca="1"/>
-        <v>巻き中測定動作</v>
+        <v>Measurement operation during winding</v>
       </c>
       <c r="N55" t="str">
         <f ca="1"/>
-        <v>【63】 巻き中測定動作</v>
+        <v>【63】 Measurement operation during winding</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -12784,75 +12943,75 @@
       <c r="AB55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';</v>
+			strRt	:= 'Measurement operation during winding';</v>
       </c>
       <c r="AE55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';</v>
+			strRt	:= '【63】 Measurement operation during winding';</v>
       </c>
       <c r="AG55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= '【63】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= '【63】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= '【63】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12860,12 +13019,12 @@
       <c r="AJ55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= '【63】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12874,12 +13033,12 @@
       <c r="AK55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= '【63】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12891,12 +13050,12 @@
       <c r="AL55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= '【63】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12908,12 +13067,12 @@
       <c r="AM55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= '【63】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12940,19 +13099,19 @@
         <v/>
       </c>
       <c r="J56">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K56" t="str">
         <f ca="1"/>
-        <v>排出動作</v>
+        <v>Discharge operation</v>
       </c>
       <c r="L56" t="str">
         <f ca="1"/>
-        <v>排出動作</v>
+        <v>Discharge operation</v>
       </c>
       <c r="N56" t="str">
         <f ca="1"/>
-        <v>【64】 排出動作</v>
+        <v>【64】 Discharge operation</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -12981,75 +13140,75 @@
       <c r="AB56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';</v>
+			strRt	:= 'Discharge operation';</v>
       </c>
       <c r="AE56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 排出動作';</v>
+			strRt	:= '【64】 Discharge operation';</v>
       </c>
       <c r="AG56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 排出動作';
+			strRt	:= '【64】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 排出動作';
+			strRt	:= '【64】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 排出動作';
+			strRt	:= '【64】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13057,12 +13216,12 @@
       <c r="AJ56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 排出動作';
+			strRt	:= '【64】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13071,12 +13230,12 @@
       <c r="AK56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 排出動作';
+			strRt	:= '【64】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13088,12 +13247,12 @@
       <c r="AL56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 排出動作';
+			strRt	:= '【64】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13105,12 +13264,12 @@
       <c r="AM56" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 排出動作';
+			strRt	:= '【64】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28021,15 +28180,15 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\精度を高める\rtc\[20260130_1906_幅50巻.xlsx]Sheet1 によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28037,12 +28196,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28050,12 +28209,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 供給開始動作';
+			strRt	:= '【13】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28063,12 +28222,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 供給動作';
+			strRt	:= '【14】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28076,12 +28235,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 カット動作';
+			strRt	:= '【15】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28094,12 +28253,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28107,12 +28266,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28120,12 +28279,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= '【23】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28133,12 +28292,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= '【24】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28146,12 +28305,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+			strRt	:= '【25】 Cut operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//Supply confirmation operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28164,12 +28336,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28177,12 +28349,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28190,12 +28362,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28208,12 +28380,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28221,12 +28393,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28234,12 +28406,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28247,12 +28419,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28260,12 +28432,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28273,12 +28445,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28291,12 +28463,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28304,12 +28476,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28317,12 +28489,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28335,12 +28507,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28348,12 +28520,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 計測準備';
+			strRt	:= '【62】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28361,12 +28533,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 巻き中測定動作';
+			strRt	:= '【63】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28374,12 +28546,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出動作
+	//Discharge operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出動作';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 排出動作';
+			strRt	:= '【64】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED407A9-B030-4436-A768-87CA48B05C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD76462-5672-4167-B396-D233B6D8FAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$90</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="118">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -661,6 +661,36 @@
   <si>
     <t>Supply confirmation operation</t>
   </si>
+  <si>
+    <t>Ｘロール部</t>
+  </si>
+  <si>
+    <t>Ｘロール部</t>
+    <rPh sb="4" eb="5">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>原点復帰</t>
+    <rPh sb="0" eb="4">
+      <t>ゲンテンフッキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>糊付け動作</t>
+    <rPh sb="0" eb="2">
+      <t>ノリヅ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Gluing operation</t>
+  </si>
 </sst>
 </file>
 
@@ -1065,7 +1095,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$97">
+    <xdr:sp macro="" textlink="$A$94">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -1434,7 +1464,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -1538,7 +1568,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="str">
-        <f t="shared" ref="D3:D63" si="0">B3&amp;C3</f>
+        <f t="shared" ref="D3:D60" si="0">B3&amp;C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="4">
@@ -1585,10 +1615,10 @@
         <v>72</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
@@ -1612,18 +1642,17 @@
         <v>1</v>
       </c>
       <c r="E5" s="4">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="9" t="s">
         <v>72</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
@@ -1648,17 +1677,17 @@
       </c>
       <c r="E6" s="4">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9" t="s">
         <v>72</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
@@ -1919,7 +1948,7 @@
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4">
-        <f t="shared" ref="C14:C93" si="8">C13</f>
+        <f t="shared" ref="C14:C90" si="8">C13</f>
         <v>3</v>
       </c>
       <c r="D14" s="4" t="str">
@@ -1927,7 +1956,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" ref="E14:E73" si="9">E13+1</f>
+        <f t="shared" ref="E14:E70" si="9">E13+1</f>
         <v>2</v>
       </c>
       <c r="F14" s="5"/>
@@ -2355,10 +2384,10 @@
         <v>77</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
@@ -2382,18 +2411,17 @@
         <v>6</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
         <v>77</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -2418,17 +2446,17 @@
       </c>
       <c r="E28" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
         <v>77</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -2456,9 +2484,15 @@
         <v>1</v>
       </c>
       <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
+      <c r="G29" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>101</v>
+      </c>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
@@ -2481,13 +2515,18 @@
         <v>7</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" ref="E30" si="19">E29+1</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
+      <c r="G30" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>117</v>
+      </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
@@ -2499,193 +2538,193 @@
       <c r="R30" s="7"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="4"/>
+      <c r="A31" s="26"/>
       <c r="B31" s="4"/>
-      <c r="C31" s="4">
+      <c r="C31" s="26">
+        <f>C29+1</f>
+        <v>8</v>
+      </c>
+      <c r="D31" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E31" s="4">
+        <f>E29</f>
+        <v>1</v>
+      </c>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="7"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="26"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="26">
+        <f t="shared" ref="C32" si="19">C31</f>
+        <v>8</v>
+      </c>
+      <c r="D32" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" ref="E32" si="20">E31+1</f>
+        <v>2</v>
+      </c>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="7"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="26"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="26">
         <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="D31" s="4" t="str">
+        <v>8</v>
+      </c>
+      <c r="D33" s="26" t="str">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E31" s="4">
+        <v>8</v>
+      </c>
+      <c r="E33" s="4">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="7"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4">
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="23"/>
+      <c r="P33" s="23"/>
+      <c r="Q33" s="23"/>
+      <c r="R33" s="7"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4">
         <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="D32" s="4" t="str">
+        <v>8</v>
+      </c>
+      <c r="D34" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E32" s="4">
+        <v>8</v>
+      </c>
+      <c r="E34" s="4">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="7"/>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4">
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4">
         <f t="shared" si="8"/>
-        <v>7</v>
-      </c>
-      <c r="D33" s="4" t="str">
+        <v>8</v>
+      </c>
+      <c r="D35" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E33" s="4">
+        <v>8</v>
+      </c>
+      <c r="E35" s="4">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="26"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="26">
-        <f t="shared" ref="C34" si="20">C29+1</f>
-        <v>8</v>
-      </c>
-      <c r="D34" s="26" t="str">
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4">
+        <f t="shared" ref="C36" si="21">C31+1</f>
+        <v>9</v>
+      </c>
+      <c r="D36" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E34" s="4">
-        <f t="shared" ref="E34" si="21">E29</f>
+        <v>9</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" ref="E36" si="22">E31</f>
         <v>1</v>
       </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="23"/>
-      <c r="P34" s="23"/>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="7"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="26"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="26">
-        <f t="shared" ref="C35" si="22">C34</f>
-        <v>8</v>
-      </c>
-      <c r="D35" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E35" s="4">
-        <f t="shared" ref="E35" si="23">E34+1</f>
-        <v>2</v>
-      </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="7"/>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="26"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="26">
-        <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="D36" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E36" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
-      </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
       <c r="R36" s="7"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4">
-        <f t="shared" si="8"/>
-        <v>8</v>
+        <f t="shared" ref="C37" si="23">C36</f>
+        <v>9</v>
       </c>
       <c r="D37" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" ref="E37" si="24">E36+1</f>
+        <v>2</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -2706,15 +2745,15 @@
       <c r="B38" s="4"/>
       <c r="C38" s="4">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E38" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -2734,7 +2773,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4">
-        <f t="shared" ref="C39" si="24">C34+1</f>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="D39" s="4" t="str">
@@ -2742,15 +2781,15 @@
         <v>9</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" ref="E39" si="25">E34</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
+      <c r="K39" s="13"/>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
@@ -2763,7 +2802,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
-        <f t="shared" ref="C40" si="26">C39</f>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="D40" s="4" t="str">
@@ -2771,8 +2810,8 @@
         <v>9</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" ref="E40" si="27">E39+1</f>
-        <v>2</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -2792,16 +2831,16 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
-        <f t="shared" si="8"/>
-        <v>9</v>
+        <f t="shared" ref="C41" si="25">C36+1</f>
+        <v>10</v>
       </c>
       <c r="D41" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E41" si="26">E36</f>
+        <v>1</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -2821,23 +2860,23 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
-        <f t="shared" si="8"/>
-        <v>9</v>
+        <f t="shared" ref="C42" si="27">C41</f>
+        <v>10</v>
       </c>
       <c r="D42" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" ref="E42" si="28">E41+1</f>
+        <v>2</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
-      <c r="K42" s="13"/>
+      <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
@@ -2851,15 +2890,15 @@
       <c r="B43" s="4"/>
       <c r="C43" s="4">
         <f t="shared" si="8"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E43" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -2879,7 +2918,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
-        <f t="shared" ref="C44" si="28">C39+1</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="D44" s="4" t="str">
@@ -2887,8 +2926,8 @@
         <v>10</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" ref="E44" si="29">E39</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -2908,7 +2947,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
-        <f t="shared" ref="C45" si="30">C44</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="D45" s="4" t="str">
@@ -2916,8 +2955,8 @@
         <v>10</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" ref="E45" si="31">E44+1</f>
-        <v>2</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -2937,16 +2976,16 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
-        <f t="shared" si="8"/>
-        <v>10</v>
+        <f t="shared" ref="C46" si="29">C41+1</f>
+        <v>11</v>
       </c>
       <c r="D46" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E46" si="30">E41</f>
+        <v>1</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -2966,16 +3005,16 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
-        <f t="shared" si="8"/>
-        <v>10</v>
+        <f t="shared" ref="C47" si="31">C46</f>
+        <v>11</v>
       </c>
       <c r="D47" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" ref="E47" si="32">E46+1</f>
+        <v>2</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -2996,15 +3035,15 @@
       <c r="B48" s="4"/>
       <c r="C48" s="4">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D48" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E48" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -3024,7 +3063,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
-        <f t="shared" ref="C49" si="32">C44+1</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="D49" s="4" t="str">
@@ -3032,8 +3071,8 @@
         <v>11</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" ref="E49" si="33">E44</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -3053,7 +3092,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <f t="shared" ref="C50" si="34">C49</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="D50" s="4" t="str">
@@ -3061,8 +3100,8 @@
         <v>11</v>
       </c>
       <c r="E50" s="4">
-        <f t="shared" ref="E50" si="35">E49+1</f>
-        <v>2</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -3082,16 +3121,16 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
-        <f t="shared" si="8"/>
-        <v>11</v>
+        <f t="shared" ref="C51" si="33">C46+1</f>
+        <v>12</v>
       </c>
       <c r="D51" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E51" si="34">E46</f>
+        <v>1</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -3111,16 +3150,16 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
-        <f t="shared" si="8"/>
-        <v>11</v>
+        <f t="shared" ref="C52" si="35">C51</f>
+        <v>12</v>
       </c>
       <c r="D52" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E52" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" ref="E52" si="36">E51+1</f>
+        <v>2</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -3141,15 +3180,15 @@
       <c r="B53" s="4"/>
       <c r="C53" s="4">
         <f t="shared" si="8"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D53" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E53" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -3169,7 +3208,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
-        <f t="shared" ref="C54" si="36">C49+1</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="D54" s="4" t="str">
@@ -3177,8 +3216,8 @@
         <v>12</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" ref="E54" si="37">E49</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -3198,7 +3237,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
-        <f t="shared" ref="C55" si="38">C54</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="D55" s="4" t="str">
@@ -3206,8 +3245,8 @@
         <v>12</v>
       </c>
       <c r="E55" s="4">
-        <f t="shared" ref="E55" si="39">E54+1</f>
-        <v>2</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -3227,16 +3266,16 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
-        <f t="shared" si="8"/>
-        <v>12</v>
+        <f t="shared" ref="C56:C86" si="37">C51+1</f>
+        <v>13</v>
       </c>
       <c r="D56" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E56" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E56" si="38">E51</f>
+        <v>1</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -3256,16 +3295,16 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4">
-        <f t="shared" si="8"/>
-        <v>12</v>
+        <f t="shared" ref="C57:C87" si="39">C56</f>
+        <v>13</v>
       </c>
       <c r="D57" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E57" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" ref="E57" si="40">E56+1</f>
+        <v>2</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -3286,15 +3325,15 @@
       <c r="B58" s="4"/>
       <c r="C58" s="4">
         <f t="shared" si="8"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D58" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E58" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -3314,7 +3353,7 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
-        <f t="shared" ref="C59:C89" si="40">C54+1</f>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="D59" s="4" t="str">
@@ -3322,8 +3361,8 @@
         <v>13</v>
       </c>
       <c r="E59" s="4">
-        <f t="shared" ref="E59" si="41">E54</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -3343,7 +3382,7 @@
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <f t="shared" ref="C60:C90" si="42">C59</f>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="D60" s="4" t="str">
@@ -3351,8 +3390,8 @@
         <v>13</v>
       </c>
       <c r="E60" s="4">
-        <f t="shared" ref="E60" si="43">E59+1</f>
-        <v>2</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -3372,16 +3411,16 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
-        <f t="shared" si="8"/>
-        <v>13</v>
+        <f t="shared" si="37"/>
+        <v>14</v>
       </c>
       <c r="D61" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f t="shared" ref="D61:D90" si="41">B61&amp;C61</f>
+        <v>14</v>
       </c>
       <c r="E61" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E61" si="42">E56</f>
+        <v>1</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -3401,16 +3440,16 @@
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
-        <f t="shared" si="8"/>
-        <v>13</v>
+        <f t="shared" si="39"/>
+        <v>14</v>
       </c>
       <c r="D62" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f t="shared" si="41"/>
+        <v>14</v>
       </c>
       <c r="E62" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" ref="E62" si="43">E61+1</f>
+        <v>2</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -3431,15 +3470,15 @@
       <c r="B63" s="4"/>
       <c r="C63" s="4">
         <f t="shared" si="8"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D63" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <f t="shared" si="41"/>
+        <v>14</v>
       </c>
       <c r="E63" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -3459,16 +3498,16 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="D64" s="4" t="str">
-        <f t="shared" ref="D64:D93" si="44">B64&amp;C64</f>
+        <f t="shared" si="41"/>
         <v>14</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" ref="E64" si="45">E59</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -3488,16 +3527,16 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="D65" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>14</v>
       </c>
       <c r="E65" s="4">
-        <f t="shared" ref="E65" si="46">E64+1</f>
-        <v>2</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -3517,16 +3556,16 @@
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4">
-        <f t="shared" si="8"/>
-        <v>14</v>
+        <f t="shared" si="37"/>
+        <v>15</v>
       </c>
       <c r="D66" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>14</v>
+        <f t="shared" si="41"/>
+        <v>15</v>
       </c>
       <c r="E66" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E66" si="44">E61</f>
+        <v>1</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -3546,16 +3585,16 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4">
-        <f t="shared" si="8"/>
-        <v>14</v>
+        <f t="shared" si="39"/>
+        <v>15</v>
       </c>
       <c r="D67" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>14</v>
+        <f t="shared" si="41"/>
+        <v>15</v>
       </c>
       <c r="E67" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" ref="E67" si="45">E66+1</f>
+        <v>2</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -3576,15 +3615,15 @@
       <c r="B68" s="4"/>
       <c r="C68" s="4">
         <f t="shared" si="8"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>14</v>
+        <f t="shared" si="41"/>
+        <v>15</v>
       </c>
       <c r="E68" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -3604,16 +3643,16 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="D69" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="E69" s="4">
-        <f t="shared" ref="E69" si="47">E64</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -3633,16 +3672,16 @@
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="D70" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>15</v>
       </c>
       <c r="E70" s="4">
-        <f t="shared" ref="E70" si="48">E69+1</f>
-        <v>2</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -3662,16 +3701,16 @@
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4">
-        <f t="shared" si="8"/>
-        <v>15</v>
+        <f t="shared" si="37"/>
+        <v>16</v>
       </c>
       <c r="D71" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>15</v>
+        <f t="shared" si="41"/>
+        <v>16</v>
       </c>
       <c r="E71" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E71" si="46">E66</f>
+        <v>1</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -3691,16 +3730,16 @@
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4">
-        <f t="shared" si="8"/>
-        <v>15</v>
+        <f t="shared" si="39"/>
+        <v>16</v>
       </c>
       <c r="D72" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>15</v>
+        <f t="shared" si="41"/>
+        <v>16</v>
       </c>
       <c r="E72" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" ref="E72:E90" si="47">E71+1</f>
+        <v>2</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -3721,15 +3760,15 @@
       <c r="B73" s="4"/>
       <c r="C73" s="4">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D73" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>15</v>
+        <f t="shared" si="41"/>
+        <v>16</v>
       </c>
       <c r="E73" s="4">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="47"/>
+        <v>3</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -3749,16 +3788,16 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="D74" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>16</v>
       </c>
       <c r="E74" s="4">
-        <f t="shared" ref="E74" si="49">E69</f>
-        <v>1</v>
+        <f t="shared" si="47"/>
+        <v>4</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -3778,16 +3817,16 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="D75" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>16</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" ref="E75:E93" si="50">E74+1</f>
-        <v>2</v>
+        <f t="shared" si="47"/>
+        <v>5</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -3807,16 +3846,16 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4">
-        <f t="shared" si="8"/>
-        <v>16</v>
+        <f t="shared" si="37"/>
+        <v>17</v>
       </c>
       <c r="D76" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>16</v>
+        <f t="shared" si="41"/>
+        <v>17</v>
       </c>
       <c r="E76" s="4">
-        <f t="shared" si="50"/>
-        <v>3</v>
+        <f t="shared" ref="E76" si="48">E71</f>
+        <v>1</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -3836,16 +3875,16 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4">
-        <f t="shared" si="8"/>
-        <v>16</v>
+        <f t="shared" si="39"/>
+        <v>17</v>
       </c>
       <c r="D77" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>16</v>
+        <f t="shared" si="41"/>
+        <v>17</v>
       </c>
       <c r="E77" s="4">
-        <f t="shared" si="50"/>
-        <v>4</v>
+        <f t="shared" ref="E77" si="49">E76+1</f>
+        <v>2</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -3866,15 +3905,15 @@
       <c r="B78" s="4"/>
       <c r="C78" s="4">
         <f t="shared" si="8"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D78" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>16</v>
+        <f t="shared" si="41"/>
+        <v>17</v>
       </c>
       <c r="E78" s="4">
-        <f t="shared" si="50"/>
-        <v>5</v>
+        <f t="shared" si="47"/>
+        <v>3</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -3894,16 +3933,16 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="D79" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>17</v>
       </c>
       <c r="E79" s="4">
-        <f t="shared" ref="E79" si="51">E74</f>
-        <v>1</v>
+        <f t="shared" si="47"/>
+        <v>4</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -3923,16 +3962,16 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="D80" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>17</v>
       </c>
       <c r="E80" s="4">
-        <f t="shared" ref="E80" si="52">E79+1</f>
-        <v>2</v>
+        <f t="shared" si="47"/>
+        <v>5</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -3952,16 +3991,16 @@
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4">
-        <f t="shared" si="8"/>
-        <v>17</v>
+        <f t="shared" si="37"/>
+        <v>18</v>
       </c>
       <c r="D81" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>17</v>
+        <f t="shared" si="41"/>
+        <v>18</v>
       </c>
       <c r="E81" s="4">
-        <f t="shared" si="50"/>
-        <v>3</v>
+        <f t="shared" ref="E81" si="50">E76</f>
+        <v>1</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -3981,16 +4020,16 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4">
-        <f t="shared" si="8"/>
-        <v>17</v>
+        <f t="shared" si="39"/>
+        <v>18</v>
       </c>
       <c r="D82" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>17</v>
+        <f t="shared" si="41"/>
+        <v>18</v>
       </c>
       <c r="E82" s="4">
-        <f t="shared" si="50"/>
-        <v>4</v>
+        <f t="shared" ref="E82" si="51">E81+1</f>
+        <v>2</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -4011,15 +4050,15 @@
       <c r="B83" s="4"/>
       <c r="C83" s="4">
         <f t="shared" si="8"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D83" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>17</v>
+        <f t="shared" si="41"/>
+        <v>18</v>
       </c>
       <c r="E83" s="4">
-        <f t="shared" si="50"/>
-        <v>5</v>
+        <f t="shared" si="47"/>
+        <v>3</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -4039,16 +4078,16 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="D84" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>18</v>
       </c>
       <c r="E84" s="4">
-        <f t="shared" ref="E84" si="53">E79</f>
-        <v>1</v>
+        <f t="shared" si="47"/>
+        <v>4</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
@@ -4068,16 +4107,16 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="D85" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>18</v>
       </c>
       <c r="E85" s="4">
-        <f t="shared" ref="E85" si="54">E84+1</f>
-        <v>2</v>
+        <f t="shared" si="47"/>
+        <v>5</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
@@ -4097,16 +4136,16 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4">
-        <f t="shared" si="8"/>
-        <v>18</v>
+        <f t="shared" si="37"/>
+        <v>19</v>
       </c>
       <c r="D86" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>18</v>
+        <f t="shared" si="41"/>
+        <v>19</v>
       </c>
       <c r="E86" s="4">
-        <f t="shared" si="50"/>
-        <v>3</v>
+        <f t="shared" ref="E86" si="52">E81</f>
+        <v>1</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
@@ -4126,16 +4165,16 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4">
-        <f t="shared" si="8"/>
-        <v>18</v>
+        <f t="shared" si="39"/>
+        <v>19</v>
       </c>
       <c r="D87" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>18</v>
+        <f t="shared" si="41"/>
+        <v>19</v>
       </c>
       <c r="E87" s="4">
-        <f t="shared" si="50"/>
-        <v>4</v>
+        <f t="shared" ref="E87" si="53">E86+1</f>
+        <v>2</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -4156,15 +4195,15 @@
       <c r="B88" s="4"/>
       <c r="C88" s="4">
         <f t="shared" si="8"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D88" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>18</v>
+        <f t="shared" si="41"/>
+        <v>19</v>
       </c>
       <c r="E88" s="4">
-        <f t="shared" si="50"/>
-        <v>5</v>
+        <f t="shared" si="47"/>
+        <v>3</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
@@ -4184,16 +4223,16 @@
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4">
-        <f t="shared" si="40"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="D89" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>19</v>
       </c>
       <c r="E89" s="4">
-        <f t="shared" ref="E89" si="55">E84</f>
-        <v>1</v>
+        <f t="shared" si="47"/>
+        <v>4</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
@@ -4213,16 +4252,16 @@
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="D90" s="4" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="41"/>
         <v>19</v>
       </c>
       <c r="E90" s="4">
-        <f t="shared" ref="E90" si="56">E89+1</f>
-        <v>2</v>
+        <f t="shared" si="47"/>
+        <v>5</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
@@ -4239,181 +4278,94 @@
       <c r="R90" s="7"/>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4">
-        <f t="shared" si="8"/>
-        <v>19</v>
-      </c>
-      <c r="D91" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>19</v>
-      </c>
-      <c r="E91" s="4">
-        <f t="shared" si="50"/>
-        <v>3</v>
-      </c>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
-      <c r="H91" s="5"/>
-      <c r="I91" s="5"/>
-      <c r="J91" s="5"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="5"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
-      <c r="O91" s="7"/>
-      <c r="P91" s="7"/>
-      <c r="Q91" s="7"/>
-      <c r="R91" s="7"/>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4">
-        <f t="shared" si="8"/>
-        <v>19</v>
-      </c>
-      <c r="D92" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>19</v>
-      </c>
-      <c r="E92" s="4">
-        <f t="shared" si="50"/>
-        <v>4</v>
-      </c>
-      <c r="F92" s="5"/>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
-      <c r="I92" s="5"/>
-      <c r="J92" s="5"/>
-      <c r="K92" s="5"/>
-      <c r="L92" s="5"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
-      <c r="O92" s="7"/>
-      <c r="P92" s="7"/>
-      <c r="Q92" s="7"/>
-      <c r="R92" s="7"/>
+      <c r="A91" s="15"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="16"/>
+      <c r="G91" s="16"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="16"/>
+      <c r="J91" s="16"/>
+      <c r="K91" s="16"/>
+      <c r="L91" s="16"/>
+      <c r="M91" s="16"/>
+      <c r="N91" s="16"/>
+      <c r="O91" s="17"/>
+      <c r="P91" s="17"/>
+      <c r="Q91" s="17"/>
+      <c r="R91" s="17"/>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4">
-        <f t="shared" si="8"/>
-        <v>19</v>
-      </c>
-      <c r="D93" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>19</v>
-      </c>
-      <c r="E93" s="4">
-        <f t="shared" si="50"/>
-        <v>5</v>
-      </c>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
-      <c r="I93" s="5"/>
-      <c r="J93" s="5"/>
-      <c r="K93" s="5"/>
-      <c r="L93" s="5"/>
-      <c r="M93" s="5"/>
-      <c r="N93" s="5"/>
-      <c r="O93" s="7"/>
-      <c r="P93" s="7"/>
-      <c r="Q93" s="7"/>
-      <c r="R93" s="7"/>
+      <c r="A93" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="15"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="15"/>
-      <c r="D94" s="15"/>
-      <c r="E94" s="15"/>
-      <c r="F94" s="16"/>
-      <c r="G94" s="16"/>
-      <c r="H94" s="16"/>
-      <c r="I94" s="16"/>
-      <c r="J94" s="16"/>
-      <c r="K94" s="16"/>
-      <c r="L94" s="16"/>
-      <c r="M94" s="16"/>
-      <c r="N94" s="16"/>
-      <c r="O94" s="17"/>
-      <c r="P94" s="17"/>
-      <c r="Q94" s="17"/>
-      <c r="R94" s="17"/>
+      <c r="A94">
+        <f>MAX(A$2:A$91)</f>
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <f>MAX(F$2:F$91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" t="s">
+        <v>40</v>
+      </c>
+      <c r="D95" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97">
-        <f>MAX(A$2:A$94)</f>
+      <c r="A96">
+        <f>ROW(A92)-ROW(A1)-1</f>
+        <v>90</v>
+      </c>
+      <c r="D96">
+        <f>COUNTIF(D$2:D$91,D95)</f>
         <v>0</v>
       </c>
-      <c r="F97">
-        <f>MAX(F$2:F$94)</f>
+      <c r="E96" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$91,$D$2:$D$91,E95)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" t="s">
-        <v>40</v>
-      </c>
-      <c r="D98" t="s">
-        <v>14</v>
-      </c>
-      <c r="E98" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99">
-        <f>ROW(A95)-ROW(A1)-1</f>
-        <v>93</v>
-      </c>
-      <c r="D99">
-        <f>COUNTIF(D$2:D$94,D98)</f>
+    <row r="97" spans="4:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="4:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D98">
+        <f>COUNTIF(D$2:D$91,D97)</f>
         <v>0</v>
       </c>
-      <c r="E99" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$94,$D$2:$D$94,E98)</f>
+      <c r="E98" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$91,$D$2:$D$91,E97)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D100" t="s">
-        <v>12</v>
-      </c>
-      <c r="E100" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D101">
-        <f>COUNTIF(D$2:D$94,D100)</f>
-        <v>0</v>
-      </c>
-      <c r="E101" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$94,$D$2:$D$94,E100)</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:R93" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R93">
-      <sortCondition ref="D1:D93"/>
+  <autoFilter ref="A1:R90" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R90">
+      <sortCondition ref="D1:D90"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:R94">
+  <conditionalFormatting sqref="A2:R91">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
@@ -4569,7 +4521,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\精度を高める\rtc\[20260130_1906_幅50巻.xlsx]Sheet1</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -4583,11 +4535,11 @@
         <v>1</v>
       </c>
       <c r="J3" cm="1">
-        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$94&amp;info_index!$E$2:$E$94,0),"")</f>
+        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$91&amp;info_index!$E$2:$E$91,0),"")</f>
         <v>1</v>
       </c>
       <c r="K3" t="str" cm="1">
-        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$94,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$94&amp;info_index!$E$2:$E$94,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$91,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$91&amp;info_index!$E$2:$E$91,0),1)&amp;"","")</f>
         <v>Return to origin operation</v>
       </c>
       <c r="L3" t="str" cm="1">
@@ -4599,7 +4551,7 @@
         <v>【11】 Return to origin operation</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$94,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$94&amp;info_index!$E$2:$E$94,0),1)&amp;"","")</f>
+        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$91,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$91&amp;info_index!$E$2:$E$91,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="P3" t="str" cm="1">
@@ -4607,7 +4559,7 @@
         <v>unknown</v>
       </c>
       <c r="Q3" t="str" cm="1">
-        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$94,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$94&amp;info_index!$E$2:$E$94,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$91,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$91&amp;info_index!$E$2:$E$91,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="R3" t="str" cm="1">
@@ -4981,7 +4933,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\精度を高める\rtc\[20260130_1906_幅50巻.xlsx]Sheet1 によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -5003,15 +4955,15 @@
       </c>
       <c r="K5" t="str">
         <f ca="1"/>
-        <v>Start supply operation</v>
+        <v>Cut operation</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>Start supply operation</v>
+        <v>Cut operation</v>
       </c>
       <c r="N5" t="str">
         <f ca="1"/>
-        <v>【13】 Start supply operation</v>
+        <v>【13】 Cut operation</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -5040,75 +4992,75 @@
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';</v>
+			strRt	:= 'Cut operation';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Start supply operation';</v>
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Start supply operation';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Start supply operation';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Start supply operation';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5116,12 +5068,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Start supply operation';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5130,12 +5082,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Start supply operation';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5147,12 +5099,12 @@
       <c r="AL5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Start supply operation';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5164,12 +5116,12 @@
       <c r="AM5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Start supply operation';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5201,144 +5153,360 @@
       <c r="I6" t="str">
         <v/>
       </c>
-      <c r="J6">
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AL6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AM6" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <f>COUNTIF(G$3:G7,G7)</f>
+        <v>5</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="Z7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AB7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AC7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AD7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AF7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AG7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AI7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AJ7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AK7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AL7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="AM7" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" ref="G8:G12" si="2">E8&amp;F8</f>
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <f>COUNTIF(G$3:G8,G8)</f>
+        <v>6</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8">
         <v>4</v>
       </c>
-      <c r="K6" t="str">
-        <f ca="1"/>
-        <v>Supply operation</v>
-      </c>
-      <c r="L6" t="str">
-        <f ca="1"/>
-        <v>Supply operation</v>
-      </c>
-      <c r="N6" t="str">
-        <f ca="1"/>
-        <v>【14】 Supply operation</v>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
+      <c r="K8" t="str">
+        <f ca="1"/>
+        <v>Start supply operation</v>
+      </c>
+      <c r="L8" t="str">
+        <f ca="1"/>
+        <v>Start supply operation</v>
+      </c>
+      <c r="N8" t="str">
+        <f ca="1"/>
+        <v>【16】 Start supply operation</v>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
         <v>unknown</v>
       </c>
-      <c r="Q6" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="R6" t="str">
+      <c r="Q8" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="R8" t="str">
         <f ca="1"/>
         <v>unknown</v>
       </c>
-      <c r="Z6" t="str">
+      <c r="Z8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="AA6" t="str">
+      <c r="AA8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="AB6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN</v>
-      </c>
-      <c r="AC6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
+      <c r="AB8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN</v>
+      </c>
+      <c r="AC8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
-      <c r="AD6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';</v>
-      </c>
-      <c r="AE6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+      <c r="AD8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';</v>
+      </c>
+      <c r="AE8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
-      <c r="AF6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply operation';</v>
-      </c>
-      <c r="AG6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply operation';
+      <c r="AF8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';</v>
+      </c>
+      <c r="AG8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
-      <c r="AH6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply operation';
+      <c r="AH8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AI6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply operation';
+      <c r="AI8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
-      <c r="AJ6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply operation';
+      <c r="AJ8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AK6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply operation';
+      <c r="AK8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5347,15 +5515,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AL6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply operation';
+      <c r="AL8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5364,15 +5532,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AM6" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply operation';
+      <c r="AM8" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5382,166 +5550,166 @@
 		END_IF;</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G7" t="str">
-        <f t="shared" si="0"/>
+      <c r="G9" t="str">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H7">
-        <f>COUNTIF(G$3:G7,G7)</f>
+      <c r="H9">
+        <f>COUNTIF(G$3:G9,G9)</f>
+        <v>7</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9">
         <v>5</v>
       </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7" t="str">
-        <f ca="1"/>
-        <v>Cut operation</v>
-      </c>
-      <c r="L7" t="str">
-        <f ca="1"/>
-        <v>Cut operation</v>
-      </c>
-      <c r="N7" t="str">
-        <f ca="1"/>
-        <v>【15】 Cut operation</v>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
+      <c r="K9" t="str">
+        <f ca="1"/>
+        <v>Supply operation</v>
+      </c>
+      <c r="L9" t="str">
+        <f ca="1"/>
+        <v>Supply operation</v>
+      </c>
+      <c r="N9" t="str">
+        <f ca="1"/>
+        <v>【17】 Supply operation</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
         <v>unknown</v>
       </c>
-      <c r="Q7" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="R7" t="str">
+      <c r="Q9" t="str">
+        <f ca="1"/>
+        <v/>
+      </c>
+      <c r="R9" t="str">
         <f ca="1"/>
         <v>unknown</v>
       </c>
-      <c r="Z7" t="str">
+      <c r="Z9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="AA7" t="str">
+      <c r="AA9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 </v>
       </c>
-      <c r="AB7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN</v>
-      </c>
-      <c r="AC7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
+      <c r="AB9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN</v>
+      </c>
+      <c r="AC9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
-      <c r="AD7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';</v>
-      </c>
-      <c r="AE7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
+      <c r="AD9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';</v>
+      </c>
+      <c r="AE9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
-      <c r="AF7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Cut operation';</v>
-      </c>
-      <c r="AG7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Cut operation';
+      <c r="AF9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';</v>
+      </c>
+      <c r="AG9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
-      <c r="AH7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Cut operation';
+      <c r="AH9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AI7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Cut operation';
+      <c r="AI9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
-      <c r="AJ7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Cut operation';
+      <c r="AJ9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
 			strRt	:= 'unknown';</v>
       </c>
-      <c r="AK7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Cut operation';
+      <c r="AK9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5550,15 +5718,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AL7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Cut operation';
+      <c r="AL9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5567,15 +5735,15 @@
 			uiErrCode	:= 3;
 		END_IF;</v>
       </c>
-      <c r="AM7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Cut operation';
+      <c r="AM9" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5583,222 +5751,6 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;</v>
-      </c>
-    </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G8" t="str">
-        <f t="shared" ref="G8:G12" si="2">E8&amp;F8</f>
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <f>COUNTIF(G$3:G8,G8)</f>
-        <v>6</v>
-      </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="R8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AL8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AM8" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G9" t="str">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <f>COUNTIF(G$3:G9,G9)</f>
-        <v>7</v>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="N9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-      <c r="Q9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="R9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="Z9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AA9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AB9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AC9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AD9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AE9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AF9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AG9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AH9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AI9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AJ9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AK9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AL9" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="AM9" t="str">
-        <f ca="1"/>
-        <v/>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.55000000000000004">
@@ -6119,7 +6071,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\精度を高める\rtc\[20260130_1906_幅50巻.xlsx]Sheet1 によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//Return to origin operation
@@ -6148,12 +6100,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
+	//Cut operation
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
 	//Start supply operation
-	ELSIF uiInfoIdx = 3 THEN
+	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Start supply operation';
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6162,24 +6127,11 @@
 			uiErrCode	:= 3;
 		END_IF;
 	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
+	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply operation';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Cut operation';
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6459,12 +6411,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
+	//Discharge operation
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
 	//Measurement preparation
-	ELSIF uiInfoIdx = 2 THEN
+	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Measurement preparation';
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6473,11 +6438,11 @@
 			uiErrCode	:= 3;
 		END_IF;
 	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
+	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Measurement operation during winding';
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6485,12 +6450,30 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12709,15 +12692,15 @@
       </c>
       <c r="K54" t="str">
         <f ca="1"/>
-        <v>Measurement preparation</v>
+        <v>Discharge operation</v>
       </c>
       <c r="L54" t="str">
         <f ca="1"/>
-        <v>Measurement preparation</v>
+        <v>Discharge operation</v>
       </c>
       <c r="N54" t="str">
         <f ca="1"/>
-        <v>【62】 Measurement preparation</v>
+        <v>【62】 Discharge operation</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -12746,75 +12729,75 @@
       <c r="AB54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';</v>
+			strRt	:= 'Discharge operation';</v>
       </c>
       <c r="AE54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
+			strRt	:= 'Discharge operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Measurement preparation';</v>
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge operation';</v>
       </c>
       <c r="AG54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Measurement preparation';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Measurement preparation';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Measurement preparation';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12822,12 +12805,12 @@
       <c r="AJ54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Measurement preparation';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12836,12 +12819,12 @@
       <c r="AK54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Measurement preparation';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12853,12 +12836,12 @@
       <c r="AL54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Measurement preparation';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12870,12 +12853,12 @@
       <c r="AM54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//Discharge operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Measurement preparation';
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12901,26 +12884,26 @@
       <c r="I55" t="str">
         <v/>
       </c>
-      <c r="J55">
-        <v>26</v>
+      <c r="J55" t="str">
+        <v/>
       </c>
       <c r="K55" t="str">
         <f ca="1"/>
-        <v>Measurement operation during winding</v>
+        <v/>
       </c>
       <c r="L55" t="str">
         <f ca="1"/>
-        <v>Measurement operation during winding</v>
+        <v/>
       </c>
       <c r="N55" t="str">
         <f ca="1"/>
-        <v>【63】 Measurement operation during winding</v>
+        <v/>
       </c>
       <c r="O55" t="str">
         <v/>
       </c>
       <c r="P55" t="str">
-        <v>unknown</v>
+        <v/>
       </c>
       <c r="Q55" t="str">
         <f ca="1"/>
@@ -12928,158 +12911,63 @@
       </c>
       <c r="R55" t="str">
         <f ca="1"/>
-        <v>unknown</v>
+        <v/>
       </c>
       <c r="Z55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-</v>
+        <v/>
       </c>
       <c r="AA55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-</v>
+        <v/>
       </c>
       <c r="AB55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN</v>
+        <v/>
       </c>
       <c r="AC55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN</v>
+        <v/>
       </c>
       <c r="AD55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';</v>
+        <v/>
       </c>
       <c r="AE55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN</v>
+        <v/>
       </c>
       <c r="AF55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Measurement operation during winding';</v>
+        <v/>
       </c>
       <c r="AG55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Measurement operation during winding';
-		ELSIF strInfoKey = 'model' THEN</v>
+        <v/>
       </c>
       <c r="AH55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Measurement operation during winding';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';</v>
+        <v/>
       </c>
       <c r="AI55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Measurement operation during winding';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN</v>
+        <v/>
       </c>
       <c r="AJ55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Measurement operation during winding';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';</v>
+        <v/>
       </c>
       <c r="AK55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Measurement operation during winding';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;</v>
+        <v/>
       </c>
       <c r="AL55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Measurement operation during winding';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;</v>
+        <v/>
       </c>
       <c r="AM55" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Measurement operation during winding';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;</v>
+        <v/>
       </c>
     </row>
     <row r="56" spans="6:39" x14ac:dyDescent="0.55000000000000004">
@@ -13098,26 +12986,26 @@
       <c r="I56" t="str">
         <v/>
       </c>
-      <c r="J56">
-        <v>27</v>
+      <c r="J56" t="str">
+        <v/>
       </c>
       <c r="K56" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v/>
       </c>
       <c r="L56" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v/>
       </c>
       <c r="N56" t="str">
         <f ca="1"/>
-        <v>【64】 Discharge operation</v>
+        <v/>
       </c>
       <c r="O56" t="str">
         <v/>
       </c>
       <c r="P56" t="str">
-        <v>unknown</v>
+        <v/>
       </c>
       <c r="Q56" t="str">
         <f ca="1"/>
@@ -13125,158 +13013,63 @@
       </c>
       <c r="R56" t="str">
         <f ca="1"/>
-        <v>unknown</v>
+        <v/>
       </c>
       <c r="Z56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-</v>
+        <v/>
       </c>
       <c r="AA56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-</v>
+        <v/>
       </c>
       <c r="AB56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN</v>
+        <v/>
       </c>
       <c r="AC56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN</v>
+        <v/>
       </c>
       <c r="AD56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';</v>
+        <v/>
       </c>
       <c r="AE56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN</v>
+        <v/>
       </c>
       <c r="AF56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';</v>
+        <v/>
       </c>
       <c r="AG56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
-		ELSIF strInfoKey = 'model' THEN</v>
+        <v/>
       </c>
       <c r="AH56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';</v>
+        <v/>
       </c>
       <c r="AI56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN</v>
+        <v/>
       </c>
       <c r="AJ56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';</v>
+        <v/>
       </c>
       <c r="AK56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;</v>
+        <v/>
       </c>
       <c r="AL56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;</v>
+        <v/>
       </c>
       <c r="AM56" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;</v>
+        <v/>
       </c>
     </row>
     <row r="57" spans="6:39" x14ac:dyDescent="0.55000000000000004">
@@ -13397,26 +13190,26 @@
       <c r="I58" t="str">
         <v/>
       </c>
-      <c r="J58" t="str">
-        <v/>
+      <c r="J58">
+        <v>26</v>
       </c>
       <c r="K58" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Measurement preparation</v>
       </c>
       <c r="L58" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Measurement preparation</v>
       </c>
       <c r="N58" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【66】 Measurement preparation</v>
       </c>
       <c r="O58" t="str">
         <v/>
       </c>
       <c r="P58" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q58" t="str">
         <f ca="1"/>
@@ -13424,63 +13217,158 @@
       </c>
       <c r="R58" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement preparation';</v>
       </c>
       <c r="AE58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';</v>
       </c>
       <c r="AG58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM58" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement preparation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="59" spans="6:39" x14ac:dyDescent="0.55000000000000004">
@@ -13499,26 +13387,26 @@
       <c r="I59" t="str">
         <v/>
       </c>
-      <c r="J59" t="str">
-        <v/>
+      <c r="J59">
+        <v>27</v>
       </c>
       <c r="K59" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Measurement operation during winding</v>
       </c>
       <c r="L59" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Measurement operation during winding</v>
       </c>
       <c r="N59" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【67】 Measurement operation during winding</v>
       </c>
       <c r="O59" t="str">
         <v/>
       </c>
       <c r="P59" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q59" t="str">
         <f ca="1"/>
@@ -13526,63 +13414,158 @@
       </c>
       <c r="R59" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement operation during winding';</v>
       </c>
       <c r="AE59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';</v>
       </c>
       <c r="AG59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM59" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Measurement operation during winding
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="60" spans="6:39" x14ac:dyDescent="0.55000000000000004">
@@ -13803,7 +13786,7 @@
         <v>10</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>●</v>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -13884,49 +13867,55 @@
       </c>
       <c r="AL62" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;</v>
       </c>
       <c r="AM62" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;</v>
       </c>
     </row>
     <row r="63" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F63">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <f>F53+1</f>
+        <v>7</v>
       </c>
       <c r="G63" t="str">
         <f t="shared" ref="G63:G96" si="5">E63&amp;F63</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H63">
         <f>COUNTIF(G$3:G63,G63)</f>
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I63" t="str">
         <v/>
       </c>
-      <c r="J63" t="str">
-        <v/>
+      <c r="J63">
+        <v>28</v>
       </c>
       <c r="K63" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Return to origin operation</v>
       </c>
       <c r="L63" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Return to origin operation</v>
       </c>
       <c r="N63" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【71】 Return to origin operation</v>
       </c>
       <c r="O63" t="str">
         <v/>
       </c>
       <c r="P63" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q63" t="str">
         <f ca="1"/>
@@ -13934,77 +13923,197 @@
       </c>
       <c r="R63" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7</v>
       </c>
       <c r="AA63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN</v>
       </c>
       <c r="AB63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';</v>
       </c>
       <c r="AG63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM63" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="64" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F64">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G64" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H64">
         <f>COUNTIF(G$3:G64,G64)</f>
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -14098,15 +14207,15 @@
     <row r="65" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F65">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G65" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H65">
         <f>COUNTIF(G$3:G65,G65)</f>
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -14200,15 +14309,15 @@
     <row r="66" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F66">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G66" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H66">
         <f>COUNTIF(G$3:G66,G66)</f>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -14302,15 +14411,15 @@
     <row r="67" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F67">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G67" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H67">
         <f>COUNTIF(G$3:G67,G67)</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -14404,39 +14513,39 @@
     <row r="68" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F68">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G68" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H68">
         <f>COUNTIF(G$3:G68,G68)</f>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I68" t="str">
         <v/>
       </c>
-      <c r="J68" t="str">
-        <v/>
+      <c r="J68">
+        <v>29</v>
       </c>
       <c r="K68" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Gluing operation</v>
       </c>
       <c r="L68" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Gluing operation</v>
       </c>
       <c r="N68" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【76】 Gluing operation</v>
       </c>
       <c r="O68" t="str">
         <v/>
       </c>
       <c r="P68" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q68" t="str">
         <f ca="1"/>
@@ -14444,77 +14553,172 @@
       </c>
       <c r="R68" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';</v>
       </c>
       <c r="AE68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';</v>
       </c>
       <c r="AG68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM68" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="69" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F69">
         <f t="shared" ref="F69:F132" si="6">F68</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G69" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H69">
         <f>COUNTIF(G$3:G69,G69)</f>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -14608,15 +14812,15 @@
     <row r="70" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F70">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G70" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H70">
         <f>COUNTIF(G$3:G70,G70)</f>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -14710,15 +14914,15 @@
     <row r="71" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F71">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G71" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H71">
         <f>COUNTIF(G$3:G71,G71)</f>
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -14812,15 +15016,15 @@
     <row r="72" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F72">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G72" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H72">
         <f>COUNTIF(G$3:G72,G72)</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -14914,15 +15118,15 @@
     <row r="73" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F73">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G73" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H73">
         <f>COUNTIF(G$3:G73,G73)</f>
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -15016,15 +15220,15 @@
     <row r="74" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F74">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G74" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H74">
         <f>COUNTIF(G$3:G74,G74)</f>
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -15118,15 +15322,15 @@
     <row r="75" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F75">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G75" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H75">
         <f>COUNTIF(G$3:G75,G75)</f>
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -15220,15 +15424,15 @@
     <row r="76" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F76">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G76" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H76">
         <f>COUNTIF(G$3:G76,G76)</f>
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -15322,15 +15526,15 @@
     <row r="77" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F77">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G77" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H77">
         <f>COUNTIF(G$3:G77,G77)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -15424,15 +15628,15 @@
     <row r="78" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F78">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G78" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H78">
         <f>COUNTIF(G$3:G78,G78)</f>
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -15526,15 +15730,15 @@
     <row r="79" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F79">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G79" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H79">
         <f>COUNTIF(G$3:G79,G79)</f>
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -15628,15 +15832,15 @@
     <row r="80" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F80">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G80" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H80">
         <f>COUNTIF(G$3:G80,G80)</f>
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -15730,15 +15934,15 @@
     <row r="81" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F81">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G81" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H81">
         <f>COUNTIF(G$3:G81,G81)</f>
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -15832,15 +16036,15 @@
     <row r="82" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F82">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G82" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H82">
         <f>COUNTIF(G$3:G82,G82)</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -15934,15 +16138,15 @@
     <row r="83" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F83">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G83" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H83">
         <f>COUNTIF(G$3:G83,G83)</f>
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -16036,15 +16240,15 @@
     <row r="84" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F84">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G84" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H84">
         <f>COUNTIF(G$3:G84,G84)</f>
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -16138,15 +16342,15 @@
     <row r="85" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F85">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G85" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H85">
         <f>COUNTIF(G$3:G85,G85)</f>
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -16240,15 +16444,15 @@
     <row r="86" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F86">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G86" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H86">
         <f>COUNTIF(G$3:G86,G86)</f>
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -16342,15 +16546,15 @@
     <row r="87" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F87">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G87" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H87">
         <f>COUNTIF(G$3:G87,G87)</f>
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -16444,15 +16648,15 @@
     <row r="88" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F88">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G88" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H88">
         <f>COUNTIF(G$3:G88,G88)</f>
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -16546,15 +16750,15 @@
     <row r="89" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F89">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G89" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H89">
         <f>COUNTIF(G$3:G89,G89)</f>
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -16648,15 +16852,15 @@
     <row r="90" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F90">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G90" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H90">
         <f>COUNTIF(G$3:G90,G90)</f>
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -16750,15 +16954,15 @@
     <row r="91" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F91">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G91" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H91">
         <f>COUNTIF(G$3:G91,G91)</f>
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -16852,15 +17056,15 @@
     <row r="92" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F92">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G92" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H92">
         <f>COUNTIF(G$3:G92,G92)</f>
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -16954,15 +17158,15 @@
     <row r="93" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F93">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G93" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H93">
         <f>COUNTIF(G$3:G93,G93)</f>
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -17056,15 +17260,15 @@
     <row r="94" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F94">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G94" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H94">
         <f>COUNTIF(G$3:G94,G94)</f>
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -17158,15 +17362,15 @@
     <row r="95" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F95">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G95" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H95">
         <f>COUNTIF(G$3:G95,G95)</f>
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -17260,15 +17464,15 @@
     <row r="96" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F96">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G96" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H96">
         <f>COUNTIF(G$3:G96,G96)</f>
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -17362,15 +17566,15 @@
     <row r="97" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F97">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G97" t="str">
         <f t="shared" ref="G97:G160" si="7">E97&amp;F97</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H97">
         <f>COUNTIF(G$3:G97,G97)</f>
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -17464,15 +17668,15 @@
     <row r="98" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F98">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G98" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H98">
         <f>COUNTIF(G$3:G98,G98)</f>
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -17566,15 +17770,15 @@
     <row r="99" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F99">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G99" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H99">
         <f>COUNTIF(G$3:G99,G99)</f>
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -17668,15 +17872,15 @@
     <row r="100" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F100">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G100" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H100">
         <f>COUNTIF(G$3:G100,G100)</f>
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -17770,15 +17974,15 @@
     <row r="101" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F101">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G101" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H101">
         <f>COUNTIF(G$3:G101,G101)</f>
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -17872,15 +18076,15 @@
     <row r="102" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F102">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G102" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H102">
         <f>COUNTIF(G$3:G102,G102)</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -17974,15 +18178,15 @@
     <row r="103" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F103">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G103" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H103">
         <f>COUNTIF(G$3:G103,G103)</f>
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -18076,15 +18280,15 @@
     <row r="104" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F104">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G104" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H104">
         <f>COUNTIF(G$3:G104,G104)</f>
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -18178,15 +18382,15 @@
     <row r="105" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F105">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G105" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H105">
         <f>COUNTIF(G$3:G105,G105)</f>
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -18280,15 +18484,15 @@
     <row r="106" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F106">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G106" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H106">
         <f>COUNTIF(G$3:G106,G106)</f>
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -18382,15 +18586,15 @@
     <row r="107" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F107">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G107" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H107">
         <f>COUNTIF(G$3:G107,G107)</f>
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -18484,15 +18688,15 @@
     <row r="108" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F108">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G108" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H108">
         <f>COUNTIF(G$3:G108,G108)</f>
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -18586,15 +18790,15 @@
     <row r="109" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F109">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G109" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H109">
         <f>COUNTIF(G$3:G109,G109)</f>
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -18688,15 +18892,15 @@
     <row r="110" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F110">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G110" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H110">
         <f>COUNTIF(G$3:G110,G110)</f>
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -18790,15 +18994,15 @@
     <row r="111" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F111">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G111" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H111">
         <f>COUNTIF(G$3:G111,G111)</f>
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="I111" t="str">
         <v/>
@@ -18892,15 +19096,15 @@
     <row r="112" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F112">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G112" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H112">
         <f>COUNTIF(G$3:G112,G112)</f>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -18994,15 +19198,15 @@
     <row r="113" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F113">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G113" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H113">
         <f>COUNTIF(G$3:G113,G113)</f>
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -19096,15 +19300,15 @@
     <row r="114" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F114">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G114" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H114">
         <f>COUNTIF(G$3:G114,G114)</f>
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -19198,15 +19402,15 @@
     <row r="115" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F115">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G115" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H115">
         <f>COUNTIF(G$3:G115,G115)</f>
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I115" t="str">
         <v/>
@@ -19300,15 +19504,15 @@
     <row r="116" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F116">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G116" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H116">
         <f>COUNTIF(G$3:G116,G116)</f>
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I116" t="str">
         <v/>
@@ -19402,15 +19606,15 @@
     <row r="117" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F117">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G117" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H117">
         <f>COUNTIF(G$3:G117,G117)</f>
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -19504,15 +19708,15 @@
     <row r="118" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F118">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G118" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H118">
         <f>COUNTIF(G$3:G118,G118)</f>
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -19606,15 +19810,15 @@
     <row r="119" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F119">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G119" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H119">
         <f>COUNTIF(G$3:G119,G119)</f>
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -19708,15 +19912,15 @@
     <row r="120" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F120">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G120" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H120">
         <f>COUNTIF(G$3:G120,G120)</f>
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -19810,15 +20014,15 @@
     <row r="121" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F121">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G121" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H121">
         <f>COUNTIF(G$3:G121,G121)</f>
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -19912,15 +20116,15 @@
     <row r="122" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F122">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G122" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H122">
         <f>COUNTIF(G$3:G122,G122)</f>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I122" t="str">
         <v/>
@@ -20014,15 +20218,15 @@
     <row r="123" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F123">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G123" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H123">
         <f>COUNTIF(G$3:G123,G123)</f>
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -20116,15 +20320,15 @@
     <row r="124" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F124">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G124" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H124">
         <f>COUNTIF(G$3:G124,G124)</f>
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -20218,15 +20422,15 @@
     <row r="125" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F125">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G125" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H125">
         <f>COUNTIF(G$3:G125,G125)</f>
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -20320,15 +20524,15 @@
     <row r="126" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F126">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G126" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H126">
         <f>COUNTIF(G$3:G126,G126)</f>
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -20422,15 +20626,15 @@
     <row r="127" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F127">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G127" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H127">
         <f>COUNTIF(G$3:G127,G127)</f>
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -20524,15 +20728,15 @@
     <row r="128" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F128">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G128" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H128">
         <f>COUNTIF(G$3:G128,G128)</f>
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I128" t="str">
         <v/>
@@ -20626,15 +20830,15 @@
     <row r="129" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F129">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G129" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H129">
         <f>COUNTIF(G$3:G129,G129)</f>
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="I129" t="str">
         <v/>
@@ -20728,15 +20932,15 @@
     <row r="130" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F130">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G130" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H130">
         <f>COUNTIF(G$3:G130,G130)</f>
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -20830,15 +21034,15 @@
     <row r="131" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F131">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G131" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H131">
         <f>COUNTIF(G$3:G131,G131)</f>
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="I131" t="str">
         <v/>
@@ -20932,15 +21136,15 @@
     <row r="132" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F132">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G132" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H132">
         <f>COUNTIF(G$3:G132,G132)</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -21034,15 +21238,15 @@
     <row r="133" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F133">
         <f t="shared" ref="F133:F196" si="8">F132</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G133" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H133">
         <f>COUNTIF(G$3:G133,G133)</f>
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I133" t="str">
         <v/>
@@ -21136,15 +21340,15 @@
     <row r="134" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F134">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G134" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H134">
         <f>COUNTIF(G$3:G134,G134)</f>
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="I134" t="str">
         <v/>
@@ -21238,15 +21442,15 @@
     <row r="135" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F135">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G135" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H135">
         <f>COUNTIF(G$3:G135,G135)</f>
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I135" t="str">
         <v/>
@@ -21340,15 +21544,15 @@
     <row r="136" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F136">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G136" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H136">
         <f>COUNTIF(G$3:G136,G136)</f>
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -21442,15 +21646,15 @@
     <row r="137" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F137">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G137" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H137">
         <f>COUNTIF(G$3:G137,G137)</f>
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -21544,15 +21748,15 @@
     <row r="138" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F138">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G138" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H138">
         <f>COUNTIF(G$3:G138,G138)</f>
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I138" t="str">
         <v/>
@@ -21646,15 +21850,15 @@
     <row r="139" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F139">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G139" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H139">
         <f>COUNTIF(G$3:G139,G139)</f>
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -21748,15 +21952,15 @@
     <row r="140" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F140">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G140" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H140">
         <f>COUNTIF(G$3:G140,G140)</f>
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -21850,15 +22054,15 @@
     <row r="141" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F141">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G141" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H141">
         <f>COUNTIF(G$3:G141,G141)</f>
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -21952,15 +22156,15 @@
     <row r="142" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F142">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G142" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H142">
         <f>COUNTIF(G$3:G142,G142)</f>
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I142" t="str">
         <v/>
@@ -22054,15 +22258,15 @@
     <row r="143" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F143">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G143" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H143">
         <f>COUNTIF(G$3:G143,G143)</f>
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -22156,15 +22360,15 @@
     <row r="144" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F144">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G144" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H144">
         <f>COUNTIF(G$3:G144,G144)</f>
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -22258,15 +22462,15 @@
     <row r="145" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F145">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G145" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H145">
         <f>COUNTIF(G$3:G145,G145)</f>
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -22360,15 +22564,15 @@
     <row r="146" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F146">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G146" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H146">
         <f>COUNTIF(G$3:G146,G146)</f>
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -22462,15 +22666,15 @@
     <row r="147" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F147">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G147" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H147">
         <f>COUNTIF(G$3:G147,G147)</f>
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -22564,15 +22768,15 @@
     <row r="148" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F148">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G148" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H148">
         <f>COUNTIF(G$3:G148,G148)</f>
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -22666,15 +22870,15 @@
     <row r="149" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F149">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G149" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H149">
         <f>COUNTIF(G$3:G149,G149)</f>
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -22768,15 +22972,15 @@
     <row r="150" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F150">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G150" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H150">
         <f>COUNTIF(G$3:G150,G150)</f>
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -22870,15 +23074,15 @@
     <row r="151" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F151">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G151" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H151">
         <f>COUNTIF(G$3:G151,G151)</f>
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -22972,15 +23176,15 @@
     <row r="152" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F152">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G152" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H152">
         <f>COUNTIF(G$3:G152,G152)</f>
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -23074,15 +23278,15 @@
     <row r="153" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F153">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G153" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H153">
         <f>COUNTIF(G$3:G153,G153)</f>
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -23176,15 +23380,15 @@
     <row r="154" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F154">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G154" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H154">
         <f>COUNTIF(G$3:G154,G154)</f>
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="I154" t="str">
         <v/>
@@ -23278,15 +23482,15 @@
     <row r="155" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F155">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G155" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H155">
         <f>COUNTIF(G$3:G155,G155)</f>
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I155" t="str">
         <v/>
@@ -23380,15 +23584,15 @@
     <row r="156" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F156">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G156" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H156">
         <f>COUNTIF(G$3:G156,G156)</f>
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -23482,15 +23686,15 @@
     <row r="157" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F157">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G157" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H157">
         <f>COUNTIF(G$3:G157,G157)</f>
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I157" t="str">
         <v/>
@@ -23584,15 +23788,15 @@
     <row r="158" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F158">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G158" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H158">
         <f>COUNTIF(G$3:G158,G158)</f>
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I158" t="str">
         <v/>
@@ -23686,15 +23890,15 @@
     <row r="159" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F159">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G159" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H159">
         <f>COUNTIF(G$3:G159,G159)</f>
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -23788,15 +23992,15 @@
     <row r="160" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F160">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G160" t="str">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H160">
         <f>COUNTIF(G$3:G160,G160)</f>
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -23890,15 +24094,15 @@
     <row r="161" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F161">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G161" t="str">
         <f t="shared" ref="G161:G202" si="9">E161&amp;F161</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H161">
         <f>COUNTIF(G$3:G161,G161)</f>
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -23992,15 +24196,15 @@
     <row r="162" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F162">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G162" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H162">
         <f>COUNTIF(G$3:G162,G162)</f>
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I162" t="str">
         <v/>
@@ -24094,15 +24298,15 @@
     <row r="163" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F163">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G163" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H163">
         <f>COUNTIF(G$3:G163,G163)</f>
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -24196,15 +24400,15 @@
     <row r="164" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F164">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G164" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H164">
         <f>COUNTIF(G$3:G164,G164)</f>
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="I164" t="str">
         <v/>
@@ -24298,15 +24502,15 @@
     <row r="165" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F165">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G165" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H165">
         <f>COUNTIF(G$3:G165,G165)</f>
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -24400,15 +24604,15 @@
     <row r="166" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F166">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G166" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H166">
         <f>COUNTIF(G$3:G166,G166)</f>
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -24502,15 +24706,15 @@
     <row r="167" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F167">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G167" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H167">
         <f>COUNTIF(G$3:G167,G167)</f>
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="I167" t="str">
         <v/>
@@ -24604,15 +24808,15 @@
     <row r="168" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F168">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G168" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H168">
         <f>COUNTIF(G$3:G168,G168)</f>
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="I168" t="str">
         <v/>
@@ -24706,15 +24910,15 @@
     <row r="169" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F169">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G169" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H169">
         <f>COUNTIF(G$3:G169,G169)</f>
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -24808,15 +25012,15 @@
     <row r="170" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F170">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G170" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H170">
         <f>COUNTIF(G$3:G170,G170)</f>
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="I170" t="str">
         <v/>
@@ -24910,15 +25114,15 @@
     <row r="171" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F171">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G171" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H171">
         <f>COUNTIF(G$3:G171,G171)</f>
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="I171" t="str">
         <v/>
@@ -25012,15 +25216,15 @@
     <row r="172" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F172">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G172" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H172">
         <f>COUNTIF(G$3:G172,G172)</f>
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I172" t="str">
         <v/>
@@ -25114,15 +25318,15 @@
     <row r="173" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F173">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G173" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H173">
         <f>COUNTIF(G$3:G173,G173)</f>
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="I173" t="str">
         <v/>
@@ -25216,15 +25420,15 @@
     <row r="174" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F174">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G174" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H174">
         <f>COUNTIF(G$3:G174,G174)</f>
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I174" t="str">
         <v/>
@@ -25318,15 +25522,15 @@
     <row r="175" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F175">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G175" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H175">
         <f>COUNTIF(G$3:G175,G175)</f>
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -25420,15 +25624,15 @@
     <row r="176" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F176">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G176" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H176">
         <f>COUNTIF(G$3:G176,G176)</f>
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="I176" t="str">
         <v/>
@@ -25522,15 +25726,15 @@
     <row r="177" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F177">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G177" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H177">
         <f>COUNTIF(G$3:G177,G177)</f>
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="I177" t="str">
         <v/>
@@ -25624,15 +25828,15 @@
     <row r="178" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F178">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G178" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H178">
         <f>COUNTIF(G$3:G178,G178)</f>
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -25726,15 +25930,15 @@
     <row r="179" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F179">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G179" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H179">
         <f>COUNTIF(G$3:G179,G179)</f>
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I179" t="str">
         <v/>
@@ -25828,15 +26032,15 @@
     <row r="180" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F180">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G180" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H180">
         <f>COUNTIF(G$3:G180,G180)</f>
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -25930,15 +26134,15 @@
     <row r="181" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F181">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G181" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H181">
         <f>COUNTIF(G$3:G181,G181)</f>
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -26032,15 +26236,15 @@
     <row r="182" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F182">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G182" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H182">
         <f>COUNTIF(G$3:G182,G182)</f>
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I182" t="str">
         <v/>
@@ -26134,15 +26338,15 @@
     <row r="183" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F183">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G183" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H183">
         <f>COUNTIF(G$3:G183,G183)</f>
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -26236,15 +26440,15 @@
     <row r="184" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F184">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G184" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H184">
         <f>COUNTIF(G$3:G184,G184)</f>
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="I184" t="str">
         <v/>
@@ -26338,15 +26542,15 @@
     <row r="185" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F185">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G185" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H185">
         <f>COUNTIF(G$3:G185,G185)</f>
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="I185" t="str">
         <v/>
@@ -26440,15 +26644,15 @@
     <row r="186" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F186">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G186" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H186">
         <f>COUNTIF(G$3:G186,G186)</f>
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="I186" t="str">
         <v/>
@@ -26542,15 +26746,15 @@
     <row r="187" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F187">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G187" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H187">
         <f>COUNTIF(G$3:G187,G187)</f>
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -26644,15 +26848,15 @@
     <row r="188" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F188">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G188" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H188">
         <f>COUNTIF(G$3:G188,G188)</f>
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="I188" t="str">
         <v/>
@@ -26746,15 +26950,15 @@
     <row r="189" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F189">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G189" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H189">
         <f>COUNTIF(G$3:G189,G189)</f>
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="I189" t="str">
         <v/>
@@ -26848,15 +27052,15 @@
     <row r="190" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F190">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G190" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H190">
         <f>COUNTIF(G$3:G190,G190)</f>
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="I190" t="str">
         <v/>
@@ -26950,15 +27154,15 @@
     <row r="191" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F191">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G191" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H191">
         <f>COUNTIF(G$3:G191,G191)</f>
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="I191" t="str">
         <v/>
@@ -27052,15 +27256,15 @@
     <row r="192" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F192">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G192" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H192">
         <f>COUNTIF(G$3:G192,G192)</f>
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="I192" t="str">
         <v/>
@@ -27154,15 +27358,15 @@
     <row r="193" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F193">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G193" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H193">
         <f>COUNTIF(G$3:G193,G193)</f>
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="I193" t="str">
         <v/>
@@ -27256,15 +27460,15 @@
     <row r="194" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F194">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G194" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H194">
         <f>COUNTIF(G$3:G194,G194)</f>
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="I194" t="str">
         <v/>
@@ -27358,15 +27562,15 @@
     <row r="195" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F195">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G195" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H195">
         <f>COUNTIF(G$3:G195,G195)</f>
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I195" t="str">
         <v/>
@@ -27460,15 +27664,15 @@
     <row r="196" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F196">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G196" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H196">
         <f>COUNTIF(G$3:G196,G196)</f>
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="I196" t="str">
         <v/>
@@ -27562,15 +27766,15 @@
     <row r="197" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F197">
         <f t="shared" ref="F197:F202" si="10">F196</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G197" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H197">
         <f>COUNTIF(G$3:G197,G197)</f>
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="I197" t="str">
         <v/>
@@ -27664,15 +27868,15 @@
     <row r="198" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F198">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G198" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H198">
         <f>COUNTIF(G$3:G198,G198)</f>
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I198" t="str">
         <v/>
@@ -27766,15 +27970,15 @@
     <row r="199" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F199">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G199" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H199">
         <f>COUNTIF(G$3:G199,G199)</f>
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="I199" t="str">
         <v/>
@@ -27868,15 +28072,15 @@
     <row r="200" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F200">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G200" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H200">
         <f>COUNTIF(G$3:G200,G200)</f>
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="I200" t="str">
         <v/>
@@ -27970,15 +28174,15 @@
     <row r="201" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F201">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G201" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H201">
         <f>COUNTIF(G$3:G201,G201)</f>
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="I201" t="str">
         <v/>
@@ -28072,15 +28276,15 @@
     <row r="202" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="F202">
         <f t="shared" si="10"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G202" t="str">
         <f t="shared" si="9"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H202">
         <f>COUNTIF(G$3:G202,G202)</f>
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="I202" t="str">
         <v>●</v>
@@ -28180,7 +28384,7 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\精度を高める\rtc\[20260130_1906_幅50巻.xlsx]Sheet1 によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//Return to origin operation
@@ -28209,12 +28413,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
+	//Cut operation
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
 	//Start supply operation
-	ELSIF uiInfoIdx = 3 THEN
+	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Start supply operation';
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28223,24 +28440,11 @@
 			uiErrCode	:= 3;
 		END_IF;
 	//Supply operation
-	ELSIF uiInfoIdx = 4 THEN
+	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【14】 Supply operation';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;
-	//Cut operation
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【15】 Cut operation';
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28520,12 +28724,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
+	//Discharge operation
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Discharge operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
 	//Measurement preparation
-	ELSIF uiInfoIdx = 2 THEN
+	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Measurement preparation';
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28534,11 +28751,11 @@
 			uiErrCode	:= 3;
 		END_IF;
 	//Measurement operation during winding
-	ELSIF uiInfoIdx = 3 THEN
+	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
 			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 Measurement operation during winding';
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28546,12 +28763,30 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
-	ELSIF uiInfoIdx = 4 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【64】 Discharge operation';
+	ELSE
+		uiErrCode	:= 2;
+	END_IF;
+//7
+ELSIF strInfoType = 7 THEN
+	//Return to origin operation
+	IF uiInfoIdx = 1 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//Gluing operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD76462-5672-4167-B396-D233B6D8FAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FE4CD1-7F72-4AC0-A9A6-E147D2218D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//Return to origin operation
@@ -28384,7 +28384,7 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//Return to origin operation

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FE4CD1-7F72-4AC0-A9A6-E147D2218D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406F1539-A43D-4F7A-8652-B8C40A13BB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//Return to origin operation
@@ -28384,7 +28384,7 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_TP1_popup.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
 //1
 IF strInfoType = 1 THEN
 	//Return to origin operation

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406F1539-A43D-4F7A-8652-B8C40A13BB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A82A81-B822-4F91-BBE6-35EBB83BEF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="120">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -627,23 +627,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>排出動作</t>
-    <rPh sb="0" eb="2">
-      <t>ハイシュツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ドウサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Measurement preparation</t>
   </si>
   <si>
     <t>Measurement operation during winding</t>
-  </si>
-  <si>
-    <t>Discharge operation</t>
   </si>
   <si>
     <t>供給確認動作</t>
@@ -690,6 +677,38 @@
   </si>
   <si>
     <t>Gluing operation</t>
+  </si>
+  <si>
+    <t>排出受渡し動作</t>
+    <rPh sb="0" eb="2">
+      <t>ハイシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ウケワタ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>排出受取り動作</t>
+    <rPh sb="0" eb="2">
+      <t>ハイシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ウケトリ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Discharge and receiving operation</t>
+  </si>
+  <si>
+    <t>Discharge and handover operation</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1114,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$94">
+    <xdr:sp macro="" textlink="$A$95">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -1464,7 +1483,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R98"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -1568,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="str">
-        <f t="shared" ref="D3:D60" si="0">B3&amp;C3</f>
+        <f t="shared" ref="D3:D61" si="0">B3&amp;C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="4">
@@ -1894,10 +1913,10 @@
         <v>73</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1948,7 +1967,7 @@
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4">
-        <f t="shared" ref="C14:C90" si="8">C13</f>
+        <f t="shared" ref="C14:C91" si="8">C13</f>
         <v>3</v>
       </c>
       <c r="D14" s="4" t="str">
@@ -1956,7 +1975,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" ref="E14:E70" si="9">E13+1</f>
+        <f t="shared" ref="E14:E71" si="9">E13+1</f>
         <v>2</v>
       </c>
       <c r="F14" s="5"/>
@@ -2368,7 +2387,7 @@
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4">
-        <f t="shared" ref="C26" si="15">C25</f>
+        <f t="shared" ref="C26:C27" si="15">C25</f>
         <v>6</v>
       </c>
       <c r="D26" s="4" t="str">
@@ -2376,7 +2395,7 @@
         <v>6</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" ref="E26" si="16">E25+1</f>
+        <f t="shared" ref="E26:E27" si="16">E25+1</f>
         <v>2</v>
       </c>
       <c r="F26" s="9"/>
@@ -2384,10 +2403,10 @@
         <v>77</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
@@ -2403,60 +2422,60 @@
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
       <c r="D27" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D27" si="17">B27&amp;C27</f>
         <v>6</v>
       </c>
       <c r="E27" s="4">
-        <v>6</v>
-      </c>
-      <c r="F27" s="5"/>
+        <f t="shared" si="16"/>
+        <v>3</v>
+      </c>
+      <c r="F27" s="9"/>
       <c r="G27" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H27" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
+      <c r="H27" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
       <c r="R27" s="7"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4">
-        <f t="shared" si="8"/>
+        <f>C26</f>
         <v>6</v>
       </c>
       <c r="D28" s="4" t="str">
-        <f t="shared" ref="D28" si="17">B28&amp;C28</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" si="9"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
         <v>77</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -2472,42 +2491,42 @@
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4">
-        <f>C25+1</f>
-        <v>7</v>
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="D29" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f t="shared" ref="D29" si="18">B29&amp;C29</f>
+        <v>6</v>
       </c>
       <c r="E29" s="4">
-        <f>E25</f>
-        <v>1</v>
-      </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="22"/>
-      <c r="Q29" s="22"/>
+        <f t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="21"/>
       <c r="R29" s="7"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
-        <f t="shared" ref="C30" si="18">C29</f>
+        <f>C25+1</f>
         <v>7</v>
       </c>
       <c r="D30" s="4" t="str">
@@ -2515,17 +2534,18 @@
         <v>7</v>
       </c>
       <c r="E30" s="4">
-        <v>6</v>
+        <f>E25</f>
+        <v>1</v>
       </c>
       <c r="F30" s="9"/>
       <c r="G30" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="H30" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="H30" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="I30" s="9" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
@@ -2538,39 +2558,44 @@
       <c r="R30" s="7"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="26"/>
+      <c r="A31" s="4"/>
       <c r="B31" s="4"/>
-      <c r="C31" s="26">
-        <f>C29+1</f>
-        <v>8</v>
-      </c>
-      <c r="D31" s="26" t="str">
+      <c r="C31" s="4">
+        <f t="shared" ref="C31" si="19">C30</f>
+        <v>7</v>
+      </c>
+      <c r="D31" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E31" s="4">
-        <f>E29</f>
-        <v>1</v>
-      </c>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
-      <c r="Q31" s="23"/>
+        <v>6</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
       <c r="R31" s="7"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="26"/>
       <c r="B32" s="4"/>
       <c r="C32" s="26">
-        <f t="shared" ref="C32" si="19">C31</f>
+        <f>C30+1</f>
         <v>8</v>
       </c>
       <c r="D32" s="26" t="str">
@@ -2578,8 +2603,8 @@
         <v>8</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" ref="E32" si="20">E31+1</f>
-        <v>2</v>
+        <f>E30</f>
+        <v>1</v>
       </c>
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
@@ -2599,7 +2624,7 @@
       <c r="A33" s="26"/>
       <c r="B33" s="4"/>
       <c r="C33" s="26">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C33" si="20">C32</f>
         <v>8</v>
       </c>
       <c r="D33" s="26" t="str">
@@ -2607,8 +2632,8 @@
         <v>8</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E33" si="21">E32+1</f>
+        <v>2</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
@@ -2625,32 +2650,32 @@
       <c r="R33" s="7"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="4"/>
+      <c r="A34" s="26"/>
       <c r="B34" s="4"/>
-      <c r="C34" s="4">
+      <c r="C34" s="26">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="D34" s="4" t="str">
+      <c r="D34" s="26" t="str">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="E34" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="23"/>
+      <c r="P34" s="23"/>
+      <c r="Q34" s="23"/>
       <c r="R34" s="7"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -2666,7 +2691,7 @@
       </c>
       <c r="E35" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -2686,16 +2711,16 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4">
-        <f t="shared" ref="C36" si="21">C31+1</f>
-        <v>9</v>
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="D36" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" ref="E36" si="22">E31</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -2715,7 +2740,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4">
-        <f t="shared" ref="C37" si="23">C36</f>
+        <f t="shared" ref="C37" si="22">C32+1</f>
         <v>9</v>
       </c>
       <c r="D37" s="4" t="str">
@@ -2723,8 +2748,8 @@
         <v>9</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" ref="E37" si="24">E36+1</f>
-        <v>2</v>
+        <f t="shared" ref="E37" si="23">E32</f>
+        <v>1</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -2744,7 +2769,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C38" si="24">C37</f>
         <v>9</v>
       </c>
       <c r="D38" s="4" t="str">
@@ -2752,8 +2777,8 @@
         <v>9</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E38" si="25">E37+1</f>
+        <v>2</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -2782,14 +2807,14 @@
       </c>
       <c r="E39" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
-      <c r="K39" s="13"/>
+      <c r="K39" s="5"/>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
@@ -2811,14 +2836,14 @@
       </c>
       <c r="E40" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
+      <c r="K40" s="13"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
@@ -2831,16 +2856,16 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
-        <f t="shared" ref="C41" si="25">C36+1</f>
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="D41" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" ref="E41" si="26">E36</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -2860,7 +2885,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
-        <f t="shared" ref="C42" si="27">C41</f>
+        <f t="shared" ref="C42" si="26">C37+1</f>
         <v>10</v>
       </c>
       <c r="D42" s="4" t="str">
@@ -2868,8 +2893,8 @@
         <v>10</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" ref="E42" si="28">E41+1</f>
-        <v>2</v>
+        <f t="shared" ref="E42" si="27">E37</f>
+        <v>1</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -2889,7 +2914,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C43" si="28">C42</f>
         <v>10</v>
       </c>
       <c r="D43" s="4" t="str">
@@ -2897,8 +2922,8 @@
         <v>10</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E43" si="29">E42+1</f>
+        <v>2</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -2927,7 +2952,7 @@
       </c>
       <c r="E44" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -2956,7 +2981,7 @@
       </c>
       <c r="E45" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -2976,16 +3001,16 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
-        <f t="shared" ref="C46" si="29">C41+1</f>
-        <v>11</v>
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="D46" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" ref="E46" si="30">E41</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -3005,7 +3030,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
-        <f t="shared" ref="C47" si="31">C46</f>
+        <f t="shared" ref="C47" si="30">C42+1</f>
         <v>11</v>
       </c>
       <c r="D47" s="4" t="str">
@@ -3013,8 +3038,8 @@
         <v>11</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" ref="E47" si="32">E46+1</f>
-        <v>2</v>
+        <f t="shared" ref="E47" si="31">E42</f>
+        <v>1</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -3034,7 +3059,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C48" si="32">C47</f>
         <v>11</v>
       </c>
       <c r="D48" s="4" t="str">
@@ -3042,8 +3067,8 @@
         <v>11</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E48" si="33">E47+1</f>
+        <v>2</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -3072,7 +3097,7 @@
       </c>
       <c r="E49" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -3101,7 +3126,7 @@
       </c>
       <c r="E50" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -3121,16 +3146,16 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
-        <f t="shared" ref="C51" si="33">C46+1</f>
-        <v>12</v>
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="D51" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" ref="E51" si="34">E46</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -3150,7 +3175,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
-        <f t="shared" ref="C52" si="35">C51</f>
+        <f t="shared" ref="C52" si="34">C47+1</f>
         <v>12</v>
       </c>
       <c r="D52" s="4" t="str">
@@ -3158,8 +3183,8 @@
         <v>12</v>
       </c>
       <c r="E52" s="4">
-        <f t="shared" ref="E52" si="36">E51+1</f>
-        <v>2</v>
+        <f t="shared" ref="E52" si="35">E47</f>
+        <v>1</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -3179,7 +3204,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C53" si="36">C52</f>
         <v>12</v>
       </c>
       <c r="D53" s="4" t="str">
@@ -3187,8 +3212,8 @@
         <v>12</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E53" si="37">E52+1</f>
+        <v>2</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -3217,7 +3242,7 @@
       </c>
       <c r="E54" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -3246,7 +3271,7 @@
       </c>
       <c r="E55" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -3266,16 +3291,16 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
-        <f t="shared" ref="C56:C86" si="37">C51+1</f>
-        <v>13</v>
+        <f t="shared" si="8"/>
+        <v>12</v>
       </c>
       <c r="D56" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E56" s="4">
-        <f t="shared" ref="E56" si="38">E51</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -3295,7 +3320,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4">
-        <f t="shared" ref="C57:C87" si="39">C56</f>
+        <f t="shared" ref="C57:C87" si="38">C52+1</f>
         <v>13</v>
       </c>
       <c r="D57" s="4" t="str">
@@ -3303,8 +3328,8 @@
         <v>13</v>
       </c>
       <c r="E57" s="4">
-        <f t="shared" ref="E57" si="40">E56+1</f>
-        <v>2</v>
+        <f t="shared" ref="E57" si="39">E52</f>
+        <v>1</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -3324,7 +3349,7 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C58:C88" si="40">C57</f>
         <v>13</v>
       </c>
       <c r="D58" s="4" t="str">
@@ -3332,8 +3357,8 @@
         <v>13</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E58" si="41">E57+1</f>
+        <v>2</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -3362,7 +3387,7 @@
       </c>
       <c r="E59" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -3391,7 +3416,7 @@
       </c>
       <c r="E60" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -3411,16 +3436,16 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
-        <f t="shared" si="37"/>
-        <v>14</v>
+        <f t="shared" si="8"/>
+        <v>13</v>
       </c>
       <c r="D61" s="4" t="str">
-        <f t="shared" ref="D61:D90" si="41">B61&amp;C61</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E61" s="4">
-        <f t="shared" ref="E61" si="42">E56</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -3440,16 +3465,16 @@
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>14</v>
       </c>
       <c r="D62" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="D62:D91" si="42">B62&amp;C62</f>
         <v>14</v>
       </c>
       <c r="E62" s="4">
-        <f t="shared" ref="E62" si="43">E61+1</f>
-        <v>2</v>
+        <f t="shared" ref="E62" si="43">E57</f>
+        <v>1</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -3469,16 +3494,16 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="40"/>
         <v>14</v>
       </c>
       <c r="D63" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>14</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E63" si="44">E62+1</f>
+        <v>2</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -3502,12 +3527,12 @@
         <v>14</v>
       </c>
       <c r="D64" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>14</v>
       </c>
       <c r="E64" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -3531,12 +3556,12 @@
         <v>14</v>
       </c>
       <c r="D65" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>14</v>
       </c>
       <c r="E65" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -3556,16 +3581,16 @@
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4">
-        <f t="shared" si="37"/>
-        <v>15</v>
+        <f t="shared" si="8"/>
+        <v>14</v>
       </c>
       <c r="D66" s="4" t="str">
-        <f t="shared" si="41"/>
-        <v>15</v>
+        <f t="shared" si="42"/>
+        <v>14</v>
       </c>
       <c r="E66" s="4">
-        <f t="shared" ref="E66" si="44">E61</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -3585,16 +3610,16 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>15</v>
       </c>
       <c r="D67" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>15</v>
       </c>
       <c r="E67" s="4">
-        <f t="shared" ref="E67" si="45">E66+1</f>
-        <v>2</v>
+        <f t="shared" ref="E67" si="45">E62</f>
+        <v>1</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -3614,16 +3639,16 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="40"/>
         <v>15</v>
       </c>
       <c r="D68" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>15</v>
       </c>
       <c r="E68" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E68" si="46">E67+1</f>
+        <v>2</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -3647,12 +3672,12 @@
         <v>15</v>
       </c>
       <c r="D69" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>15</v>
       </c>
       <c r="E69" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -3676,12 +3701,12 @@
         <v>15</v>
       </c>
       <c r="D70" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>15</v>
       </c>
       <c r="E70" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -3701,16 +3726,16 @@
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4">
-        <f t="shared" si="37"/>
-        <v>16</v>
+        <f t="shared" si="8"/>
+        <v>15</v>
       </c>
       <c r="D71" s="4" t="str">
-        <f t="shared" si="41"/>
-        <v>16</v>
+        <f t="shared" si="42"/>
+        <v>15</v>
       </c>
       <c r="E71" s="4">
-        <f t="shared" ref="E71" si="46">E66</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -3730,16 +3755,16 @@
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>16</v>
       </c>
       <c r="D72" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>16</v>
       </c>
       <c r="E72" s="4">
-        <f t="shared" ref="E72:E90" si="47">E71+1</f>
-        <v>2</v>
+        <f t="shared" ref="E72" si="47">E67</f>
+        <v>1</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -3759,16 +3784,16 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="40"/>
         <v>16</v>
       </c>
       <c r="D73" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>16</v>
       </c>
       <c r="E73" s="4">
-        <f t="shared" si="47"/>
-        <v>3</v>
+        <f t="shared" ref="E73:E91" si="48">E72+1</f>
+        <v>2</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -3792,12 +3817,12 @@
         <v>16</v>
       </c>
       <c r="D74" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>16</v>
       </c>
       <c r="E74" s="4">
-        <f t="shared" si="47"/>
-        <v>4</v>
+        <f t="shared" si="48"/>
+        <v>3</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -3821,12 +3846,12 @@
         <v>16</v>
       </c>
       <c r="D75" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>16</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" si="47"/>
-        <v>5</v>
+        <f t="shared" si="48"/>
+        <v>4</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -3846,16 +3871,16 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4">
-        <f t="shared" si="37"/>
-        <v>17</v>
+        <f t="shared" si="8"/>
+        <v>16</v>
       </c>
       <c r="D76" s="4" t="str">
-        <f t="shared" si="41"/>
-        <v>17</v>
+        <f t="shared" si="42"/>
+        <v>16</v>
       </c>
       <c r="E76" s="4">
-        <f t="shared" ref="E76" si="48">E71</f>
-        <v>1</v>
+        <f t="shared" si="48"/>
+        <v>5</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -3875,16 +3900,16 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>17</v>
       </c>
       <c r="D77" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>17</v>
       </c>
       <c r="E77" s="4">
-        <f t="shared" ref="E77" si="49">E76+1</f>
-        <v>2</v>
+        <f t="shared" ref="E77" si="49">E72</f>
+        <v>1</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -3904,16 +3929,16 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="40"/>
         <v>17</v>
       </c>
       <c r="D78" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>17</v>
       </c>
       <c r="E78" s="4">
-        <f t="shared" si="47"/>
-        <v>3</v>
+        <f t="shared" ref="E78" si="50">E77+1</f>
+        <v>2</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -3937,12 +3962,12 @@
         <v>17</v>
       </c>
       <c r="D79" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>17</v>
       </c>
       <c r="E79" s="4">
-        <f t="shared" si="47"/>
-        <v>4</v>
+        <f t="shared" si="48"/>
+        <v>3</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -3966,12 +3991,12 @@
         <v>17</v>
       </c>
       <c r="D80" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>17</v>
       </c>
       <c r="E80" s="4">
-        <f t="shared" si="47"/>
-        <v>5</v>
+        <f t="shared" si="48"/>
+        <v>4</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -3991,16 +4016,16 @@
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4">
-        <f t="shared" si="37"/>
-        <v>18</v>
+        <f t="shared" si="8"/>
+        <v>17</v>
       </c>
       <c r="D81" s="4" t="str">
-        <f t="shared" si="41"/>
-        <v>18</v>
+        <f t="shared" si="42"/>
+        <v>17</v>
       </c>
       <c r="E81" s="4">
-        <f t="shared" ref="E81" si="50">E76</f>
-        <v>1</v>
+        <f t="shared" si="48"/>
+        <v>5</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -4020,16 +4045,16 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>18</v>
       </c>
       <c r="D82" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>18</v>
       </c>
       <c r="E82" s="4">
-        <f t="shared" ref="E82" si="51">E81+1</f>
-        <v>2</v>
+        <f t="shared" ref="E82" si="51">E77</f>
+        <v>1</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -4049,16 +4074,16 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="40"/>
         <v>18</v>
       </c>
       <c r="D83" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>18</v>
       </c>
       <c r="E83" s="4">
-        <f t="shared" si="47"/>
-        <v>3</v>
+        <f t="shared" ref="E83" si="52">E82+1</f>
+        <v>2</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -4082,12 +4107,12 @@
         <v>18</v>
       </c>
       <c r="D84" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>18</v>
       </c>
       <c r="E84" s="4">
-        <f t="shared" si="47"/>
-        <v>4</v>
+        <f t="shared" si="48"/>
+        <v>3</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
@@ -4111,12 +4136,12 @@
         <v>18</v>
       </c>
       <c r="D85" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>18</v>
       </c>
       <c r="E85" s="4">
-        <f t="shared" si="47"/>
-        <v>5</v>
+        <f t="shared" si="48"/>
+        <v>4</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
@@ -4136,16 +4161,16 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4">
-        <f t="shared" si="37"/>
-        <v>19</v>
+        <f t="shared" si="8"/>
+        <v>18</v>
       </c>
       <c r="D86" s="4" t="str">
-        <f t="shared" si="41"/>
-        <v>19</v>
+        <f t="shared" si="42"/>
+        <v>18</v>
       </c>
       <c r="E86" s="4">
-        <f t="shared" ref="E86" si="52">E81</f>
-        <v>1</v>
+        <f t="shared" si="48"/>
+        <v>5</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
@@ -4165,16 +4190,16 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>19</v>
       </c>
       <c r="D87" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>19</v>
       </c>
       <c r="E87" s="4">
-        <f t="shared" ref="E87" si="53">E86+1</f>
-        <v>2</v>
+        <f t="shared" ref="E87" si="53">E82</f>
+        <v>1</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -4194,16 +4219,16 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="40"/>
         <v>19</v>
       </c>
       <c r="D88" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>19</v>
       </c>
       <c r="E88" s="4">
-        <f t="shared" si="47"/>
-        <v>3</v>
+        <f t="shared" ref="E88" si="54">E87+1</f>
+        <v>2</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
@@ -4227,12 +4252,12 @@
         <v>19</v>
       </c>
       <c r="D89" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>19</v>
       </c>
       <c r="E89" s="4">
-        <f t="shared" si="47"/>
-        <v>4</v>
+        <f t="shared" si="48"/>
+        <v>3</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
@@ -4256,12 +4281,12 @@
         <v>19</v>
       </c>
       <c r="D90" s="4" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>19</v>
       </c>
       <c r="E90" s="4">
-        <f t="shared" si="47"/>
-        <v>5</v>
+        <f t="shared" si="48"/>
+        <v>4</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
@@ -4278,94 +4303,123 @@
       <c r="R90" s="7"/>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="15"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="15"/>
-      <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="16"/>
-      <c r="G91" s="16"/>
-      <c r="H91" s="16"/>
-      <c r="I91" s="16"/>
-      <c r="J91" s="16"/>
-      <c r="K91" s="16"/>
-      <c r="L91" s="16"/>
-      <c r="M91" s="16"/>
-      <c r="N91" s="16"/>
-      <c r="O91" s="17"/>
-      <c r="P91" s="17"/>
-      <c r="Q91" s="17"/>
-      <c r="R91" s="17"/>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" t="s">
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4">
+        <f t="shared" si="8"/>
+        <v>19</v>
+      </c>
+      <c r="D91" s="4" t="str">
+        <f t="shared" si="42"/>
+        <v>19</v>
+      </c>
+      <c r="E91" s="4">
+        <f t="shared" si="48"/>
+        <v>5</v>
+      </c>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+      <c r="K91" s="5"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="7"/>
+      <c r="P91" s="7"/>
+      <c r="Q91" s="7"/>
+      <c r="R91" s="7"/>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="15"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="15"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="15"/>
+      <c r="F92" s="16"/>
+      <c r="G92" s="16"/>
+      <c r="H92" s="16"/>
+      <c r="I92" s="16"/>
+      <c r="J92" s="16"/>
+      <c r="K92" s="16"/>
+      <c r="L92" s="16"/>
+      <c r="M92" s="16"/>
+      <c r="N92" s="16"/>
+      <c r="O92" s="17"/>
+      <c r="P92" s="17"/>
+      <c r="Q92" s="17"/>
+      <c r="R92" s="17"/>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" t="s">
         <v>9</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F94" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94">
-        <f>MAX(A$2:A$91)</f>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95">
+        <f>MAX(A$2:A$92)</f>
         <v>0</v>
       </c>
-      <c r="F94">
-        <f>MAX(F$2:F$91)</f>
+      <c r="F95">
+        <f>MAX(F$2:F$92)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" t="s">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
         <v>40</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D96" t="s">
         <v>14</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E96" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96">
-        <f>ROW(A92)-ROW(A1)-1</f>
-        <v>90</v>
-      </c>
-      <c r="D96">
-        <f>COUNTIF(D$2:D$91,D95)</f>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97">
+        <f>ROW(A93)-ROW(A1)-1</f>
+        <v>91</v>
+      </c>
+      <c r="D97">
+        <f>COUNTIF(D$2:D$92,D96)</f>
         <v>0</v>
       </c>
-      <c r="E96" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$91,$D$2:$D$91,E95)</f>
+      <c r="E97" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$92,$D$2:$D$92,E96)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="4:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D97" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D98" t="s">
         <v>12</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E98" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="4:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D98">
-        <f>COUNTIF(D$2:D$91,D97)</f>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D99">
+        <f>COUNTIF(D$2:D$92,D98)</f>
         <v>0</v>
       </c>
-      <c r="E98" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$91,$D$2:$D$91,E97)</f>
+      <c r="E99" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$92,$D$2:$D$92,E98)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R90" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R90">
-      <sortCondition ref="D1:D90"/>
+  <autoFilter ref="A1:R91" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R91">
+      <sortCondition ref="D1:D91"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:R91">
+  <conditionalFormatting sqref="A2:R92">
     <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
@@ -4521,7 +4575,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -4535,23 +4589,23 @@
         <v>1</v>
       </c>
       <c r="J3" cm="1">
-        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$91&amp;info_index!$E$2:$E$91,0),"")</f>
+        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$92&amp;info_index!$E$2:$E$92,0),"")</f>
         <v>1</v>
       </c>
       <c r="K3" t="str" cm="1">
-        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$91,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$91&amp;info_index!$E$2:$E$91,0),1)&amp;"","")</f>
-        <v>Return to origin operation</v>
+        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$92,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$92&amp;info_index!$E$2:$E$92,0),1)&amp;"","")</f>
+        <v>原点復帰動作</v>
       </c>
       <c r="L3" t="str" cm="1">
         <f t="array" aca="1" ref="L3:L202" ca="1">IF(LEN(_xlfn.ANCHORARRAY($J3)),IF(LEN(_xlfn.ANCHORARRAY(K3)),_xlfn.ANCHORARRAY(K3),"unknown"),"")</f>
-        <v>Return to origin operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N3" t="str" cm="1">
         <f t="array" aca="1" ref="N3:N202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(L3)),"【"&amp;G3:G202&amp;H3:H202&amp;"】 "&amp;_xlfn.ANCHORARRAY(L3),"")</f>
-        <v>【11】 Return to origin operation</v>
+        <v>【11】 原点復帰動作</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$91,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$91&amp;info_index!$E$2:$E$91,0),1)&amp;"","")</f>
+        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$92,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$92&amp;info_index!$E$2:$E$92,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="P3" t="str" cm="1">
@@ -4559,7 +4613,7 @@
         <v>unknown</v>
       </c>
       <c r="Q3" t="str" cm="1">
-        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$91,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$91&amp;info_index!$E$2:$E$91,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$92,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$92&amp;info_index!$E$2:$E$92,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="R3" t="str" cm="1">
@@ -4579,14 +4633,14 @@
         <f t="array" aca="1" ref="AB3:AB202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AA3)),_xlfn.ANCHORARRAY(AA3),"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;$B$7&amp;_xlfn.ANCHORARRAY(L3)&amp;CHAR(10)&amp;CHAR(9)&amp;IF(H3:H202=1,"IF ","ELSIF ")&amp;$B$26&amp;" = "&amp;H3:H202&amp;" THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC3" t="str" cm="1">
         <f t="array" aca="1" ref="AC3:AC202" ca="1">IF(LEN(AB3:AB202),AB3:AB202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"IF "&amp;$B$27&amp;" = '"&amp;$L$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -4594,54 +4648,54 @@
         <f t="array" aca="1" ref="AD3:AD202" ca="1">IF(LEN(AC3:AC202),AC3:AC202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(L3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE3" t="str" cm="1">
         <f t="array" aca="1" ref="AE3:AE202" ca="1">IF(LEN(AD3:AD202),AD3:AD202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;N$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF3" t="str" cm="1">
         <f t="array" aca="1" ref="AF3:AF202" ca="1">IF(LEN(AE3:AE202),AE3:AE202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(N3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Return to origin operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';</v>
       </c>
       <c r="AG3" t="str" cm="1">
         <f t="array" aca="1" ref="AG3:AG202" ca="1">IF(LEN(AF3:AF202),AF3:AF202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;P$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH3" t="str" cm="1">
         <f t="array" aca="1" ref="AH3:AH202" ca="1">IF(LEN(AG3:AG202),AG3:AG202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(P3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -4649,12 +4703,12 @@
         <f t="array" aca="1" ref="AI3:AI202" ca="1">IF(LEN(AH3:AH202),AH3:AH202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;R$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4663,12 +4717,12 @@
         <f t="array" aca="1" ref="AJ3:AJ202" ca="1">IF(LEN(AI3:AI202),AI3:AI202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(R3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4678,12 +4732,12 @@
         <f t="array" aca="1" ref="AK3:AK202" ca="1">IF(LEN(AJ3:AJ202),AJ3:AJ202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 3"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4696,12 +4750,12 @@
         <f t="array" aca="1" ref="AL3:AL202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AK3)),_xlfn.ANCHORARRAY(AK3),"")&amp;IF(I3:I202="●",CHAR(10)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 2"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4714,12 +4768,12 @@
         <f t="array" aca="1" ref="AM3:AM202" ca="1">_xlfn.ANCHORARRAY(AL3)</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4751,15 +4805,15 @@
       </c>
       <c r="K4" t="str">
         <f ca="1"/>
-        <v>Preparation for supply operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="L4" t="str">
         <f ca="1"/>
-        <v>Preparation for supply operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="N4" t="str">
         <f ca="1"/>
-        <v>【12】 Preparation for supply operation</v>
+        <v>【12】 供給準備動作</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -4788,75 +4842,75 @@
       <c r="AB4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';</v>
+			strRt	:= '供給準備動作';</v>
       </c>
       <c r="AE4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Preparation for supply operation';</v>
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';</v>
       </c>
       <c r="AG4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4864,12 +4918,12 @@
       <c r="AJ4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4878,12 +4932,12 @@
       <c r="AK4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4895,12 +4949,12 @@
       <c r="AL4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4912,12 +4966,12 @@
       <c r="AM4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4933,7 +4987,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -4955,15 +5009,15 @@
       </c>
       <c r="K5" t="str">
         <f ca="1"/>
-        <v>Cut operation</v>
+        <v>カット動作</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>Cut operation</v>
+        <v>カット動作</v>
       </c>
       <c r="N5" t="str">
         <f ca="1"/>
-        <v>【13】 Cut operation</v>
+        <v>【13】 カット動作</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -4992,75 +5046,75 @@
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';</v>
+			strRt	:= 'カット動作';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
+			strRt	:= 'カット動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Cut operation';</v>
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 カット動作';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 カット動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5068,12 +5122,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5082,12 +5136,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5099,12 +5153,12 @@
       <c r="AL5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5116,12 +5170,12 @@
       <c r="AM5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5374,15 +5428,15 @@
       </c>
       <c r="K8" t="str">
         <f ca="1"/>
-        <v>Start supply operation</v>
+        <v>供給開始動作</v>
       </c>
       <c r="L8" t="str">
         <f ca="1"/>
-        <v>Start supply operation</v>
+        <v>供給開始動作</v>
       </c>
       <c r="N8" t="str">
         <f ca="1"/>
-        <v>【16】 Start supply operation</v>
+        <v>【16】 供給開始動作</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -5411,75 +5465,75 @@
       <c r="AB8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';</v>
+			strRt	:= '供給開始動作';</v>
       </c>
       <c r="AE8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
+			strRt	:= '供給開始動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 Start supply operation';</v>
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 供給開始動作';</v>
       </c>
       <c r="AG8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5487,12 +5541,12 @@
       <c r="AJ8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5501,12 +5555,12 @@
       <c r="AK8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5518,12 +5572,12 @@
       <c r="AL8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5535,12 +5589,12 @@
       <c r="AM8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5577,15 +5631,15 @@
       </c>
       <c r="K9" t="str">
         <f ca="1"/>
-        <v>Supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="L9" t="str">
         <f ca="1"/>
-        <v>Supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="N9" t="str">
         <f ca="1"/>
-        <v>【17】 Supply operation</v>
+        <v>【17】 供給動作</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -5614,75 +5668,75 @@
       <c r="AB9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';</v>
+			strRt	:= '供給動作';</v>
       </c>
       <c r="AE9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 Supply operation';</v>
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 供給動作';</v>
       </c>
       <c r="AG9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 供給動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5690,12 +5744,12 @@
       <c r="AJ9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5704,12 +5758,12 @@
       <c r="AK9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5721,12 +5775,12 @@
       <c r="AL9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5738,12 +5792,12 @@
       <c r="AM9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6071,15 +6125,15 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6087,12 +6141,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6100,12 +6154,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6113,12 +6167,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6126,12 +6180,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6144,12 +6198,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6157,12 +6211,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6170,12 +6224,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6183,12 +6237,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6196,12 +6250,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6209,12 +6263,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 Supply confirmation operation';
+			strRt	:= '供給確認動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 供給確認動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6227,12 +6281,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6240,12 +6294,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6253,12 +6307,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6271,12 +6325,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6284,12 +6338,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6297,12 +6351,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6310,12 +6364,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6323,12 +6377,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Foil brazing operation';
+			strRt	:= '箔ロウ巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 箔ロウ巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6336,12 +6390,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6354,12 +6408,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6367,12 +6421,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6380,12 +6434,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Welding operation';
+			strRt	:= '溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6398,12 +6452,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6411,12 +6465,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Discharge operation';
+			strRt	:= '排出受取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 排出受取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6424,12 +6478,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Measurement preparation
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 Measurement preparation';
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 排出受渡し動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6437,12 +6491,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Measurement operation during winding
+	//計測準備
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '計測準備';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 計測準備';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 Measurement operation during winding';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6455,12 +6522,12 @@
 	END_IF;
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 Return to origin operation';
+			strRt	:= '原点復帰';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 原点復帰';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6468,12 +6535,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 Gluing operation';
+			strRt	:= '糊付け動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 糊付け動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6509,15 +6576,15 @@
       </c>
       <c r="K13" t="str">
         <f ca="1"/>
-        <v>Return to origin operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L13" t="str">
         <f ca="1"/>
-        <v>Return to origin operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N13" t="str">
         <f ca="1"/>
-        <v>【21】 Return to origin operation</v>
+        <v>【21】 原点復帰動作</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -6549,7 +6616,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC13" t="str">
@@ -6557,7 +6624,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -6566,20 +6633,20 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF13" t="str">
@@ -6587,24 +6654,24 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Return to origin operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';</v>
       </c>
       <c r="AG13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH13" t="str">
@@ -6612,12 +6679,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -6626,12 +6693,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6641,12 +6708,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6657,12 +6724,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6676,12 +6743,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6695,12 +6762,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6742,15 +6809,15 @@
       </c>
       <c r="K14" t="str">
         <f ca="1"/>
-        <v>Preparation for supply operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="L14" t="str">
         <f ca="1"/>
-        <v>Preparation for supply operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="N14" t="str">
         <f ca="1"/>
-        <v>【22】 Preparation for supply operation</v>
+        <v>【22】 供給準備動作</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -6779,75 +6846,75 @@
       <c r="AB14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';</v>
+			strRt	:= '供給準備動作';</v>
       </c>
       <c r="AE14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Preparation for supply operation';</v>
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';</v>
       </c>
       <c r="AG14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6855,12 +6922,12 @@
       <c r="AJ14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6869,12 +6936,12 @@
       <c r="AK14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6886,12 +6953,12 @@
       <c r="AL14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6903,12 +6970,12 @@
       <c r="AM14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6939,15 +7006,15 @@
       </c>
       <c r="K15" t="str">
         <f ca="1"/>
-        <v>Start supply operation</v>
+        <v>供給開始動作</v>
       </c>
       <c r="L15" t="str">
         <f ca="1"/>
-        <v>Start supply operation</v>
+        <v>供給開始動作</v>
       </c>
       <c r="N15" t="str">
         <f ca="1"/>
-        <v>【23】 Start supply operation</v>
+        <v>【23】 供給開始動作</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -6976,75 +7043,75 @@
       <c r="AB15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';</v>
+			strRt	:= '供給開始動作';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
+			strRt	:= '供給開始動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Start supply operation';</v>
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7052,12 +7119,12 @@
       <c r="AJ15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7066,12 +7133,12 @@
       <c r="AK15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7083,12 +7150,12 @@
       <c r="AL15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7100,12 +7167,12 @@
       <c r="AM15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7136,15 +7203,15 @@
       </c>
       <c r="K16" t="str">
         <f ca="1"/>
-        <v>Supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="L16" t="str">
         <f ca="1"/>
-        <v>Supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="N16" t="str">
         <f ca="1"/>
-        <v>【24】 Supply operation</v>
+        <v>【24】 供給動作</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -7173,75 +7240,75 @@
       <c r="AB16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';</v>
+			strRt	:= '供給動作';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply operation';</v>
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7249,12 +7316,12 @@
       <c r="AJ16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7263,12 +7330,12 @@
       <c r="AK16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7280,12 +7347,12 @@
       <c r="AL16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7297,12 +7364,12 @@
       <c r="AM16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7333,15 +7400,15 @@
       </c>
       <c r="K17" t="str">
         <f ca="1"/>
-        <v>Cut operation</v>
+        <v>カット動作</v>
       </c>
       <c r="L17" t="str">
         <f ca="1"/>
-        <v>Cut operation</v>
+        <v>カット動作</v>
       </c>
       <c r="N17" t="str">
         <f ca="1"/>
-        <v>【25】 Cut operation</v>
+        <v>【25】 カット動作</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -7370,75 +7437,75 @@
       <c r="AB17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';</v>
+			strRt	:= 'カット動作';</v>
       </c>
       <c r="AE17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
+			strRt	:= 'カット動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Cut operation';</v>
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 カット動作';</v>
       </c>
       <c r="AG17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 カット動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7446,12 +7513,12 @@
       <c r="AJ17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7460,12 +7527,12 @@
       <c r="AK17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7477,12 +7544,12 @@
       <c r="AL17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7494,12 +7561,12 @@
       <c r="AM17" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7530,15 +7597,15 @@
       </c>
       <c r="K18" t="str">
         <f ca="1"/>
-        <v>Supply confirmation operation</v>
+        <v>供給確認動作</v>
       </c>
       <c r="L18" t="str">
         <f ca="1"/>
-        <v>Supply confirmation operation</v>
+        <v>供給確認動作</v>
       </c>
       <c r="N18" t="str">
         <f ca="1"/>
-        <v>【26】 Supply confirmation operation</v>
+        <v>【26】 供給確認動作</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -7567,75 +7634,75 @@
       <c r="AB18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';</v>
+			strRt	:= '供給確認動作';</v>
       </c>
       <c r="AE18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
+			strRt	:= '供給確認動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 Supply confirmation operation';</v>
+			strRt	:= '供給確認動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 供給確認動作';</v>
       </c>
       <c r="AG18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 Supply confirmation operation';
+			strRt	:= '供給確認動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 供給確認動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 Supply confirmation operation';
+			strRt	:= '供給確認動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 供給確認動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 Supply confirmation operation';
+			strRt	:= '供給確認動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 供給確認動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7643,12 +7710,12 @@
       <c r="AJ18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 Supply confirmation operation';
+			strRt	:= '供給確認動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 供給確認動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7657,12 +7724,12 @@
       <c r="AK18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 Supply confirmation operation';
+			strRt	:= '供給確認動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 供給確認動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7674,12 +7741,12 @@
       <c r="AL18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 Supply confirmation operation';
+			strRt	:= '供給確認動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 供給確認動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7691,12 +7758,12 @@
       <c r="AM18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 Supply confirmation operation';
+			strRt	:= '供給確認動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 供給確認動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8125,7 +8192,7 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <f>F13+1</f>
@@ -8147,15 +8214,15 @@
       </c>
       <c r="K23" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L23" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N23" t="str">
         <f ca="1"/>
-        <v>【31】 Home return operation</v>
+        <v>【31】 原点復帰動作</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -8187,7 +8254,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC23" t="str">
@@ -8195,7 +8262,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -8204,20 +8271,20 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF23" t="str">
@@ -8225,24 +8292,24 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';</v>
       </c>
       <c r="AG23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH23" t="str">
@@ -8250,12 +8317,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -8264,12 +8331,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8279,12 +8346,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8295,12 +8362,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8314,12 +8381,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8333,12 +8400,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8369,15 +8436,15 @@
       </c>
       <c r="K24" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="L24" t="str">
         <f ca="1"/>
-        <v>Supply preparation operation</v>
+        <v>供給準備動作</v>
       </c>
       <c r="N24" t="str">
         <f ca="1"/>
-        <v>【32】 Supply preparation operation</v>
+        <v>【32】 供給準備動作</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -8406,75 +8473,75 @@
       <c r="AB24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';</v>
+			strRt	:= '供給準備動作';</v>
       </c>
       <c r="AE24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
+			strRt	:= '供給準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';</v>
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';</v>
       </c>
       <c r="AG24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8482,12 +8549,12 @@
       <c r="AJ24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8496,12 +8563,12 @@
       <c r="AK24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8513,12 +8580,12 @@
       <c r="AL24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8530,12 +8597,12 @@
       <c r="AM24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8572,15 +8639,15 @@
       </c>
       <c r="K25" t="str">
         <f ca="1"/>
-        <v>supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="L25" t="str">
         <f ca="1"/>
-        <v>supply operation</v>
+        <v>供給動作</v>
       </c>
       <c r="N25" t="str">
         <f ca="1"/>
-        <v>【33】 supply operation</v>
+        <v>【33】 供給動作</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -8609,75 +8676,75 @@
       <c r="AB25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';</v>
+			strRt	:= '供給動作';</v>
       </c>
       <c r="AE25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
+			strRt	:= '供給動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 supply operation';</v>
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 供給動作';</v>
       </c>
       <c r="AG25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8685,12 +8752,12 @@
       <c r="AJ25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8699,12 +8766,12 @@
       <c r="AK25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8716,12 +8783,12 @@
       <c r="AL25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8733,12 +8800,12 @@
       <c r="AM25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9513,15 +9580,15 @@
       </c>
       <c r="K33" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L33" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N33" t="str">
         <f ca="1"/>
-        <v>【41】 Home return operation</v>
+        <v>【41】 原点復帰動作</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -9553,7 +9620,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC33" t="str">
@@ -9561,7 +9628,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -9570,20 +9637,20 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF33" t="str">
@@ -9591,24 +9658,24 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';</v>
       </c>
       <c r="AG33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH33" t="str">
@@ -9616,12 +9683,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -9630,12 +9697,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9645,12 +9712,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9661,12 +9728,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9680,12 +9747,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9699,12 +9766,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9735,15 +9802,15 @@
       </c>
       <c r="K34" t="str">
         <f ca="1"/>
-        <v>Circumference gauge preset</v>
+        <v>周長測定子プリセット</v>
       </c>
       <c r="L34" t="str">
         <f ca="1"/>
-        <v>Circumference gauge preset</v>
+        <v>周長測定子プリセット</v>
       </c>
       <c r="N34" t="str">
         <f ca="1"/>
-        <v>【42】 Circumference gauge preset</v>
+        <v>【42】 周長測定子プリセット</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -9772,75 +9839,75 @@
       <c r="AB34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';</v>
+			strRt	:= '周長測定子プリセット';</v>
       </c>
       <c r="AE34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';</v>
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';</v>
       </c>
       <c r="AG34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9848,12 +9915,12 @@
       <c r="AJ34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9862,12 +9929,12 @@
       <c r="AK34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9879,12 +9946,12 @@
       <c r="AL34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9896,12 +9963,12 @@
       <c r="AM34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9932,15 +9999,15 @@
       </c>
       <c r="K35" t="str">
         <f ca="1"/>
-        <v>Winding preparation operation</v>
+        <v>巻き準備動作</v>
       </c>
       <c r="L35" t="str">
         <f ca="1"/>
-        <v>Winding preparation operation</v>
+        <v>巻き準備動作</v>
       </c>
       <c r="N35" t="str">
         <f ca="1"/>
-        <v>【43】 Winding preparation operation</v>
+        <v>【43】 巻き準備動作</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -9969,75 +10036,75 @@
       <c r="AB35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';</v>
+			strRt	:= '巻き準備動作';</v>
       </c>
       <c r="AE35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
+			strRt	:= '巻き準備動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';</v>
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';</v>
       </c>
       <c r="AG35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10045,12 +10112,12 @@
       <c r="AJ35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10059,12 +10126,12 @@
       <c r="AK35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10076,12 +10143,12 @@
       <c r="AL35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10093,12 +10160,12 @@
       <c r="AM35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10129,15 +10196,15 @@
       </c>
       <c r="K36" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻き動作</v>
       </c>
       <c r="L36" t="str">
         <f ca="1"/>
-        <v>Winding operation</v>
+        <v>巻き動作</v>
       </c>
       <c r="N36" t="str">
         <f ca="1"/>
-        <v>【44】 Winding operation</v>
+        <v>【44】 巻き動作</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -10166,75 +10233,75 @@
       <c r="AB36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';</v>
+			strRt	:= '巻き動作';</v>
       </c>
       <c r="AE36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
+			strRt	:= '巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';</v>
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';</v>
       </c>
       <c r="AG36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10242,12 +10309,12 @@
       <c r="AJ36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10256,12 +10323,12 @@
       <c r="AK36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10273,12 +10340,12 @@
       <c r="AL36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10290,12 +10357,12 @@
       <c r="AM36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10326,15 +10393,15 @@
       </c>
       <c r="K37" t="str">
         <f ca="1"/>
-        <v>Foil brazing operation</v>
+        <v>箔ロウ巻き動作</v>
       </c>
       <c r="L37" t="str">
         <f ca="1"/>
-        <v>Foil brazing operation</v>
+        <v>箔ロウ巻き動作</v>
       </c>
       <c r="N37" t="str">
         <f ca="1"/>
-        <v>【45】 Foil brazing operation</v>
+        <v>【45】 箔ロウ巻き動作</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -10363,75 +10430,75 @@
       <c r="AB37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';</v>
+			strRt	:= '箔ロウ巻き動作';</v>
       </c>
       <c r="AE37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
+			strRt	:= '箔ロウ巻き動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Foil brazing operation';</v>
+			strRt	:= '箔ロウ巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 箔ロウ巻き動作';</v>
       </c>
       <c r="AG37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Foil brazing operation';
+			strRt	:= '箔ロウ巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 箔ロウ巻き動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Foil brazing operation';
+			strRt	:= '箔ロウ巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 箔ロウ巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Foil brazing operation';
+			strRt	:= '箔ロウ巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 箔ロウ巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10439,12 +10506,12 @@
       <c r="AJ37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Foil brazing operation';
+			strRt	:= '箔ロウ巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 箔ロウ巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10453,12 +10520,12 @@
       <c r="AK37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Foil brazing operation';
+			strRt	:= '箔ロウ巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 箔ロウ巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10470,12 +10537,12 @@
       <c r="AL37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Foil brazing operation';
+			strRt	:= '箔ロウ巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 箔ロウ巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10487,12 +10554,12 @@
       <c r="AM37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Foil brazing operation';
+			strRt	:= '箔ロウ巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 箔ロウ巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10523,15 +10590,15 @@
       </c>
       <c r="K38" t="str">
         <f ca="1"/>
-        <v>Circumference measurement operation</v>
+        <v>周長測定動作</v>
       </c>
       <c r="L38" t="str">
         <f ca="1"/>
-        <v>Circumference measurement operation</v>
+        <v>周長測定動作</v>
       </c>
       <c r="N38" t="str">
         <f ca="1"/>
-        <v>【46】 Circumference measurement operation</v>
+        <v>【46】 周長測定動作</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -10560,75 +10627,75 @@
       <c r="AB38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';</v>
+			strRt	:= '周長測定動作';</v>
       </c>
       <c r="AE38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
+			strRt	:= '周長測定動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';</v>
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';</v>
       </c>
       <c r="AG38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10636,12 +10703,12 @@
       <c r="AJ38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10650,12 +10717,12 @@
       <c r="AK38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10667,12 +10734,12 @@
       <c r="AL38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10684,12 +10751,12 @@
       <c r="AM38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11134,15 +11201,15 @@
       </c>
       <c r="K43" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L43" t="str">
         <f ca="1"/>
-        <v>Home return operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N43" t="str">
         <f ca="1"/>
-        <v>【51】 Home return operation</v>
+        <v>【51】 原点復帰動作</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -11174,7 +11241,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC43" t="str">
@@ -11182,7 +11249,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -11191,20 +11258,20 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF43" t="str">
@@ -11212,24 +11279,24 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';</v>
       </c>
       <c r="AG43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH43" t="str">
@@ -11237,12 +11304,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -11251,12 +11318,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11266,12 +11333,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11282,12 +11349,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11301,12 +11368,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11320,12 +11387,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11356,15 +11423,15 @@
       </c>
       <c r="K44" t="str">
         <f ca="1"/>
-        <v>Winding clamping operation</v>
+        <v>巻き押え動作</v>
       </c>
       <c r="L44" t="str">
         <f ca="1"/>
-        <v>Winding clamping operation</v>
+        <v>巻き押え動作</v>
       </c>
       <c r="N44" t="str">
         <f ca="1"/>
-        <v>【52】 Winding clamping operation</v>
+        <v>【52】 巻き押え動作</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -11393,75 +11460,75 @@
       <c r="AB44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';</v>
+			strRt	:= '巻き押え動作';</v>
       </c>
       <c r="AE44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
+			strRt	:= '巻き押え動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';</v>
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';</v>
       </c>
       <c r="AG44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11469,12 +11536,12 @@
       <c r="AJ44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11483,12 +11550,12 @@
       <c r="AK44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11500,12 +11567,12 @@
       <c r="AL44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11517,12 +11584,12 @@
       <c r="AM44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11553,15 +11620,15 @@
       </c>
       <c r="K45" t="str">
         <f ca="1"/>
-        <v>Welding operation</v>
+        <v>溶接動作</v>
       </c>
       <c r="L45" t="str">
         <f ca="1"/>
-        <v>Welding operation</v>
+        <v>溶接動作</v>
       </c>
       <c r="N45" t="str">
         <f ca="1"/>
-        <v>【53】 Welding operation</v>
+        <v>【53】 溶接動作</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -11590,75 +11657,75 @@
       <c r="AB45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';</v>
+			strRt	:= '溶接動作';</v>
       </c>
       <c r="AE45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
+			strRt	:= '溶接動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Welding operation';</v>
+			strRt	:= '溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 溶接動作';</v>
       </c>
       <c r="AG45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Welding operation';
+			strRt	:= '溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 溶接動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Welding operation';
+			strRt	:= '溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Welding operation';
+			strRt	:= '溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11666,12 +11733,12 @@
       <c r="AJ45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Welding operation';
+			strRt	:= '溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11680,12 +11747,12 @@
       <c r="AK45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Welding operation';
+			strRt	:= '溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11697,12 +11764,12 @@
       <c r="AL45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Welding operation';
+			strRt	:= '溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11714,12 +11781,12 @@
       <c r="AM45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Welding operation';
+			strRt	:= '溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12470,15 +12537,15 @@
       </c>
       <c r="K53" t="str">
         <f ca="1"/>
-        <v>Return to origin operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="L53" t="str">
         <f ca="1"/>
-        <v>Return to origin operation</v>
+        <v>原点復帰動作</v>
       </c>
       <c r="N53" t="str">
         <f ca="1"/>
-        <v>【61】 Return to origin operation</v>
+        <v>【61】 原点復帰動作</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -12510,7 +12577,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC53" t="str">
@@ -12518,7 +12585,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -12527,20 +12594,20 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';</v>
+			strRt	:= '原点復帰動作';</v>
       </c>
       <c r="AE53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
+			strRt	:= '原点復帰動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF53" t="str">
@@ -12548,24 +12615,24 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Return to origin operation';</v>
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';</v>
       </c>
       <c r="AG53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH53" t="str">
@@ -12573,12 +12640,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -12587,12 +12654,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12602,12 +12669,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12618,12 +12685,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12637,12 +12704,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12656,12 +12723,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12692,15 +12759,15 @@
       </c>
       <c r="K54" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v>排出受取り動作</v>
       </c>
       <c r="L54" t="str">
         <f ca="1"/>
-        <v>Discharge operation</v>
+        <v>排出受取り動作</v>
       </c>
       <c r="N54" t="str">
         <f ca="1"/>
-        <v>【62】 Discharge operation</v>
+        <v>【62】 排出受取り動作</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -12729,75 +12796,75 @@
       <c r="AB54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';</v>
+			strRt	:= '排出受取り動作';</v>
       </c>
       <c r="AE54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
+			strRt	:= '排出受取り動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Discharge operation';</v>
+			strRt	:= '排出受取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 排出受取り動作';</v>
       </c>
       <c r="AG54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Discharge operation';
+			strRt	:= '排出受取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 排出受取り動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Discharge operation';
+			strRt	:= '排出受取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 排出受取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Discharge operation';
+			strRt	:= '排出受取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 排出受取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12805,12 +12872,12 @@
       <c r="AJ54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Discharge operation';
+			strRt	:= '排出受取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 排出受取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12819,12 +12886,12 @@
       <c r="AK54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Discharge operation';
+			strRt	:= '排出受取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 排出受取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12836,12 +12903,12 @@
       <c r="AL54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Discharge operation';
+			strRt	:= '排出受取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 排出受取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12853,12 +12920,12 @@
       <c r="AM54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Discharge operation';
+			strRt	:= '排出受取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 排出受取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12884,26 +12951,26 @@
       <c r="I55" t="str">
         <v/>
       </c>
-      <c r="J55" t="str">
-        <v/>
+      <c r="J55">
+        <v>26</v>
       </c>
       <c r="K55" t="str">
         <f ca="1"/>
-        <v/>
+        <v>排出受渡し動作</v>
       </c>
       <c r="L55" t="str">
         <f ca="1"/>
-        <v/>
+        <v>排出受渡し動作</v>
       </c>
       <c r="N55" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【63】 排出受渡し動作</v>
       </c>
       <c r="O55" t="str">
         <v/>
       </c>
       <c r="P55" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q55" t="str">
         <f ca="1"/>
@@ -12911,63 +12978,158 @@
       </c>
       <c r="R55" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';</v>
       </c>
       <c r="AE55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 排出受渡し動作';</v>
       </c>
       <c r="AG55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 排出受渡し動作';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 排出受渡し動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 排出受渡し動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 排出受渡し動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 排出受渡し動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 排出受渡し動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM55" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 排出受渡し動作';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="56" spans="6:39" x14ac:dyDescent="0.55000000000000004">
@@ -13191,19 +13353,19 @@
         <v/>
       </c>
       <c r="J58">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K58" t="str">
         <f ca="1"/>
-        <v>Measurement preparation</v>
+        <v>計測準備</v>
       </c>
       <c r="L58" t="str">
         <f ca="1"/>
-        <v>Measurement preparation</v>
+        <v>計測準備</v>
       </c>
       <c r="N58" t="str">
         <f ca="1"/>
-        <v>【66】 Measurement preparation</v>
+        <v>【66】 計測準備</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -13232,75 +13394,75 @@
       <c r="AB58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';</v>
+			strRt	:= '計測準備';</v>
       </c>
       <c r="AE58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
+			strRt	:= '計測準備';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 Measurement preparation';</v>
+			strRt	:= '計測準備';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 計測準備';</v>
       </c>
       <c r="AG58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 Measurement preparation';
+			strRt	:= '計測準備';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 計測準備';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 Measurement preparation';
+			strRt	:= '計測準備';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 Measurement preparation';
+			strRt	:= '計測準備';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13308,12 +13470,12 @@
       <c r="AJ58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 Measurement preparation';
+			strRt	:= '計測準備';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13322,12 +13484,12 @@
       <c r="AK58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 Measurement preparation';
+			strRt	:= '計測準備';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13339,12 +13501,12 @@
       <c r="AL58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 Measurement preparation';
+			strRt	:= '計測準備';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13356,12 +13518,12 @@
       <c r="AM58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement preparation
+	//計測準備
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 Measurement preparation';
+			strRt	:= '計測準備';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 計測準備';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13388,19 +13550,19 @@
         <v/>
       </c>
       <c r="J59">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K59" t="str">
         <f ca="1"/>
-        <v>Measurement operation during winding</v>
+        <v>巻き中測定動作</v>
       </c>
       <c r="L59" t="str">
         <f ca="1"/>
-        <v>Measurement operation during winding</v>
+        <v>巻き中測定動作</v>
       </c>
       <c r="N59" t="str">
         <f ca="1"/>
-        <v>【67】 Measurement operation during winding</v>
+        <v>【67】 巻き中測定動作</v>
       </c>
       <c r="O59" t="str">
         <v/>
@@ -13429,75 +13591,75 @@
       <c r="AB59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';</v>
+			strRt	:= '巻き中測定動作';</v>
       </c>
       <c r="AE59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
+			strRt	:= '巻き中測定動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 Measurement operation during winding';</v>
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 巻き中測定動作';</v>
       </c>
       <c r="AG59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 Measurement operation during winding';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 Measurement operation during winding';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 Measurement operation during winding';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13505,12 +13667,12 @@
       <c r="AJ59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 Measurement operation during winding';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13519,12 +13681,12 @@
       <c r="AK59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 Measurement operation during winding';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13536,12 +13698,12 @@
       <c r="AL59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 Measurement operation during winding';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13553,12 +13715,12 @@
       <c r="AM59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Measurement operation during winding
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 Measurement operation during winding';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13897,19 +14059,19 @@
         <v/>
       </c>
       <c r="J63">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K63" t="str">
         <f ca="1"/>
-        <v>Return to origin operation</v>
+        <v>原点復帰</v>
       </c>
       <c r="L63" t="str">
         <f ca="1"/>
-        <v>Return to origin operation</v>
+        <v>原点復帰</v>
       </c>
       <c r="N63" t="str">
         <f ca="1"/>
-        <v>【71】 Return to origin operation</v>
+        <v>【71】 原点復帰</v>
       </c>
       <c r="O63" t="str">
         <v/>
@@ -13941,7 +14103,7 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC63" t="str">
@@ -13949,7 +14111,7 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -13958,20 +14120,20 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';</v>
+			strRt	:= '原点復帰';</v>
       </c>
       <c r="AE63" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
+			strRt	:= '原点復帰';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF63" t="str">
@@ -13979,24 +14141,24 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 Return to origin operation';</v>
+			strRt	:= '原点復帰';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 原点復帰';</v>
       </c>
       <c r="AG63" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 Return to origin operation';
+			strRt	:= '原点復帰';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 原点復帰';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH63" t="str">
@@ -14004,12 +14166,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 Return to origin operation';
+			strRt	:= '原点復帰';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 原点復帰';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -14018,12 +14180,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 Return to origin operation';
+			strRt	:= '原点復帰';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 原点復帰';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14033,12 +14195,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 Return to origin operation';
+			strRt	:= '原点復帰';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 原点復帰';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14049,12 +14211,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 Return to origin operation';
+			strRt	:= '原点復帰';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 原点復帰';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14068,12 +14230,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 Return to origin operation';
+			strRt	:= '原点復帰';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 原点復帰';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14087,12 +14249,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 Return to origin operation';
+			strRt	:= '原点復帰';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 原点復帰';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14527,19 +14689,19 @@
         <v/>
       </c>
       <c r="J68">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K68" t="str">
         <f ca="1"/>
-        <v>Gluing operation</v>
+        <v>糊付け動作</v>
       </c>
       <c r="L68" t="str">
         <f ca="1"/>
-        <v>Gluing operation</v>
+        <v>糊付け動作</v>
       </c>
       <c r="N68" t="str">
         <f ca="1"/>
-        <v>【76】 Gluing operation</v>
+        <v>【76】 糊付け動作</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -14568,75 +14730,75 @@
       <c r="AB68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';</v>
+			strRt	:= '糊付け動作';</v>
       </c>
       <c r="AE68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
+			strRt	:= '糊付け動作';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 Gluing operation';</v>
+			strRt	:= '糊付け動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 糊付け動作';</v>
       </c>
       <c r="AG68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 Gluing operation';
+			strRt	:= '糊付け動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 糊付け動作';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 Gluing operation';
+			strRt	:= '糊付け動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 糊付け動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 Gluing operation';
+			strRt	:= '糊付け動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 糊付け動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14644,12 +14806,12 @@
       <c r="AJ68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 Gluing operation';
+			strRt	:= '糊付け動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 糊付け動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14658,12 +14820,12 @@
       <c r="AK68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 Gluing operation';
+			strRt	:= '糊付け動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 糊付け動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14675,12 +14837,12 @@
       <c r="AL68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 Gluing operation';
+			strRt	:= '糊付け動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 糊付け動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14692,12 +14854,12 @@
       <c r="AM68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 Gluing operation';
+			strRt	:= '糊付け動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 糊付け動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28384,15 +28546,15 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28400,12 +28562,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28413,12 +28575,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28426,12 +28588,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28439,12 +28601,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28457,12 +28619,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28470,12 +28632,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Preparation for supply operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Preparation for supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 Preparation for supply operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28483,12 +28645,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Start supply operation
+	//供給開始動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Start supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 Start supply operation';
+			strRt	:= '供給開始動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 供給開始動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28496,12 +28658,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 Supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28509,12 +28671,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Cut operation
+	//カット動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Cut operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 Cut operation';
+			strRt	:= 'カット動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【25】 カット動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28522,12 +28684,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply confirmation operation
+	//供給確認動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply confirmation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 Supply confirmation operation';
+			strRt	:= '供給確認動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 供給確認動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28540,12 +28702,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28553,12 +28715,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Supply preparation operation
+	//供給準備動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Supply preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 Supply preparation operation';
+			strRt	:= '供給準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 供給準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28566,12 +28728,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//supply operation
+	//供給動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'supply operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 supply operation';
+			strRt	:= '供給動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 供給動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28584,12 +28746,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28597,12 +28759,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference gauge preset
+	//周長測定子プリセット
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference gauge preset';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 Circumference gauge preset';
+			strRt	:= '周長測定子プリセット';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 周長測定子プリセット';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28610,12 +28772,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding preparation operation
+	//巻き準備動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding preparation operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 Winding preparation operation';
+			strRt	:= '巻き準備動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 巻き準備動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28623,12 +28785,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding operation
+	//巻き動作
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 Winding operation';
+			strRt	:= '巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28636,12 +28798,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Foil brazing operation
+	//箔ロウ巻き動作
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Foil brazing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 Foil brazing operation';
+			strRt	:= '箔ロウ巻き動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 箔ロウ巻き動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28649,12 +28811,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Circumference measurement operation
+	//周長測定動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Circumference measurement operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 Circumference measurement operation';
+			strRt	:= '周長測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 周長測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28667,12 +28829,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//Home return operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Home return operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 Home return operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28680,12 +28842,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Winding clamping operation
+	//巻き押え動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Winding clamping operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 Winding clamping operation';
+			strRt	:= '巻き押え動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 巻き押え動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28693,12 +28855,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Welding operation
+	//溶接動作
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Welding operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 Welding operation';
+			strRt	:= '溶接動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 溶接動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28711,12 +28873,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//Return to origin operation
+	//原点復帰動作
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 Return to origin operation';
+			strRt	:= '原点復帰動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 原点復帰動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28724,12 +28886,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Discharge operation
+	//排出受取り動作
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Discharge operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 Discharge operation';
+			strRt	:= '排出受取り動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 排出受取り動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28737,12 +28899,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Measurement preparation
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement preparation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 Measurement preparation';
+	//排出受渡し動作
+	ELSIF uiInfoIdx = 3 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '排出受渡し動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 排出受渡し動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28750,12 +28912,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Measurement operation during winding
+	//計測準備
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= '計測準備';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 計測準備';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//巻き中測定動作
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Measurement operation during winding';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 Measurement operation during winding';
+			strRt	:= '巻き中測定動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 巻き中測定動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28768,12 +28943,12 @@
 	END_IF;
 //7
 ELSIF strInfoType = 7 THEN
-	//Return to origin operation
+	//原点復帰
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Return to origin operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 Return to origin operation';
+			strRt	:= '原点復帰';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 原点復帰';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28781,12 +28956,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//Gluing operation
+	//糊付け動作
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'Gluing operation';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 Gluing operation';
+			strRt	:= '糊付け動作';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 糊付け動作';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3A82A81-B822-4F91-BBE6-35EBB83BEF3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0783D7D-DDBA-499E-897B-40F1A1736272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -1808,10 +1808,10 @@
         <v>73</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1843,10 +1843,10 @@
         <v>73</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1870,18 +1870,17 @@
         <v>2</v>
       </c>
       <c r="E11" s="4">
-        <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1906,17 +1905,17 @@
       </c>
       <c r="E12" s="4">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -4575,7 +4574,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -4594,15 +4593,15 @@
       </c>
       <c r="K3" t="str" cm="1">
         <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$92,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$92&amp;info_index!$E$2:$E$92,0),1)&amp;"","")</f>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="L3" t="str" cm="1">
         <f t="array" aca="1" ref="L3:L202" ca="1">IF(LEN(_xlfn.ANCHORARRAY($J3)),IF(LEN(_xlfn.ANCHORARRAY(K3)),_xlfn.ANCHORARRAY(K3),"unknown"),"")</f>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="N3" t="str" cm="1">
         <f t="array" aca="1" ref="N3:N202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(L3)),"【"&amp;G3:G202&amp;H3:H202&amp;"】 "&amp;_xlfn.ANCHORARRAY(L3),"")</f>
-        <v>【11】 原点復帰動作</v>
+        <v>【11】 Return to origin operation</v>
       </c>
       <c r="O3" t="str" cm="1">
         <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$92,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$92&amp;info_index!$E$2:$E$92,0),1)&amp;"","")</f>
@@ -4633,14 +4632,14 @@
         <f t="array" aca="1" ref="AB3:AB202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AA3)),_xlfn.ANCHORARRAY(AA3),"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;$B$7&amp;_xlfn.ANCHORARRAY(L3)&amp;CHAR(10)&amp;CHAR(9)&amp;IF(H3:H202=1,"IF ","ELSIF ")&amp;$B$26&amp;" = "&amp;H3:H202&amp;" THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC3" t="str" cm="1">
         <f t="array" aca="1" ref="AC3:AC202" ca="1">IF(LEN(AB3:AB202),AB3:AB202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"IF "&amp;$B$27&amp;" = '"&amp;$L$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -4648,54 +4647,54 @@
         <f t="array" aca="1" ref="AD3:AD202" ca="1">IF(LEN(AC3:AC202),AC3:AC202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(L3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE3" t="str" cm="1">
         <f t="array" aca="1" ref="AE3:AE202" ca="1">IF(LEN(AD3:AD202),AD3:AD202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;N$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF3" t="str" cm="1">
         <f t="array" aca="1" ref="AF3:AF202" ca="1">IF(LEN(AE3:AE202),AE3:AE202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(N3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';</v>
       </c>
       <c r="AG3" t="str" cm="1">
         <f t="array" aca="1" ref="AG3:AG202" ca="1">IF(LEN(AF3:AF202),AF3:AF202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;P$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH3" t="str" cm="1">
         <f t="array" aca="1" ref="AH3:AH202" ca="1">IF(LEN(AG3:AG202),AG3:AG202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(P3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -4703,12 +4702,12 @@
         <f t="array" aca="1" ref="AI3:AI202" ca="1">IF(LEN(AH3:AH202),AH3:AH202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;R$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4717,12 +4716,12 @@
         <f t="array" aca="1" ref="AJ3:AJ202" ca="1">IF(LEN(AI3:AI202),AI3:AI202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(R3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4732,12 +4731,12 @@
         <f t="array" aca="1" ref="AK3:AK202" ca="1">IF(LEN(AJ3:AJ202),AJ3:AJ202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 3"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4750,12 +4749,12 @@
         <f t="array" aca="1" ref="AL3:AL202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AK3)),_xlfn.ANCHORARRAY(AK3),"")&amp;IF(I3:I202="●",CHAR(10)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 2"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4768,12 +4767,12 @@
         <f t="array" aca="1" ref="AM3:AM202" ca="1">_xlfn.ANCHORARRAY(AL3)</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4805,15 +4804,15 @@
       </c>
       <c r="K4" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="L4" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="N4" t="str">
         <f ca="1"/>
-        <v>【12】 供給準備動作</v>
+        <v>【12】 Preparation for supply operation</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -4842,75 +4841,75 @@
       <c r="AB4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Preparation for supply operation';</v>
       </c>
       <c r="AE4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';</v>
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';</v>
       </c>
       <c r="AG4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4918,12 +4917,12 @@
       <c r="AJ4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4932,12 +4931,12 @@
       <c r="AK4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4949,12 +4948,12 @@
       <c r="AL4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4966,12 +4965,12 @@
       <c r="AM4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4987,7 +4986,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -5009,15 +5008,15 @@
       </c>
       <c r="K5" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="N5" t="str">
         <f ca="1"/>
-        <v>【13】 カット動作</v>
+        <v>【13】 Cut operation</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -5046,75 +5045,75 @@
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';</v>
+			strRt	:= 'Cut operation';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';</v>
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5122,12 +5121,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5136,12 +5135,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5153,12 +5152,12 @@
       <c r="AL5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5170,12 +5169,12 @@
       <c r="AM5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5428,15 +5427,15 @@
       </c>
       <c r="K8" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="L8" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="N8" t="str">
         <f ca="1"/>
-        <v>【16】 供給開始動作</v>
+        <v>【16】 Start supply operation</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -5465,75 +5464,75 @@
       <c r="AB8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';</v>
+			strRt	:= 'Start supply operation';</v>
       </c>
       <c r="AE8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';</v>
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';</v>
       </c>
       <c r="AG8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5541,12 +5540,12 @@
       <c r="AJ8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5555,12 +5554,12 @@
       <c r="AK8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5572,12 +5571,12 @@
       <c r="AL8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5589,12 +5588,12 @@
       <c r="AM8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5631,15 +5630,15 @@
       </c>
       <c r="K9" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply operation</v>
       </c>
       <c r="L9" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply operation</v>
       </c>
       <c r="N9" t="str">
         <f ca="1"/>
-        <v>【17】 供給動作</v>
+        <v>【17】 Supply operation</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -5668,75 +5667,75 @@
       <c r="AB9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= 'Supply operation';</v>
       </c>
       <c r="AE9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';</v>
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';</v>
       </c>
       <c r="AG9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5744,12 +5743,12 @@
       <c r="AJ9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5758,12 +5757,12 @@
       <c r="AK9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5775,12 +5774,12 @@
       <c r="AL9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5792,12 +5791,12 @@
       <c r="AM9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6125,15 +6124,15 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6141,12 +6140,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6154,12 +6153,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6167,12 +6166,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6180,12 +6179,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6198,12 +6197,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6211,12 +6210,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6224,12 +6223,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6237,12 +6236,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6250,12 +6249,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6263,12 +6262,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給確認動作
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給確認動作';
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6281,12 +6280,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6294,12 +6293,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6307,12 +6306,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6325,12 +6324,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6338,12 +6337,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6351,12 +6350,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6364,12 +6363,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6377,12 +6376,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6390,12 +6389,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6408,12 +6407,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6421,12 +6420,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6434,12 +6433,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6452,12 +6451,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6465,12 +6464,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6478,12 +6477,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6491,12 +6490,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6504,12 +6503,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6522,12 +6521,12 @@
 	END_IF;
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6535,12 +6534,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6576,15 +6575,15 @@
       </c>
       <c r="K13" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="L13" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="N13" t="str">
         <f ca="1"/>
-        <v>【21】 原点復帰動作</v>
+        <v>【21】 Return to origin operation</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -6616,7 +6615,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC13" t="str">
@@ -6624,7 +6623,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -6633,20 +6632,20 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF13" t="str">
@@ -6654,24 +6653,24 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';</v>
       </c>
       <c r="AG13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH13" t="str">
@@ -6679,12 +6678,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -6693,12 +6692,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6708,12 +6707,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6724,12 +6723,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6743,12 +6742,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6762,12 +6761,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6809,15 +6808,15 @@
       </c>
       <c r="K14" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="L14" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="N14" t="str">
         <f ca="1"/>
-        <v>【22】 供給準備動作</v>
+        <v>【22】 Preparation for supply operation</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -6846,75 +6845,75 @@
       <c r="AB14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Preparation for supply operation';</v>
       </c>
       <c r="AE14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';</v>
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';</v>
       </c>
       <c r="AG14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6922,12 +6921,12 @@
       <c r="AJ14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6936,12 +6935,12 @@
       <c r="AK14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6953,12 +6952,12 @@
       <c r="AL14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6970,12 +6969,12 @@
       <c r="AM14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7006,15 +7005,15 @@
       </c>
       <c r="K15" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="L15" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="N15" t="str">
         <f ca="1"/>
-        <v>【23】 供給開始動作</v>
+        <v>【23】 Cut operation</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -7043,75 +7042,75 @@
       <c r="AB15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';</v>
+			strRt	:= 'Cut operation';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';</v>
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7119,12 +7118,12 @@
       <c r="AJ15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7133,12 +7132,12 @@
       <c r="AK15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7150,12 +7149,12 @@
       <c r="AL15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7167,12 +7166,12 @@
       <c r="AM15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7203,15 +7202,15 @@
       </c>
       <c r="K16" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply confirmation operation</v>
       </c>
       <c r="L16" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply confirmation operation</v>
       </c>
       <c r="N16" t="str">
         <f ca="1"/>
-        <v>【24】 供給動作</v>
+        <v>【24】 Supply confirmation operation</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -7240,75 +7239,75 @@
       <c r="AB16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= 'Supply confirmation operation';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply confirmation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';</v>
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7316,12 +7315,12 @@
       <c r="AJ16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7330,12 +7329,12 @@
       <c r="AK16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7347,12 +7346,12 @@
       <c r="AL16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7364,12 +7363,12 @@
       <c r="AM16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7395,26 +7394,26 @@
       <c r="I17" t="str">
         <v/>
       </c>
-      <c r="J17">
-        <v>10</v>
+      <c r="J17" t="str">
+        <v/>
       </c>
       <c r="K17" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v/>
       </c>
       <c r="L17" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v/>
       </c>
       <c r="N17" t="str">
         <f ca="1"/>
-        <v>【25】 カット動作</v>
+        <v/>
       </c>
       <c r="O17" t="str">
         <v/>
       </c>
       <c r="P17" t="str">
-        <v>unknown</v>
+        <v/>
       </c>
       <c r="Q17" t="str">
         <f ca="1"/>
@@ -7422,158 +7421,63 @@
       </c>
       <c r="R17" t="str">
         <f ca="1"/>
-        <v>unknown</v>
+        <v/>
       </c>
       <c r="Z17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-</v>
+        <v/>
       </c>
       <c r="AA17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-</v>
+        <v/>
       </c>
       <c r="AB17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN</v>
+        <v/>
       </c>
       <c r="AC17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN</v>
+        <v/>
       </c>
       <c r="AD17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';</v>
+        <v/>
       </c>
       <c r="AE17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN</v>
+        <v/>
       </c>
       <c r="AF17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';</v>
+        <v/>
       </c>
       <c r="AG17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
-		ELSIF strInfoKey = 'model' THEN</v>
+        <v/>
       </c>
       <c r="AH17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';</v>
+        <v/>
       </c>
       <c r="AI17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN</v>
+        <v/>
       </c>
       <c r="AJ17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';</v>
+        <v/>
       </c>
       <c r="AK17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;</v>
+        <v/>
       </c>
       <c r="AL17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;</v>
+        <v/>
       </c>
       <c r="AM17" t="str">
         <f ca="1"/>
-        <v xml:space="preserve">
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
-		ELSIF strInfoKey = 'model' THEN
-			strRt	:= 'unknown';
-		ELSIF strInfoKey = 'mf' THEN
-			strRt	:= 'unknown';
-		ELSE
-			uiErrCode	:= 3;
-		END_IF;</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.55000000000000004">
@@ -7593,19 +7497,19 @@
         <v/>
       </c>
       <c r="J18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K18" t="str">
         <f ca="1"/>
-        <v>供給確認動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="L18" t="str">
         <f ca="1"/>
-        <v>供給確認動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="N18" t="str">
         <f ca="1"/>
-        <v>【26】 供給確認動作</v>
+        <v>【26】 Start supply operation</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -7634,75 +7538,75 @@
       <c r="AB18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';</v>
+			strRt	:= 'Start supply operation';</v>
       </c>
       <c r="AE18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給確認動作';</v>
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';</v>
       </c>
       <c r="AG18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給確認動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給確認動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給確認動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7710,12 +7614,12 @@
       <c r="AJ18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給確認動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7724,12 +7628,12 @@
       <c r="AK18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給確認動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7741,12 +7645,12 @@
       <c r="AL18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給確認動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7758,12 +7662,12 @@
       <c r="AM18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給確認動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7789,26 +7693,26 @@
       <c r="I19" t="str">
         <v/>
       </c>
-      <c r="J19" t="str">
-        <v/>
+      <c r="J19">
+        <v>11</v>
       </c>
       <c r="K19" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Supply operation</v>
       </c>
       <c r="L19" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Supply operation</v>
       </c>
       <c r="N19" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【27】 Supply operation</v>
       </c>
       <c r="O19" t="str">
         <v/>
       </c>
       <c r="P19" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q19" t="str">
         <f ca="1"/>
@@ -7816,63 +7720,158 @@
       </c>
       <c r="R19" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';</v>
       </c>
       <c r="AE19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';</v>
       </c>
       <c r="AG19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM19" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.55000000000000004">
@@ -8192,7 +8191,7 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <f>F13+1</f>
@@ -8214,15 +8213,15 @@
       </c>
       <c r="K23" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L23" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N23" t="str">
         <f ca="1"/>
-        <v>【31】 原点復帰動作</v>
+        <v>【31】 Home return operation</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -8254,7 +8253,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC23" t="str">
@@ -8262,7 +8261,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -8271,20 +8270,20 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF23" t="str">
@@ -8292,24 +8291,24 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';</v>
       </c>
       <c r="AG23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH23" t="str">
@@ -8317,12 +8316,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -8331,12 +8330,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8346,12 +8345,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8362,12 +8361,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8381,12 +8380,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8400,12 +8399,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8436,15 +8435,15 @@
       </c>
       <c r="K24" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="L24" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="N24" t="str">
         <f ca="1"/>
-        <v>【32】 供給準備動作</v>
+        <v>【32】 Supply preparation operation</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -8473,75 +8472,75 @@
       <c r="AB24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';</v>
       </c>
       <c r="AE24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';</v>
       </c>
       <c r="AG24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8549,12 +8548,12 @@
       <c r="AJ24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8563,12 +8562,12 @@
       <c r="AK24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8580,12 +8579,12 @@
       <c r="AL24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8597,12 +8596,12 @@
       <c r="AM24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8639,15 +8638,15 @@
       </c>
       <c r="K25" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>supply operation</v>
       </c>
       <c r="L25" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>supply operation</v>
       </c>
       <c r="N25" t="str">
         <f ca="1"/>
-        <v>【33】 供給動作</v>
+        <v>【33】 supply operation</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -8676,75 +8675,75 @@
       <c r="AB25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= 'supply operation';</v>
       </c>
       <c r="AE25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';</v>
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';</v>
       </c>
       <c r="AG25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8752,12 +8751,12 @@
       <c r="AJ25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8766,12 +8765,12 @@
       <c r="AK25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8783,12 +8782,12 @@
       <c r="AL25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8800,12 +8799,12 @@
       <c r="AM25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9580,15 +9579,15 @@
       </c>
       <c r="K33" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L33" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N33" t="str">
         <f ca="1"/>
-        <v>【41】 原点復帰動作</v>
+        <v>【41】 Home return operation</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -9620,7 +9619,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC33" t="str">
@@ -9628,7 +9627,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -9637,20 +9636,20 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF33" t="str">
@@ -9658,24 +9657,24 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';</v>
       </c>
       <c r="AG33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH33" t="str">
@@ -9683,12 +9682,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -9697,12 +9696,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9712,12 +9711,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9728,12 +9727,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9747,12 +9746,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9766,12 +9765,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9802,15 +9801,15 @@
       </c>
       <c r="K34" t="str">
         <f ca="1"/>
-        <v>周長測定子プリセット</v>
+        <v>Circumference gauge preset</v>
       </c>
       <c r="L34" t="str">
         <f ca="1"/>
-        <v>周長測定子プリセット</v>
+        <v>Circumference gauge preset</v>
       </c>
       <c r="N34" t="str">
         <f ca="1"/>
-        <v>【42】 周長測定子プリセット</v>
+        <v>【42】 Circumference gauge preset</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -9839,75 +9838,75 @@
       <c r="AB34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';</v>
+			strRt	:= 'Circumference gauge preset';</v>
       </c>
       <c r="AE34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';</v>
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';</v>
       </c>
       <c r="AG34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9915,12 +9914,12 @@
       <c r="AJ34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9929,12 +9928,12 @@
       <c r="AK34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9946,12 +9945,12 @@
       <c r="AL34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9963,12 +9962,12 @@
       <c r="AM34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9999,15 +9998,15 @@
       </c>
       <c r="K35" t="str">
         <f ca="1"/>
-        <v>巻き準備動作</v>
+        <v>Winding preparation operation</v>
       </c>
       <c r="L35" t="str">
         <f ca="1"/>
-        <v>巻き準備動作</v>
+        <v>Winding preparation operation</v>
       </c>
       <c r="N35" t="str">
         <f ca="1"/>
-        <v>【43】 巻き準備動作</v>
+        <v>【43】 Winding preparation operation</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -10036,75 +10035,75 @@
       <c r="AB35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';</v>
+			strRt	:= 'Winding preparation operation';</v>
       </c>
       <c r="AE35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';</v>
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';</v>
       </c>
       <c r="AG35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10112,12 +10111,12 @@
       <c r="AJ35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10126,12 +10125,12 @@
       <c r="AK35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10143,12 +10142,12 @@
       <c r="AL35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10160,12 +10159,12 @@
       <c r="AM35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10196,15 +10195,15 @@
       </c>
       <c r="K36" t="str">
         <f ca="1"/>
-        <v>巻き動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="L36" t="str">
         <f ca="1"/>
-        <v>巻き動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="N36" t="str">
         <f ca="1"/>
-        <v>【44】 巻き動作</v>
+        <v>【44】 Winding operation</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -10233,75 +10232,75 @@
       <c r="AB36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';</v>
+			strRt	:= 'Winding operation';</v>
       </c>
       <c r="AE36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';</v>
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';</v>
       </c>
       <c r="AG36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10309,12 +10308,12 @@
       <c r="AJ36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10323,12 +10322,12 @@
       <c r="AK36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10340,12 +10339,12 @@
       <c r="AL36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10357,12 +10356,12 @@
       <c r="AM36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10393,15 +10392,15 @@
       </c>
       <c r="K37" t="str">
         <f ca="1"/>
-        <v>箔ロウ巻き動作</v>
+        <v>Foil brazing operation</v>
       </c>
       <c r="L37" t="str">
         <f ca="1"/>
-        <v>箔ロウ巻き動作</v>
+        <v>Foil brazing operation</v>
       </c>
       <c r="N37" t="str">
         <f ca="1"/>
-        <v>【45】 箔ロウ巻き動作</v>
+        <v>【45】 Foil brazing operation</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -10430,75 +10429,75 @@
       <c r="AB37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';</v>
+			strRt	:= 'Foil brazing operation';</v>
       </c>
       <c r="AE37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';</v>
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';</v>
       </c>
       <c r="AG37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10506,12 +10505,12 @@
       <c r="AJ37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10520,12 +10519,12 @@
       <c r="AK37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10537,12 +10536,12 @@
       <c r="AL37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10554,12 +10553,12 @@
       <c r="AM37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10590,15 +10589,15 @@
       </c>
       <c r="K38" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>Circumference measurement operation</v>
       </c>
       <c r="L38" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>Circumference measurement operation</v>
       </c>
       <c r="N38" t="str">
         <f ca="1"/>
-        <v>【46】 周長測定動作</v>
+        <v>【46】 Circumference measurement operation</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -10627,75 +10626,75 @@
       <c r="AB38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';</v>
+			strRt	:= 'Circumference measurement operation';</v>
       </c>
       <c r="AE38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';</v>
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';</v>
       </c>
       <c r="AG38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10703,12 +10702,12 @@
       <c r="AJ38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10717,12 +10716,12 @@
       <c r="AK38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10734,12 +10733,12 @@
       <c r="AL38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10751,12 +10750,12 @@
       <c r="AM38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11201,15 +11200,15 @@
       </c>
       <c r="K43" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L43" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N43" t="str">
         <f ca="1"/>
-        <v>【51】 原点復帰動作</v>
+        <v>【51】 Home return operation</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -11241,7 +11240,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC43" t="str">
@@ -11249,7 +11248,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -11258,20 +11257,20 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF43" t="str">
@@ -11279,24 +11278,24 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';</v>
       </c>
       <c r="AG43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH43" t="str">
@@ -11304,12 +11303,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -11318,12 +11317,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11333,12 +11332,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11349,12 +11348,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11368,12 +11367,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11387,12 +11386,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11423,15 +11422,15 @@
       </c>
       <c r="K44" t="str">
         <f ca="1"/>
-        <v>巻き押え動作</v>
+        <v>Winding clamping operation</v>
       </c>
       <c r="L44" t="str">
         <f ca="1"/>
-        <v>巻き押え動作</v>
+        <v>Winding clamping operation</v>
       </c>
       <c r="N44" t="str">
         <f ca="1"/>
-        <v>【52】 巻き押え動作</v>
+        <v>【52】 Winding clamping operation</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -11460,75 +11459,75 @@
       <c r="AB44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';</v>
+			strRt	:= 'Winding clamping operation';</v>
       </c>
       <c r="AE44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';</v>
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';</v>
       </c>
       <c r="AG44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11536,12 +11535,12 @@
       <c r="AJ44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11550,12 +11549,12 @@
       <c r="AK44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11567,12 +11566,12 @@
       <c r="AL44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11584,12 +11583,12 @@
       <c r="AM44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11620,15 +11619,15 @@
       </c>
       <c r="K45" t="str">
         <f ca="1"/>
-        <v>溶接動作</v>
+        <v>Welding operation</v>
       </c>
       <c r="L45" t="str">
         <f ca="1"/>
-        <v>溶接動作</v>
+        <v>Welding operation</v>
       </c>
       <c r="N45" t="str">
         <f ca="1"/>
-        <v>【53】 溶接動作</v>
+        <v>【53】 Welding operation</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -11657,75 +11656,75 @@
       <c r="AB45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';</v>
+			strRt	:= 'Welding operation';</v>
       </c>
       <c r="AE45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';</v>
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';</v>
       </c>
       <c r="AG45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11733,12 +11732,12 @@
       <c r="AJ45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11747,12 +11746,12 @@
       <c r="AK45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11764,12 +11763,12 @@
       <c r="AL45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11781,12 +11780,12 @@
       <c r="AM45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12537,15 +12536,15 @@
       </c>
       <c r="K53" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="L53" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="N53" t="str">
         <f ca="1"/>
-        <v>【61】 原点復帰動作</v>
+        <v>【61】 Return to origin operation</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -12577,7 +12576,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC53" t="str">
@@ -12585,7 +12584,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -12594,20 +12593,20 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF53" t="str">
@@ -12615,24 +12614,24 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';</v>
       </c>
       <c r="AG53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH53" t="str">
@@ -12640,12 +12639,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -12654,12 +12653,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12669,12 +12668,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12685,12 +12684,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12704,12 +12703,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12723,12 +12722,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12759,15 +12758,15 @@
       </c>
       <c r="K54" t="str">
         <f ca="1"/>
-        <v>排出受取り動作</v>
+        <v>Discharge and receiving operation</v>
       </c>
       <c r="L54" t="str">
         <f ca="1"/>
-        <v>排出受取り動作</v>
+        <v>Discharge and receiving operation</v>
       </c>
       <c r="N54" t="str">
         <f ca="1"/>
-        <v>【62】 排出受取り動作</v>
+        <v>【62】 Discharge and receiving operation</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -12796,75 +12795,75 @@
       <c r="AB54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';</v>
+			strRt	:= 'Discharge and receiving operation';</v>
       </c>
       <c r="AE54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';</v>
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';</v>
       </c>
       <c r="AG54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12872,12 +12871,12 @@
       <c r="AJ54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12886,12 +12885,12 @@
       <c r="AK54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12903,12 +12902,12 @@
       <c r="AL54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12920,12 +12919,12 @@
       <c r="AM54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12956,15 +12955,15 @@
       </c>
       <c r="K55" t="str">
         <f ca="1"/>
-        <v>排出受渡し動作</v>
+        <v>Discharge and handover operation</v>
       </c>
       <c r="L55" t="str">
         <f ca="1"/>
-        <v>排出受渡し動作</v>
+        <v>Discharge and handover operation</v>
       </c>
       <c r="N55" t="str">
         <f ca="1"/>
-        <v>【63】 排出受渡し動作</v>
+        <v>【63】 Discharge and handover operation</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -12993,75 +12992,75 @@
       <c r="AB55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';</v>
+			strRt	:= 'Discharge and handover operation';</v>
       </c>
       <c r="AE55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';</v>
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';</v>
       </c>
       <c r="AG55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13069,12 +13068,12 @@
       <c r="AJ55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13083,12 +13082,12 @@
       <c r="AK55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13100,12 +13099,12 @@
       <c r="AL55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13117,12 +13116,12 @@
       <c r="AM55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13357,15 +13356,15 @@
       </c>
       <c r="K58" t="str">
         <f ca="1"/>
-        <v>計測準備</v>
+        <v>Measurement preparation</v>
       </c>
       <c r="L58" t="str">
         <f ca="1"/>
-        <v>計測準備</v>
+        <v>Measurement preparation</v>
       </c>
       <c r="N58" t="str">
         <f ca="1"/>
-        <v>【66】 計測準備</v>
+        <v>【66】 Measurement preparation</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -13394,75 +13393,75 @@
       <c r="AB58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';</v>
+			strRt	:= 'Measurement preparation';</v>
       </c>
       <c r="AE58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';</v>
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';</v>
       </c>
       <c r="AG58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13470,12 +13469,12 @@
       <c r="AJ58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13484,12 +13483,12 @@
       <c r="AK58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13501,12 +13500,12 @@
       <c r="AL58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13518,12 +13517,12 @@
       <c r="AM58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13554,15 +13553,15 @@
       </c>
       <c r="K59" t="str">
         <f ca="1"/>
-        <v>巻き中測定動作</v>
+        <v>Measurement operation during winding</v>
       </c>
       <c r="L59" t="str">
         <f ca="1"/>
-        <v>巻き中測定動作</v>
+        <v>Measurement operation during winding</v>
       </c>
       <c r="N59" t="str">
         <f ca="1"/>
-        <v>【67】 巻き中測定動作</v>
+        <v>【67】 Measurement operation during winding</v>
       </c>
       <c r="O59" t="str">
         <v/>
@@ -13591,75 +13590,75 @@
       <c r="AB59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';</v>
+			strRt	:= 'Measurement operation during winding';</v>
       </c>
       <c r="AE59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';</v>
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';</v>
       </c>
       <c r="AG59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13667,12 +13666,12 @@
       <c r="AJ59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13681,12 +13680,12 @@
       <c r="AK59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13698,12 +13697,12 @@
       <c r="AL59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13715,12 +13714,12 @@
       <c r="AM59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14063,15 +14062,15 @@
       </c>
       <c r="K63" t="str">
         <f ca="1"/>
-        <v>原点復帰</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="L63" t="str">
         <f ca="1"/>
-        <v>原点復帰</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="N63" t="str">
         <f ca="1"/>
-        <v>【71】 原点復帰</v>
+        <v>【71】 Return to origin operation</v>
       </c>
       <c r="O63" t="str">
         <v/>
@@ -14103,7 +14102,7 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC63" t="str">
@@ -14111,7 +14110,7 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -14120,20 +14119,20 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';</v>
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE63" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF63" t="str">
@@ -14141,24 +14140,24 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';</v>
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';</v>
       </c>
       <c r="AG63" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH63" t="str">
@@ -14166,12 +14165,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -14180,12 +14179,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14195,12 +14194,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14211,12 +14210,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14230,12 +14229,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14249,12 +14248,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14693,15 +14692,15 @@
       </c>
       <c r="K68" t="str">
         <f ca="1"/>
-        <v>糊付け動作</v>
+        <v>Gluing operation</v>
       </c>
       <c r="L68" t="str">
         <f ca="1"/>
-        <v>糊付け動作</v>
+        <v>Gluing operation</v>
       </c>
       <c r="N68" t="str">
         <f ca="1"/>
-        <v>【76】 糊付け動作</v>
+        <v>【76】 Gluing operation</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -14730,75 +14729,75 @@
       <c r="AB68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';</v>
+			strRt	:= 'Gluing operation';</v>
       </c>
       <c r="AE68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
+			strRt	:= 'Gluing operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';</v>
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';</v>
       </c>
       <c r="AG68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14806,12 +14805,12 @@
       <c r="AJ68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14820,12 +14819,12 @@
       <c r="AK68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14837,12 +14836,12 @@
       <c r="AL68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14854,12 +14853,12 @@
       <c r="AM68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28546,15 +28545,15 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_Pos_info.xlsx]info_script によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28562,12 +28561,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28575,12 +28574,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28588,12 +28587,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28601,12 +28600,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28619,12 +28618,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28632,12 +28631,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28645,12 +28644,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 供給開始動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28658,12 +28657,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28671,12 +28670,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
-	ELSIF uiInfoIdx = 5 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【25】 カット動作';
+	//Start supply operation
+	ELSIF uiInfoIdx = 6 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28684,12 +28683,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給確認動作
-	ELSIF uiInfoIdx = 6 THEN
-		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給確認動作';
+	//Supply operation
+	ELSIF uiInfoIdx = 7 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28702,12 +28701,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28715,12 +28714,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28728,12 +28727,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28746,12 +28745,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28759,12 +28758,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28772,12 +28771,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28785,12 +28784,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28798,12 +28797,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28811,12 +28810,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28829,12 +28828,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28842,12 +28841,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28855,12 +28854,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28873,12 +28872,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28886,12 +28885,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28899,12 +28898,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28912,12 +28911,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28925,12 +28924,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28943,12 +28942,12 @@
 	END_IF;
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28956,12 +28955,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E9E1D5-D857-486E-98D4-B7B862806806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2568BEBB-C68C-400C-B23F-A66703F75F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$88</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="126">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -659,13 +659,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>原点復帰</t>
-    <rPh sb="0" eb="4">
-      <t>ゲンテンフッキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>糊付け動作</t>
     <rPh sb="0" eb="2">
       <t>ノリヅ</t>
@@ -732,6 +725,26 @@
   </si>
   <si>
     <t>Feed operation</t>
+  </si>
+  <si>
+    <t>ひらき動作</t>
+    <rPh sb="3" eb="5">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>とじ動作</t>
+    <rPh sb="2" eb="4">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Opening action</t>
+  </si>
+  <si>
+    <t>Binding action</t>
   </si>
 </sst>
 </file>
@@ -1092,15 +1105,15 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="lightUp">
-          <fgColor rgb="FF33CCCC"/>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <patternFill patternType="lightUp">
+          <fgColor rgb="FF33CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1137,7 +1150,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$91">
+    <xdr:sp macro="" textlink="$A$92">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -1506,7 +1519,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R95"/>
+  <dimension ref="A1:R96"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -1610,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="str">
-        <f t="shared" ref="D3:D57" si="0">B3&amp;C3</f>
+        <f t="shared" ref="D3:D58" si="0">B3&amp;C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="4">
@@ -1989,7 +2002,7 @@
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4">
-        <f t="shared" ref="C14:C87" si="8">C13</f>
+        <f t="shared" ref="C14:C88" si="8">C13</f>
         <v>3</v>
       </c>
       <c r="D14" s="4" t="str">
@@ -1997,7 +2010,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" ref="E14:E67" si="9">E13+1</f>
+        <f t="shared" ref="E14:E68" si="9">E13+1</f>
         <v>2</v>
       </c>
       <c r="F14" s="5"/>
@@ -2425,10 +2438,10 @@
         <v>77</v>
       </c>
       <c r="H26" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I26" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>118</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
@@ -2460,10 +2473,10 @@
         <v>77</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
@@ -2564,10 +2577,10 @@
         <v>112</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
@@ -2583,25 +2596,26 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4">
-        <f t="shared" ref="C31" si="19">C30</f>
+        <f>C26+1</f>
         <v>7</v>
       </c>
       <c r="D31" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D31" si="19">B31&amp;C31</f>
         <v>7</v>
       </c>
       <c r="E31" s="4">
-        <v>6</v>
+        <f>E26</f>
+        <v>2</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
@@ -2614,74 +2628,79 @@
       <c r="R31" s="7"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="26"/>
+      <c r="A32" s="4"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="26">
+      <c r="C32" s="4">
+        <f t="shared" ref="C32" si="20">C30</f>
+        <v>7</v>
+      </c>
+      <c r="D32" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="E32" s="4">
+        <v>6</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="7"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="26"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="26">
         <f>C30+1</f>
         <v>8</v>
       </c>
-      <c r="D32" s="26" t="str">
+      <c r="D33" s="26" t="str">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E33" s="4">
         <f>E30</f>
         <v>1</v>
       </c>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11" t="s">
+      <c r="F33" s="11"/>
+      <c r="G33" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="H33" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="I33" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="I32" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="23"/>
-      <c r="P32" s="23"/>
-      <c r="Q32" s="23"/>
-      <c r="R32" s="7"/>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4">
-        <f>C32+1</f>
-        <v>9</v>
-      </c>
-      <c r="D33" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E33" s="4">
-        <f>E32</f>
-        <v>1</v>
-      </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="23"/>
+      <c r="P33" s="23"/>
+      <c r="Q33" s="23"/>
       <c r="R33" s="7"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4">
-        <f t="shared" ref="C34" si="20">C33</f>
+        <f>C33+1</f>
         <v>9</v>
       </c>
       <c r="D34" s="4" t="str">
@@ -2689,8 +2708,8 @@
         <v>9</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" ref="E34" si="21">E33+1</f>
-        <v>2</v>
+        <f>E33</f>
+        <v>1</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -2710,7 +2729,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C35" si="21">C34</f>
         <v>9</v>
       </c>
       <c r="D35" s="4" t="str">
@@ -2718,8 +2737,8 @@
         <v>9</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E35" si="22">E34+1</f>
+        <v>2</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -2748,14 +2767,14 @@
       </c>
       <c r="E36" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
-      <c r="K36" s="13"/>
+      <c r="K36" s="5"/>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
@@ -2777,14 +2796,14 @@
       </c>
       <c r="E37" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
+      <c r="K37" s="13"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
@@ -2797,16 +2816,16 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4">
-        <f t="shared" ref="C38" si="22">C33+1</f>
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="D38" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" ref="E38" si="23">E33</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -2826,7 +2845,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4">
-        <f t="shared" ref="C39" si="24">C38</f>
+        <f t="shared" ref="C39" si="23">C34+1</f>
         <v>10</v>
       </c>
       <c r="D39" s="4" t="str">
@@ -2834,8 +2853,8 @@
         <v>10</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" ref="E39" si="25">E38+1</f>
-        <v>2</v>
+        <f t="shared" ref="E39" si="24">E34</f>
+        <v>1</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -2855,7 +2874,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C40" si="25">C39</f>
         <v>10</v>
       </c>
       <c r="D40" s="4" t="str">
@@ -2863,8 +2882,8 @@
         <v>10</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E40" si="26">E39+1</f>
+        <v>2</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -2893,7 +2912,7 @@
       </c>
       <c r="E41" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -2922,7 +2941,7 @@
       </c>
       <c r="E42" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -2942,16 +2961,16 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
-        <f t="shared" ref="C43" si="26">C38+1</f>
-        <v>11</v>
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="D43" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" ref="E43" si="27">E38</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -2971,7 +2990,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
-        <f t="shared" ref="C44" si="28">C43</f>
+        <f t="shared" ref="C44" si="27">C39+1</f>
         <v>11</v>
       </c>
       <c r="D44" s="4" t="str">
@@ -2979,8 +2998,8 @@
         <v>11</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" ref="E44" si="29">E43+1</f>
-        <v>2</v>
+        <f t="shared" ref="E44" si="28">E39</f>
+        <v>1</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -3000,7 +3019,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C45" si="29">C44</f>
         <v>11</v>
       </c>
       <c r="D45" s="4" t="str">
@@ -3008,8 +3027,8 @@
         <v>11</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E45" si="30">E44+1</f>
+        <v>2</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -3038,7 +3057,7 @@
       </c>
       <c r="E46" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -3067,7 +3086,7 @@
       </c>
       <c r="E47" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -3087,16 +3106,16 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
-        <f t="shared" ref="C48" si="30">C43+1</f>
-        <v>12</v>
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="D48" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" ref="E48" si="31">E43</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -3116,7 +3135,7 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
-        <f t="shared" ref="C49" si="32">C48</f>
+        <f t="shared" ref="C49" si="31">C44+1</f>
         <v>12</v>
       </c>
       <c r="D49" s="4" t="str">
@@ -3124,8 +3143,8 @@
         <v>12</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" ref="E49" si="33">E48+1</f>
-        <v>2</v>
+        <f t="shared" ref="E49" si="32">E44</f>
+        <v>1</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -3145,7 +3164,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C50" si="33">C49</f>
         <v>12</v>
       </c>
       <c r="D50" s="4" t="str">
@@ -3153,8 +3172,8 @@
         <v>12</v>
       </c>
       <c r="E50" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E50" si="34">E49+1</f>
+        <v>2</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -3183,7 +3202,7 @@
       </c>
       <c r="E51" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -3212,7 +3231,7 @@
       </c>
       <c r="E52" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -3232,16 +3251,16 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
-        <f t="shared" ref="C53:C83" si="34">C48+1</f>
-        <v>13</v>
+        <f t="shared" si="8"/>
+        <v>12</v>
       </c>
       <c r="D53" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" ref="E53" si="35">E48</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -3261,7 +3280,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
-        <f t="shared" ref="C54:C84" si="36">C53</f>
+        <f t="shared" ref="C54:C84" si="35">C49+1</f>
         <v>13</v>
       </c>
       <c r="D54" s="4" t="str">
@@ -3269,8 +3288,8 @@
         <v>13</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" ref="E54" si="37">E53+1</f>
-        <v>2</v>
+        <f t="shared" ref="E54" si="36">E49</f>
+        <v>1</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -3290,7 +3309,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C55:C85" si="37">C54</f>
         <v>13</v>
       </c>
       <c r="D55" s="4" t="str">
@@ -3298,8 +3317,8 @@
         <v>13</v>
       </c>
       <c r="E55" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E55" si="38">E54+1</f>
+        <v>2</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -3328,7 +3347,7 @@
       </c>
       <c r="E56" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -3357,7 +3376,7 @@
       </c>
       <c r="E57" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -3377,16 +3396,16 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
-        <f t="shared" si="34"/>
-        <v>14</v>
+        <f t="shared" si="8"/>
+        <v>13</v>
       </c>
       <c r="D58" s="4" t="str">
-        <f t="shared" ref="D58:D87" si="38">B58&amp;C58</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" ref="E58" si="39">E53</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -3406,16 +3425,16 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>14</v>
       </c>
       <c r="D59" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="D59:D88" si="39">B59&amp;C59</f>
         <v>14</v>
       </c>
       <c r="E59" s="4">
-        <f t="shared" ref="E59" si="40">E58+1</f>
-        <v>2</v>
+        <f t="shared" ref="E59" si="40">E54</f>
+        <v>1</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -3435,16 +3454,16 @@
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>14</v>
       </c>
       <c r="D60" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>14</v>
       </c>
       <c r="E60" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E60" si="41">E59+1</f>
+        <v>2</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -3468,12 +3487,12 @@
         <v>14</v>
       </c>
       <c r="D61" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>14</v>
       </c>
       <c r="E61" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -3497,12 +3516,12 @@
         <v>14</v>
       </c>
       <c r="D62" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>14</v>
       </c>
       <c r="E62" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -3522,16 +3541,16 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
-        <f t="shared" si="34"/>
-        <v>15</v>
+        <f t="shared" si="8"/>
+        <v>14</v>
       </c>
       <c r="D63" s="4" t="str">
-        <f t="shared" si="38"/>
-        <v>15</v>
+        <f t="shared" si="39"/>
+        <v>14</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" ref="E63" si="41">E58</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -3551,16 +3570,16 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>15</v>
       </c>
       <c r="D64" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>15</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" ref="E64" si="42">E63+1</f>
-        <v>2</v>
+        <f t="shared" ref="E64" si="42">E59</f>
+        <v>1</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -3580,16 +3599,16 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>15</v>
       </c>
       <c r="D65" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>15</v>
       </c>
       <c r="E65" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E65" si="43">E64+1</f>
+        <v>2</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -3613,12 +3632,12 @@
         <v>15</v>
       </c>
       <c r="D66" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>15</v>
       </c>
       <c r="E66" s="4">
         <f t="shared" si="9"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -3642,12 +3661,12 @@
         <v>15</v>
       </c>
       <c r="D67" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>15</v>
       </c>
       <c r="E67" s="4">
         <f t="shared" si="9"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -3667,16 +3686,16 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4">
-        <f t="shared" si="34"/>
-        <v>16</v>
+        <f t="shared" si="8"/>
+        <v>15</v>
       </c>
       <c r="D68" s="4" t="str">
-        <f t="shared" si="38"/>
-        <v>16</v>
+        <f t="shared" si="39"/>
+        <v>15</v>
       </c>
       <c r="E68" s="4">
-        <f t="shared" ref="E68" si="43">E63</f>
-        <v>1</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -3696,16 +3715,16 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>16</v>
       </c>
       <c r="D69" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>16</v>
       </c>
       <c r="E69" s="4">
-        <f t="shared" ref="E69:E87" si="44">E68+1</f>
-        <v>2</v>
+        <f t="shared" ref="E69" si="44">E64</f>
+        <v>1</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -3725,16 +3744,16 @@
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>16</v>
       </c>
       <c r="D70" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>16</v>
       </c>
       <c r="E70" s="4">
-        <f t="shared" si="44"/>
-        <v>3</v>
+        <f t="shared" ref="E70:E88" si="45">E69+1</f>
+        <v>2</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -3758,12 +3777,12 @@
         <v>16</v>
       </c>
       <c r="D71" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>16</v>
       </c>
       <c r="E71" s="4">
-        <f t="shared" si="44"/>
-        <v>4</v>
+        <f t="shared" si="45"/>
+        <v>3</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -3787,12 +3806,12 @@
         <v>16</v>
       </c>
       <c r="D72" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>16</v>
       </c>
       <c r="E72" s="4">
-        <f t="shared" si="44"/>
-        <v>5</v>
+        <f t="shared" si="45"/>
+        <v>4</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -3812,16 +3831,16 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4">
-        <f t="shared" si="34"/>
-        <v>17</v>
+        <f t="shared" si="8"/>
+        <v>16</v>
       </c>
       <c r="D73" s="4" t="str">
-        <f t="shared" si="38"/>
-        <v>17</v>
+        <f t="shared" si="39"/>
+        <v>16</v>
       </c>
       <c r="E73" s="4">
-        <f t="shared" ref="E73" si="45">E68</f>
-        <v>1</v>
+        <f t="shared" si="45"/>
+        <v>5</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -3841,16 +3860,16 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>17</v>
       </c>
       <c r="D74" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>17</v>
       </c>
       <c r="E74" s="4">
-        <f t="shared" ref="E74" si="46">E73+1</f>
-        <v>2</v>
+        <f t="shared" ref="E74" si="46">E69</f>
+        <v>1</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -3870,16 +3889,16 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>17</v>
       </c>
       <c r="D75" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>17</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" si="44"/>
-        <v>3</v>
+        <f t="shared" ref="E75" si="47">E74+1</f>
+        <v>2</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -3903,12 +3922,12 @@
         <v>17</v>
       </c>
       <c r="D76" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>17</v>
       </c>
       <c r="E76" s="4">
-        <f t="shared" si="44"/>
-        <v>4</v>
+        <f t="shared" si="45"/>
+        <v>3</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -3932,12 +3951,12 @@
         <v>17</v>
       </c>
       <c r="D77" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>17</v>
       </c>
       <c r="E77" s="4">
-        <f t="shared" si="44"/>
-        <v>5</v>
+        <f t="shared" si="45"/>
+        <v>4</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -3957,16 +3976,16 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4">
-        <f t="shared" si="34"/>
-        <v>18</v>
+        <f t="shared" si="8"/>
+        <v>17</v>
       </c>
       <c r="D78" s="4" t="str">
-        <f t="shared" si="38"/>
-        <v>18</v>
+        <f t="shared" si="39"/>
+        <v>17</v>
       </c>
       <c r="E78" s="4">
-        <f t="shared" ref="E78" si="47">E73</f>
-        <v>1</v>
+        <f t="shared" si="45"/>
+        <v>5</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -3986,16 +4005,16 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>18</v>
       </c>
       <c r="D79" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>18</v>
       </c>
       <c r="E79" s="4">
-        <f t="shared" ref="E79" si="48">E78+1</f>
-        <v>2</v>
+        <f t="shared" ref="E79" si="48">E74</f>
+        <v>1</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -4015,16 +4034,16 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>18</v>
       </c>
       <c r="D80" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>18</v>
       </c>
       <c r="E80" s="4">
-        <f t="shared" si="44"/>
-        <v>3</v>
+        <f t="shared" ref="E80" si="49">E79+1</f>
+        <v>2</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -4048,12 +4067,12 @@
         <v>18</v>
       </c>
       <c r="D81" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>18</v>
       </c>
       <c r="E81" s="4">
-        <f t="shared" si="44"/>
-        <v>4</v>
+        <f t="shared" si="45"/>
+        <v>3</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -4077,12 +4096,12 @@
         <v>18</v>
       </c>
       <c r="D82" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>18</v>
       </c>
       <c r="E82" s="4">
-        <f t="shared" si="44"/>
-        <v>5</v>
+        <f t="shared" si="45"/>
+        <v>4</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -4102,16 +4121,16 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4">
-        <f t="shared" si="34"/>
-        <v>19</v>
+        <f t="shared" si="8"/>
+        <v>18</v>
       </c>
       <c r="D83" s="4" t="str">
-        <f t="shared" si="38"/>
-        <v>19</v>
+        <f t="shared" si="39"/>
+        <v>18</v>
       </c>
       <c r="E83" s="4">
-        <f t="shared" ref="E83" si="49">E78</f>
-        <v>1</v>
+        <f t="shared" si="45"/>
+        <v>5</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -4131,16 +4150,16 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>19</v>
       </c>
       <c r="D84" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>19</v>
       </c>
       <c r="E84" s="4">
-        <f t="shared" ref="E84" si="50">E83+1</f>
-        <v>2</v>
+        <f t="shared" ref="E84" si="50">E79</f>
+        <v>1</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
@@ -4160,16 +4179,16 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="37"/>
         <v>19</v>
       </c>
       <c r="D85" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>19</v>
       </c>
       <c r="E85" s="4">
-        <f t="shared" si="44"/>
-        <v>3</v>
+        <f t="shared" ref="E85" si="51">E84+1</f>
+        <v>2</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
@@ -4193,12 +4212,12 @@
         <v>19</v>
       </c>
       <c r="D86" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>19</v>
       </c>
       <c r="E86" s="4">
-        <f t="shared" si="44"/>
-        <v>4</v>
+        <f t="shared" si="45"/>
+        <v>3</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
@@ -4222,12 +4241,12 @@
         <v>19</v>
       </c>
       <c r="D87" s="4" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>19</v>
       </c>
       <c r="E87" s="4">
-        <f t="shared" si="44"/>
-        <v>5</v>
+        <f t="shared" si="45"/>
+        <v>4</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -4244,100 +4263,129 @@
       <c r="R87" s="7"/>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="15"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="15"/>
-      <c r="E88" s="15"/>
-      <c r="F88" s="16"/>
-      <c r="G88" s="16"/>
-      <c r="H88" s="16"/>
-      <c r="I88" s="16"/>
-      <c r="J88" s="16"/>
-      <c r="K88" s="16"/>
-      <c r="L88" s="16"/>
-      <c r="M88" s="16"/>
-      <c r="N88" s="16"/>
-      <c r="O88" s="17"/>
-      <c r="P88" s="17"/>
-      <c r="Q88" s="17"/>
-      <c r="R88" s="17"/>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" t="s">
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
+      <c r="C88" s="4">
+        <f t="shared" si="8"/>
+        <v>19</v>
+      </c>
+      <c r="D88" s="4" t="str">
+        <f t="shared" si="39"/>
+        <v>19</v>
+      </c>
+      <c r="E88" s="4">
+        <f t="shared" si="45"/>
+        <v>5</v>
+      </c>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+      <c r="L88" s="5"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="7"/>
+      <c r="P88" s="7"/>
+      <c r="Q88" s="7"/>
+      <c r="R88" s="7"/>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="15"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
+      <c r="E89" s="15"/>
+      <c r="F89" s="16"/>
+      <c r="G89" s="16"/>
+      <c r="H89" s="16"/>
+      <c r="I89" s="16"/>
+      <c r="J89" s="16"/>
+      <c r="K89" s="16"/>
+      <c r="L89" s="16"/>
+      <c r="M89" s="16"/>
+      <c r="N89" s="16"/>
+      <c r="O89" s="17"/>
+      <c r="P89" s="17"/>
+      <c r="Q89" s="17"/>
+      <c r="R89" s="17"/>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" t="s">
         <v>9</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F91" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91">
-        <f>MAX(A$2:A$88)</f>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92">
+        <f>MAX(A$2:A$89)</f>
         <v>0</v>
       </c>
-      <c r="F91">
-        <f>MAX(F$2:F$88)</f>
+      <c r="F92">
+        <f>MAX(F$2:F$89)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" t="s">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" t="s">
         <v>40</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D93" t="s">
         <v>14</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E93" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93">
-        <f>ROW(A89)-ROW(A1)-1</f>
-        <v>87</v>
-      </c>
-      <c r="D93">
-        <f>COUNTIF(D$2:D$88,D92)</f>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94">
+        <f>ROW(A90)-ROW(A1)-1</f>
+        <v>88</v>
+      </c>
+      <c r="D94">
+        <f>COUNTIF(D$2:D$89,D93)</f>
         <v>0</v>
       </c>
-      <c r="E93" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$88,$D$2:$D$88,E92)</f>
+      <c r="E94" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$89,$D$2:$D$89,E93)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="D94" t="s">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="D95" t="s">
         <v>12</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E95" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="D95">
-        <f>COUNTIF(D$2:D$88,D94)</f>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="D96">
+        <f>COUNTIF(D$2:D$89,D95)</f>
         <v>0</v>
       </c>
-      <c r="E95" s="25">
-        <f>_xlfn.MAXIFS(E$2:E$88,$D$2:$D$88,E94)</f>
+      <c r="E96" s="25">
+        <f>_xlfn.MAXIFS(E$2:E$89,$D$2:$D$89,E95)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R87" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R87">
-      <sortCondition ref="D1:D87"/>
+  <autoFilter ref="A1:R88" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R88">
+      <sortCondition ref="D1:D88"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A2:R88">
-    <cfRule type="expression" dxfId="2" priority="2">
+  <conditionalFormatting sqref="A2:R89">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>MOD(ROW(A2),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4487,7 +4535,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -4501,23 +4549,23 @@
         <v>1</v>
       </c>
       <c r="J3" cm="1">
-        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$88&amp;info_index!$E$2:$E$88,0),"")</f>
+        <f t="array" ref="J3:J202">IFERROR(MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$89&amp;info_index!$E$2:$E$89,0),"")</f>
         <v>1</v>
       </c>
       <c r="K3" t="str" cm="1">
-        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$88,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$88&amp;info_index!$E$2:$E$88,0),1)&amp;"","")</f>
-        <v>原点復帰動作</v>
+        <f t="array" aca="1" ref="K3:K202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$H$2:$H$89,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$89&amp;info_index!$E$2:$E$89,0),1)&amp;"","")</f>
+        <v>Return to origin operation</v>
       </c>
       <c r="L3" t="str" cm="1">
         <f t="array" aca="1" ref="L3:L202" ca="1">IF(LEN(_xlfn.ANCHORARRAY($J3)),IF(LEN(_xlfn.ANCHORARRAY(K3)),_xlfn.ANCHORARRAY(K3),"unknown"),"")</f>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="N3" t="str" cm="1">
         <f t="array" aca="1" ref="N3:N202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(L3)),"【"&amp;G3:G202&amp;H3:H202&amp;"】 "&amp;_xlfn.ANCHORARRAY(L3),"")</f>
-        <v>【11】 原点復帰動作</v>
+        <v>【11】 Return to origin operation</v>
       </c>
       <c r="O3" t="str" cm="1">
-        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$88,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$88&amp;info_index!$E$2:$E$88,0),1)&amp;"","")</f>
+        <f t="array" ref="O3:O202">IFERROR(INDEX(info_index!$J$2:$J$89,MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$89&amp;info_index!$E$2:$E$89,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="P3" t="str" cm="1">
@@ -4525,7 +4573,7 @@
         <v>unknown</v>
       </c>
       <c r="Q3" t="str" cm="1">
-        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$88,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$88&amp;info_index!$E$2:$E$88,0),1)&amp;"","")</f>
+        <f t="array" aca="1" ref="Q3:Q202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(J3)),INDEX(OFFSET(info_index!$L$2:$L$89,0,$B$23),MATCH($G$3:$G$202&amp;$H$3:$H$202,info_index!$D$2:$D$89&amp;info_index!$E$2:$E$89,0),1)&amp;"","")</f>
         <v/>
       </c>
       <c r="R3" t="str" cm="1">
@@ -4545,14 +4593,14 @@
         <f t="array" aca="1" ref="AB3:AB202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AA3)),_xlfn.ANCHORARRAY(AA3),"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;$B$7&amp;_xlfn.ANCHORARRAY(L3)&amp;CHAR(10)&amp;CHAR(9)&amp;IF(H3:H202=1,"IF ","ELSIF ")&amp;$B$26&amp;" = "&amp;H3:H202&amp;" THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC3" t="str" cm="1">
         <f t="array" aca="1" ref="AC3:AC202" ca="1">IF(LEN(AB3:AB202),AB3:AB202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"IF "&amp;$B$27&amp;" = '"&amp;$L$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -4560,54 +4608,54 @@
         <f t="array" aca="1" ref="AD3:AD202" ca="1">IF(LEN(AC3:AC202),AC3:AC202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(L3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE3" t="str" cm="1">
         <f t="array" aca="1" ref="AE3:AE202" ca="1">IF(LEN(AD3:AD202),AD3:AD202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;N$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF3" t="str" cm="1">
         <f t="array" aca="1" ref="AF3:AF202" ca="1">IF(LEN(AE3:AE202),AE3:AE202,"")&amp;IF(LEN(N3:N202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(N3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';</v>
       </c>
       <c r="AG3" t="str" cm="1">
         <f t="array" aca="1" ref="AG3:AG202" ca="1">IF(LEN(AF3:AF202),AF3:AF202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;P$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH3" t="str" cm="1">
         <f t="array" aca="1" ref="AH3:AH202" ca="1">IF(LEN(AG3:AG202),AG3:AG202,"")&amp;IF(LEN(P3:P202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(P3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -4615,12 +4663,12 @@
         <f t="array" aca="1" ref="AI3:AI202" ca="1">IF(LEN(AH3:AH202),AH3:AH202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSIF "&amp;$B$27&amp;" = '"&amp;R$2&amp;"' THEN","")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4629,12 +4677,12 @@
         <f t="array" aca="1" ref="AJ3:AJ202" ca="1">IF(LEN(AI3:AI202),AI3:AI202,"")&amp;IF(LEN(R3:R202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$28&amp;CHAR(9)&amp;$B$8&amp;" '"&amp;_xlfn.ANCHORARRAY(R3)&amp;"'"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4644,12 +4692,12 @@
         <f t="array" aca="1" ref="AK3:AK202" ca="1">IF(LEN(AJ3:AJ202),AJ3:AJ202,"")&amp;IF(LEN(L3:L202),CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 3"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4662,12 +4710,12 @@
         <f t="array" aca="1" ref="AL3:AL202" ca="1">IF(LEN(_xlfn.ANCHORARRAY(AK3)),_xlfn.ANCHORARRAY(AK3),"")&amp;IF(I3:I202="●",CHAR(10)&amp;CHAR(9)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 2"&amp;$B$9&amp;CHAR(10)&amp;CHAR(9)&amp;"END_IF"&amp;$B$9,"")</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4680,12 +4728,12 @@
         <f t="array" aca="1" ref="AM3:AM202" ca="1">_xlfn.ANCHORARRAY(AL3)</f>
         <v>//1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4717,15 +4765,15 @@
       </c>
       <c r="K4" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="L4" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="N4" t="str">
         <f ca="1"/>
-        <v>【12】 供給準備動作</v>
+        <v>【12】 Preparation for supply operation</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -4754,75 +4802,75 @@
       <c r="AB4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Preparation for supply operation';</v>
       </c>
       <c r="AE4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';</v>
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';</v>
       </c>
       <c r="AG4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -4830,12 +4878,12 @@
       <c r="AJ4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4844,12 +4892,12 @@
       <c r="AK4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4861,12 +4909,12 @@
       <c r="AL4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4878,12 +4926,12 @@
       <c r="AM4" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -4899,7 +4947,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。</v>
       </c>
       <c r="F5">
         <f t="shared" ref="F5:F68" si="1">F4</f>
@@ -4921,15 +4969,15 @@
       </c>
       <c r="K5" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="L5" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="N5" t="str">
         <f ca="1"/>
-        <v>【13】 カット動作</v>
+        <v>【13】 Cut operation</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -4958,75 +5006,75 @@
       <c r="AB5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';</v>
+			strRt	:= 'Cut operation';</v>
       </c>
       <c r="AE5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';</v>
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';</v>
       </c>
       <c r="AG5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5034,12 +5082,12 @@
       <c r="AJ5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5048,12 +5096,12 @@
       <c r="AK5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5065,12 +5113,12 @@
       <c r="AL5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5082,12 +5130,12 @@
       <c r="AM5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5340,15 +5388,15 @@
       </c>
       <c r="K8" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="L8" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="N8" t="str">
         <f ca="1"/>
-        <v>【16】 供給開始動作</v>
+        <v>【16】 Start supply operation</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -5377,75 +5425,75 @@
       <c r="AB8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';</v>
+			strRt	:= 'Start supply operation';</v>
       </c>
       <c r="AE8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';</v>
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';</v>
       </c>
       <c r="AG8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5453,12 +5501,12 @@
       <c r="AJ8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5467,12 +5515,12 @@
       <c r="AK8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5484,12 +5532,12 @@
       <c r="AL8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5501,12 +5549,12 @@
       <c r="AM8" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5543,15 +5591,15 @@
       </c>
       <c r="K9" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply operation</v>
       </c>
       <c r="L9" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply operation</v>
       </c>
       <c r="N9" t="str">
         <f ca="1"/>
-        <v>【17】 供給動作</v>
+        <v>【17】 Supply operation</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -5580,75 +5628,75 @@
       <c r="AB9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= 'Supply operation';</v>
       </c>
       <c r="AE9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';</v>
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';</v>
       </c>
       <c r="AG9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -5656,12 +5704,12 @@
       <c r="AJ9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5670,12 +5718,12 @@
       <c r="AK9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5687,12 +5735,12 @@
       <c r="AL9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -5704,12 +5752,12 @@
       <c r="AM9" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6037,15 +6085,15 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AM$205</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6053,12 +6101,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6066,12 +6114,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6079,12 +6127,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6092,12 +6140,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6110,12 +6158,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6123,12 +6171,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6136,12 +6184,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6149,12 +6197,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給確認動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6162,12 +6210,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6175,12 +6223,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【27】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6193,12 +6241,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6206,12 +6254,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6219,12 +6267,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6237,12 +6285,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6250,12 +6298,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6263,12 +6311,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6276,12 +6324,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6289,12 +6337,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6302,12 +6350,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6320,12 +6368,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6333,12 +6381,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6346,12 +6394,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6364,12 +6412,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6377,12 +6425,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6390,12 +6438,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6403,12 +6451,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6416,12 +6464,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6434,12 +6482,12 @@
 	END_IF;
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Opening action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Opening action';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6447,12 +6495,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//糊付け動作
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【72】 Binding action';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6465,12 +6526,12 @@
 	END_IF;
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【81】 送り動作';
+			strRt	:= 'Feed operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【81】 Feed operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6506,15 +6567,15 @@
       </c>
       <c r="K13" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="L13" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="N13" t="str">
         <f ca="1"/>
-        <v>【21】 原点復帰動作</v>
+        <v>【21】 Return to origin operation</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -6546,7 +6607,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC13" t="str">
@@ -6554,7 +6615,7 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -6563,20 +6624,20 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF13" t="str">
@@ -6584,24 +6645,24 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';</v>
       </c>
       <c r="AG13" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH13" t="str">
@@ -6609,12 +6670,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -6623,12 +6684,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6638,12 +6699,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6654,12 +6715,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6673,12 +6734,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6692,12 +6753,12 @@
         <v xml:space="preserve">
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6739,15 +6800,15 @@
       </c>
       <c r="K14" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="L14" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Preparation for supply operation</v>
       </c>
       <c r="N14" t="str">
         <f ca="1"/>
-        <v>【22】 供給準備動作</v>
+        <v>【22】 Preparation for supply operation</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -6776,75 +6837,75 @@
       <c r="AB14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Preparation for supply operation';</v>
       </c>
       <c r="AE14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Preparation for supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';</v>
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';</v>
       </c>
       <c r="AG14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -6852,12 +6913,12 @@
       <c r="AJ14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6866,12 +6927,12 @@
       <c r="AK14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6883,12 +6944,12 @@
       <c r="AL14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6900,12 +6961,12 @@
       <c r="AM14" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -6936,15 +6997,15 @@
       </c>
       <c r="K15" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="L15" t="str">
         <f ca="1"/>
-        <v>カット動作</v>
+        <v>Cut operation</v>
       </c>
       <c r="N15" t="str">
         <f ca="1"/>
-        <v>【23】 カット動作</v>
+        <v>【23】 Cut operation</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -6973,75 +7034,75 @@
       <c r="AB15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';</v>
+			strRt	:= 'Cut operation';</v>
       </c>
       <c r="AE15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
+			strRt	:= 'Cut operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 カット動作';</v>
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';</v>
       </c>
       <c r="AG15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7049,12 +7110,12 @@
       <c r="AJ15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7063,12 +7124,12 @@
       <c r="AK15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7080,12 +7141,12 @@
       <c r="AL15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7097,12 +7158,12 @@
       <c r="AM15" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7133,15 +7194,15 @@
       </c>
       <c r="K16" t="str">
         <f ca="1"/>
-        <v>供給確認動作</v>
+        <v>Supply confirmation operation</v>
       </c>
       <c r="L16" t="str">
         <f ca="1"/>
-        <v>供給確認動作</v>
+        <v>Supply confirmation operation</v>
       </c>
       <c r="N16" t="str">
         <f ca="1"/>
-        <v>【24】 供給確認動作</v>
+        <v>【24】 Supply confirmation operation</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -7170,75 +7231,75 @@
       <c r="AB16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';</v>
+			strRt	:= 'Supply confirmation operation';</v>
       </c>
       <c r="AE16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
+			strRt	:= 'Supply confirmation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給確認動作';</v>
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';</v>
       </c>
       <c r="AG16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給確認動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給確認動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給確認動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7246,12 +7307,12 @@
       <c r="AJ16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給確認動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7260,12 +7321,12 @@
       <c r="AK16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給確認動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7277,12 +7338,12 @@
       <c r="AL16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給確認動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7294,12 +7355,12 @@
       <c r="AM16" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給確認動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7432,15 +7493,15 @@
       </c>
       <c r="K18" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="L18" t="str">
         <f ca="1"/>
-        <v>供給開始動作</v>
+        <v>Start supply operation</v>
       </c>
       <c r="N18" t="str">
         <f ca="1"/>
-        <v>【26】 供給開始動作</v>
+        <v>【26】 Start supply operation</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -7469,75 +7530,75 @@
       <c r="AB18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';</v>
+			strRt	:= 'Start supply operation';</v>
       </c>
       <c r="AE18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
+			strRt	:= 'Start supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給開始動作';</v>
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';</v>
       </c>
       <c r="AG18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7545,12 +7606,12 @@
       <c r="AJ18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7559,12 +7620,12 @@
       <c r="AK18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7576,12 +7637,12 @@
       <c r="AL18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7593,12 +7654,12 @@
       <c r="AM18" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7629,15 +7690,15 @@
       </c>
       <c r="K19" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply operation</v>
       </c>
       <c r="L19" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>Supply operation</v>
       </c>
       <c r="N19" t="str">
         <f ca="1"/>
-        <v>【27】 供給動作</v>
+        <v>【27】 Supply operation</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -7666,75 +7727,75 @@
       <c r="AB19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= 'Supply operation';</v>
       </c>
       <c r="AE19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'Supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【27】 供給動作';</v>
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';</v>
       </c>
       <c r="AG19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【27】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【27】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【27】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -7742,12 +7803,12 @@
       <c r="AJ19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【27】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7756,12 +7817,12 @@
       <c r="AK19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【27】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7773,12 +7834,12 @@
       <c r="AL19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【27】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -7790,12 +7851,12 @@
       <c r="AM19" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【27】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8122,7 +8183,7 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <f>F13+1</f>
@@ -8144,15 +8205,15 @@
       </c>
       <c r="K23" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L23" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N23" t="str">
         <f ca="1"/>
-        <v>【31】 原点復帰動作</v>
+        <v>【31】 Home return operation</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -8184,7 +8245,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC23" t="str">
@@ -8192,7 +8253,7 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -8201,20 +8262,20 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF23" t="str">
@@ -8222,24 +8283,24 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';</v>
       </c>
       <c r="AG23" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH23" t="str">
@@ -8247,12 +8308,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -8261,12 +8322,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8276,12 +8337,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8292,12 +8353,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8311,12 +8372,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8330,12 +8391,12 @@
         <v xml:space="preserve">
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8366,15 +8427,15 @@
       </c>
       <c r="K24" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="L24" t="str">
         <f ca="1"/>
-        <v>供給準備動作</v>
+        <v>Supply preparation operation</v>
       </c>
       <c r="N24" t="str">
         <f ca="1"/>
-        <v>【32】 供給準備動作</v>
+        <v>【32】 Supply preparation operation</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -8403,75 +8464,75 @@
       <c r="AB24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';</v>
       </c>
       <c r="AE24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
+			strRt	:= 'Supply preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';</v>
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';</v>
       </c>
       <c r="AG24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8479,12 +8540,12 @@
       <c r="AJ24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8493,12 +8554,12 @@
       <c r="AK24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8510,12 +8571,12 @@
       <c r="AL24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8527,12 +8588,12 @@
       <c r="AM24" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8569,15 +8630,15 @@
       </c>
       <c r="K25" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>supply operation</v>
       </c>
       <c r="L25" t="str">
         <f ca="1"/>
-        <v>供給動作</v>
+        <v>supply operation</v>
       </c>
       <c r="N25" t="str">
         <f ca="1"/>
-        <v>【33】 供給動作</v>
+        <v>【33】 supply operation</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -8606,75 +8667,75 @@
       <c r="AB25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';</v>
+			strRt	:= 'supply operation';</v>
       </c>
       <c r="AE25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
+			strRt	:= 'supply operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';</v>
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';</v>
       </c>
       <c r="AG25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -8682,12 +8743,12 @@
       <c r="AJ25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8696,12 +8757,12 @@
       <c r="AK25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8713,12 +8774,12 @@
       <c r="AL25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -8730,12 +8791,12 @@
       <c r="AM25" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9510,15 +9571,15 @@
       </c>
       <c r="K33" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L33" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N33" t="str">
         <f ca="1"/>
-        <v>【41】 原点復帰動作</v>
+        <v>【41】 Home return operation</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -9550,7 +9611,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC33" t="str">
@@ -9558,7 +9619,7 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -9567,20 +9628,20 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF33" t="str">
@@ -9588,24 +9649,24 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';</v>
       </c>
       <c r="AG33" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH33" t="str">
@@ -9613,12 +9674,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -9627,12 +9688,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9642,12 +9703,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9658,12 +9719,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9677,12 +9738,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9696,12 +9757,12 @@
         <v xml:space="preserve">
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9732,15 +9793,15 @@
       </c>
       <c r="K34" t="str">
         <f ca="1"/>
-        <v>周長測定子プリセット</v>
+        <v>Circumference gauge preset</v>
       </c>
       <c r="L34" t="str">
         <f ca="1"/>
-        <v>周長測定子プリセット</v>
+        <v>Circumference gauge preset</v>
       </c>
       <c r="N34" t="str">
         <f ca="1"/>
-        <v>【42】 周長測定子プリセット</v>
+        <v>【42】 Circumference gauge preset</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -9769,75 +9830,75 @@
       <c r="AB34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';</v>
+			strRt	:= 'Circumference gauge preset';</v>
       </c>
       <c r="AE34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';</v>
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';</v>
       </c>
       <c r="AG34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -9845,12 +9906,12 @@
       <c r="AJ34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9859,12 +9920,12 @@
       <c r="AK34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9876,12 +9937,12 @@
       <c r="AL34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9893,12 +9954,12 @@
       <c r="AM34" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -9929,15 +9990,15 @@
       </c>
       <c r="K35" t="str">
         <f ca="1"/>
-        <v>巻き準備動作</v>
+        <v>Winding preparation operation</v>
       </c>
       <c r="L35" t="str">
         <f ca="1"/>
-        <v>巻き準備動作</v>
+        <v>Winding preparation operation</v>
       </c>
       <c r="N35" t="str">
         <f ca="1"/>
-        <v>【43】 巻き準備動作</v>
+        <v>【43】 Winding preparation operation</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -9966,75 +10027,75 @@
       <c r="AB35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';</v>
+			strRt	:= 'Winding preparation operation';</v>
       </c>
       <c r="AE35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
+			strRt	:= 'Winding preparation operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';</v>
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';</v>
       </c>
       <c r="AG35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10042,12 +10103,12 @@
       <c r="AJ35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10056,12 +10117,12 @@
       <c r="AK35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10073,12 +10134,12 @@
       <c r="AL35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10090,12 +10151,12 @@
       <c r="AM35" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10126,15 +10187,15 @@
       </c>
       <c r="K36" t="str">
         <f ca="1"/>
-        <v>巻き動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="L36" t="str">
         <f ca="1"/>
-        <v>巻き動作</v>
+        <v>Winding operation</v>
       </c>
       <c r="N36" t="str">
         <f ca="1"/>
-        <v>【44】 巻き動作</v>
+        <v>【44】 Winding operation</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -10163,75 +10224,75 @@
       <c r="AB36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN</v>
       </c>
       <c r="AC36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';</v>
+			strRt	:= 'Winding operation';</v>
       </c>
       <c r="AE36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
+			strRt	:= 'Winding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';</v>
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';</v>
       </c>
       <c r="AG36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10239,12 +10300,12 @@
       <c r="AJ36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10253,12 +10314,12 @@
       <c r="AK36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10270,12 +10331,12 @@
       <c r="AL36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10287,12 +10348,12 @@
       <c r="AM36" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10323,15 +10384,15 @@
       </c>
       <c r="K37" t="str">
         <f ca="1"/>
-        <v>箔ロウ巻き動作</v>
+        <v>Foil brazing operation</v>
       </c>
       <c r="L37" t="str">
         <f ca="1"/>
-        <v>箔ロウ巻き動作</v>
+        <v>Foil brazing operation</v>
       </c>
       <c r="N37" t="str">
         <f ca="1"/>
-        <v>【45】 箔ロウ巻き動作</v>
+        <v>【45】 Foil brazing operation</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -10360,75 +10421,75 @@
       <c r="AB37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN</v>
       </c>
       <c r="AC37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';</v>
+			strRt	:= 'Foil brazing operation';</v>
       </c>
       <c r="AE37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';</v>
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';</v>
       </c>
       <c r="AG37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10436,12 +10497,12 @@
       <c r="AJ37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10450,12 +10511,12 @@
       <c r="AK37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10467,12 +10528,12 @@
       <c r="AL37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10484,12 +10545,12 @@
       <c r="AM37" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10520,15 +10581,15 @@
       </c>
       <c r="K38" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>Circumference measurement operation</v>
       </c>
       <c r="L38" t="str">
         <f ca="1"/>
-        <v>周長測定動作</v>
+        <v>Circumference measurement operation</v>
       </c>
       <c r="N38" t="str">
         <f ca="1"/>
-        <v>【46】 周長測定動作</v>
+        <v>【46】 Circumference measurement operation</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -10557,75 +10618,75 @@
       <c r="AB38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';</v>
+			strRt	:= 'Circumference measurement operation';</v>
       </c>
       <c r="AE38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
+			strRt	:= 'Circumference measurement operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';</v>
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';</v>
       </c>
       <c r="AG38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -10633,12 +10694,12 @@
       <c r="AJ38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10647,12 +10708,12 @@
       <c r="AK38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10664,12 +10725,12 @@
       <c r="AL38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -10681,12 +10742,12 @@
       <c r="AM38" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11131,15 +11192,15 @@
       </c>
       <c r="K43" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="L43" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Home return operation</v>
       </c>
       <c r="N43" t="str">
         <f ca="1"/>
-        <v>【51】 原点復帰動作</v>
+        <v>【51】 Home return operation</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -11171,7 +11232,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC43" t="str">
@@ -11179,7 +11240,7 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -11188,20 +11249,20 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Home return operation';</v>
       </c>
       <c r="AE43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Home return operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF43" t="str">
@@ -11209,24 +11270,24 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';</v>
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';</v>
       </c>
       <c r="AG43" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH43" t="str">
@@ -11234,12 +11295,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -11248,12 +11309,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11263,12 +11324,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11279,12 +11340,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11298,12 +11359,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11317,12 +11378,12 @@
         <v xml:space="preserve">
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11353,15 +11414,15 @@
       </c>
       <c r="K44" t="str">
         <f ca="1"/>
-        <v>巻き押え動作</v>
+        <v>Winding clamping operation</v>
       </c>
       <c r="L44" t="str">
         <f ca="1"/>
-        <v>巻き押え動作</v>
+        <v>Winding clamping operation</v>
       </c>
       <c r="N44" t="str">
         <f ca="1"/>
-        <v>【52】 巻き押え動作</v>
+        <v>【52】 Winding clamping operation</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -11390,75 +11451,75 @@
       <c r="AB44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';</v>
+			strRt	:= 'Winding clamping operation';</v>
       </c>
       <c r="AE44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
+			strRt	:= 'Winding clamping operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';</v>
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';</v>
       </c>
       <c r="AG44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11466,12 +11527,12 @@
       <c r="AJ44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11480,12 +11541,12 @@
       <c r="AK44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11497,12 +11558,12 @@
       <c r="AL44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11514,12 +11575,12 @@
       <c r="AM44" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11550,15 +11611,15 @@
       </c>
       <c r="K45" t="str">
         <f ca="1"/>
-        <v>溶接動作</v>
+        <v>Welding operation</v>
       </c>
       <c r="L45" t="str">
         <f ca="1"/>
-        <v>溶接動作</v>
+        <v>Welding operation</v>
       </c>
       <c r="N45" t="str">
         <f ca="1"/>
-        <v>【53】 溶接動作</v>
+        <v>【53】 Welding operation</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -11587,75 +11648,75 @@
       <c r="AB45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';</v>
+			strRt	:= 'Welding operation';</v>
       </c>
       <c r="AE45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
+			strRt	:= 'Welding operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';</v>
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';</v>
       </c>
       <c r="AG45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -11663,12 +11724,12 @@
       <c r="AJ45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11677,12 +11738,12 @@
       <c r="AK45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11694,12 +11755,12 @@
       <c r="AL45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -11711,12 +11772,12 @@
       <c r="AM45" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12467,15 +12528,15 @@
       </c>
       <c r="K53" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="L53" t="str">
         <f ca="1"/>
-        <v>原点復帰動作</v>
+        <v>Return to origin operation</v>
       </c>
       <c r="N53" t="str">
         <f ca="1"/>
-        <v>【61】 原点復帰動作</v>
+        <v>【61】 Return to origin operation</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -12507,7 +12568,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC53" t="str">
@@ -12515,7 +12576,7 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -12524,20 +12585,20 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';</v>
       </c>
       <c r="AE53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
+			strRt	:= 'Return to origin operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF53" t="str">
@@ -12545,24 +12606,24 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';</v>
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';</v>
       </c>
       <c r="AG53" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH53" t="str">
@@ -12570,12 +12631,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -12584,12 +12645,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12599,12 +12660,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12615,12 +12676,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12634,12 +12695,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12653,12 +12714,12 @@
         <v xml:space="preserve">
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12689,15 +12750,15 @@
       </c>
       <c r="K54" t="str">
         <f ca="1"/>
-        <v>排出受取り動作</v>
+        <v>Discharge and receiving operation</v>
       </c>
       <c r="L54" t="str">
         <f ca="1"/>
-        <v>排出受取り動作</v>
+        <v>Discharge and receiving operation</v>
       </c>
       <c r="N54" t="str">
         <f ca="1"/>
-        <v>【62】 排出受取り動作</v>
+        <v>【62】 Discharge and receiving operation</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -12726,75 +12787,75 @@
       <c r="AB54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';</v>
+			strRt	:= 'Discharge and receiving operation';</v>
       </c>
       <c r="AE54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';</v>
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';</v>
       </c>
       <c r="AG54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12802,12 +12863,12 @@
       <c r="AJ54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12816,12 +12877,12 @@
       <c r="AK54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12833,12 +12894,12 @@
       <c r="AL54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12850,12 +12911,12 @@
       <c r="AM54" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -12886,15 +12947,15 @@
       </c>
       <c r="K55" t="str">
         <f ca="1"/>
-        <v>排出受渡し動作</v>
+        <v>Discharge and handover operation</v>
       </c>
       <c r="L55" t="str">
         <f ca="1"/>
-        <v>排出受渡し動作</v>
+        <v>Discharge and handover operation</v>
       </c>
       <c r="N55" t="str">
         <f ca="1"/>
-        <v>【63】 排出受渡し動作</v>
+        <v>【63】 Discharge and handover operation</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -12923,75 +12984,75 @@
       <c r="AB55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN</v>
       </c>
       <c r="AC55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';</v>
+			strRt	:= 'Discharge and handover operation';</v>
       </c>
       <c r="AE55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';</v>
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';</v>
       </c>
       <c r="AG55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -12999,12 +13060,12 @@
       <c r="AJ55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13013,12 +13074,12 @@
       <c r="AK55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13030,12 +13091,12 @@
       <c r="AL55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13047,12 +13108,12 @@
       <c r="AM55" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13287,15 +13348,15 @@
       </c>
       <c r="K58" t="str">
         <f ca="1"/>
-        <v>計測準備</v>
+        <v>Measurement preparation</v>
       </c>
       <c r="L58" t="str">
         <f ca="1"/>
-        <v>計測準備</v>
+        <v>Measurement preparation</v>
       </c>
       <c r="N58" t="str">
         <f ca="1"/>
-        <v>【66】 計測準備</v>
+        <v>【66】 Measurement preparation</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -13324,75 +13385,75 @@
       <c r="AB58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';</v>
+			strRt	:= 'Measurement preparation';</v>
       </c>
       <c r="AE58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
+			strRt	:= 'Measurement preparation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';</v>
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';</v>
       </c>
       <c r="AG58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13400,12 +13461,12 @@
       <c r="AJ58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13414,12 +13475,12 @@
       <c r="AK58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13431,12 +13492,12 @@
       <c r="AL58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13448,12 +13509,12 @@
       <c r="AM58" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13484,15 +13545,15 @@
       </c>
       <c r="K59" t="str">
         <f ca="1"/>
-        <v>巻き中測定動作</v>
+        <v>Measurement operation during winding</v>
       </c>
       <c r="L59" t="str">
         <f ca="1"/>
-        <v>巻き中測定動作</v>
+        <v>Measurement operation during winding</v>
       </c>
       <c r="N59" t="str">
         <f ca="1"/>
-        <v>【67】 巻き中測定動作</v>
+        <v>【67】 Measurement operation during winding</v>
       </c>
       <c r="O59" t="str">
         <v/>
@@ -13521,75 +13582,75 @@
       <c r="AB59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN</v>
       </c>
       <c r="AC59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';</v>
+			strRt	:= 'Measurement operation during winding';</v>
       </c>
       <c r="AE59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';</v>
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';</v>
       </c>
       <c r="AG59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -13597,12 +13658,12 @@
       <c r="AJ59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13611,12 +13672,12 @@
       <c r="AK59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13628,12 +13689,12 @@
       <c r="AL59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13645,12 +13706,12 @@
       <c r="AM59" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -13993,15 +14054,15 @@
       </c>
       <c r="K63" t="str">
         <f ca="1"/>
-        <v>原点復帰</v>
+        <v>Opening action</v>
       </c>
       <c r="L63" t="str">
         <f ca="1"/>
-        <v>原点復帰</v>
+        <v>Opening action</v>
       </c>
       <c r="N63" t="str">
         <f ca="1"/>
-        <v>【71】 原点復帰</v>
+        <v>【71】 Opening action</v>
       </c>
       <c r="O63" t="str">
         <v/>
@@ -14033,7 +14094,7 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC63" t="str">
@@ -14041,7 +14102,7 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -14050,20 +14111,20 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';</v>
+			strRt	:= 'Opening action';</v>
       </c>
       <c r="AE63" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
+			strRt	:= 'Opening action';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF63" t="str">
@@ -14071,24 +14132,24 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';</v>
+			strRt	:= 'Opening action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Opening action';</v>
       </c>
       <c r="AG63" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Opening action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Opening action';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH63" t="str">
@@ -14096,12 +14157,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Opening action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Opening action';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -14110,12 +14171,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Opening action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Opening action';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14125,12 +14186,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Opening action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Opening action';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14141,12 +14202,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Opening action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Opening action';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14160,12 +14221,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Opening action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Opening action';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14179,12 +14240,12 @@
         <v xml:space="preserve">
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Opening action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Opening action';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14210,26 +14271,26 @@
       <c r="I64" t="str">
         <v/>
       </c>
-      <c r="J64" t="str">
-        <v/>
+      <c r="J64">
+        <v>30</v>
       </c>
       <c r="K64" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Binding action</v>
       </c>
       <c r="L64" t="str">
         <f ca="1"/>
-        <v/>
+        <v>Binding action</v>
       </c>
       <c r="N64" t="str">
         <f ca="1"/>
-        <v/>
+        <v>【72】 Binding action</v>
       </c>
       <c r="O64" t="str">
         <v/>
       </c>
       <c r="P64" t="str">
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Q64" t="str">
         <f ca="1"/>
@@ -14237,63 +14298,158 @@
       </c>
       <c r="R64" t="str">
         <f ca="1"/>
-        <v/>
+        <v>unknown</v>
       </c>
       <c r="Z64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AA64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+</v>
       </c>
       <c r="AB64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN</v>
       </c>
       <c r="AC64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';</v>
       </c>
       <c r="AE64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【72】 Binding action';</v>
       </c>
       <c r="AG64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【72】 Binding action';
+		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【72】 Binding action';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AI64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【72】 Binding action';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN</v>
       </c>
       <c r="AJ64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【72】 Binding action';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';</v>
       </c>
       <c r="AK64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【72】 Binding action';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AL64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【72】 Binding action';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
       <c r="AM64" t="str">
         <f ca="1"/>
-        <v/>
+        <v xml:space="preserve">
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【72】 Binding action';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;</v>
       </c>
     </row>
     <row r="65" spans="6:39" x14ac:dyDescent="0.55000000000000004">
@@ -14619,19 +14775,19 @@
         <v/>
       </c>
       <c r="J68">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K68" t="str">
         <f ca="1"/>
-        <v>糊付け動作</v>
+        <v>Gluing operation</v>
       </c>
       <c r="L68" t="str">
         <f ca="1"/>
-        <v>糊付け動作</v>
+        <v>Gluing operation</v>
       </c>
       <c r="N68" t="str">
         <f ca="1"/>
-        <v>【76】 糊付け動作</v>
+        <v>【76】 Gluing operation</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -14660,75 +14816,75 @@
       <c r="AB68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN</v>
       </c>
       <c r="AC68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
       <c r="AD68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';</v>
+			strRt	:= 'Gluing operation';</v>
       </c>
       <c r="AE68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
+			strRt	:= 'Gluing operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';</v>
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';</v>
       </c>
       <c r="AG68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
       <c r="AI68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -14736,12 +14892,12 @@
       <c r="AJ68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14750,12 +14906,12 @@
       <c r="AK68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14767,12 +14923,12 @@
       <c r="AL68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -14784,12 +14940,12 @@
       <c r="AM68" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
-	//糊付け動作
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15230,19 +15386,19 @@
         <v/>
       </c>
       <c r="J73">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K73" t="str">
         <f ca="1"/>
-        <v>送り動作</v>
+        <v>Feed operation</v>
       </c>
       <c r="L73" t="str">
         <f ca="1"/>
-        <v>送り動作</v>
+        <v>Feed operation</v>
       </c>
       <c r="N73" t="str">
         <f ca="1"/>
-        <v>【81】 送り動作</v>
+        <v>【81】 Feed operation</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -15274,7 +15430,7 @@
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN</v>
       </c>
       <c r="AC73" t="str">
@@ -15282,7 +15438,7 @@
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN</v>
       </c>
@@ -15291,20 +15447,20 @@
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';</v>
+			strRt	:= 'Feed operation';</v>
       </c>
       <c r="AE73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
+			strRt	:= 'Feed operation';
 		ELSIF strInfoKey = 'index_name' THEN</v>
       </c>
       <c r="AF73" t="str">
@@ -15312,24 +15468,24 @@
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【81】 送り動作';</v>
+			strRt	:= 'Feed operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【81】 Feed operation';</v>
       </c>
       <c r="AG73" t="str">
         <f ca="1"/>
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【81】 送り動作';
+			strRt	:= 'Feed operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【81】 Feed operation';
 		ELSIF strInfoKey = 'model' THEN</v>
       </c>
       <c r="AH73" t="str">
@@ -15337,12 +15493,12 @@
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【81】 送り動作';
+			strRt	:= 'Feed operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【81】 Feed operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';</v>
       </c>
@@ -15351,12 +15507,12 @@
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【81】 送り動作';
+			strRt	:= 'Feed operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【81】 Feed operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN</v>
@@ -15366,12 +15522,12 @@
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【81】 送り動作';
+			strRt	:= 'Feed operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【81】 Feed operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15382,12 +15538,12 @@
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【81】 送り動作';
+			strRt	:= 'Feed operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【81】 Feed operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15401,12 +15557,12 @@
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【81】 送り動作';
+			strRt	:= 'Feed operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【81】 Feed operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -15420,12 +15576,12 @@
         <v xml:space="preserve">
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【81】 送り動作';
+			strRt	:= 'Feed operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【81】 Feed operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28602,15 +28758,15 @@
     <row r="205" spans="6:39" x14ac:dyDescent="0.55000000000000004">
       <c r="AM205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AM$3:AM$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\vt5-w10\[TP_メッセージ.xlsx]err によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_cycle_info.xlsx]info_script によって生成されました。
 //1
 IF strInfoType = 1 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【11】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【11】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28618,12 +28774,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【12】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【12】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28631,12 +28787,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【13】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【13】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28644,12 +28800,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【16】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【16】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28657,12 +28813,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【17】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【17】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28675,12 +28831,12 @@
 	END_IF;
 //2
 ELSIF strInfoType = 2 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【21】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【21】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28688,12 +28844,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Preparation for supply operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【22】 供給準備動作';
+			strRt	:= 'Preparation for supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【22】 Preparation for supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28701,12 +28857,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//カット動作
+	//Cut operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= 'カット動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【23】 カット動作';
+			strRt	:= 'Cut operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【23】 Cut operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28714,12 +28870,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給確認動作
+	//Supply confirmation operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給確認動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【24】 供給確認動作';
+			strRt	:= 'Supply confirmation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【24】 Supply confirmation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28727,12 +28883,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給開始動作
+	//Start supply operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給開始動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【26】 供給開始動作';
+			strRt	:= 'Start supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【26】 Start supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28740,12 +28896,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//Supply operation
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【27】 供給動作';
+			strRt	:= 'Supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【27】 Supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28758,12 +28914,12 @@
 	END_IF;
 //3
 ELSIF strInfoType = 3 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【31】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【31】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28771,12 +28927,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給準備動作
+	//Supply preparation operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【32】 供給準備動作';
+			strRt	:= 'Supply preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【32】 Supply preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28784,12 +28940,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//供給動作
+	//supply operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '供給動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【33】 供給動作';
+			strRt	:= 'supply operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【33】 supply operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28802,12 +28958,12 @@
 	END_IF;
 //4
 ELSIF strInfoType = 4 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【41】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【41】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28815,12 +28971,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定子プリセット
+	//Circumference gauge preset
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定子プリセット';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【42】 周長測定子プリセット';
+			strRt	:= 'Circumference gauge preset';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【42】 Circumference gauge preset';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28828,12 +28984,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き準備動作
+	//Winding preparation operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き準備動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【43】 巻き準備動作';
+			strRt	:= 'Winding preparation operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【43】 Winding preparation operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28841,12 +28997,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き動作
+	//Winding operation
 	ELSIF uiInfoIdx = 4 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【44】 巻き動作';
+			strRt	:= 'Winding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【44】 Winding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28854,12 +29010,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//箔ロウ巻き動作
+	//Foil brazing operation
 	ELSIF uiInfoIdx = 5 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '箔ロウ巻き動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【45】 箔ロウ巻き動作';
+			strRt	:= 'Foil brazing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【45】 Foil brazing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28867,12 +29023,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//周長測定動作
+	//Circumference measurement operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '周長測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【46】 周長測定動作';
+			strRt	:= 'Circumference measurement operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【46】 Circumference measurement operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28885,12 +29041,12 @@
 	END_IF;
 //5
 ELSIF strInfoType = 5 THEN
-	//原点復帰動作
+	//Home return operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【51】 原点復帰動作';
+			strRt	:= 'Home return operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【51】 Home return operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28898,12 +29054,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き押え動作
+	//Winding clamping operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き押え動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【52】 巻き押え動作';
+			strRt	:= 'Winding clamping operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【52】 Winding clamping operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28911,12 +29067,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//溶接動作
+	//Welding operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '溶接動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【53】 溶接動作';
+			strRt	:= 'Welding operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【53】 Welding operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28929,12 +29085,12 @@
 	END_IF;
 //6
 ELSIF strInfoType = 6 THEN
-	//原点復帰動作
+	//Return to origin operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【61】 原点復帰動作';
+			strRt	:= 'Return to origin operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【61】 Return to origin operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28942,12 +29098,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出受取り動作
+	//Discharge and receiving operation
 	ELSIF uiInfoIdx = 2 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受取り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【62】 排出受取り動作';
+			strRt	:= 'Discharge and receiving operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【62】 Discharge and receiving operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28955,12 +29111,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//排出受渡し動作
+	//Discharge and handover operation
 	ELSIF uiInfoIdx = 3 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '排出受渡し動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【63】 排出受渡し動作';
+			strRt	:= 'Discharge and handover operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【63】 Discharge and handover operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28968,12 +29124,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//計測準備
+	//Measurement preparation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '計測準備';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【66】 計測準備';
+			strRt	:= 'Measurement preparation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【66】 Measurement preparation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28981,12 +29137,12 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//巻き中測定動作
+	//Measurement operation during winding
 	ELSIF uiInfoIdx = 7 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '巻き中測定動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【67】 巻き中測定動作';
+			strRt	:= 'Measurement operation during winding';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【67】 Measurement operation during winding';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -28999,12 +29155,12 @@
 	END_IF;
 //7
 ELSIF strInfoType = 7 THEN
-	//原点復帰
+	//Opening action
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '原点復帰';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【71】 原点復帰';
+			strRt	:= 'Opening action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【71】 Opening action';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -29012,12 +29168,25 @@
 		ELSE
 			uiErrCode	:= 3;
 		END_IF;
-	//糊付け動作
+	//Binding action
+	ELSIF uiInfoIdx = 2 THEN
+		IF strInfoKey = 'name' THEN
+			strRt	:= 'Binding action';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【72】 Binding action';
+		ELSIF strInfoKey = 'model' THEN
+			strRt	:= 'unknown';
+		ELSIF strInfoKey = 'mf' THEN
+			strRt	:= 'unknown';
+		ELSE
+			uiErrCode	:= 3;
+		END_IF;
+	//Gluing operation
 	ELSIF uiInfoIdx = 6 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '糊付け動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【76】 糊付け動作';
+			strRt	:= 'Gluing operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【76】 Gluing operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -29030,12 +29199,12 @@
 	END_IF;
 //8
 ELSIF strInfoType = 8 THEN
-	//送り動作
+	//Feed operation
 	IF uiInfoIdx = 1 THEN
 		IF strInfoKey = 'name' THEN
-			strRt	:= '送り動作';
-		ELSIF strInfoKey = 'index_name' THEN
-			strRt	:= '【81】 送り動作';
+			strRt	:= 'Feed operation';
+		ELSIF strInfoKey = 'index_name' THEN
+			strRt	:= '【81】 Feed operation';
 		ELSIF strInfoKey = 'model' THEN
 			strRt	:= 'unknown';
 		ELSIF strInfoKey = 'mf' THEN
@@ -29055,7 +29224,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>_xlfn.ISFORMULA(A1)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/doc/kv_script_cycle_info.xlsx
+++ b/doc/kv_script_cycle_info.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2568BEBB-C68C-400C-B23F-A66703F75F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BADA3E-1C8F-4C8B-AB90-08D156404917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
     <sheet name="info_script" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">info_index!$A$1:$R$89</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="128">
   <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
@@ -746,6 +746,16 @@
   <si>
     <t>Binding action</t>
   </si>
+  <si>
+    <t>ひらき動作</t>
+    <rPh sb="3" eb="5">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Opening motion</t>
+  </si>
 </sst>
 </file>
 
@@ -1105,15 +1115,15 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <patternFill patternType="lightUp">
+          <fgColor rgb="FF33CCCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="lightUp">
-          <fgColor rgb="FF33CCCC"/>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1150,7 +1160,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="$A$92">
+    <xdr:sp macro="" textlink="$A$93">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="正方形/長方形 1">
           <a:extLst>
@@ -1519,7 +1529,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D32264-F25D-40E9-9C76-26E43E79C8CC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
@@ -1623,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="str">
-        <f t="shared" ref="D3:D58" si="0">B3&amp;C3</f>
+        <f t="shared" ref="D3:D59" si="0">B3&amp;C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="4">
@@ -1828,7 +1838,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4">
-        <f t="shared" ref="C9:C12" si="4">C8</f>
+        <f t="shared" ref="C9:C13" si="4">C8</f>
         <v>2</v>
       </c>
       <c r="D9" s="4" t="str">
@@ -1836,7 +1846,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" ref="E9:E12" si="5">E8+1</f>
+        <f t="shared" ref="E9:E13" si="5">E8+1</f>
         <v>3</v>
       </c>
       <c r="F9" s="5"/>
@@ -1898,7 +1908,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4">
-        <f t="shared" si="4"/>
+        <f>C10</f>
         <v>2</v>
       </c>
       <c r="D11" s="4" t="str">
@@ -1906,17 +1916,18 @@
         <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>6</v>
+        <f>E10+1</f>
+        <v>5</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1932,7 +1943,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4">
-        <f t="shared" si="4"/>
+        <f>C10</f>
         <v>2</v>
       </c>
       <c r="D12" s="4" t="str">
@@ -1940,18 +1951,17 @@
         <v>2</v>
       </c>
       <c r="E12" s="4">
-        <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
         <v>73</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1967,26 +1977,26 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4">
-        <f>C7+1</f>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f t="shared" ref="D13" si="8">B13&amp;C13</f>
+        <v>2</v>
       </c>
       <c r="E13" s="4">
-        <f>E7</f>
-        <v>1</v>
+        <f t="shared" si="5"/>
+        <v>7</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -2002,7 +2012,7 @@
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4">
-        <f t="shared" ref="C14:C88" si="8">C13</f>
+        <f>C7+1</f>
         <v>3</v>
       </c>
       <c r="D14" s="4" t="str">
@@ -2010,18 +2020,18 @@
         <v>3</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" ref="E14:E68" si="9">E13+1</f>
-        <v>2</v>
+        <f>E7</f>
+        <v>1</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
         <v>74</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -2037,7 +2047,7 @@
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C15:C89" si="9">C14</f>
         <v>3</v>
       </c>
       <c r="D15" s="4" t="str">
@@ -2045,18 +2055,18 @@
         <v>3</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E15:E69" si="10">E14+1</f>
+        <v>2</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
         <v>74</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -2072,26 +2082,26 @@
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4">
-        <f>C13+1</f>
-        <v>4</v>
+        <f t="shared" si="9"/>
+        <v>3</v>
       </c>
       <c r="D16" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="4">
-        <f>E13</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2107,7 +2117,7 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4">
-        <f t="shared" ref="C17" si="10">C16</f>
+        <f>C14+1</f>
         <v>4</v>
       </c>
       <c r="D17" s="4" t="str">
@@ -2115,18 +2125,18 @@
         <v>4</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" ref="E17" si="11">E16+1</f>
-        <v>2</v>
+        <f>E14</f>
+        <v>1</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -2142,7 +2152,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C18" si="11">C17</f>
         <v>4</v>
       </c>
       <c r="D18" s="4" t="str">
@@ -2150,18 +2160,18 @@
         <v>4</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E18" si="12">E17+1</f>
+        <v>2</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -2177,7 +2187,7 @@
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="D19" s="4" t="str">
@@ -2185,18 +2195,18 @@
         <v>4</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -2212,7 +2222,7 @@
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="D20" s="4" t="str">
@@ -2220,21 +2230,21 @@
         <v>4</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J20" s="5"/>
-      <c r="K20" s="6"/>
+      <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
@@ -2247,26 +2257,26 @@
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="D21" s="4" t="str">
-        <f t="shared" ref="D21" si="12">B21&amp;C21</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" si="9"/>
-        <v>6</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
         <v>75</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="6"/>
@@ -2282,29 +2292,29 @@
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4">
-        <f>C16+1</f>
-        <v>5</v>
+        <f t="shared" si="9"/>
+        <v>4</v>
       </c>
       <c r="D22" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ref="D22" si="13">B22&amp;C22</f>
+        <v>4</v>
       </c>
       <c r="E22" s="4">
-        <f>E16</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>6</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
+      <c r="K22" s="6"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
@@ -2317,7 +2327,7 @@
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4">
-        <f t="shared" ref="C23" si="13">C22</f>
+        <f>C17+1</f>
         <v>5</v>
       </c>
       <c r="D23" s="4" t="str">
@@ -2325,18 +2335,18 @@
         <v>5</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" ref="E23" si="14">E22+1</f>
-        <v>2</v>
+        <f>E17</f>
+        <v>1</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -2352,7 +2362,7 @@
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C24" si="14">C23</f>
         <v>5</v>
       </c>
       <c r="D24" s="4" t="str">
@@ -2360,53 +2370,53 @@
         <v>5</v>
       </c>
       <c r="E24" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E24" si="15">E23+1</f>
+        <v>2</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4">
-        <f>C22+1</f>
-        <v>6</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="D25" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="4">
-        <f>E22</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -2422,7 +2432,7 @@
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4">
-        <f t="shared" ref="C26:C27" si="15">C25</f>
+        <f>C23+1</f>
         <v>6</v>
       </c>
       <c r="D26" s="4" t="str">
@@ -2430,53 +2440,53 @@
         <v>6</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" ref="E26:E27" si="16">E25+1</f>
-        <v>2</v>
-      </c>
-      <c r="F26" s="9"/>
+        <f>E23</f>
+        <v>1</v>
+      </c>
+      <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H26" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22"/>
+      <c r="H26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
       <c r="R26" s="7"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="C27:C28" si="16">C26</f>
         <v>6</v>
       </c>
       <c r="D27" s="4" t="str">
-        <f t="shared" ref="D27" si="17">B27&amp;C27</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="16"/>
-        <v>3</v>
+        <f t="shared" ref="E27:E28" si="17">E26+1</f>
+        <v>2</v>
       </c>
       <c r="F27" s="9"/>
       <c r="G27" s="5" t="s">
         <v>77</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
@@ -2492,60 +2502,60 @@
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4">
-        <f>C26</f>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="D28" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D28" si="18">B28&amp;C28</f>
         <v>6</v>
       </c>
       <c r="E28" s="4">
-        <v>6</v>
-      </c>
-      <c r="F28" s="5"/>
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+      <c r="F28" s="9"/>
       <c r="G28" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
+      <c r="H28" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
       <c r="R28" s="7"/>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4">
-        <f t="shared" si="8"/>
+        <f>C27</f>
         <v>6</v>
       </c>
       <c r="D29" s="4" t="str">
-        <f t="shared" ref="D29" si="18">B29&amp;C29</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" si="9"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
         <v>77</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -2561,35 +2571,35 @@
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4">
-        <f>C25+1</f>
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="D30" s="4" t="str">
+        <f t="shared" ref="D30" si="19">B30&amp;C30</f>
+        <v>6</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="D30" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E30" s="4">
-        <f>E25</f>
-        <v>1</v>
-      </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="22"/>
-      <c r="P30" s="22"/>
-      <c r="Q30" s="22"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
       <c r="R30" s="7"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
@@ -2600,22 +2610,22 @@
         <v>7</v>
       </c>
       <c r="D31" s="4" t="str">
-        <f t="shared" ref="D31" si="19">B31&amp;C31</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="E31" s="4">
         <f>E26</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9" t="s">
         <v>112</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
@@ -2631,25 +2641,26 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4">
-        <f t="shared" ref="C32" si="20">C30</f>
+        <f>C27+1</f>
         <v>7</v>
       </c>
       <c r="D32" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D32" si="20">B32&amp;C32</f>
         <v>7</v>
       </c>
       <c r="E32" s="4">
-        <v>6</v>
+        <f>E27</f>
+        <v>2</v>
       </c>
       <c r="F32" s="9"/>
       <c r="G32" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
@@ -2662,74 +2673,79 @@
       <c r="R32" s="7"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="26"/>
+      <c r="A33" s="4"/>
       <c r="B33" s="4"/>
-      <c r="C33" s="26">
-        <f>C30+1</f>
+      <c r="C33" s="4">
+        <f t="shared" ref="C33" si="21">C31</f>
+        <v>7</v>
+      </c>
+      <c r="D33" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="E33" s="4">
+        <v>6</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="7"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="26"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="26">
+        <f>C31+1</f>
         <v>8</v>
       </c>
-      <c r="D33" s="26" t="str">
+      <c r="D34" s="26" t="str">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="E33" s="4">
-        <f>E30</f>
+      <c r="E34" s="4">
+        <f>E31</f>
         <v>1</v>
       </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11" t="s">
+      <c r="F34" s="11"/>
+      <c r="G34" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="H33" s="11" t="s">
+      <c r="H34" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I34" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
-      <c r="O33" s="23"/>
-      <c r="P33" s="23"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="7"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4">
-        <f>C33+1</f>
-        <v>9</v>
-      </c>
-      <c r="D34" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E34" s="4">
-        <f>E33</f>
-        <v>1</v>
-      </c>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="11"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="23"/>
+      <c r="P34" s="23"/>
+      <c r="Q34" s="23"/>
       <c r="R34" s="7"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4">
-        <f t="shared" ref="C35" si="21">C34</f>
+        <f>C34+1</f>
         <v>9</v>
       </c>
       <c r="D35" s="4" t="str">
@@ -2737,8 +2753,8 @@
         <v>9</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" ref="E35" si="22">E34+1</f>
-        <v>2</v>
+        <f>E34</f>
+        <v>1</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -2758,7 +2774,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C36" si="22">C35</f>
         <v>9</v>
       </c>
       <c r="D36" s="4" t="str">
@@ -2766,8 +2782,8 @@
         <v>9</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E36" si="23">E35+1</f>
+        <v>2</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -2787,7 +2803,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="D37" s="4" t="str">
@@ -2795,15 +2811,15 @@
         <v>9</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
-      <c r="K37" s="13"/>
+      <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
@@ -2816,7 +2832,7 @@
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="D38" s="4" t="str">
@@ -2824,15 +2840,15 @@
         <v>9</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
+      <c r="K38" s="13"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
@@ -2845,16 +2861,16 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4">
-        <f t="shared" ref="C39" si="23">C34+1</f>
-        <v>10</v>
+        <f t="shared" si="9"/>
+        <v>9</v>
       </c>
       <c r="D39" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" ref="E39" si="24">E34</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -2874,7 +2890,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4">
-        <f t="shared" ref="C40" si="25">C39</f>
+        <f t="shared" ref="C40" si="24">C35+1</f>
         <v>10</v>
       </c>
       <c r="D40" s="4" t="str">
@@ -2882,8 +2898,8 @@
         <v>10</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" ref="E40" si="26">E39+1</f>
-        <v>2</v>
+        <f t="shared" ref="E40" si="25">E35</f>
+        <v>1</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -2903,7 +2919,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C41" si="26">C40</f>
         <v>10</v>
       </c>
       <c r="D41" s="4" t="str">
@@ -2911,8 +2927,8 @@
         <v>10</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E41" si="27">E40+1</f>
+        <v>2</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -2932,7 +2948,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="D42" s="4" t="str">
@@ -2940,8 +2956,8 @@
         <v>10</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -2961,7 +2977,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="D43" s="4" t="str">
@@ -2969,8 +2985,8 @@
         <v>10</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -2990,16 +3006,16 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4">
-        <f t="shared" ref="C44" si="27">C39+1</f>
-        <v>11</v>
+        <f t="shared" si="9"/>
+        <v>10</v>
       </c>
       <c r="D44" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" ref="E44" si="28">E39</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -3019,7 +3035,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4">
-        <f t="shared" ref="C45" si="29">C44</f>
+        <f t="shared" ref="C45" si="28">C40+1</f>
         <v>11</v>
       </c>
       <c r="D45" s="4" t="str">
@@ -3027,8 +3043,8 @@
         <v>11</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" ref="E45" si="30">E44+1</f>
-        <v>2</v>
+        <f t="shared" ref="E45" si="29">E40</f>
+        <v>1</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -3048,7 +3064,7 @@
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C46" si="30">C45</f>
         <v>11</v>
       </c>
       <c r="D46" s="4" t="str">
@@ -3056,8 +3072,8 @@
         <v>11</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E46" si="31">E45+1</f>
+        <v>2</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -3077,7 +3093,7 @@
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="D47" s="4" t="str">
@@ -3085,8 +3101,8 @@
         <v>11</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -3106,7 +3122,7 @@
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="D48" s="4" t="str">
@@ -3114,8 +3130,8 @@
         <v>11</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -3135,16 +3151,16 @@
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4">
-        <f t="shared" ref="C49" si="31">C44+1</f>
-        <v>12</v>
+        <f t="shared" si="9"/>
+        <v>11</v>
       </c>
       <c r="D49" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" ref="E49" si="32">E44</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -3164,7 +3180,7 @@
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4">
-        <f t="shared" ref="C50" si="33">C49</f>
+        <f t="shared" ref="C50" si="32">C45+1</f>
         <v>12</v>
       </c>
       <c r="D50" s="4" t="str">
@@ -3172,8 +3188,8 @@
         <v>12</v>
       </c>
       <c r="E50" s="4">
-        <f t="shared" ref="E50" si="34">E49+1</f>
-        <v>2</v>
+        <f t="shared" ref="E50" si="33">E45</f>
+        <v>1</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -3193,7 +3209,7 @@
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C51" si="34">C50</f>
         <v>12</v>
       </c>
       <c r="D51" s="4" t="str">
@@ -3201,8 +3217,8 @@
         <v>12</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E51" si="35">E50+1</f>
+        <v>2</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -3222,7 +3238,7 @@
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="D52" s="4" t="str">
@@ -3230,8 +3246,8 @@
         <v>12</v>
       </c>
       <c r="E52" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -3251,7 +3267,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="D53" s="4" t="str">
@@ -3259,8 +3275,8 @@
         <v>12</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -3280,16 +3296,16 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4">
-        <f t="shared" ref="C54:C84" si="35">C49+1</f>
-        <v>13</v>
+        <f t="shared" si="9"/>
+        <v>12</v>
       </c>
       <c r="D54" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" ref="E54" si="36">E49</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -3309,7 +3325,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4">
-        <f t="shared" ref="C55:C85" si="37">C54</f>
+        <f t="shared" ref="C55:C85" si="36">C50+1</f>
         <v>13</v>
       </c>
       <c r="D55" s="4" t="str">
@@ -3317,8 +3333,8 @@
         <v>13</v>
       </c>
       <c r="E55" s="4">
-        <f t="shared" ref="E55" si="38">E54+1</f>
-        <v>2</v>
+        <f t="shared" ref="E55" si="37">E50</f>
+        <v>1</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -3338,7 +3354,7 @@
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C56:C86" si="38">C55</f>
         <v>13</v>
       </c>
       <c r="D56" s="4" t="str">
@@ -3346,8 +3362,8 @@
         <v>13</v>
       </c>
       <c r="E56" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E56" si="39">E55+1</f>
+        <v>2</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -3367,7 +3383,7 @@
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="D57" s="4" t="str">
@@ -3375,8 +3391,8 @@
         <v>13</v>
       </c>
       <c r="E57" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -3396,7 +3412,7 @@
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="D58" s="4" t="str">
@@ -3404,8 +3420,8 @@
         <v>13</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -3425,16 +3441,16 @@
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4">
-        <f t="shared" si="35"/>
-        <v>14</v>
+        <f t="shared" si="9"/>
+        <v>13</v>
       </c>
       <c r="D59" s="4" t="str">
-        <f t="shared" ref="D59:D88" si="39">B59&amp;C59</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="E59" s="4">
-        <f t="shared" ref="E59" si="40">E54</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -3454,16 +3470,16 @@
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>14</v>
       </c>
       <c r="D60" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="D60:D89" si="40">B60&amp;C60</f>
         <v>14</v>
       </c>
       <c r="E60" s="4">
-        <f t="shared" ref="E60" si="41">E59+1</f>
-        <v>2</v>
+        <f t="shared" ref="E60" si="41">E55</f>
+        <v>1</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -3483,16 +3499,16 @@
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>14</v>
       </c>
       <c r="D61" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>14</v>
       </c>
       <c r="E61" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E61" si="42">E60+1</f>
+        <v>2</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -3512,16 +3528,16 @@
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="D62" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>14</v>
       </c>
       <c r="E62" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -3541,16 +3557,16 @@
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="D63" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>14</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -3570,16 +3586,16 @@
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4">
-        <f t="shared" si="35"/>
-        <v>15</v>
+        <f t="shared" si="9"/>
+        <v>14</v>
       </c>
       <c r="D64" s="4" t="str">
-        <f t="shared" si="39"/>
-        <v>15</v>
+        <f t="shared" si="40"/>
+        <v>14</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" ref="E64" si="42">E59</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -3599,16 +3615,16 @@
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>15</v>
       </c>
       <c r="D65" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15</v>
       </c>
       <c r="E65" s="4">
-        <f t="shared" ref="E65" si="43">E64+1</f>
-        <v>2</v>
+        <f t="shared" ref="E65" si="43">E60</f>
+        <v>1</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -3628,16 +3644,16 @@
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>15</v>
       </c>
       <c r="D66" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15</v>
       </c>
       <c r="E66" s="4">
-        <f t="shared" si="9"/>
-        <v>3</v>
+        <f t="shared" ref="E66" si="44">E65+1</f>
+        <v>2</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -3657,16 +3673,16 @@
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="D67" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15</v>
       </c>
       <c r="E67" s="4">
-        <f t="shared" si="9"/>
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>3</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -3686,16 +3702,16 @@
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="D68" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15</v>
       </c>
       <c r="E68" s="4">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>4</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -3715,16 +3731,16 @@
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4">
-        <f t="shared" si="35"/>
-        <v>16</v>
+        <f t="shared" si="9"/>
+        <v>15</v>
       </c>
       <c r="D69" s="4" t="str">
-        <f t="shared" si="39"/>
-        <v>16</v>
+        <f t="shared" si="40"/>
+        <v>15</v>
       </c>
       <c r="E69" s="4">
-        <f t="shared" ref="E69" si="44">E64</f>
-        <v>1</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -3744,16 +3760,16 @@
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>16</v>
       </c>
       <c r="D70" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>16</v>
       </c>
       <c r="E70" s="4">
-        <f t="shared" ref="E70:E88" si="45">E69+1</f>
-        <v>2</v>
+        <f t="shared" ref="E70" si="45">E65</f>
+        <v>1</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -3773,16 +3789,16 @@
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>16</v>
       </c>
       <c r="D71" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>16</v>
       </c>
       <c r="E71" s="4">
-        <f t="shared" si="45"/>
-        <v>3</v>
+        <f t="shared" ref="E71:E89" si="46">E70+1</f>
+        <v>2</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -3802,16 +3818,16 @@
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="D72" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>16</v>
       </c>
       <c r="E72" s="4">
-        <f t="shared" si="45"/>
-        <v>4</v>
+        <f t="shared" si="46"/>
+        <v>3</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -3831,16 +3847,16 @@
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="D73" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>16</v>
       </c>
       <c r="E73" s="4">
-        <f t="shared" si="45"/>
-        <v>5</v>
+        <f t="shared" si="46"/>
+        <v>4</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -3860,16 +3876,16 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4">
-        <f t="shared" si="35"/>
-        <v>17</v>
+        <f t="shared" si="9"/>
+        <v>16</v>
       </c>
       <c r="D74" s="4" t="str">
-        <f t="shared" si="39"/>
-        <v>17</v>
+        <f t="shared" si="40"/>
+        <v>16</v>
       </c>
       <c r="E74" s="4">
-        <f t="shared" ref="E74" si="46">E69</f>
-        <v>1</v>
+        <f t="shared" si="46"/>
+        <v>5</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -3889,16 +3905,16 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>17</v>
       </c>
       <c r="D75" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>17</v>
       </c>
       <c r="E75" s="4">
-        <f t="shared" ref="E75" si="47">E74+1</f>
-        <v>2</v>
+        <f t="shared" ref="E75" si="47">E70</f>
+        <v>1</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -3918,16 +3934,16 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>17</v>
       </c>
       <c r="D76" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>17</v>
       </c>
       <c r="E76" s="4">
-        <f t="shared" si="45"/>
-        <v>3</v>
+        <f t="shared" ref="E76" si="48">E75+1</f>
+        <v>2</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -3947,16 +3963,16 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
       <c r="D77" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>17</v>
       </c>
       <c r="E77" s="4">
-        <f t="shared" si="45"/>
-        <v>4</v>
+        <f t="shared" si="46"/>
+        <v>3</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -3976,16 +3992,16 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
       <c r="D78" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>17</v>
       </c>
       <c r="E78" s="4">
-        <f t="shared" si="45"/>
-        <v>5</v>
+        <f t="shared" si="46"/>
+        <v>4</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -4005,16 +4021,16 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4">
-        <f t="shared" si="35"/>
-        <v>18</v>
+        <f t="shared" si="9"/>
+        <v>17</v>
       </c>
       <c r="D79" s="4" t="str">
-        <f t="shared" si="39"/>
-        <v>18</v>
+        <f t="shared" si="40"/>
+        <v>17</v>
       </c>
       <c r="E79" s="4">
-        <f t="shared" ref="E79" si="48">E74</f>
-        <v>1</v>
+        <f t="shared" si="46"/>
+        <v>5</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -4034,16 +4050,16 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>18</v>
       </c>
       <c r="D80" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>18</v>
       </c>
       <c r="E80" s="4">
-        <f t="shared" ref="E80" si="49">E79+1</f>
-        <v>2</v>
+        <f t="shared" ref="E80" si="49">E75</f>
+        <v>1</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -4063,16 +4079,16 @@
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>18</v>
       </c>
       <c r="D81" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>18</v>
       </c>
       <c r="E81" s="4">
-        <f t="shared" si="45"/>
-        <v>3</v>
+        <f t="shared" ref="E81" si="50">E80+1</f>
+        <v>2</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -4092,16 +4108,16 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="D82" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>18</v>
       </c>
       <c r="E82" s="4">
-        <f t="shared" si="45"/>
-        <v>4</v>
+        <f t="shared" si="46"/>
+        <v>3</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -4121,16 +4137,16 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="D83" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>18</v>
       </c>
       <c r="E83" s="4">
-        <f t="shared" si="45"/>
-        <v>5</v>
+        <f t="shared" si="46"/>
+        <v>4</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -4150,16 +4166,16 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4">
-        <f t="shared" si="35"/>
-        <v>19</v>
+        <f t="shared" si="9"/>
+        <v>18</v>
       </c>
       <c r="D84" s="4" t="str">
-        <f t="shared" si="39"/>
-        <v>19</v>
+        <f t="shared" si="40"/>
+        <v>18</v>
       </c>
       <c r="E84" s="4">
-        <f t="shared" ref="E84" si="50">E79</f>
-        <v>1</v>
+        <f t="shared" si="46"/>
+        <v>5</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
@@ -4179,16 +4195,16 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>19</v>
       </c>
       <c r="D85" s="4" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>19</v>
       </c>
       <c r="E85" s="4">
-        <f t="shared" ref=